--- a/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results.xlsx
@@ -578,70 +578,70 @@
         <v>10.20008632565869</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02280213944059894</v>
+        <v>0.02280213944059888</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05579128143712271</v>
+        <v>0.05579128143712251</v>
       </c>
       <c r="G2" t="n">
-        <v>4.010483954252142e-05</v>
+        <v>4.010483954252127e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00114532624146651</v>
+        <v>0.001145326241466513</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002234417210028187</v>
+        <v>0.0002234417210028195</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002172280437535946</v>
+        <v>0.002172280437535925</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004087489492760879</v>
+        <v>0.004087489492760882</v>
       </c>
       <c r="L2" t="n">
-        <v>3.329041918983529e-05</v>
+        <v>3.329041918983525e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001345287036150599</v>
+        <v>0.0001345287036150598</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004181531270246583</v>
+        <v>0.004181531270246569</v>
       </c>
       <c r="O2" t="n">
-        <v>3.242675186689183e-05</v>
+        <v>3.242675186689206e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.773778149478629e-07</v>
+        <v>4.773778149478628e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.86953034717722e-05</v>
+        <v>5.869530347177221e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>5.318463955165519e-07</v>
+        <v>5.318463955165452e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>2.679209913088794e-06</v>
+        <v>2.679209913088789e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008762886933745839</v>
+        <v>0.0008762886933745828</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003073003273574051</v>
+        <v>0.003073003273574045</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004491492021052262</v>
+        <v>0.004491492021052261</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002992821928195295</v>
+        <v>0.0002992821928195261</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8933790211696021</v>
+        <v>-0.8933790211696022</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.068829112605489</v>
+        <v>2.068829112605486</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.925189943549443</v>
+        <v>8.925189943549441</v>
       </c>
     </row>
     <row r="3">
@@ -662,70 +662,70 @@
         <v>10.18902909921034</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02076847699769263</v>
+        <v>0.0207684769976926</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05267885211657142</v>
+        <v>0.05267885211657136</v>
       </c>
       <c r="G3" t="n">
-        <v>3.94839418063846e-05</v>
+        <v>3.948394180638485e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001133335664104356</v>
+        <v>0.00113333566410436</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002190167026321967</v>
+        <v>0.0002190167026321962</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002081262456268528</v>
+        <v>0.002081262456268537</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003869750027926286</v>
+        <v>0.003869750027926281</v>
       </c>
       <c r="L3" t="n">
-        <v>3.285777781588818e-05</v>
+        <v>3.28577778158882e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001273715634376781</v>
+        <v>0.000127371563437678</v>
       </c>
       <c r="N3" t="n">
         <v>0.004126072192052787</v>
       </c>
       <c r="O3" t="n">
-        <v>3.108978222078868e-05</v>
+        <v>3.108978222078863e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.738079301459342e-07</v>
+        <v>4.73807930145934e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.843554502209941e-05</v>
+        <v>5.843554502209935e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.150740251408739e-07</v>
+        <v>5.150740251408649e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.478017037797967e-06</v>
+        <v>2.478017037797965e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000829193023006254</v>
+        <v>0.0008291930230062517</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002939059961235936</v>
+        <v>0.002939059961235925</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004486964668614885</v>
+        <v>0.004486964668614887</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002858948217060443</v>
+        <v>0.0002858948217060439</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8754016989576094</v>
+        <v>-0.8754016989576096</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.045530269936733</v>
+        <v>2.045530269936735</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.925189944090109</v>
+        <v>8.925189944090103</v>
       </c>
     </row>
     <row r="4">
@@ -743,73 +743,73 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.21363275522016</v>
+        <v>10.21363275522015</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02107327232722539</v>
+        <v>0.02107327232722546</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05125802228129434</v>
+        <v>0.0512580222812944</v>
       </c>
       <c r="G4" t="n">
-        <v>3.933887801134972e-05</v>
+        <v>3.933887801134976e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001120311520254873</v>
+        <v>0.001120311520254866</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002166100336657495</v>
+        <v>0.0002166100336657493</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00199302542701326</v>
+        <v>0.001993025427013273</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003569416533588157</v>
+        <v>0.003569416533588163</v>
       </c>
       <c r="L4" t="n">
-        <v>3.260833872528322e-05</v>
+        <v>3.260833872528327e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001214677816079298</v>
+        <v>0.0001214677816079299</v>
       </c>
       <c r="N4" t="n">
         <v>0.004047020145379852</v>
       </c>
       <c r="O4" t="n">
-        <v>3.00591622942299e-05</v>
+        <v>3.005916229423104e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.74034444509213e-07</v>
+        <v>4.740344445092132e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.817496370844628e-05</v>
+        <v>5.817496370844624e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.737836485007958e-07</v>
+        <v>4.737836485008045e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>2.502263403317572e-06</v>
+        <v>2.502263403317577e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0008202495370808446</v>
+        <v>0.0008202495370798036</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00286784945760995</v>
+        <v>0.002867849457609953</v>
       </c>
       <c r="V4" t="n">
         <v>0.004476661901931694</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002814414811790723</v>
+        <v>0.000281441481179075</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8346503381500572</v>
+        <v>-0.834650338150058</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.031084167839075</v>
+        <v>2.031084167839078</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.925189945679071</v>
+        <v>8.925189945679065</v>
       </c>
     </row>
     <row r="5">
@@ -830,37 +830,37 @@
         <v>10.28249841781726</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02259484360412419</v>
+        <v>0.02259484360412415</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04960649959564417</v>
+        <v>0.04960649959564408</v>
       </c>
       <c r="G5" t="n">
-        <v>3.919861300280303e-05</v>
+        <v>3.919861300280301e-05</v>
       </c>
       <c r="H5" t="n">
         <v>0.0010910869847508</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002140162672597562</v>
+        <v>0.0002140162672597558</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001881469232512534</v>
+        <v>0.001881469232512527</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003415563880839496</v>
+        <v>0.003415563880839495</v>
       </c>
       <c r="L5" t="n">
-        <v>3.219092836217396e-05</v>
+        <v>3.219092836217395e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001140959614549085</v>
+        <v>0.0001140959614549086</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003984466512089086</v>
+        <v>0.003984466512089091</v>
       </c>
       <c r="O5" t="n">
-        <v>2.930124706378527e-05</v>
+        <v>2.930124706378508e-05</v>
       </c>
       <c r="P5" t="n">
         <v>4.769799960909287e-07</v>
@@ -869,22 +869,22 @@
         <v>5.792200788341426e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.567685486867253e-07</v>
+        <v>4.567685486867234e-07</v>
       </c>
       <c r="S5" t="n">
         <v>2.569422549772487e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0008049512519034689</v>
+        <v>0.0008049512519034685</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00272471270929363</v>
+        <v>0.002724712709293636</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004473757720860037</v>
+        <v>0.004473757720860036</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002752750533536005</v>
+        <v>0.0002752750533536022</v>
       </c>
       <c r="X5" t="n">
         <v>-0.7512873356564107</v>
@@ -893,7 +893,7 @@
         <v>2.017252949637026</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.925189949095156</v>
+        <v>8.925189949095154</v>
       </c>
     </row>
     <row r="6">
@@ -911,70 +911,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.67850042172362</v>
+        <v>10.67850042172361</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01373962941416203</v>
+        <v>0.01373962941416204</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03079085740377783</v>
+        <v>0.03079085740377786</v>
       </c>
       <c r="G6" t="n">
-        <v>3.599421573179585e-05</v>
+        <v>3.599421573179587e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009582645687425371</v>
+        <v>0.0009582645687425394</v>
       </c>
       <c r="I6" t="n">
         <v>0.00019129072384295</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001123065831364149</v>
+        <v>0.001123065831364148</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003021955219494393</v>
+        <v>0.00302195521949439</v>
       </c>
       <c r="L6" t="n">
         <v>2.949785401874817e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>6.765252205622785e-05</v>
+        <v>6.765252205622786e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003589767574783412</v>
+        <v>0.003589767574783435</v>
       </c>
       <c r="O6" t="n">
-        <v>2.371074285636723e-05</v>
+        <v>2.371074285636719e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.64417070663814e-07</v>
+        <v>4.644170706638141e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.647540433350844e-05</v>
+        <v>5.647540433350838e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>3.935332972846572e-07</v>
+        <v>3.935332972846631e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.66639180139364e-06</v>
+        <v>1.666391801393639e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005329680766877166</v>
+        <v>0.0005329680766877176</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001816761348185858</v>
+        <v>0.001816761348185862</v>
       </c>
       <c r="V6" t="n">
         <v>0.004474124591890409</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001969281941815576</v>
+        <v>0.0001969281941815567</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2399754807840885</v>
+        <v>-0.2399754807840886</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.93263446465126</v>
+        <v>1.932634464651259</v>
       </c>
       <c r="Z6" t="n">
         <v>8.925189969828166</v>
@@ -998,70 +998,70 @@
         <v>10.78805907040962</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01185738075383621</v>
+        <v>0.0118573807538362</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02496184651645383</v>
+        <v>0.0249618465164538</v>
       </c>
       <c r="G7" t="n">
-        <v>3.466205223224516e-05</v>
+        <v>3.466205223224526e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009177299064127776</v>
+        <v>0.0009177299064127787</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001819140148745456</v>
+        <v>0.0001819140148745449</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007930724914394939</v>
+        <v>0.0007930724914394901</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002610529344917881</v>
+        <v>0.002610529344917878</v>
       </c>
       <c r="L7" t="n">
-        <v>2.834832487474957e-05</v>
+        <v>2.834832487474959e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.939832179420269e-05</v>
+        <v>4.939832179420266e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003277995852546188</v>
+        <v>0.003277995852546184</v>
       </c>
       <c r="O7" t="n">
-        <v>1.935999696519284e-05</v>
+        <v>1.935999696519326e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.605384289451955e-07</v>
+        <v>4.605384289451959e-07</v>
       </c>
       <c r="Q7" t="n">
         <v>5.55610383898784e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.202856507172356e-07</v>
+        <v>3.202856507172354e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.475154880496072e-06</v>
+        <v>1.475154880498078e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004611173467181576</v>
+        <v>0.0004611173467181575</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001530684113894626</v>
+        <v>0.00153068411389104</v>
       </c>
       <c r="V7" t="n">
         <v>0.004449761711081688</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001710622880939422</v>
+        <v>0.0001710622880939379</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.07069633046104792</v>
+        <v>-0.07069633046104801</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.882162744357824</v>
+        <v>1.882162744357825</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.925189976459356</v>
+        <v>8.925189976459363</v>
       </c>
     </row>
     <row r="8">
@@ -1079,73 +1079,73 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.79050591699847</v>
+        <v>10.79050591699846</v>
       </c>
       <c r="E8" t="n">
         <v>0.01141556514512947</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02248281503189183</v>
+        <v>0.0224828150318918</v>
       </c>
       <c r="G8" t="n">
-        <v>3.389035324393255e-05</v>
+        <v>3.389035324393253e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008982856254188459</v>
+        <v>0.0008982856254188452</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001771217017074158</v>
+        <v>0.0001771217017074168</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0006771731769008243</v>
+        <v>0.0006771731769008172</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002448804300056375</v>
+        <v>0.002448804300056377</v>
       </c>
       <c r="L8" t="n">
-        <v>2.765541921811573e-05</v>
+        <v>2.765541921811571e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.352794636395493e-05</v>
+        <v>4.352794636395484e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003138597376794613</v>
+        <v>0.00313859737679461</v>
       </c>
       <c r="O8" t="n">
-        <v>1.660794474598566e-05</v>
+        <v>1.660794474598603e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.586081903533449e-07</v>
+        <v>4.58608190353345e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.498777083214003e-05</v>
+        <v>5.498777083214e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.667596769109679e-07</v>
+        <v>2.667596769109674e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.404529303436115e-06</v>
+        <v>1.404529303436114e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0004305359312472168</v>
+        <v>0.0004305359312472172</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00139606635346739</v>
+        <v>0.001396066353467391</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004432713402793496</v>
+        <v>0.004432713402793497</v>
       </c>
       <c r="W8" t="n">
         <v>0.0001574928778863483</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.02750211053265116</v>
+        <v>-0.02750211053265122</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.84498407935192</v>
+        <v>1.844984079351919</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.92518997792433</v>
+        <v>8.925189977924328</v>
       </c>
     </row>
     <row r="9">
@@ -1166,67 +1166,67 @@
         <v>10.29806910126119</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01900176836938497</v>
+        <v>0.01900176836938499</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04781958141335538</v>
+        <v>0.04781958141335539</v>
       </c>
       <c r="G9" t="n">
-        <v>3.865082727739575e-05</v>
+        <v>3.865082727739569e-05</v>
       </c>
       <c r="H9" t="n">
         <v>0.001108967784076361</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002132322881441471</v>
+        <v>0.0002132322881441464</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001825800765632978</v>
+        <v>0.001825800765632988</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003550679011382639</v>
+        <v>0.003550679011382641</v>
       </c>
       <c r="L9" t="n">
         <v>3.22195979095663e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001116719534621416</v>
+        <v>0.0001116719534621415</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003979223893688779</v>
+        <v>0.00397922389368878</v>
       </c>
       <c r="O9" t="n">
-        <v>2.950538003336702e-05</v>
+        <v>2.95053800333665e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.717226071728159e-07</v>
+        <v>4.71722607172816e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.804541033259291e-05</v>
+        <v>5.804541033259287e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>5.059932245218345e-07</v>
+        <v>5.059932245218344e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31932242215432e-06</v>
+        <v>2.319322422154328e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0007681132126295448</v>
+        <v>0.0007681132126295463</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002709865058321571</v>
+        <v>0.002709865058321575</v>
       </c>
       <c r="V9" t="n">
         <v>0.004483748049092571</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0002687012292583038</v>
+        <v>0.0002687012292583042</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7201044224460219</v>
+        <v>-0.7201044224460221</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.006980502187039</v>
+        <v>2.006980502187038</v>
       </c>
       <c r="Z9" t="n">
         <v>8.925189950237939</v>
@@ -1250,70 +1250,70 @@
         <v>10.61420917619273</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01520223975346713</v>
+        <v>0.0152022397534671</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03771587804860257</v>
+        <v>0.03771587804860253</v>
       </c>
       <c r="G10" t="n">
-        <v>3.692877260451848e-05</v>
+        <v>3.692877260451845e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001053580870777552</v>
+        <v>0.001053580870777551</v>
       </c>
       <c r="I10" t="n">
         <v>0.0001999136913332694</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001231110052292761</v>
+        <v>0.001231110052292783</v>
       </c>
       <c r="K10" t="n">
-        <v>0.003030863976280352</v>
+        <v>0.00303086397628035</v>
       </c>
       <c r="L10" t="n">
-        <v>3.084938776627832e-05</v>
+        <v>3.084938776627834e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>7.892444792857958e-05</v>
+        <v>7.892444792857943e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003651622398944339</v>
+        <v>0.003651622398944337</v>
       </c>
       <c r="O10" t="n">
-        <v>2.565338000536203e-05</v>
+        <v>2.565338000536192e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>4.663005104049472e-07</v>
+        <v>4.66300510404947e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.708220726514607e-05</v>
+        <v>5.708220726514603e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.089192477896341e-07</v>
+        <v>4.08919247789634e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.988462934634097e-06</v>
+        <v>1.988462934634098e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0006499518852321101</v>
+        <v>0.0006499518852321091</v>
       </c>
       <c r="U10" t="n">
-        <v>0.00226903666734786</v>
+        <v>0.002269036667342656</v>
       </c>
       <c r="V10" t="n">
         <v>0.004467505190775396</v>
       </c>
       <c r="W10" t="n">
-        <v>0.000232211278582469</v>
+        <v>0.0002322112785824674</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3251828354846269</v>
+        <v>-0.3251828354846258</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.944265829784541</v>
+        <v>1.944265829784542</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.925189966200916</v>
+        <v>8.925189966200918</v>
       </c>
     </row>
     <row r="11">
@@ -1334,67 +1334,67 @@
         <v>10.8375017376456</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0115306500452492</v>
+        <v>0.01153065004524919</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02248107878999545</v>
+        <v>0.02248107878999553</v>
       </c>
       <c r="G11" t="n">
-        <v>3.495559723025826e-05</v>
+        <v>3.495559723025814e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0009106286434073734</v>
+        <v>0.0009106286434073738</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001839364047960218</v>
+        <v>0.0001839364047960227</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0007774857514576427</v>
+        <v>0.0007774857514576489</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00271345235271119</v>
+        <v>0.002713452352711191</v>
       </c>
       <c r="L11" t="n">
-        <v>2.856515258657365e-05</v>
+        <v>2.856515258657355e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.626331101109526e-05</v>
+        <v>4.626331101109531e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003300139308314216</v>
+        <v>0.003300139308314219</v>
       </c>
       <c r="O11" t="n">
-        <v>2.058098829970972e-05</v>
+        <v>2.058098829970993e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>4.630275099501097e-07</v>
+        <v>4.630275099501092e-07</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.575044531408424e-05</v>
+        <v>5.575044531408423e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.88065794405089e-07</v>
+        <v>2.880657944050878e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.581711234406289e-06</v>
+        <v>1.581711234406284e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.000482777844079911</v>
+        <v>0.0004827778440799133</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001563511213170713</v>
+        <v>0.001563511213172279</v>
       </c>
       <c r="V11" t="n">
-        <v>0.004456854148702481</v>
+        <v>0.004456854148702482</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0001747010238558096</v>
+        <v>0.0001747010238558121</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.04964680913109988</v>
+        <v>-0.04964680913109992</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.913194905202195</v>
+        <v>1.913194905202194</v>
       </c>
       <c r="Z11" t="n">
         <v>8.925189977749785</v>
@@ -1566,79 +1566,79 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.495175991793104</v>
+        <v>4.495175991793101</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1520282652691767</v>
+        <v>0.1520282652691768</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02279952694155899</v>
+        <v>0.02279952694155886</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0557848892882818</v>
+        <v>0.05578488928828166</v>
       </c>
       <c r="H2" t="n">
-        <v>4.010483954252142e-05</v>
+        <v>4.010483954252127e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00114532624146651</v>
+        <v>0.001145326241466513</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002234417210028187</v>
+        <v>0.0002234417210028195</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002172280437535946</v>
+        <v>0.002172280437535925</v>
       </c>
       <c r="L2" t="n">
         <v>0.0006520258697178699</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004087489492760879</v>
+        <v>0.004087489492760882</v>
       </c>
       <c r="N2" t="n">
-        <v>3.329041918983529e-05</v>
+        <v>3.329041918983525e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001345287036150599</v>
+        <v>0.0001345287036150598</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004181531270246583</v>
+        <v>0.004181531270246569</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.242675186689183e-05</v>
+        <v>3.242675186689206e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>4.773778149478629e-07</v>
+        <v>4.773778149478628e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>5.86953034717722e-05</v>
+        <v>5.869530347177221e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>5.318463955165519e-07</v>
+        <v>5.318463955165452e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>2.678902949203054e-06</v>
+        <v>2.678902949203049e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008761882947529487</v>
+        <v>0.0008761882947529459</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003072651191782646</v>
+        <v>0.003072651191782642</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004491492021052262</v>
+        <v>0.004491492021052261</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002992821928195295</v>
+        <v>0.0002992821928195261</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.4064903212640072</v>
+        <v>-0.4064903212640071</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.03644393780742</v>
+        <v>2.036443937807416</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.61310525087269</v>
+        <v>2.613105250872692</v>
       </c>
     </row>
     <row r="3">
@@ -1656,79 +1656,79 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.471625342259953</v>
+        <v>4.47162534225995</v>
       </c>
       <c r="E3" t="n">
         <v>0.1489880991750844</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02076609750052483</v>
+        <v>0.02076609750052478</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05267281656666426</v>
+        <v>0.0526728165666643</v>
       </c>
       <c r="H3" t="n">
-        <v>3.94839418063846e-05</v>
+        <v>3.948394180638485e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001133335664104356</v>
+        <v>0.00113333566410436</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002190167026321967</v>
+        <v>0.0002190167026321962</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002081262456268528</v>
+        <v>0.002081262456268537</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000631024361855566</v>
+        <v>0.0006310243618555657</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003869750027926286</v>
+        <v>0.003869750027926281</v>
       </c>
       <c r="N3" t="n">
-        <v>3.285777781588818e-05</v>
+        <v>3.28577778158882e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001273715634376781</v>
+        <v>0.000127371563437678</v>
       </c>
       <c r="P3" t="n">
         <v>0.004126072192052787</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.108978222078868e-05</v>
+        <v>3.108978222078863e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>4.738079301459342e-07</v>
+        <v>4.73807930145934e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>5.843554502209941e-05</v>
+        <v>5.843554502209935e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.150740251408739e-07</v>
+        <v>5.150740251408649e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>2.477733125091042e-06</v>
+        <v>2.477733125091041e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008290980202552057</v>
+        <v>0.0008290980202552061</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002938723225670088</v>
+        <v>0.002938723225670072</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004486964668614885</v>
+        <v>0.004486964668614887</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002858948217060443</v>
+        <v>0.0002858948217060439</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.39831058197278</v>
+        <v>-0.3983105819727797</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.013509812112061</v>
+        <v>2.013509812112059</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.61310525151193</v>
+        <v>2.613105251511928</v>
       </c>
     </row>
     <row r="4">
@@ -1746,61 +1746,61 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.467415346160646</v>
+        <v>4.467415346160647</v>
       </c>
       <c r="E4" t="n">
         <v>0.1421568783114497</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02107085790888245</v>
+        <v>0.02107085790888249</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05125214951947078</v>
+        <v>0.05125214951947083</v>
       </c>
       <c r="H4" t="n">
-        <v>3.933887801134972e-05</v>
+        <v>3.933887801134976e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001120311520254873</v>
+        <v>0.001120311520254866</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002166100336657495</v>
+        <v>0.0002166100336657493</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00199302542701326</v>
+        <v>0.001993025427013273</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006316809502153861</v>
+        <v>0.0006316809502153868</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003569416533588157</v>
+        <v>0.003569416533588163</v>
       </c>
       <c r="N4" t="n">
-        <v>3.260833872528322e-05</v>
+        <v>3.260833872528327e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001214677816079298</v>
+        <v>0.0001214677816079299</v>
       </c>
       <c r="P4" t="n">
         <v>0.004047020145379852</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.00591622942299e-05</v>
+        <v>3.005916229423104e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.74034444509213e-07</v>
+        <v>4.740344445092132e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.817496370844628e-05</v>
+        <v>5.817496370844624e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.737836485007958e-07</v>
+        <v>4.737836485008045e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.501976712642953e-06</v>
+        <v>2.501976712642957e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0008201555590061861</v>
+        <v>0.000820155559006661</v>
       </c>
       <c r="W4" t="n">
         <v>0.002867520880812395</v>
@@ -1809,16 +1809,16 @@
         <v>0.004476661901931694</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002814414811790723</v>
+        <v>0.000281441481179075</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.3797685820443268</v>
+        <v>-0.379768582044327</v>
       </c>
       <c r="AA4" t="n">
         <v>1.999289847368495</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.613105251744475</v>
+        <v>2.613105251744476</v>
       </c>
     </row>
     <row r="5">
@@ -1836,46 +1836,46 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.477093256207611</v>
+        <v>4.47709325620761</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1281873922631927</v>
+        <v>0.1281873922631928</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02259225485549478</v>
+        <v>0.02259225485549474</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04960081605297016</v>
+        <v>0.04960081605296998</v>
       </c>
       <c r="H5" t="n">
-        <v>3.919861300280303e-05</v>
+        <v>3.919861300280301e-05</v>
       </c>
       <c r="I5" t="n">
         <v>0.0010910869847508</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002140162672597562</v>
+        <v>0.0002140162672597558</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001881469232512534</v>
+        <v>0.001881469232512527</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006294417153692999</v>
+        <v>0.0006294417153693002</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003415563880839496</v>
+        <v>0.003415563880839495</v>
       </c>
       <c r="N5" t="n">
-        <v>3.219092836217396e-05</v>
+        <v>3.219092836217395e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001140959614549085</v>
+        <v>0.0001140959614549086</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003984466512089086</v>
+        <v>0.003984466512089091</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.930124706378527e-05</v>
+        <v>2.930124706378508e-05</v>
       </c>
       <c r="R5" t="n">
         <v>4.769799960909287e-07</v>
@@ -1884,31 +1884,31 @@
         <v>5.792200788341426e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.567685486867253e-07</v>
+        <v>4.567685486867234e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.569128164503852e-06</v>
+        <v>2.569128164503851e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0008048590265937227</v>
+        <v>0.0008048590265937203</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002724400532036937</v>
+        <v>0.002724400532036946</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004473757720860037</v>
+        <v>0.004473757720860036</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002752750533536005</v>
+        <v>0.0002752750533536022</v>
       </c>
       <c r="Z5" t="n">
         <v>-0.3418381484185069</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.985675141210095</v>
+        <v>1.985675141210097</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.613105251684223</v>
+        <v>2.613105251684221</v>
       </c>
     </row>
     <row r="6">
@@ -1926,79 +1926,79 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.508805161931165</v>
+        <v>4.508805161931168</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04136300592575514</v>
+        <v>0.04136300592575508</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01373805522991726</v>
+        <v>0.01373805522991727</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03078732961702694</v>
+        <v>0.03078732961702706</v>
       </c>
       <c r="H6" t="n">
-        <v>3.599421573179585e-05</v>
+        <v>3.599421573179587e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009582645687425371</v>
+        <v>0.0009582645687425394</v>
       </c>
       <c r="J6" t="n">
         <v>0.00019129072384295</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001123065831364149</v>
+        <v>0.001123065831364148</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004991595838911687</v>
+        <v>0.0004991595838911691</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003021955219494393</v>
+        <v>0.00302195521949439</v>
       </c>
       <c r="N6" t="n">
         <v>2.949785401874817e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>6.765252205622785e-05</v>
+        <v>6.765252205622786e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003589767574783412</v>
+        <v>0.003589767574783435</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.371074285636723e-05</v>
+        <v>2.371074285636719e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.64417070663814e-07</v>
+        <v>4.644170706638141e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>5.647540433350844e-05</v>
+        <v>5.647540433350838e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.935332972846572e-07</v>
+        <v>3.935332972846631e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.666200878651818e-06</v>
+        <v>1.666200878651816e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005329070131812704</v>
+        <v>0.0005329070131812725</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001816553197223079</v>
+        <v>0.001816553197223083</v>
       </c>
       <c r="X6" t="n">
         <v>0.004474124591890409</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001969281941815576</v>
+        <v>0.0001969281941815567</v>
       </c>
       <c r="Z6" t="n">
         <v>-0.1091896137785957</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9023812626941</v>
+        <v>1.902381262694101</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.613105250854123</v>
+        <v>2.613105250854125</v>
       </c>
     </row>
     <row r="7">
@@ -2016,79 +2016,79 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.49805067204214</v>
+        <v>4.498050672042138</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01254387007551676</v>
+        <v>0.01254387007551678</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01185602222360196</v>
+        <v>0.01185602222360194</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0249589865742878</v>
+        <v>0.02495898657428778</v>
       </c>
       <c r="H7" t="n">
-        <v>3.466205223224516e-05</v>
+        <v>3.466205223224526e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009177299064127776</v>
+        <v>0.0009177299064127787</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001819140148745456</v>
+        <v>0.0001819140148745449</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007930724914394939</v>
+        <v>0.0007930724914394901</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004707545455963319</v>
+        <v>0.0004707545455963314</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002610529344917881</v>
+        <v>0.002610529344917878</v>
       </c>
       <c r="N7" t="n">
-        <v>2.834832487474957e-05</v>
+        <v>2.834832487474959e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>4.939832179420269e-05</v>
+        <v>4.939832179420266e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003277995852546188</v>
+        <v>0.003277995852546184</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.935999696519284e-05</v>
+        <v>1.935999696519326e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>4.605384289451955e-07</v>
+        <v>4.605384289451959e-07</v>
       </c>
       <c r="S7" t="n">
         <v>5.55610383898784e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.202856507172356e-07</v>
+        <v>3.202856507172354e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>1.474985868255591e-06</v>
+        <v>1.474985868256083e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0004610645153323679</v>
+        <v>0.000461064515332368</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001530508739528477</v>
+        <v>0.00153050873953436</v>
       </c>
       <c r="X7" t="n">
         <v>0.004449761711081688</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001710622880939422</v>
+        <v>0.0001710622880939379</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.03216705720677765</v>
+        <v>-0.03216705720677762</v>
       </c>
       <c r="AA7" t="n">
         <v>1.852699619973581</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.613105251447903</v>
+        <v>2.613105251447895</v>
       </c>
     </row>
     <row r="8">
@@ -2106,79 +2106,79 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.470166377637432</v>
+        <v>4.470166377637435</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005182853889729516</v>
+        <v>0.005182853889729433</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01141425723483181</v>
+        <v>0.0114142572348318</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02248023911866053</v>
+        <v>0.02248023911866059</v>
       </c>
       <c r="H8" t="n">
-        <v>3.389035324393255e-05</v>
+        <v>3.389035324393253e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008982856254188459</v>
+        <v>0.0008982856254188452</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001771217017074158</v>
+        <v>0.0001771217017074168</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0006771731769008243</v>
+        <v>0.0006771731769008172</v>
       </c>
       <c r="L8" t="n">
         <v>0.0004589979810556905</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002448804300056375</v>
+        <v>0.002448804300056377</v>
       </c>
       <c r="N8" t="n">
-        <v>2.765541921811573e-05</v>
+        <v>2.765541921811571e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>4.352794636395493e-05</v>
+        <v>4.352794636395484e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003138597376794613</v>
+        <v>0.00313859737679461</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.660794474598566e-05</v>
+        <v>1.660794474598603e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>4.586081903533449e-07</v>
+        <v>4.58608190353345e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>5.498777083214003e-05</v>
+        <v>5.498777083214e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.667596769109679e-07</v>
+        <v>2.667596769109674e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>1.404368382945891e-06</v>
+        <v>1.404368382945893e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004304866036518811</v>
+        <v>0.0004304866036518827</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001395906402598845</v>
+        <v>0.001395906402598848</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004432713402793496</v>
+        <v>0.004432713402793497</v>
       </c>
       <c r="Y8" t="n">
         <v>0.0001574928778863483</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.01251354853981196</v>
+        <v>-0.0125135485398121</v>
       </c>
       <c r="AA8" t="n">
         <v>1.81610294482737</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.613105252487133</v>
+        <v>2.613105252487136</v>
       </c>
     </row>
     <row r="9">
@@ -2199,73 +2199,73 @@
         <v>4.470253281959859</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1226329346964657</v>
+        <v>0.1226329346964659</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01899959128851268</v>
+        <v>0.01899959128851271</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04781410260243675</v>
+        <v>0.04781410260243673</v>
       </c>
       <c r="H9" t="n">
-        <v>3.865082727739575e-05</v>
+        <v>3.865082727739569e-05</v>
       </c>
       <c r="I9" t="n">
         <v>0.001108967784076361</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002132322881441471</v>
+        <v>0.0002132322881441464</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001825800765632978</v>
+        <v>0.001825800765632988</v>
       </c>
       <c r="L9" t="n">
         <v>0.0006064044076557117</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003550679011382639</v>
+        <v>0.003550679011382641</v>
       </c>
       <c r="N9" t="n">
         <v>3.22195979095663e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0001116719534621416</v>
+        <v>0.0001116719534621415</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003979223893688779</v>
+        <v>0.00397922389368878</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.950538003336702e-05</v>
+        <v>2.95053800333665e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.717226071728159e-07</v>
+        <v>4.71722607172816e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>5.804541033259291e-05</v>
+        <v>5.804541033259287e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>5.059932245218345e-07</v>
+        <v>5.059932245218344e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>2.319056691492637e-06</v>
+        <v>2.319056691492629e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0007680252079475353</v>
+        <v>0.0007680252079475363</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002709554582197967</v>
+        <v>0.002709554582197972</v>
       </c>
       <c r="X9" t="n">
         <v>0.004483748049092571</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002687012292583038</v>
+        <v>0.0002687012292583042</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.3276498228495399</v>
+        <v>-0.3276498228495404</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.975563497281409</v>
+        <v>1.975563497281408</v>
       </c>
       <c r="AB9" t="n">
         <v>2.61310525177996</v>
@@ -2286,79 +2286,79 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.505014507966624</v>
+        <v>4.505014507966621</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05555088518970951</v>
+        <v>0.05555088518970927</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0152004979942403</v>
+        <v>0.01520049799424027</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03771155684464494</v>
+        <v>0.03771155684464485</v>
       </c>
       <c r="H10" t="n">
-        <v>3.692877260451848e-05</v>
+        <v>3.692877260451845e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001053580870777552</v>
+        <v>0.001053580870777551</v>
       </c>
       <c r="J10" t="n">
         <v>0.0001999136913332694</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001231110052292761</v>
+        <v>0.001231110052292783</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0005572350871556448</v>
+        <v>0.0005572350871556445</v>
       </c>
       <c r="M10" t="n">
-        <v>0.003030863976280352</v>
+        <v>0.00303086397628035</v>
       </c>
       <c r="N10" t="n">
-        <v>3.084938776627832e-05</v>
+        <v>3.084938776627834e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>7.892444792857958e-05</v>
+        <v>7.892444792857943e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003651622398944339</v>
+        <v>0.003651622398944337</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.565338000536203e-05</v>
+        <v>2.565338000536192e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.663005104049472e-07</v>
+        <v>4.66300510404947e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>5.708220726514607e-05</v>
+        <v>5.708220726514603e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>4.089192477896341e-07</v>
+        <v>4.08919247789634e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>1.98823511138438e-06</v>
+        <v>1.988235111384381e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0006498774185935461</v>
+        <v>0.0006498774185935457</v>
       </c>
       <c r="W10" t="n">
-        <v>0.002268776698048727</v>
+        <v>0.00226877669804764</v>
       </c>
       <c r="X10" t="n">
         <v>0.004467505190775396</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.000232211278582469</v>
+        <v>0.0002322112785824674</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.147959233576621</v>
+        <v>-0.1479592335766207</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.913830551990051</v>
+        <v>1.91383055199005</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.613105251211375</v>
+        <v>2.613105251211374</v>
       </c>
     </row>
     <row r="11">
@@ -2376,79 +2376,79 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.531811533699258</v>
+        <v>4.531811533699257</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008811355868500372</v>
+        <v>0.0088113558685004</v>
       </c>
       <c r="F11" t="n">
         <v>0.01152932894938218</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02247850307568998</v>
+        <v>0.02247850307568989</v>
       </c>
       <c r="H11" t="n">
-        <v>3.495559723025826e-05</v>
+        <v>3.495559723025814e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0009106286434073734</v>
+        <v>0.0009106286434073738</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001839364047960218</v>
+        <v>0.0001839364047960227</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0007774857514576427</v>
+        <v>0.0007774857514576489</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004788453409431053</v>
+        <v>0.0004788453409431045</v>
       </c>
       <c r="M11" t="n">
-        <v>0.00271345235271119</v>
+        <v>0.002713452352711191</v>
       </c>
       <c r="N11" t="n">
-        <v>2.856515258657365e-05</v>
+        <v>2.856515258657355e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>4.626331101109526e-05</v>
+        <v>4.626331101109531e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.003300139308314216</v>
+        <v>0.003300139308314219</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.058098829970972e-05</v>
+        <v>2.058098829970993e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>4.630275099501097e-07</v>
+        <v>4.630275099501092e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>5.575044531408424e-05</v>
+        <v>5.575044531408423e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88065794405089e-07</v>
+        <v>2.880657944050878e-07</v>
       </c>
       <c r="U11" t="n">
-        <v>1.58153001373215e-06</v>
+        <v>1.581530013732139e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0004827225309959116</v>
+        <v>0.0004827225309959145</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001563332077720648</v>
+        <v>0.00156333207772114</v>
       </c>
       <c r="X11" t="n">
-        <v>0.004456854148702481</v>
+        <v>0.004456854148702482</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0001747010238558096</v>
+        <v>0.0001747010238558121</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.02258945745895519</v>
+        <v>-0.02258945745895521</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.883246007514019</v>
+        <v>1.883246007514016</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.613105250049958</v>
+        <v>2.613105250049959</v>
       </c>
     </row>
   </sheetData>
@@ -2610,67 +2610,67 @@
         <v>11.09346538391463</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02280213944059894</v>
+        <v>0.02280213944059888</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05579128143712271</v>
+        <v>0.05579128143712251</v>
       </c>
       <c r="G2" t="n">
-        <v>4.010483954252142e-05</v>
+        <v>4.010483954252127e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00114532624146651</v>
+        <v>0.001145326241466513</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002234417210028187</v>
+        <v>0.0002234417210028195</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002172280437535946</v>
+        <v>0.002172280437535925</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004087489492760879</v>
+        <v>0.004087489492760882</v>
       </c>
       <c r="L2" t="n">
-        <v>3.329041918983529e-05</v>
+        <v>3.329041918983525e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001345287036150599</v>
+        <v>0.0001345287036150598</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004181531270246583</v>
+        <v>0.004181531270246569</v>
       </c>
       <c r="O2" t="n">
-        <v>3.242675186689183e-05</v>
+        <v>3.242675186689206e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.773778149478629e-07</v>
+        <v>4.773778149478628e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.86953034717722e-05</v>
+        <v>5.869530347177221e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>5.318463955165519e-07</v>
+        <v>5.318463955165452e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>2.679209913088794e-06</v>
+        <v>2.679209913088789e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008762886933745839</v>
+        <v>0.0008762886933745828</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003073003273574051</v>
+        <v>0.003073003273574045</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004491492021052262</v>
+        <v>0.004491492021052261</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002992821928195295</v>
+        <v>0.0002992821928195261</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.068829112605489</v>
+        <v>2.068829112605486</v>
       </c>
       <c r="Z2" t="n">
         <v>8.925189980635777</v>
@@ -2694,70 +2694,70 @@
         <v>11.064430834508</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02076847699769263</v>
+        <v>0.0207684769976926</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05267885211657142</v>
+        <v>0.05267885211657136</v>
       </c>
       <c r="G3" t="n">
-        <v>3.94839418063846e-05</v>
+        <v>3.948394180638485e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001133335664104356</v>
+        <v>0.00113333566410436</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002190167026321967</v>
+        <v>0.0002190167026321962</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002081262456268528</v>
+        <v>0.002081262456268537</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003869750027926286</v>
+        <v>0.003869750027926281</v>
       </c>
       <c r="L3" t="n">
-        <v>3.285777781588818e-05</v>
+        <v>3.28577778158882e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001273715634376781</v>
+        <v>0.000127371563437678</v>
       </c>
       <c r="N3" t="n">
         <v>0.004126072192052787</v>
       </c>
       <c r="O3" t="n">
-        <v>3.108978222078868e-05</v>
+        <v>3.108978222078863e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.738079301459342e-07</v>
+        <v>4.73807930145934e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.843554502209941e-05</v>
+        <v>5.843554502209935e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.150740251408739e-07</v>
+        <v>5.150740251408649e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.478017037797967e-06</v>
+        <v>2.478017037797965e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000829193023006254</v>
+        <v>0.0008291930230062517</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002939059961235936</v>
+        <v>0.002939059961235925</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004486964668614885</v>
+        <v>0.004486964668614887</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002858948217060443</v>
+        <v>0.0002858948217060439</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.045530269936733</v>
+        <v>2.045530269936735</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.92518998043016</v>
+        <v>8.925189980430158</v>
       </c>
     </row>
     <row r="4">
@@ -2778,70 +2778,70 @@
         <v>11.04828312801857</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02107327232722539</v>
+        <v>0.02107327232722546</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05125802228129434</v>
+        <v>0.0512580222812944</v>
       </c>
       <c r="G4" t="n">
-        <v>3.933887801134972e-05</v>
+        <v>3.933887801134976e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001120311520254873</v>
+        <v>0.001120311520254866</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002166100336657495</v>
+        <v>0.0002166100336657493</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00199302542701326</v>
+        <v>0.001993025427013273</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003569416533588157</v>
+        <v>0.003569416533588163</v>
       </c>
       <c r="L4" t="n">
-        <v>3.260833872528322e-05</v>
+        <v>3.260833872528327e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001214677816079298</v>
+        <v>0.0001214677816079299</v>
       </c>
       <c r="N4" t="n">
         <v>0.004047020145379852</v>
       </c>
       <c r="O4" t="n">
-        <v>3.00591622942299e-05</v>
+        <v>3.005916229423104e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.74034444509213e-07</v>
+        <v>4.740344445092132e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.817496370844628e-05</v>
+        <v>5.817496370844624e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.737836485007958e-07</v>
+        <v>4.737836485008045e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>2.502263403317572e-06</v>
+        <v>2.502263403317577e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0008202495370808446</v>
+        <v>0.0008202495370798036</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00286784945760995</v>
+        <v>0.002867849457609953</v>
       </c>
       <c r="V4" t="n">
         <v>0.004476661901931694</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002814414811790723</v>
+        <v>0.000281441481179075</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.031084167839075</v>
+        <v>2.031084167839078</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.925189980327428</v>
+        <v>8.925189980327431</v>
       </c>
     </row>
     <row r="5">
@@ -2859,40 +2859,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.03378578466143</v>
+        <v>11.03378578466144</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02259484360412419</v>
+        <v>0.02259484360412415</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04960649959564417</v>
+        <v>0.04960649959564408</v>
       </c>
       <c r="G5" t="n">
-        <v>3.919861300280303e-05</v>
+        <v>3.919861300280301e-05</v>
       </c>
       <c r="H5" t="n">
         <v>0.0010910869847508</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002140162672597562</v>
+        <v>0.0002140162672597558</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001881469232512534</v>
+        <v>0.001881469232512527</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003415563880839496</v>
+        <v>0.003415563880839495</v>
       </c>
       <c r="L5" t="n">
-        <v>3.219092836217396e-05</v>
+        <v>3.219092836217395e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001140959614549085</v>
+        <v>0.0001140959614549086</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003984466512089086</v>
+        <v>0.003984466512089091</v>
       </c>
       <c r="O5" t="n">
-        <v>2.930124706378527e-05</v>
+        <v>2.930124706378508e-05</v>
       </c>
       <c r="P5" t="n">
         <v>4.769799960909287e-07</v>
@@ -2901,22 +2901,22 @@
         <v>5.792200788341426e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.567685486867253e-07</v>
+        <v>4.567685486867234e-07</v>
       </c>
       <c r="S5" t="n">
         <v>2.569422549772487e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0008049512519034689</v>
+        <v>0.0008049512519034685</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00272471270929363</v>
+        <v>0.002724712709293636</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004473757720860037</v>
+        <v>0.004473757720860036</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002752750533536005</v>
+        <v>0.0002752750533536022</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>2.017252949637026</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.925189980282916</v>
+        <v>8.925189980282918</v>
       </c>
     </row>
     <row r="6">
@@ -2946,70 +2946,70 @@
         <v>10.91847591246967</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01373962941416203</v>
+        <v>0.01373962941416204</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03079085740377783</v>
+        <v>0.03079085740377786</v>
       </c>
       <c r="G6" t="n">
-        <v>3.599421573179585e-05</v>
+        <v>3.599421573179587e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009582645687425371</v>
+        <v>0.0009582645687425394</v>
       </c>
       <c r="I6" t="n">
         <v>0.00019129072384295</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001123065831364149</v>
+        <v>0.001123065831364148</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003021955219494393</v>
+        <v>0.00302195521949439</v>
       </c>
       <c r="L6" t="n">
         <v>2.949785401874817e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>6.765252205622785e-05</v>
+        <v>6.765252205622786e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003589767574783412</v>
+        <v>0.003589767574783435</v>
       </c>
       <c r="O6" t="n">
-        <v>2.371074285636723e-05</v>
+        <v>2.371074285636719e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.64417070663814e-07</v>
+        <v>4.644170706638141e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.647540433350844e-05</v>
+        <v>5.647540433350838e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>3.935332972846572e-07</v>
+        <v>3.935332972846631e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.66639180139364e-06</v>
+        <v>1.666391801393639e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005329680766877166</v>
+        <v>0.0005329680766877176</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001816761348185858</v>
+        <v>0.001816761348185862</v>
       </c>
       <c r="V6" t="n">
         <v>0.004474124591890409</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001969281941815576</v>
+        <v>0.0001969281941815567</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.93263446465126</v>
+        <v>1.932634464651259</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.925189979790128</v>
+        <v>8.925189979790131</v>
       </c>
     </row>
     <row r="7">
@@ -3030,70 +3030,70 @@
         <v>10.85875540380544</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01185738075383621</v>
+        <v>0.0118573807538362</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02496184651645383</v>
+        <v>0.0249618465164538</v>
       </c>
       <c r="G7" t="n">
-        <v>3.466205223224516e-05</v>
+        <v>3.466205223224526e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009177299064127776</v>
+        <v>0.0009177299064127787</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001819140148745456</v>
+        <v>0.0001819140148745449</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007930724914394939</v>
+        <v>0.0007930724914394901</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002610529344917881</v>
+        <v>0.002610529344917878</v>
       </c>
       <c r="L7" t="n">
-        <v>2.834832487474957e-05</v>
+        <v>2.834832487474959e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.939832179420269e-05</v>
+        <v>4.939832179420266e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003277995852546188</v>
+        <v>0.003277995852546184</v>
       </c>
       <c r="O7" t="n">
-        <v>1.935999696519284e-05</v>
+        <v>1.935999696519326e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.605384289451955e-07</v>
+        <v>4.605384289451959e-07</v>
       </c>
       <c r="Q7" t="n">
         <v>5.55610383898784e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.202856507172356e-07</v>
+        <v>3.202856507172354e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.475154880496072e-06</v>
+        <v>1.475154880498078e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004611173467181576</v>
+        <v>0.0004611173467181575</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001530684113894626</v>
+        <v>0.00153068411389104</v>
       </c>
       <c r="V7" t="n">
         <v>0.004449761711081688</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001710622880939422</v>
+        <v>0.0001710622880939379</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.882162744357824</v>
+        <v>1.882162744357825</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.925189979394132</v>
+        <v>8.925189979394137</v>
       </c>
     </row>
     <row r="8">
@@ -3117,55 +3117,55 @@
         <v>0.01141556514512947</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02248281503189183</v>
+        <v>0.0224828150318918</v>
       </c>
       <c r="G8" t="n">
-        <v>3.389035324393255e-05</v>
+        <v>3.389035324393253e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008982856254188459</v>
+        <v>0.0008982856254188452</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001771217017074158</v>
+        <v>0.0001771217017074168</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0006771731769008243</v>
+        <v>0.0006771731769008172</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002448804300056375</v>
+        <v>0.002448804300056377</v>
       </c>
       <c r="L8" t="n">
-        <v>2.765541921811573e-05</v>
+        <v>2.765541921811571e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.352794636395493e-05</v>
+        <v>4.352794636395484e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003138597376794613</v>
+        <v>0.00313859737679461</v>
       </c>
       <c r="O8" t="n">
-        <v>1.660794474598566e-05</v>
+        <v>1.660794474598603e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.586081903533449e-07</v>
+        <v>4.58608190353345e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.498777083214003e-05</v>
+        <v>5.498777083214e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.667596769109679e-07</v>
+        <v>2.667596769109674e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.404529303436115e-06</v>
+        <v>1.404529303436114e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0004305359312472168</v>
+        <v>0.0004305359312472172</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00139606635346739</v>
+        <v>0.001396066353467391</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004432713402793496</v>
+        <v>0.004432713402793497</v>
       </c>
       <c r="W8" t="n">
         <v>0.0001574928778863483</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.84498407935192</v>
+        <v>1.844984079351919</v>
       </c>
       <c r="Z8" t="n">
         <v>8.925189979066008</v>
@@ -3198,70 +3198,70 @@
         <v>11.0181735536005</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01900176836938497</v>
+        <v>0.01900176836938499</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04781958141335538</v>
+        <v>0.04781958141335539</v>
       </c>
       <c r="G9" t="n">
-        <v>3.865082727739575e-05</v>
+        <v>3.865082727739569e-05</v>
       </c>
       <c r="H9" t="n">
         <v>0.001108967784076361</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002132322881441471</v>
+        <v>0.0002132322881441464</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001825800765632978</v>
+        <v>0.001825800765632988</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003550679011382639</v>
+        <v>0.003550679011382641</v>
       </c>
       <c r="L9" t="n">
         <v>3.22195979095663e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001116719534621416</v>
+        <v>0.0001116719534621415</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003979223893688779</v>
+        <v>0.00397922389368878</v>
       </c>
       <c r="O9" t="n">
-        <v>2.950538003336702e-05</v>
+        <v>2.95053800333665e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.717226071728159e-07</v>
+        <v>4.71722607172816e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.804541033259291e-05</v>
+        <v>5.804541033259287e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>5.059932245218345e-07</v>
+        <v>5.059932245218344e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31932242215432e-06</v>
+        <v>2.319322422154328e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0007681132126295448</v>
+        <v>0.0007681132126295463</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002709865058321571</v>
+        <v>0.002709865058321575</v>
       </c>
       <c r="V9" t="n">
         <v>0.004483748049092571</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0002687012292583038</v>
+        <v>0.0002687012292583042</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.006980502187039</v>
+        <v>2.006980502187038</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.925189980131224</v>
+        <v>8.925189980131226</v>
       </c>
     </row>
     <row r="10">
@@ -3282,70 +3282,70 @@
         <v>10.93939202517648</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01520223975346713</v>
+        <v>0.0152022397534671</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03771587804860257</v>
+        <v>0.03771587804860253</v>
       </c>
       <c r="G10" t="n">
-        <v>3.692877260451848e-05</v>
+        <v>3.692877260451845e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001053580870777552</v>
+        <v>0.001053580870777551</v>
       </c>
       <c r="I10" t="n">
         <v>0.0001999136913332694</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001231110052292761</v>
+        <v>0.001231110052292783</v>
       </c>
       <c r="K10" t="n">
-        <v>0.003030863976280352</v>
+        <v>0.00303086397628035</v>
       </c>
       <c r="L10" t="n">
-        <v>3.084938776627832e-05</v>
+        <v>3.084938776627834e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>7.892444792857958e-05</v>
+        <v>7.892444792857943e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003651622398944339</v>
+        <v>0.003651622398944337</v>
       </c>
       <c r="O10" t="n">
-        <v>2.565338000536203e-05</v>
+        <v>2.565338000536192e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>4.663005104049472e-07</v>
+        <v>4.66300510404947e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.708220726514607e-05</v>
+        <v>5.708220726514603e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.089192477896341e-07</v>
+        <v>4.08919247789634e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.988462934634097e-06</v>
+        <v>1.988462934634098e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0006499518852321101</v>
+        <v>0.0006499518852321091</v>
       </c>
       <c r="U10" t="n">
-        <v>0.00226903666734786</v>
+        <v>0.002269036667342656</v>
       </c>
       <c r="V10" t="n">
         <v>0.004467505190775396</v>
       </c>
       <c r="W10" t="n">
-        <v>0.000232211278582469</v>
+        <v>0.0002322112785824674</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.944265829784541</v>
+        <v>1.944265829784542</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.925189979700042</v>
+        <v>8.925189979700047</v>
       </c>
     </row>
     <row r="11">
@@ -3366,70 +3366,70 @@
         <v>10.88714854883766</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0115306500452492</v>
+        <v>0.01153065004524919</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02248107878999545</v>
+        <v>0.02248107878999553</v>
       </c>
       <c r="G11" t="n">
-        <v>3.495559723025826e-05</v>
+        <v>3.495559723025814e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0009106286434073734</v>
+        <v>0.0009106286434073738</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001839364047960218</v>
+        <v>0.0001839364047960227</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0007774857514576427</v>
+        <v>0.0007774857514576489</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00271345235271119</v>
+        <v>0.002713452352711191</v>
       </c>
       <c r="L11" t="n">
-        <v>2.856515258657365e-05</v>
+        <v>2.856515258657355e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.626331101109526e-05</v>
+        <v>4.626331101109531e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003300139308314216</v>
+        <v>0.003300139308314219</v>
       </c>
       <c r="O11" t="n">
-        <v>2.058098829970972e-05</v>
+        <v>2.058098829970993e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>4.630275099501097e-07</v>
+        <v>4.630275099501092e-07</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.575044531408424e-05</v>
+        <v>5.575044531408423e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.88065794405089e-07</v>
+        <v>2.880657944050878e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.581711234406289e-06</v>
+        <v>1.581711234406284e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.000482777844079911</v>
+        <v>0.0004827778440799133</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001563511213170713</v>
+        <v>0.001563511213172279</v>
       </c>
       <c r="V11" t="n">
-        <v>0.004456854148702481</v>
+        <v>0.004456854148702482</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0001747010238558096</v>
+        <v>0.0001747010238558121</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.913194905202195</v>
+        <v>1.913194905202194</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.925189979810748</v>
+        <v>8.925189979810746</v>
       </c>
     </row>
   </sheetData>
@@ -3598,79 +3598,79 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.901666310329686</v>
+        <v>4.901666310329683</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1520282652691767</v>
+        <v>0.1520282652691768</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02279952694155899</v>
+        <v>0.02279952694155886</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0557848892882818</v>
+        <v>0.05578488928828166</v>
       </c>
       <c r="H2" t="n">
-        <v>4.010483954252142e-05</v>
+        <v>4.010483954252127e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00114532624146651</v>
+        <v>0.001145326241466513</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002234417210028187</v>
+        <v>0.0002234417210028195</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002172280437535946</v>
+        <v>0.002172280437535925</v>
       </c>
       <c r="L2" t="n">
         <v>0.0006520258697178699</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004087489492760879</v>
+        <v>0.004087489492760882</v>
       </c>
       <c r="N2" t="n">
-        <v>3.329041918983529e-05</v>
+        <v>3.329041918983525e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001345287036150599</v>
+        <v>0.0001345287036150598</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004181531270246583</v>
+        <v>0.004181531270246569</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.242675186689183e-05</v>
+        <v>3.242675186689206e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>4.773778149478629e-07</v>
+        <v>4.773778149478628e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>5.86953034717722e-05</v>
+        <v>5.869530347177221e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>5.318463955165519e-07</v>
+        <v>5.318463955165452e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>2.678902949203054e-06</v>
+        <v>2.678902949203049e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008761882947529487</v>
+        <v>0.0008761882947529459</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003072651191782646</v>
+        <v>0.003072651191782642</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004491492021052262</v>
+        <v>0.004491492021052261</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002992821928195295</v>
+        <v>0.0002992821928195261</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.03644393780742</v>
+        <v>2.036443937807416</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.613105248145264</v>
+        <v>2.613105248145267</v>
       </c>
     </row>
     <row r="3">
@@ -3694,73 +3694,73 @@
         <v>0.1489880991750844</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02076609750052483</v>
+        <v>0.02076609750052478</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05267281656666426</v>
+        <v>0.0526728165666643</v>
       </c>
       <c r="H3" t="n">
-        <v>3.94839418063846e-05</v>
+        <v>3.948394180638485e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001133335664104356</v>
+        <v>0.00113333566410436</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002190167026321967</v>
+        <v>0.0002190167026321962</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002081262456268528</v>
+        <v>0.002081262456268537</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000631024361855566</v>
+        <v>0.0006310243618555657</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003869750027926286</v>
+        <v>0.003869750027926281</v>
       </c>
       <c r="N3" t="n">
-        <v>3.285777781588818e-05</v>
+        <v>3.28577778158882e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001273715634376781</v>
+        <v>0.000127371563437678</v>
       </c>
       <c r="P3" t="n">
         <v>0.004126072192052787</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.108978222078868e-05</v>
+        <v>3.108978222078863e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>4.738079301459342e-07</v>
+        <v>4.73807930145934e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>5.843554502209941e-05</v>
+        <v>5.843554502209935e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.150740251408739e-07</v>
+        <v>5.150740251408649e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>2.477733125091042e-06</v>
+        <v>2.477733125091041e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008290980202552057</v>
+        <v>0.0008290980202552061</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002938723225670088</v>
+        <v>0.002938723225670072</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004486964668614885</v>
+        <v>0.004486964668614887</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002858948217060443</v>
+        <v>0.0002858948217060439</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.013509812112061</v>
+        <v>2.013509812112059</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.613105248839389</v>
+        <v>2.613105248839392</v>
       </c>
     </row>
     <row r="4">
@@ -3778,61 +3778,61 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.847183925656845</v>
+        <v>4.847183925656844</v>
       </c>
       <c r="E4" t="n">
         <v>0.1421568783114497</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02107085790888245</v>
+        <v>0.02107085790888249</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05125214951947078</v>
+        <v>0.05125214951947083</v>
       </c>
       <c r="H4" t="n">
-        <v>3.933887801134972e-05</v>
+        <v>3.933887801134976e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001120311520254873</v>
+        <v>0.001120311520254866</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002166100336657495</v>
+        <v>0.0002166100336657493</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00199302542701326</v>
+        <v>0.001993025427013273</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006316809502153861</v>
+        <v>0.0006316809502153868</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003569416533588157</v>
+        <v>0.003569416533588163</v>
       </c>
       <c r="N4" t="n">
-        <v>3.260833872528322e-05</v>
+        <v>3.260833872528327e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001214677816079298</v>
+        <v>0.0001214677816079299</v>
       </c>
       <c r="P4" t="n">
         <v>0.004047020145379852</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.00591622942299e-05</v>
+        <v>3.005916229423104e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.74034444509213e-07</v>
+        <v>4.740344445092132e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.817496370844628e-05</v>
+        <v>5.817496370844624e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.737836485007958e-07</v>
+        <v>4.737836485008045e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.501976712642953e-06</v>
+        <v>2.501976712642957e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0008201555590061861</v>
+        <v>0.000820155559006661</v>
       </c>
       <c r="W4" t="n">
         <v>0.002867520880812395</v>
@@ -3841,7 +3841,7 @@
         <v>0.004476661901931694</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002814414811790723</v>
+        <v>0.000281441481179075</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -3850,7 +3850,7 @@
         <v>1.999289847368495</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.613105249196347</v>
+        <v>2.613105249196346</v>
       </c>
     </row>
     <row r="5">
@@ -3868,46 +3868,46 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.818931402332491</v>
+        <v>4.818931402332492</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1281873922631927</v>
+        <v>0.1281873922631928</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02259225485549478</v>
+        <v>0.02259225485549474</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04960081605297016</v>
+        <v>0.04960081605296998</v>
       </c>
       <c r="H5" t="n">
-        <v>3.919861300280303e-05</v>
+        <v>3.919861300280301e-05</v>
       </c>
       <c r="I5" t="n">
         <v>0.0010910869847508</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002140162672597562</v>
+        <v>0.0002140162672597558</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001881469232512534</v>
+        <v>0.001881469232512527</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006294417153692999</v>
+        <v>0.0006294417153693002</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003415563880839496</v>
+        <v>0.003415563880839495</v>
       </c>
       <c r="N5" t="n">
-        <v>3.219092836217396e-05</v>
+        <v>3.219092836217395e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001140959614549085</v>
+        <v>0.0001140959614549086</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003984466512089086</v>
+        <v>0.003984466512089091</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.930124706378527e-05</v>
+        <v>2.930124706378508e-05</v>
       </c>
       <c r="R5" t="n">
         <v>4.769799960909287e-07</v>
@@ -3916,28 +3916,28 @@
         <v>5.792200788341426e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.567685486867253e-07</v>
+        <v>4.567685486867234e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.569128164503852e-06</v>
+        <v>2.569128164503851e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0008048590265937227</v>
+        <v>0.0008048590265937203</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002724400532036937</v>
+        <v>0.002724400532036946</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004473757720860037</v>
+        <v>0.004473757720860036</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002752750533536005</v>
+        <v>0.0002752750533536022</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.985675141210095</v>
+        <v>1.985675141210097</v>
       </c>
       <c r="AB5" t="n">
         <v>2.613105249390596</v>
@@ -3958,79 +3958,79 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.617994774977133</v>
+        <v>4.617994774977132</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04136300592575514</v>
+        <v>0.04136300592575508</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01373805522991726</v>
+        <v>0.01373805522991727</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03078732961702694</v>
+        <v>0.03078732961702706</v>
       </c>
       <c r="H6" t="n">
-        <v>3.599421573179585e-05</v>
+        <v>3.599421573179587e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009582645687425371</v>
+        <v>0.0009582645687425394</v>
       </c>
       <c r="J6" t="n">
         <v>0.00019129072384295</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001123065831364149</v>
+        <v>0.001123065831364148</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004991595838911687</v>
+        <v>0.0004991595838911691</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003021955219494393</v>
+        <v>0.00302195521949439</v>
       </c>
       <c r="N6" t="n">
         <v>2.949785401874817e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>6.765252205622785e-05</v>
+        <v>6.765252205622786e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003589767574783412</v>
+        <v>0.003589767574783435</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.371074285636723e-05</v>
+        <v>2.371074285636719e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.64417070663814e-07</v>
+        <v>4.644170706638141e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>5.647540433350844e-05</v>
+        <v>5.647540433350838e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.935332972846572e-07</v>
+        <v>3.935332972846631e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.666200878651818e-06</v>
+        <v>1.666200878651816e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005329070131812704</v>
+        <v>0.0005329070131812725</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001816553197223079</v>
+        <v>0.001816553197223083</v>
       </c>
       <c r="X6" t="n">
         <v>0.004474124591890409</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001969281941815576</v>
+        <v>0.0001969281941815567</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9023812626941</v>
+        <v>1.902381262694101</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.613105250121496</v>
+        <v>2.613105250121493</v>
       </c>
     </row>
     <row r="7">
@@ -4048,70 +4048,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.530217729033085</v>
+        <v>4.530217729033088</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01254387007551676</v>
+        <v>0.01254387007551678</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01185602222360196</v>
+        <v>0.01185602222360194</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0249589865742878</v>
+        <v>0.02495898657428778</v>
       </c>
       <c r="H7" t="n">
-        <v>3.466205223224516e-05</v>
+        <v>3.466205223224526e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009177299064127776</v>
+        <v>0.0009177299064127787</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001819140148745456</v>
+        <v>0.0001819140148745449</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007930724914394939</v>
+        <v>0.0007930724914394901</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004707545455963319</v>
+        <v>0.0004707545455963314</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002610529344917881</v>
+        <v>0.002610529344917878</v>
       </c>
       <c r="N7" t="n">
-        <v>2.834832487474957e-05</v>
+        <v>2.834832487474959e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>4.939832179420269e-05</v>
+        <v>4.939832179420266e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003277995852546188</v>
+        <v>0.003277995852546184</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.935999696519284e-05</v>
+        <v>1.935999696519326e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>4.605384289451955e-07</v>
+        <v>4.605384289451959e-07</v>
       </c>
       <c r="S7" t="n">
         <v>5.55610383898784e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.202856507172356e-07</v>
+        <v>3.202856507172354e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>1.474985868255591e-06</v>
+        <v>1.474985868256083e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0004610645153323679</v>
+        <v>0.000461064515332368</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001530508739528477</v>
+        <v>0.00153050873953436</v>
       </c>
       <c r="X7" t="n">
         <v>0.004449761711081688</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001710622880939422</v>
+        <v>0.0001710622880939379</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v>1.852699619973581</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.613105251232069</v>
+        <v>2.613105251232066</v>
       </c>
     </row>
     <row r="8">
@@ -4141,64 +4141,64 @@
         <v>4.482679926093283</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005182853889729516</v>
+        <v>0.005182853889729433</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01141425723483181</v>
+        <v>0.0114142572348318</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02248023911866053</v>
+        <v>0.02248023911866059</v>
       </c>
       <c r="H8" t="n">
-        <v>3.389035324393255e-05</v>
+        <v>3.389035324393253e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008982856254188459</v>
+        <v>0.0008982856254188452</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001771217017074158</v>
+        <v>0.0001771217017074168</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0006771731769008243</v>
+        <v>0.0006771731769008172</v>
       </c>
       <c r="L8" t="n">
         <v>0.0004589979810556905</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002448804300056375</v>
+        <v>0.002448804300056377</v>
       </c>
       <c r="N8" t="n">
-        <v>2.765541921811573e-05</v>
+        <v>2.765541921811571e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>4.352794636395493e-05</v>
+        <v>4.352794636395484e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003138597376794613</v>
+        <v>0.00313859737679461</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.660794474598566e-05</v>
+        <v>1.660794474598603e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>4.586081903533449e-07</v>
+        <v>4.58608190353345e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>5.498777083214003e-05</v>
+        <v>5.498777083214e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.667596769109679e-07</v>
+        <v>2.667596769109674e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>1.404368382945891e-06</v>
+        <v>1.404368382945893e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004304866036518811</v>
+        <v>0.0004304866036518827</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001395906402598845</v>
+        <v>0.001395906402598848</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004432713402793496</v>
+        <v>0.004432713402793497</v>
       </c>
       <c r="Y8" t="n">
         <v>0.0001574928778863483</v>
@@ -4210,7 +4210,7 @@
         <v>1.81610294482737</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.613105252403173</v>
+        <v>2.613105252403172</v>
       </c>
     </row>
     <row r="9">
@@ -4228,76 +4228,76 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.797903102610973</v>
+        <v>4.797903102610972</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1226329346964657</v>
+        <v>0.1226329346964659</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01899959128851268</v>
+        <v>0.01899959128851271</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04781410260243675</v>
+        <v>0.04781410260243673</v>
       </c>
       <c r="H9" t="n">
-        <v>3.865082727739575e-05</v>
+        <v>3.865082727739569e-05</v>
       </c>
       <c r="I9" t="n">
         <v>0.001108967784076361</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002132322881441471</v>
+        <v>0.0002132322881441464</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001825800765632978</v>
+        <v>0.001825800765632988</v>
       </c>
       <c r="L9" t="n">
         <v>0.0006064044076557117</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003550679011382639</v>
+        <v>0.003550679011382641</v>
       </c>
       <c r="N9" t="n">
         <v>3.22195979095663e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0001116719534621416</v>
+        <v>0.0001116719534621415</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003979223893688779</v>
+        <v>0.00397922389368878</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.950538003336702e-05</v>
+        <v>2.95053800333665e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.717226071728159e-07</v>
+        <v>4.71722607172816e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>5.804541033259291e-05</v>
+        <v>5.804541033259287e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>5.059932245218345e-07</v>
+        <v>5.059932245218344e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>2.319056691492637e-06</v>
+        <v>2.319056691492629e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0007680252079475353</v>
+        <v>0.0007680252079475363</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002709554582197967</v>
+        <v>0.002709554582197972</v>
       </c>
       <c r="X9" t="n">
         <v>0.004483748049092571</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002687012292583038</v>
+        <v>0.0002687012292583042</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.975563497281409</v>
+        <v>1.975563497281408</v>
       </c>
       <c r="AB9" t="n">
         <v>2.613105249581534</v>
@@ -4318,79 +4318,79 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.652973740550482</v>
+        <v>4.65297374055048</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05555088518970951</v>
+        <v>0.05555088518970927</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0152004979942403</v>
+        <v>0.01520049799424027</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03771155684464494</v>
+        <v>0.03771155684464485</v>
       </c>
       <c r="H10" t="n">
-        <v>3.692877260451848e-05</v>
+        <v>3.692877260451845e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001053580870777552</v>
+        <v>0.001053580870777551</v>
       </c>
       <c r="J10" t="n">
         <v>0.0001999136913332694</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001231110052292761</v>
+        <v>0.001231110052292783</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0005572350871556448</v>
+        <v>0.0005572350871556445</v>
       </c>
       <c r="M10" t="n">
-        <v>0.003030863976280352</v>
+        <v>0.00303086397628035</v>
       </c>
       <c r="N10" t="n">
-        <v>3.084938776627832e-05</v>
+        <v>3.084938776627834e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>7.892444792857958e-05</v>
+        <v>7.892444792857943e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003651622398944339</v>
+        <v>0.003651622398944337</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.565338000536203e-05</v>
+        <v>2.565338000536192e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.663005104049472e-07</v>
+        <v>4.66300510404947e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>5.708220726514607e-05</v>
+        <v>5.708220726514603e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>4.089192477896341e-07</v>
+        <v>4.08919247789634e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>1.98823511138438e-06</v>
+        <v>1.988235111384381e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0006498774185935461</v>
+        <v>0.0006498774185935457</v>
       </c>
       <c r="W10" t="n">
-        <v>0.002268776698048727</v>
+        <v>0.00226877669804764</v>
       </c>
       <c r="X10" t="n">
         <v>0.004467505190775396</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.000232211278582469</v>
+        <v>0.0002322112785824674</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.913830551990051</v>
+        <v>1.91383055199005</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.613105250218612</v>
+        <v>2.613105250218613</v>
       </c>
     </row>
     <row r="11">
@@ -4411,76 +4411,76 @@
         <v>4.554400991006646</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008811355868500372</v>
+        <v>0.0088113558685004</v>
       </c>
       <c r="F11" t="n">
         <v>0.01152932894938218</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02247850307568998</v>
+        <v>0.02247850307568989</v>
       </c>
       <c r="H11" t="n">
-        <v>3.495559723025826e-05</v>
+        <v>3.495559723025814e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0009106286434073734</v>
+        <v>0.0009106286434073738</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001839364047960218</v>
+        <v>0.0001839364047960227</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0007774857514576427</v>
+        <v>0.0007774857514576489</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004788453409431053</v>
+        <v>0.0004788453409431045</v>
       </c>
       <c r="M11" t="n">
-        <v>0.00271345235271119</v>
+        <v>0.002713452352711191</v>
       </c>
       <c r="N11" t="n">
-        <v>2.856515258657365e-05</v>
+        <v>2.856515258657355e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>4.626331101109526e-05</v>
+        <v>4.626331101109531e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.003300139308314216</v>
+        <v>0.003300139308314219</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.058098829970972e-05</v>
+        <v>2.058098829970993e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>4.630275099501097e-07</v>
+        <v>4.630275099501092e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>5.575044531408424e-05</v>
+        <v>5.575044531408423e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88065794405089e-07</v>
+        <v>2.880657944050878e-07</v>
       </c>
       <c r="U11" t="n">
-        <v>1.58153001373215e-06</v>
+        <v>1.581530013732139e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0004827225309959116</v>
+        <v>0.0004827225309959145</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001563332077720648</v>
+        <v>0.00156333207772114</v>
       </c>
       <c r="X11" t="n">
-        <v>0.004456854148702481</v>
+        <v>0.004456854148702482</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0001747010238558096</v>
+        <v>0.0001747010238558121</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.883246007514019</v>
+        <v>1.883246007514016</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.61310524989839</v>
+        <v>2.613105249898393</v>
       </c>
     </row>
   </sheetData>
@@ -4584,37 +4584,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.814497822647357</v>
+        <v>2.814497822647341</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3316061237056713</v>
+        <v>0.3316061237056703</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3896056037941993</v>
+        <v>0.3896056037941991</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0162097783370172</v>
+        <v>0.01620977833701715</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1051921292319187</v>
+        <v>0.1051921292319186</v>
       </c>
       <c r="I2" t="n">
-        <v>4.975707223949867e-06</v>
+        <v>4.975707223949856e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001627403646346911</v>
+        <v>0.001627403646346913</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005707042405615812</v>
+        <v>0.005707042405615806</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007200793272003672</v>
+        <v>0.0007200793272003519</v>
       </c>
       <c r="M2" t="n">
-        <v>7.365330589025411e-05</v>
+        <v>7.365330589025407e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.96375105651323</v>
+        <v>1.963751056513221</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.577894528137837</v>
+        <v>2.577894528137831</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3210731524388423</v>
+        <v>0.321073152438842</v>
       </c>
       <c r="F3" t="n">
         <v>0.3798460614300329</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0160079357225288</v>
+        <v>0.01600793572252889</v>
       </c>
       <c r="H3" t="n">
-        <v>0.104592651661771</v>
+        <v>0.1045926516617706</v>
       </c>
       <c r="I3" t="n">
-        <v>4.602060934384714e-06</v>
+        <v>4.602060934384718e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001539939701799806</v>
+        <v>0.001539939701799803</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005458288956494626</v>
+        <v>0.00545828895649461</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007160930981524248</v>
+        <v>0.0007160930981524359</v>
       </c>
       <c r="M3" t="n">
-        <v>7.351039303148401e-05</v>
+        <v>7.351039303148407e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.748582253197442</v>
+        <v>1.748582253197428</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -4686,37 +4686,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.337984898729336</v>
+        <v>2.337984898729337</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3155314455303503</v>
+        <v>0.315531445530351</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3606817838698081</v>
+        <v>0.3606817838698083</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01611010528667949</v>
+        <v>0.01611010528667946</v>
       </c>
       <c r="H4" t="n">
-        <v>0.104158305694005</v>
+        <v>0.1041583056940041</v>
       </c>
       <c r="I4" t="n">
-        <v>4.647090185538589e-06</v>
+        <v>4.647090185538594e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001523330265072672</v>
+        <v>0.001523330265072162</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00532604003654925</v>
+        <v>0.005326040036549249</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007087949414877446</v>
+        <v>0.0007087949414877527</v>
       </c>
       <c r="M4" t="n">
-        <v>7.319457898364644e-05</v>
+        <v>7.319457898364647e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.533867229218627</v>
+        <v>1.533867229218629</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -4737,31 +4737,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.227770700948081</v>
+        <v>2.22777070094808</v>
       </c>
       <c r="E5" t="n">
         <v>0.3161557599532963</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3218901798810226</v>
+        <v>0.3218901798810227</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01633945768732281</v>
+        <v>0.01633945768732269</v>
       </c>
       <c r="H5" t="n">
-        <v>0.103071209647023</v>
+        <v>0.1030712096470231</v>
       </c>
       <c r="I5" t="n">
-        <v>4.771815108560679e-06</v>
+        <v>4.771815108560678e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001494918983188625</v>
+        <v>0.001494918983188619</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005060212954792472</v>
+        <v>0.005060212954792497</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007033676546520807</v>
+        <v>0.0007033676546520805</v>
       </c>
       <c r="M5" t="n">
         <v>7.29631172858842e-05</v>
@@ -4788,37 +4788,37 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.746487441609779</v>
+        <v>1.746487441609786</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2775950586237409</v>
+        <v>0.2775950586237396</v>
       </c>
       <c r="F6" t="n">
         <v>0.1243199140497868</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01558487775487403</v>
+        <v>0.01558487775487438</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09821226073434944</v>
+        <v>0.09821226073434985</v>
       </c>
       <c r="I6" t="n">
-        <v>3.094747329658143e-06</v>
+        <v>3.094747329658136e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000989804156947314</v>
+        <v>0.0009898041569473162</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003374006836940845</v>
+        <v>0.00337400683694085</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0006917345102333224</v>
+        <v>0.0006917345102333101</v>
       </c>
       <c r="M6" t="n">
-        <v>7.263890194936936e-05</v>
+        <v>7.263890194936925e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.225644025149134</v>
+        <v>1.225644025149129</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -4839,37 +4839,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.373939156152136</v>
+        <v>1.373939156152135</v>
       </c>
       <c r="E7" t="n">
         <v>0.2582014555696419</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06065012256228286</v>
+        <v>0.06065012256228285</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01548406397157342</v>
+        <v>0.01548406397157347</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09666454035286404</v>
+        <v>0.09666454035286512</v>
       </c>
       <c r="I7" t="n">
-        <v>2.739590787369899e-06</v>
+        <v>2.739590787374012e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008563662376528751</v>
+        <v>0.0008563662376528703</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00284271716295596</v>
+        <v>0.002842717162960237</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0006614402326322339</v>
+        <v>0.0006614402326322337</v>
       </c>
       <c r="M7" t="n">
-        <v>7.19815332531225e-05</v>
+        <v>7.198153325312249e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9385037167302209</v>
+        <v>0.938503716730221</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -4890,37 +4890,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.258707075820505</v>
+        <v>1.2587070758205</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2476113112014834</v>
+        <v>0.2476113112014836</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04570984582401667</v>
+        <v>0.04570984582401666</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01545173457086189</v>
+        <v>0.01545173457086182</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09579940826704395</v>
+        <v>0.09579940826704388</v>
       </c>
       <c r="I8" t="n">
-        <v>2.608428166533412e-06</v>
+        <v>2.608428166533415e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0007995718188452996</v>
+        <v>0.0007995718188452967</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002592711159407696</v>
+        <v>0.002592711159407703</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0006294382284737129</v>
+        <v>0.0006294382284737161</v>
       </c>
       <c r="M8" t="n">
-        <v>7.149862428957494e-05</v>
+        <v>7.149862428957491e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.850038936217428</v>
+        <v>0.8500389362174294</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4941,31 +4941,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.331559636120078</v>
+        <v>2.331559636120081</v>
       </c>
       <c r="E9" t="n">
-        <v>0.310342946513661</v>
+        <v>0.3103429465136617</v>
       </c>
       <c r="F9" t="n">
-        <v>0.308221268603292</v>
+        <v>0.3082212686032922</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01590309543927487</v>
+        <v>0.01590309543927488</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1033365562115362</v>
+        <v>0.1033365562115365</v>
       </c>
       <c r="I9" t="n">
-        <v>4.307340486538311e-06</v>
+        <v>4.307340486538316e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001426505046215695</v>
+        <v>0.001426505046215653</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005032638570329559</v>
+        <v>0.005032638570329566</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0007103377946539115</v>
+        <v>0.0007103377946539121</v>
       </c>
       <c r="M9" t="n">
         <v>7.330762679802308e-05</v>
@@ -4992,34 +4992,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.753168763145598</v>
+        <v>1.753168763145599</v>
       </c>
       <c r="E10" t="n">
         <v>0.2836990359725868</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1551582724409538</v>
+        <v>0.1551582724409531</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01569118613689884</v>
+        <v>0.01569118613689893</v>
       </c>
       <c r="H10" t="n">
-        <v>0.100909597787707</v>
+        <v>0.1009095977877071</v>
       </c>
       <c r="I10" t="n">
-        <v>3.692883241466089e-06</v>
+        <v>3.692883241466088e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001207061184258191</v>
+        <v>0.00120706118425819</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004213952061748932</v>
+        <v>0.004213952061743437</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0006935453723401093</v>
+        <v>0.0006935453723401096</v>
       </c>
       <c r="M10" t="n">
-        <v>7.272157731626982e-05</v>
+        <v>7.272157731626978e-05</v>
       </c>
       <c r="N10" t="n">
         <v>1.191519682090644</v>
@@ -5043,37 +5043,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.474303753888943</v>
+        <v>1.474303753888949</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2630364714492293</v>
+        <v>0.263036471449229</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1054363032410881</v>
+        <v>0.1054363032410882</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01567014923114058</v>
+        <v>0.01567014923114065</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0966088961857732</v>
+        <v>0.09660889618577376</v>
       </c>
       <c r="I11" t="n">
-        <v>2.937482418525679e-06</v>
+        <v>2.937482418525668e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0008965931316602112</v>
+        <v>0.0008965931316602087</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002903682163945705</v>
+        <v>0.002903682163948153</v>
       </c>
       <c r="L11" t="n">
         <v>0.0006685920851291757</v>
       </c>
       <c r="M11" t="n">
-        <v>7.214487662854439e-05</v>
+        <v>7.214487662854438e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9890079704830367</v>
+        <v>0.9890079704830415</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -5180,37 +5180,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.591141144537395</v>
+        <v>4.59114114453739</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3316061237056713</v>
+        <v>0.3316061237056703</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3896056037941993</v>
+        <v>0.3896056037941991</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0162097783370172</v>
+        <v>0.01620977833701715</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1051921292319187</v>
+        <v>0.1051921292319186</v>
       </c>
       <c r="I2" t="n">
-        <v>4.975707223949867e-06</v>
+        <v>4.975707223949856e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001627403646346911</v>
+        <v>0.001627403646346913</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005707042405615812</v>
+        <v>0.005707042405615806</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007200793272003672</v>
+        <v>0.0007200793272003519</v>
       </c>
       <c r="M2" t="n">
-        <v>7.365330589025411e-05</v>
+        <v>7.365330589025407e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.740394420753287</v>
+        <v>3.740394420753286</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -5231,37 +5231,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.889452877438809</v>
+        <v>3.889452877438803</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3210731524388423</v>
+        <v>0.321073152438842</v>
       </c>
       <c r="F3" t="n">
         <v>0.3798460614300329</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0160079357225288</v>
+        <v>0.01600793572252889</v>
       </c>
       <c r="H3" t="n">
-        <v>0.104592651661771</v>
+        <v>0.1045926516617706</v>
       </c>
       <c r="I3" t="n">
-        <v>4.602060934384714e-06</v>
+        <v>4.602060934384718e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001539939701799806</v>
+        <v>0.001539939701799803</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005458288956494626</v>
+        <v>0.00545828895649461</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007160930981524248</v>
+        <v>0.0007160930981524359</v>
       </c>
       <c r="M3" t="n">
-        <v>7.351039303148401e-05</v>
+        <v>7.351039303148407e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.060140590066415</v>
+        <v>3.060140590066414</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -5282,37 +5282,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.40901286126904</v>
+        <v>3.409012861269042</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3155314455303503</v>
+        <v>0.315531445530351</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3606817838698081</v>
+        <v>0.3606817838698083</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01611010528667949</v>
+        <v>0.01611010528667946</v>
       </c>
       <c r="H4" t="n">
-        <v>0.104158305694005</v>
+        <v>0.1041583056940041</v>
       </c>
       <c r="I4" t="n">
-        <v>4.647090185538589e-06</v>
+        <v>4.647090185538594e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001523330265072672</v>
+        <v>0.001523330265072162</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00532604003654925</v>
+        <v>0.005326040036549249</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007087949414877446</v>
+        <v>0.0007087949414877527</v>
       </c>
       <c r="M4" t="n">
-        <v>7.319457898364644e-05</v>
+        <v>7.319457898364647e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.604895191758332</v>
+        <v>2.604895191758333</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -5333,37 +5333,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.136335139886621</v>
+        <v>3.136335139886617</v>
       </c>
       <c r="E5" t="n">
         <v>0.3161557599532963</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3218901798810226</v>
+        <v>0.3218901798810227</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01633945768732281</v>
+        <v>0.01633945768732269</v>
       </c>
       <c r="H5" t="n">
-        <v>0.103071209647023</v>
+        <v>0.1030712096470231</v>
       </c>
       <c r="I5" t="n">
-        <v>4.771815108560679e-06</v>
+        <v>4.771815108560678e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001494918983188625</v>
+        <v>0.001494918983188619</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005060212954792472</v>
+        <v>0.005060212954792497</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007033676546520807</v>
+        <v>0.0007033676546520805</v>
       </c>
       <c r="M5" t="n">
         <v>7.29631172858842e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>2.371542277045951</v>
+        <v>2.371542277045949</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -5384,37 +5384,37 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.519660853326021</v>
+        <v>2.519660853326022</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2775950586237409</v>
+        <v>0.2775950586237396</v>
       </c>
       <c r="F6" t="n">
         <v>0.1243199140497868</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01558487775487403</v>
+        <v>0.01558487775487438</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09821226073434944</v>
+        <v>0.09821226073434985</v>
       </c>
       <c r="I6" t="n">
-        <v>3.094747329658143e-06</v>
+        <v>3.094747329658136e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000989804156947314</v>
+        <v>0.0009898041569473162</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003374006836940845</v>
+        <v>0.00337400683694085</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0006917345102333224</v>
+        <v>0.0006917345102333101</v>
       </c>
       <c r="M6" t="n">
-        <v>7.263890194936936e-05</v>
+        <v>7.263890194936925e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.998817429536609</v>
+        <v>1.99881742953661</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -5435,37 +5435,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.96860701519246</v>
+        <v>1.968607015192468</v>
       </c>
       <c r="E7" t="n">
         <v>0.2582014555696419</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06065012256228286</v>
+        <v>0.06065012256228285</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01548406397157342</v>
+        <v>0.01548406397157347</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09666454035286404</v>
+        <v>0.09666454035286512</v>
       </c>
       <c r="I7" t="n">
-        <v>2.739590787369899e-06</v>
+        <v>2.739590787374012e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008563662376528751</v>
+        <v>0.0008563662376528703</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00284271716295596</v>
+        <v>0.002842717162960237</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0006614402326322339</v>
+        <v>0.0006614402326322337</v>
       </c>
       <c r="M7" t="n">
-        <v>7.19815332531225e-05</v>
+        <v>7.198153325312249e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.53317157577054</v>
+        <v>1.533171575770538</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -5486,37 +5486,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.77506913559289</v>
+        <v>1.775069135592889</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2476113112014834</v>
+        <v>0.2476113112014836</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04570984582401667</v>
+        <v>0.04570984582401666</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01545173457086189</v>
+        <v>0.01545173457086182</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09579940826704395</v>
+        <v>0.09579940826704388</v>
       </c>
       <c r="I8" t="n">
-        <v>2.608428166533412e-06</v>
+        <v>2.608428166533415e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0007995718188452996</v>
+        <v>0.0007995718188452967</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002592711159407696</v>
+        <v>0.002592711159407703</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0006294382284737129</v>
+        <v>0.0006294382284737161</v>
       </c>
       <c r="M8" t="n">
-        <v>7.149862428957494e-05</v>
+        <v>7.149862428957491e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.366400995989813</v>
+        <v>1.366400995989814</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -5537,37 +5537,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.587850815181611</v>
+        <v>3.587850815181613</v>
       </c>
       <c r="E9" t="n">
-        <v>0.310342946513661</v>
+        <v>0.3103429465136617</v>
       </c>
       <c r="F9" t="n">
-        <v>0.308221268603292</v>
+        <v>0.3082212686032922</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01590309543927487</v>
+        <v>0.01590309543927488</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1033365562115362</v>
+        <v>0.1033365562115365</v>
       </c>
       <c r="I9" t="n">
-        <v>4.307340486538311e-06</v>
+        <v>4.307340486538316e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001426505046215695</v>
+        <v>0.001426505046215653</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005032638570329559</v>
+        <v>0.005032638570329566</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0007103377946539115</v>
+        <v>0.0007103377946539121</v>
       </c>
       <c r="M9" t="n">
         <v>7.330762679802308e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.84279980447367</v>
+        <v>2.842799804473671</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5588,37 +5588,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.68134868874864</v>
+        <v>2.681348688748633</v>
       </c>
       <c r="E10" t="n">
         <v>0.2836990359725868</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1551582724409538</v>
+        <v>0.1551582724409531</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01569118613689884</v>
+        <v>0.01569118613689893</v>
       </c>
       <c r="H10" t="n">
-        <v>0.100909597787707</v>
+        <v>0.1009095977877071</v>
       </c>
       <c r="I10" t="n">
-        <v>3.692883241466089e-06</v>
+        <v>3.692883241466088e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001207061184258191</v>
+        <v>0.00120706118425819</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004213952061748932</v>
+        <v>0.004213952061743437</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0006935453723401093</v>
+        <v>0.0006935453723401096</v>
       </c>
       <c r="M10" t="n">
-        <v>7.272157731626982e-05</v>
+        <v>7.272157731626978e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.119699607693677</v>
+        <v>2.119699607693676</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5639,37 +5639,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.588437814956448</v>
+        <v>1.58843781495644</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2630364714492293</v>
+        <v>0.263036471449229</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1054363032410881</v>
+        <v>0.1054363032410882</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01567014923114058</v>
+        <v>0.01567014923114065</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0966088961857732</v>
+        <v>0.09660889618577376</v>
       </c>
       <c r="I11" t="n">
-        <v>2.937482418525679e-06</v>
+        <v>2.937482418525668e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0008965931316602112</v>
+        <v>0.0008965931316602087</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002903682163945705</v>
+        <v>0.002903682163948153</v>
       </c>
       <c r="L11" t="n">
         <v>0.0006685920851291757</v>
       </c>
       <c r="M11" t="n">
-        <v>7.214487662854439e-05</v>
+        <v>7.214487662854438e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.103142031550547</v>
+        <v>1.103142031550532</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>

--- a/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results.xlsx
@@ -575,73 +575,73 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.20008632565869</v>
+        <v>10.24507192971876</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02280213944059888</v>
+        <v>0.02236365771525902</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05579128143712251</v>
+        <v>0.05297266872821096</v>
       </c>
       <c r="G2" t="n">
-        <v>4.010483954252127e-05</v>
+        <v>3.987099995124913e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001145326241466513</v>
+        <v>0.001115047877934225</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002234417210028195</v>
+        <v>0.0002204552969457201</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002172280437535925</v>
+        <v>0.002082938453430552</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004087489492760882</v>
+        <v>0.003875358811066434</v>
       </c>
       <c r="L2" t="n">
-        <v>3.329041918983525e-05</v>
+        <v>3.281297100841981e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001345287036150598</v>
+        <v>0.0001275696534852123</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004181531270246569</v>
+        <v>0.004157778150090817</v>
       </c>
       <c r="O2" t="n">
-        <v>3.242675186689206e-05</v>
+        <v>3.146384357918766e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.773778149478628e-07</v>
+        <v>4.776230107809116e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.869530347177221e-05</v>
+        <v>5.842311683215346e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>5.318463955165452e-07</v>
+        <v>5.260035306051285e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>2.679209913088789e-06</v>
+        <v>2.602430330095509e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008762886933745828</v>
+        <v>0.0008400848151645752</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003073003273574045</v>
+        <v>0.002914804860842479</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004491492021052261</v>
+        <v>0.004490217877914886</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002992821928195261</v>
+        <v>0.0002874343647440914</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8933790211696022</v>
+        <v>-0.834706821546644</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.068829112605486</v>
+        <v>2.058974611707972</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.925189943549441</v>
+        <v>8.925189945964103</v>
       </c>
     </row>
     <row r="3">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10.18902909921034</v>
+        <v>10.24329115008202</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0207684769976926</v>
+        <v>0.02005735802428355</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05267885211657136</v>
+        <v>0.0494241759873064</v>
       </c>
       <c r="G3" t="n">
-        <v>3.948394180638485e-05</v>
+        <v>3.911753746663408e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00113333566410436</v>
+        <v>0.001100074248113156</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002190167026321962</v>
+        <v>0.0002152958685212293</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002081262456268537</v>
+        <v>0.001970042623700984</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003869750027926281</v>
+        <v>0.00366482954191396</v>
       </c>
       <c r="L3" t="n">
-        <v>3.28577778158882e-05</v>
+        <v>3.227089836273612e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000127371563437678</v>
+        <v>0.0001197009649556254</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004126072192052787</v>
+        <v>0.004050736803665503</v>
       </c>
       <c r="O3" t="n">
-        <v>3.108978222078863e-05</v>
+        <v>2.95705763628912e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.73807930145934e-07</v>
+        <v>4.733795125129375e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.843554502209935e-05</v>
+        <v>5.802689914056454e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.150740251408649e-07</v>
+        <v>5.025883200395271e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.478017037797965e-06</v>
+        <v>2.380649607801304e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008291930230062517</v>
+        <v>0.0007881617926617884</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002939059961235925</v>
+        <v>0.002765289720491218</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004486964668614887</v>
+        <v>0.004480739709009162</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002858948217060439</v>
+        <v>0.0002716392972616066</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8754016989576096</v>
+        <v>-0.8035680573876948</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.045530269936735</v>
+        <v>2.032598873332667</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.925189944090103</v>
+        <v>8.925189947026391</v>
       </c>
     </row>
     <row r="4">
@@ -743,73 +743,73 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.21363275522015</v>
+        <v>10.26406291180962</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02107327232722546</v>
+        <v>0.02030105077470803</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0512580222812944</v>
+        <v>0.04783479141759864</v>
       </c>
       <c r="G4" t="n">
-        <v>3.933887801134976e-05</v>
+        <v>3.876779959824269e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001120311520254866</v>
+        <v>0.0010849088577586</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002166100336657493</v>
+        <v>0.0002121268381683213</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001993025427013273</v>
+        <v>0.001860520502540842</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003569416533588163</v>
+        <v>0.003422024622077298</v>
       </c>
       <c r="L4" t="n">
-        <v>3.260833872528327e-05</v>
+        <v>3.187772904606673e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001214677816079299</v>
+        <v>0.0001132308690536361</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004047020145379852</v>
+        <v>0.003919628787678779</v>
       </c>
       <c r="O4" t="n">
-        <v>3.005916229423104e-05</v>
+        <v>2.773715584498818e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.740344445092132e-07</v>
+        <v>4.727414790302063e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.817496370844624e-05</v>
+        <v>5.761236249791588e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.737836485008045e-07</v>
+        <v>4.275304306641996e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>2.502263403317577e-06</v>
+        <v>2.396652309378753e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0008202495370798036</v>
+        <v>0.0007768790768258387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002867849457609953</v>
+        <v>0.002683355646266978</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004476661901931694</v>
+        <v>0.004464258220244087</v>
       </c>
       <c r="W4" t="n">
-        <v>0.000281441481179075</v>
+        <v>0.0002649056565987174</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.834650338150058</v>
+        <v>-0.7620424084315085</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.031084167839078</v>
+        <v>2.013818398393047</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.925189945679065</v>
+        <v>8.925189948607354</v>
       </c>
     </row>
     <row r="5">
@@ -827,73 +827,73 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.28249841781726</v>
+        <v>10.32203259234388</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02259484360412415</v>
+        <v>0.02201441562572904</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04960649959564408</v>
+        <v>0.0466391030000324</v>
       </c>
       <c r="G5" t="n">
-        <v>3.919861300280301e-05</v>
+        <v>3.874614160360768e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0010910869847508</v>
+        <v>0.001059466132098395</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002140162672597558</v>
+        <v>0.0002099058059956951</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001881469232512527</v>
+        <v>0.001757486776130354</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003415563880839495</v>
+        <v>0.003301649855513185</v>
       </c>
       <c r="L5" t="n">
-        <v>3.219092836217395e-05</v>
+        <v>3.147707138709098e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001140959614549086</v>
+        <v>0.0001068647890104635</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003984466512089091</v>
+        <v>0.003844587028155852</v>
       </c>
       <c r="O5" t="n">
-        <v>2.930124706378508e-05</v>
+        <v>2.678385539397262e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.769799960909287e-07</v>
+        <v>4.759677398392056e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.792200788341426e-05</v>
+        <v>5.734158341098631e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.567685486867234e-07</v>
+        <v>3.913830566289079e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.569422549772487e-06</v>
+        <v>2.487561949338785e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0008049512519034685</v>
+        <v>0.0007694311655315005</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002724712709293636</v>
+        <v>0.002563492781802208</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004473757720860036</v>
+        <v>0.004459030194024529</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002752750533536022</v>
+        <v>0.0002599184462097203</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7512873356564107</v>
+        <v>-0.6936305723171284</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.017252949637026</v>
+        <v>2.003330158067112</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.925189949095154</v>
+        <v>8.925189951429118</v>
       </c>
     </row>
     <row r="6">
@@ -911,73 +911,73 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.67850042172361</v>
+        <v>10.67252253740813</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01373962941416204</v>
+        <v>0.01282232736138852</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03079085740377786</v>
+        <v>0.02857476734967646</v>
       </c>
       <c r="G6" t="n">
-        <v>3.599421573179587e-05</v>
+        <v>3.533826784116757e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009582645687425394</v>
+        <v>0.0009416546565259189</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00019129072384295</v>
+        <v>0.0001868813796941302</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001123065831364148</v>
+        <v>0.001027832706441007</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00302195521949439</v>
+        <v>0.002828996149939954</v>
       </c>
       <c r="L6" t="n">
-        <v>2.949785401874817e-05</v>
+        <v>2.881934551697532e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>6.765252205622786e-05</v>
+        <v>6.358601305521095e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003589767574783435</v>
+        <v>0.003354300193802101</v>
       </c>
       <c r="O6" t="n">
-        <v>2.371074285636719e-05</v>
+        <v>2.030728009792041e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.644170706638141e-07</v>
+        <v>4.606506127988125e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.647540433350838e-05</v>
+        <v>5.57899140535472e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>3.935332972846631e-07</v>
+        <v>2.630799976260342e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.666391801393639e-06</v>
+        <v>1.585370138917008e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005329680766877176</v>
+        <v>0.0005074101462132019</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001816761348185862</v>
+        <v>0.001716477522810486</v>
       </c>
       <c r="V6" t="n">
-        <v>0.004474124591890409</v>
+        <v>0.004450086451568004</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001969281941815567</v>
+        <v>0.000183226448066897</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2399754807840886</v>
+        <v>-0.2205294731201305</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.932634464651259</v>
+        <v>1.911061929788442</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.925189969828166</v>
+        <v>8.925189970452381</v>
       </c>
     </row>
     <row r="7">
@@ -995,73 +995,73 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.78805907040962</v>
+        <v>10.75895864233425</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0118573807538362</v>
+        <v>0.01088812799210035</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0249618465164538</v>
+        <v>0.02304894641848435</v>
       </c>
       <c r="G7" t="n">
-        <v>3.466205223224526e-05</v>
+        <v>3.385458150065116e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009177299064127787</v>
+        <v>0.000905773015519929</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001819140148745449</v>
+        <v>0.0001776478641214097</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007930724914394901</v>
+        <v>0.0006957893246142024</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002610529344917878</v>
+        <v>0.002460563826394581</v>
       </c>
       <c r="L7" t="n">
-        <v>2.834832487474959e-05</v>
+        <v>2.766097064172988e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.939832179420266e-05</v>
+        <v>4.631282320516487e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003277995852546184</v>
+        <v>0.003020780359802032</v>
       </c>
       <c r="O7" t="n">
-        <v>1.935999696519326e-05</v>
+        <v>1.54954427050206e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.605384289451959e-07</v>
+        <v>4.569446863872299e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.55610383898784e-05</v>
+        <v>5.481852080252701e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.202856507172354e-07</v>
+        <v>1.747254058409834e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.475154880498078e-06</v>
+        <v>1.409664399378769e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004611173467181575</v>
+        <v>0.0004424543270775139</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00153068411389104</v>
+        <v>0.0014560108781312</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004449761711081688</v>
+        <v>0.00442158411886585</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001710622880939379</v>
+        <v>0.0001582081497870693</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.07069633046104801</v>
+        <v>-0.06675868800768836</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.882162744357825</v>
+        <v>1.852671284051603</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.925189976459363</v>
+        <v>8.925189976342095</v>
       </c>
     </row>
     <row r="8">
@@ -1079,73 +1079,73 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.79050591699846</v>
+        <v>10.77005952698809</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01141556514512947</v>
+        <v>0.01058181405154486</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0224828150318918</v>
+        <v>0.02091707121689519</v>
       </c>
       <c r="G8" t="n">
-        <v>3.389035324393253e-05</v>
+        <v>3.337934035364732e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008982856254188452</v>
+        <v>0.0008891996048512561</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001771217017074168</v>
+        <v>0.0001737624900552019</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0006771731769008172</v>
+        <v>0.0005963807786516016</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002448804300056377</v>
+        <v>0.002334128841608283</v>
       </c>
       <c r="L8" t="n">
-        <v>2.765541921811571e-05</v>
+        <v>2.71040534223464e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.352794636395484e-05</v>
+        <v>4.111266534990582e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00313859737679461</v>
+        <v>0.002912538779137925</v>
       </c>
       <c r="O8" t="n">
-        <v>1.660794474598603e-05</v>
+        <v>1.343481035649852e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.58608190353345e-07</v>
+        <v>4.556831621244479e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.498777083214e-05</v>
+        <v>5.439842899292991e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.667596769109674e-07</v>
+        <v>1.373230990401052e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.404529303436114e-06</v>
+        <v>1.355154411771046e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0004305359312472172</v>
+        <v>0.0004169228282149806</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001396066353467391</v>
+        <v>0.001339598441213309</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004432713402793497</v>
+        <v>0.004410358447779871</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0001574928778863483</v>
+        <v>0.0001472081074076261</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.02750211053265122</v>
+        <v>-0.02526993019331653</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.844984079351919</v>
+        <v>1.825249118300723</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.925189977924328</v>
+        <v>8.925189977834176</v>
       </c>
     </row>
     <row r="9">
@@ -1163,73 +1163,73 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.29806910126119</v>
+        <v>10.34455406936769</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01900176836938499</v>
+        <v>0.01811068851555999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04781958141335539</v>
+        <v>0.04433260708189948</v>
       </c>
       <c r="G9" t="n">
-        <v>3.865082727739569e-05</v>
+        <v>3.806921752945501e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001108967784076361</v>
+        <v>0.001074485115876923</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002132322881441464</v>
+        <v>0.0002085693333614094</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001825800765632988</v>
+        <v>0.001697622871425569</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003550679011382641</v>
+        <v>0.00333810811535771</v>
       </c>
       <c r="L9" t="n">
-        <v>3.22195979095663e-05</v>
+        <v>3.149480810926924e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001116719534621415</v>
+        <v>0.0001036498255976518</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00397922389368878</v>
+        <v>0.003808397360833145</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95053800333665e-05</v>
+        <v>2.716550998084804e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.71722607172816e-07</v>
+        <v>4.70206826371508e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.804541033259287e-05</v>
+        <v>5.748183282585366e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>5.059932245218344e-07</v>
+        <v>4.847722732011943e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>2.319322422154328e-06</v>
+        <v>2.205621356290984e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0007681132126295463</v>
+        <v>0.0007239091855345023</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002709865058321575</v>
+        <v>0.002526413289075408</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004483748049092571</v>
+        <v>0.004470482136277214</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0002687012292583042</v>
+        <v>0.0002519523378874566</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7201044224460221</v>
+        <v>-0.6520333968600271</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.006980502187038</v>
+        <v>1.99059325610557</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.925189950237939</v>
+        <v>8.925189952984555</v>
       </c>
     </row>
     <row r="10">
@@ -1247,73 +1247,73 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.61420917619273</v>
+        <v>10.62969562273195</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0152022397534671</v>
+        <v>0.01410898328530927</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03771587804860253</v>
+        <v>0.03423095481113834</v>
       </c>
       <c r="G10" t="n">
-        <v>3.692877260451845e-05</v>
+        <v>3.597559159370257e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001053580870777551</v>
+        <v>0.001019814762690255</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001999136913332694</v>
+        <v>0.0001945659832336154</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001231110052292783</v>
+        <v>0.001086276849466629</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00303086397628035</v>
+        <v>0.002873608041095243</v>
       </c>
       <c r="L10" t="n">
-        <v>3.084938776627834e-05</v>
+        <v>2.992015170139257e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>7.892444792857943e-05</v>
+        <v>7.148531142234192e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003651622398944337</v>
+        <v>0.003407950193712568</v>
       </c>
       <c r="O10" t="n">
-        <v>2.565338000536192e-05</v>
+        <v>2.186257952717815e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>4.66300510404947e-07</v>
+        <v>4.633067793183591e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.708220726514603e-05</v>
+        <v>5.626430326440551e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.08919247789634e-07</v>
+        <v>2.961891139972981e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.988462934634098e-06</v>
+        <v>1.864267812418454e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0006499518852321091</v>
+        <v>0.0006057848336001974</v>
       </c>
       <c r="U10" t="n">
-        <v>0.002269036667342656</v>
+        <v>0.00208826546168496</v>
       </c>
       <c r="V10" t="n">
-        <v>0.004467505190775396</v>
+        <v>0.0044435029580982</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0002322112785824674</v>
+        <v>0.0002126036878080657</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3251828354846258</v>
+        <v>-0.2785827505310934</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.944265829784542</v>
+        <v>1.918597962742309</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.925189966200918</v>
+        <v>8.925189967951678</v>
       </c>
     </row>
     <row r="11">
@@ -1331,73 +1331,73 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.8375017376456</v>
+        <v>10.81399469658047</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01153065004524919</v>
+        <v>0.01268189202413571</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02248107878999553</v>
+        <v>0.02458622888367573</v>
       </c>
       <c r="G11" t="n">
-        <v>3.495559723025814e-05</v>
+        <v>3.45163181055891e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0009106286434073738</v>
+        <v>0.000902060096143756</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001839364047960227</v>
+        <v>0.0001806862074612486</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0007774857514576489</v>
+        <v>0.0007350539239766847</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002713452352711191</v>
+        <v>0.002595983512692795</v>
       </c>
       <c r="L11" t="n">
-        <v>2.856515258657355e-05</v>
+        <v>2.79745967271702e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.626331101109531e-05</v>
+        <v>4.773149134990697e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003300139308314219</v>
+        <v>0.003158234078010126</v>
       </c>
       <c r="O11" t="n">
-        <v>2.058098829970993e-05</v>
+        <v>1.740378168929434e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>4.630275099501092e-07</v>
+        <v>4.618835132529723e-07</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.575044531408423e-05</v>
+        <v>5.511580607320554e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.880657944050878e-07</v>
+        <v>2.37630699118626e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.581711234406284e-06</v>
+        <v>1.545769971481762e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0004827778440799133</v>
+        <v>0.0004706528194851993</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001563511213172279</v>
+        <v>0.001509076353165634</v>
       </c>
       <c r="V11" t="n">
-        <v>0.004456854148702482</v>
+        <v>0.004431192493218526</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0001747010238558121</v>
+        <v>0.0001663307048131952</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.04964680913109992</v>
+        <v>-0.04800055357829988</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.913194905202194</v>
+        <v>1.88520289430888</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.925189977749785</v>
+        <v>8.925189977474984</v>
       </c>
     </row>
   </sheetData>
@@ -1566,79 +1566,79 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.495175991793101</v>
+        <v>4.498372411198862</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1520282652691768</v>
+        <v>0.142076449933259</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02279952694155886</v>
+        <v>0.02236109545418415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05578488928828166</v>
+        <v>0.05296659951498824</v>
       </c>
       <c r="H2" t="n">
-        <v>4.010483954252127e-05</v>
+        <v>3.987099995124913e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001145326241466513</v>
+        <v>0.001115047877934225</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002234417210028195</v>
+        <v>0.0002204552969457201</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002172280437535925</v>
+        <v>0.002082938453430552</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006520258697178699</v>
+        <v>0.0006361631112596295</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004087489492760882</v>
+        <v>0.003875358811066434</v>
       </c>
       <c r="N2" t="n">
-        <v>3.329041918983525e-05</v>
+        <v>3.281297100841981e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001345287036150598</v>
+        <v>0.0001275696534852123</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004181531270246569</v>
+        <v>0.004157778150090817</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.242675186689206e-05</v>
+        <v>3.146384357918766e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>4.773778149478628e-07</v>
+        <v>4.776230107809116e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>5.869530347177221e-05</v>
+        <v>5.842311683215346e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>5.318463955165452e-07</v>
+        <v>5.260035306051285e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>2.678902949203049e-06</v>
+        <v>2.602132163041634e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008761882947529459</v>
+        <v>0.0008399885645132336</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003072651191782642</v>
+        <v>0.002914470904245384</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004491492021052261</v>
+        <v>0.004490217877914886</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002992821928195261</v>
+        <v>0.0002874343647440914</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.4064903212640071</v>
+        <v>-0.3797942821710154</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.036443937807416</v>
+        <v>2.026743697951657</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.613105250872692</v>
+        <v>2.613105250760084</v>
       </c>
     </row>
     <row r="3">
@@ -1656,79 +1656,79 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.47162534225995</v>
+        <v>4.474734471092456</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1489880991750844</v>
+        <v>0.1367993228268539</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02076609750052478</v>
+        <v>0.02005506000182299</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0526728165666643</v>
+        <v>0.04941851333391129</v>
       </c>
       <c r="H3" t="n">
-        <v>3.948394180638485e-05</v>
+        <v>3.911753746663408e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00113333566410436</v>
+        <v>0.001100074248113156</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002190167026321962</v>
+        <v>0.0002152958685212293</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002081262456268537</v>
+        <v>0.001970042623700984</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006310243618555657</v>
+        <v>0.0006130805146831815</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003869750027926281</v>
+        <v>0.00366482954191396</v>
       </c>
       <c r="N3" t="n">
-        <v>3.28577778158882e-05</v>
+        <v>3.227089836273612e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000127371563437678</v>
+        <v>0.0001197009649556254</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004126072192052787</v>
+        <v>0.004050736803665503</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.108978222078863e-05</v>
+        <v>2.95705763628912e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>4.73807930145934e-07</v>
+        <v>4.733795125129375e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>5.843554502209935e-05</v>
+        <v>5.802689914056454e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.150740251408649e-07</v>
+        <v>5.025883200395271e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>2.477733125091041e-06</v>
+        <v>2.380376850728175e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008290980202552061</v>
+        <v>0.0007880714909629381</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002938723225670072</v>
+        <v>0.002764972894223283</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004486964668614887</v>
+        <v>0.004480739709009162</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002858948217060439</v>
+        <v>0.0002716392972616066</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.3983105819727797</v>
+        <v>-0.3656260445621183</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.013509812112059</v>
+        <v>2.000780841864457</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.613105251511928</v>
+        <v>2.613105251414503</v>
       </c>
     </row>
     <row r="4">
@@ -1746,79 +1746,79 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.467415346160647</v>
+        <v>4.46615103166139</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1421568783114497</v>
+        <v>0.1297813404727585</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02107085790888249</v>
+        <v>0.02029872483175</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05125214951947083</v>
+        <v>0.04782931086403119</v>
       </c>
       <c r="H4" t="n">
-        <v>3.933887801134976e-05</v>
+        <v>3.876779959824269e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001120311520254866</v>
+        <v>0.0010849088577586</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002166100336657493</v>
+        <v>0.0002121268381683213</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001993025427013273</v>
+        <v>0.001860520502540842</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006316809502153868</v>
+        <v>0.0006130564338965225</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003569416533588163</v>
+        <v>0.003422024622077298</v>
       </c>
       <c r="N4" t="n">
-        <v>3.260833872528327e-05</v>
+        <v>3.187772904606673e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001214677816079299</v>
+        <v>0.0001132308690536361</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004047020145379852</v>
+        <v>0.003919628787678779</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.005916229423104e-05</v>
+        <v>2.773715584498818e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.740344445092132e-07</v>
+        <v>4.727414790302063e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.817496370844624e-05</v>
+        <v>5.761236249791588e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.737836485008045e-07</v>
+        <v>4.275304306641996e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.501976712642957e-06</v>
+        <v>2.396377718835449e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.000820155559006661</v>
+        <v>0.0007767900678165003</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002867520880812395</v>
+        <v>0.002683048207395486</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004476661901931694</v>
+        <v>0.004464258220244087</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.000281441481179075</v>
+        <v>0.0002649056565987174</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.379768582044327</v>
+        <v>-0.3467317410415395</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.999289847368495</v>
+        <v>1.982294353972873</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.613105251744476</v>
+        <v>2.613105251801673</v>
       </c>
     </row>
     <row r="5">
@@ -1836,79 +1836,79 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.47709325620761</v>
+        <v>4.475509325197674</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1281873922631928</v>
+        <v>0.1182890106177126</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02259225485549474</v>
+        <v>0.02201189337820754</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04960081605296998</v>
+        <v>0.04663375943952431</v>
       </c>
       <c r="H5" t="n">
-        <v>3.919861300280301e-05</v>
+        <v>3.874614160360768e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0010910869847508</v>
+        <v>0.001059466132098395</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002140162672597558</v>
+        <v>0.0002099058059956951</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001881469232512527</v>
+        <v>0.001757486776130354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006294417153693002</v>
+        <v>0.0006140965727205201</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003415563880839495</v>
+        <v>0.003301649855513185</v>
       </c>
       <c r="N5" t="n">
-        <v>3.219092836217395e-05</v>
+        <v>3.147707138709098e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001140959614549086</v>
+        <v>0.0001068647890104635</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003984466512089091</v>
+        <v>0.003844587028155852</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.930124706378508e-05</v>
+        <v>2.678385539397262e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.769799960909287e-07</v>
+        <v>4.759677398392056e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>5.792200788341426e-05</v>
+        <v>5.734158341098631e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.567685486867234e-07</v>
+        <v>3.913830566289079e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.569128164503851e-06</v>
+        <v>2.487276943047097e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0008048590265937203</v>
+        <v>0.0007693430098494871</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002724400532036946</v>
+        <v>0.002563199075923047</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004473757720860036</v>
+        <v>0.004459030194024529</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002752750533536022</v>
+        <v>0.0002599184462097203</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.3418381484185069</v>
+        <v>-0.3156041360928705</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.985675141210097</v>
+        <v>1.971970295161116</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.613105251684221</v>
+        <v>2.613105251728817</v>
       </c>
     </row>
     <row r="6">
@@ -1926,79 +1926,79 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.508805161931168</v>
+        <v>4.488995850941786</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04136300592575508</v>
+        <v>0.03780075441389463</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01373805522991727</v>
+        <v>0.01282085827477018</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03078732961702706</v>
+        <v>0.0285714934659927</v>
       </c>
       <c r="H6" t="n">
-        <v>3.599421573179587e-05</v>
+        <v>3.533826784116757e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009582645687425394</v>
+        <v>0.0009416546565259189</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00019129072384295</v>
+        <v>0.0001868813796941302</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001123065831364148</v>
+        <v>0.001027832706441007</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004991595838911691</v>
+        <v>0.0004899292141898202</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00302195521949439</v>
+        <v>0.002828996149939954</v>
       </c>
       <c r="N6" t="n">
-        <v>2.949785401874817e-05</v>
+        <v>2.881934551697532e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>6.765252205622786e-05</v>
+        <v>6.358601305521095e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003589767574783435</v>
+        <v>0.003354300193802101</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.371074285636719e-05</v>
+        <v>2.030728009792041e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.644170706638141e-07</v>
+        <v>4.606506127988125e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>5.647540433350838e-05</v>
+        <v>5.57899140535472e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.935332972846631e-07</v>
+        <v>2.630799976260342e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.666200878651816e-06</v>
+        <v>1.585188499032877e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005329070131812725</v>
+        <v>0.0005073520109438052</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001816553197223083</v>
+        <v>0.001716280861621284</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004474124591890409</v>
+        <v>0.004450086451568004</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001969281941815567</v>
+        <v>0.000183226448066897</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.1091896137785957</v>
+        <v>-0.1003416178940761</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.902381262694101</v>
+        <v>1.881146421412698</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.613105250854125</v>
+        <v>2.61310525145604</v>
       </c>
     </row>
     <row r="7">
@@ -2016,79 +2016,79 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.498050672042138</v>
+        <v>4.466257644770501</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01254387007551678</v>
+        <v>0.01154134168185622</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01185602222360194</v>
+        <v>0.01088688051161718</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02495898657428778</v>
+        <v>0.02304630564214194</v>
       </c>
       <c r="H7" t="n">
-        <v>3.466205223224526e-05</v>
+        <v>3.385458150065116e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009177299064127787</v>
+        <v>0.000905773015519929</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001819140148745449</v>
+        <v>0.0001776478641214097</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007930724914394901</v>
+        <v>0.0006957893246142024</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004707545455963314</v>
+        <v>0.0004646888140058464</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002610529344917878</v>
+        <v>0.002460563826394581</v>
       </c>
       <c r="N7" t="n">
-        <v>2.834832487474959e-05</v>
+        <v>2.766097064172988e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>4.939832179420266e-05</v>
+        <v>4.631282320516487e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003277995852546184</v>
+        <v>0.003020780359802032</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.935999696519326e-05</v>
+        <v>1.54954427050206e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>4.605384289451959e-07</v>
+        <v>4.569446863872299e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>5.55610383898784e-05</v>
+        <v>5.481852080252701e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.202856507172354e-07</v>
+        <v>1.747254058409834e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>1.474985868256083e-06</v>
+        <v>1.409502890547562e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000461064515332368</v>
+        <v>0.0004424036339612939</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00153050873953436</v>
+        <v>0.001455844059266967</v>
       </c>
       <c r="X7" t="n">
-        <v>0.004449761711081688</v>
+        <v>0.00442158411886585</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001710622880939379</v>
+        <v>0.0001582081497870693</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.03216705720677762</v>
+        <v>-0.03037541725558051</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.852699619973581</v>
+        <v>1.823669815050713</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.613105251447895</v>
+        <v>2.613105252461576</v>
       </c>
     </row>
     <row r="8">
@@ -2106,79 +2106,79 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.470166377637435</v>
+        <v>4.448086169331719</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005182853889729433</v>
+        <v>0.004460776312794375</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0114142572348318</v>
+        <v>0.010580601666228</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02248023911866059</v>
+        <v>0.0209146746949102</v>
       </c>
       <c r="H8" t="n">
-        <v>3.389035324393253e-05</v>
+        <v>3.337934035364732e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008982856254188452</v>
+        <v>0.0008891996048512561</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001771217017074168</v>
+        <v>0.0001737624900552019</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0006771731769008172</v>
+        <v>0.0005963807786516016</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004589979810556905</v>
+        <v>0.0004545762296667365</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002448804300056377</v>
+        <v>0.002334128841608283</v>
       </c>
       <c r="N8" t="n">
-        <v>2.765541921811571e-05</v>
+        <v>2.71040534223464e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>4.352794636395484e-05</v>
+        <v>4.111266534990582e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00313859737679461</v>
+        <v>0.002912538779137925</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.660794474598603e-05</v>
+        <v>1.343481035649852e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>4.58608190353345e-07</v>
+        <v>4.556831621244479e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>5.498777083214e-05</v>
+        <v>5.439842899292991e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.667596769109674e-07</v>
+        <v>1.373230990401052e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>1.404368382945893e-06</v>
+        <v>1.354999148287588e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004304866036518827</v>
+        <v>0.000416875060307444</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001395906402598848</v>
+        <v>0.001339444960014497</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004432713402793497</v>
+        <v>0.004410358447779871</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001574928778863483</v>
+        <v>0.0001472081074076261</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.0125135485398121</v>
+        <v>-0.01149789932290151</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.81610294482737</v>
+        <v>1.796676912222405</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.613105252487136</v>
+        <v>2.613105253154918</v>
       </c>
     </row>
     <row r="9">
@@ -2196,79 +2196,79 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.470253281959859</v>
+        <v>4.468268125441164</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1226329346964659</v>
+        <v>0.1110232245261395</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01899959128851271</v>
+        <v>0.01810861352797018</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04781410260243673</v>
+        <v>0.04432752778248799</v>
       </c>
       <c r="H9" t="n">
-        <v>3.865082727739569e-05</v>
+        <v>3.806921752945501e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001108967784076361</v>
+        <v>0.001074485115876923</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002132322881441464</v>
+        <v>0.0002085693333614094</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001825800765632988</v>
+        <v>0.001697622871425569</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0006064044076557117</v>
+        <v>0.0005874317082775567</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003550679011382641</v>
+        <v>0.00333810811535771</v>
       </c>
       <c r="N9" t="n">
-        <v>3.22195979095663e-05</v>
+        <v>3.149480810926924e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0001116719534621415</v>
+        <v>0.0001036498255976518</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00397922389368878</v>
+        <v>0.003808397360833145</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95053800333665e-05</v>
+        <v>2.716550998084804e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.71722607172816e-07</v>
+        <v>4.70206826371508e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>5.804541033259287e-05</v>
+        <v>5.748183282585366e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>5.059932245218344e-07</v>
+        <v>4.847722732011943e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>2.319056691492629e-06</v>
+        <v>2.205368652649252e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0007680252079475363</v>
+        <v>0.0007238262454201688</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002709554582197972</v>
+        <v>0.002526123831492402</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004483748049092571</v>
+        <v>0.004470482136277214</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002687012292583042</v>
+        <v>0.0002519523378874566</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.3276498228495404</v>
+        <v>-0.2966772877848641</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.975563497281408</v>
+        <v>1.95943277496286</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.61310525177996</v>
+        <v>2.613105251828566</v>
       </c>
     </row>
     <row r="10">
@@ -2286,79 +2286,79 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.505014507966621</v>
+        <v>4.487410812502763</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05555088518970927</v>
+        <v>0.04747377678283905</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01520049799424027</v>
+        <v>0.01410736678325322</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03771155684464485</v>
+        <v>0.03422703288368871</v>
       </c>
       <c r="H10" t="n">
-        <v>3.692877260451845e-05</v>
+        <v>3.597559159370257e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001053580870777551</v>
+        <v>0.001019814762690255</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001999136913332694</v>
+        <v>0.0001945659832336154</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001231110052292783</v>
+        <v>0.001086276849466629</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0005572350871556445</v>
+        <v>0.0005387477895499014</v>
       </c>
       <c r="M10" t="n">
-        <v>0.00303086397628035</v>
+        <v>0.002873608041095243</v>
       </c>
       <c r="N10" t="n">
-        <v>3.084938776627834e-05</v>
+        <v>2.992015170139257e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>7.892444792857943e-05</v>
+        <v>7.148531142234192e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003651622398944337</v>
+        <v>0.003407950193712568</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.565338000536192e-05</v>
+        <v>2.186257952717815e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.66300510404947e-07</v>
+        <v>4.633067793183591e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>5.708220726514603e-05</v>
+        <v>5.626430326440551e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>4.08919247789634e-07</v>
+        <v>2.961891139972981e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>1.988235111384381e-06</v>
+        <v>1.864054218519384e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0006498774185935457</v>
+        <v>0.0006057154272930828</v>
       </c>
       <c r="W10" t="n">
-        <v>0.00226877669804764</v>
+        <v>0.002088026203806194</v>
       </c>
       <c r="X10" t="n">
-        <v>0.004467505190775396</v>
+        <v>0.0044435029580982</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0002322112785824674</v>
+        <v>0.0002126036878080657</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.1479592335766207</v>
+        <v>-0.1267560453946425</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.91383055199005</v>
+        <v>1.888564486312557</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.613105251211374</v>
+        <v>2.613105251750693</v>
       </c>
     </row>
     <row r="11">
@@ -2376,79 +2376,79 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.531811533699257</v>
+        <v>4.507538323009507</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0088113558685004</v>
+        <v>0.008507665310968386</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01152932894938218</v>
+        <v>0.01268043902755069</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02247850307568989</v>
+        <v>0.02458341197697613</v>
       </c>
       <c r="H11" t="n">
-        <v>3.495559723025814e-05</v>
+        <v>3.45163181055891e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0009106286434073738</v>
+        <v>0.000902060096143756</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001839364047960227</v>
+        <v>0.0001806862074612486</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0007774857514576489</v>
+        <v>0.0007350539239766847</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004788453409431045</v>
+        <v>0.000475751125884555</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002713452352711191</v>
+        <v>0.002595983512692795</v>
       </c>
       <c r="N11" t="n">
-        <v>2.856515258657355e-05</v>
+        <v>2.79745967271702e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>4.626331101109531e-05</v>
+        <v>4.773149134990697e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.003300139308314219</v>
+        <v>0.003158234078010126</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.058098829970993e-05</v>
+        <v>1.740378168929434e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>4.630275099501092e-07</v>
+        <v>4.618835132529723e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>5.575044531408423e-05</v>
+        <v>5.511580607320554e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.880657944050878e-07</v>
+        <v>2.37630699118626e-07</v>
       </c>
       <c r="U11" t="n">
-        <v>1.581530013732139e-06</v>
+        <v>1.545592868689409e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0004827225309959145</v>
+        <v>0.0004705988955958132</v>
       </c>
       <c r="W11" t="n">
-        <v>0.00156333207772114</v>
+        <v>0.001508903454452629</v>
       </c>
       <c r="X11" t="n">
-        <v>0.004456854148702482</v>
+        <v>0.004431192493218526</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0001747010238558121</v>
+        <v>0.0001663307048131952</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.02258945745895521</v>
+        <v>-0.02184040590000499</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.883246007514016</v>
+        <v>1.855692179823078</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.613105250049959</v>
+        <v>2.613105251177663</v>
       </c>
     </row>
   </sheetData>
@@ -2607,73 +2607,73 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.09346538391463</v>
+        <v>11.07977878591611</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02280213944059888</v>
+        <v>0.02236365771525902</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05579128143712251</v>
+        <v>0.05297266872821096</v>
       </c>
       <c r="G2" t="n">
-        <v>4.010483954252127e-05</v>
+        <v>3.987099995124913e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001145326241466513</v>
+        <v>0.001115047877934225</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002234417210028195</v>
+        <v>0.0002204552969457201</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002172280437535925</v>
+        <v>0.002082938453430552</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004087489492760882</v>
+        <v>0.003875358811066434</v>
       </c>
       <c r="L2" t="n">
-        <v>3.329041918983525e-05</v>
+        <v>3.281297100841981e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001345287036150598</v>
+        <v>0.0001275696534852123</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004181531270246569</v>
+        <v>0.004157778150090817</v>
       </c>
       <c r="O2" t="n">
-        <v>3.242675186689206e-05</v>
+        <v>3.146384357918766e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.773778149478628e-07</v>
+        <v>4.776230107809116e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.869530347177221e-05</v>
+        <v>5.842311683215346e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>5.318463955165452e-07</v>
+        <v>5.260035306051285e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>2.679209913088789e-06</v>
+        <v>2.602430330095509e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008762886933745828</v>
+        <v>0.0008400848151645752</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003073003273574045</v>
+        <v>0.002914804860842479</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004491492021052261</v>
+        <v>0.004490217877914886</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002992821928195261</v>
+        <v>0.0002874343647440914</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.068829112605486</v>
+        <v>2.058974611707972</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.925189980635777</v>
+        <v>8.925189980614809</v>
       </c>
     </row>
     <row r="3">
@@ -2691,73 +2691,73 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.064430834508</v>
+        <v>11.04685924082778</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0207684769976926</v>
+        <v>0.02005735802428355</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05267885211657136</v>
+        <v>0.0494241759873064</v>
       </c>
       <c r="G3" t="n">
-        <v>3.948394180638485e-05</v>
+        <v>3.911753746663408e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00113333566410436</v>
+        <v>0.001100074248113156</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002190167026321962</v>
+        <v>0.0002152958685212293</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002081262456268537</v>
+        <v>0.001970042623700984</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003869750027926281</v>
+        <v>0.00366482954191396</v>
       </c>
       <c r="L3" t="n">
-        <v>3.28577778158882e-05</v>
+        <v>3.227089836273612e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000127371563437678</v>
+        <v>0.0001197009649556254</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004126072192052787</v>
+        <v>0.004050736803665503</v>
       </c>
       <c r="O3" t="n">
-        <v>3.108978222078863e-05</v>
+        <v>2.95705763628912e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.73807930145934e-07</v>
+        <v>4.733795125129375e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.843554502209935e-05</v>
+        <v>5.802689914056454e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.150740251408649e-07</v>
+        <v>5.025883200395271e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.478017037797965e-06</v>
+        <v>2.380649607801304e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008291930230062517</v>
+        <v>0.0007881617926617884</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002939059961235925</v>
+        <v>0.002765289720491218</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004486964668614887</v>
+        <v>0.004480739709009162</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002858948217060439</v>
+        <v>0.0002716392972616066</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.045530269936735</v>
+        <v>2.032598873332667</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.925189980430158</v>
+        <v>8.925189980384454</v>
       </c>
     </row>
     <row r="4">
@@ -2775,73 +2775,73 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.04828312801857</v>
+        <v>11.02610535187536</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02107327232722546</v>
+        <v>0.02030105077470803</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0512580222812944</v>
+        <v>0.04783479141759864</v>
       </c>
       <c r="G4" t="n">
-        <v>3.933887801134976e-05</v>
+        <v>3.876779959824269e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001120311520254866</v>
+        <v>0.0010849088577586</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002166100336657493</v>
+        <v>0.0002121268381683213</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001993025427013273</v>
+        <v>0.001860520502540842</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003569416533588163</v>
+        <v>0.003422024622077298</v>
       </c>
       <c r="L4" t="n">
-        <v>3.260833872528327e-05</v>
+        <v>3.187772904606673e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001214677816079299</v>
+        <v>0.0001132308690536361</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004047020145379852</v>
+        <v>0.003919628787678779</v>
       </c>
       <c r="O4" t="n">
-        <v>3.005916229423104e-05</v>
+        <v>2.773715584498818e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.740344445092132e-07</v>
+        <v>4.727414790302063e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.817496370844624e-05</v>
+        <v>5.761236249791588e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.737836485008045e-07</v>
+        <v>4.275304306641996e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>2.502263403317577e-06</v>
+        <v>2.396652309378753e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0008202495370798036</v>
+        <v>0.0007768790768258387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002867849457609953</v>
+        <v>0.002683355646266978</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004476661901931694</v>
+        <v>0.004464258220244087</v>
       </c>
       <c r="W4" t="n">
-        <v>0.000281441481179075</v>
+        <v>0.0002649056565987174</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.031084167839078</v>
+        <v>2.013818398393047</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.925189980327431</v>
+        <v>8.925189980241583</v>
       </c>
     </row>
     <row r="5">
@@ -2859,73 +2859,73 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.03378578466144</v>
+        <v>11.0156631934553</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02259484360412415</v>
+        <v>0.02201441562572904</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04960649959564408</v>
+        <v>0.0466391030000324</v>
       </c>
       <c r="G5" t="n">
-        <v>3.919861300280301e-05</v>
+        <v>3.874614160360768e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0010910869847508</v>
+        <v>0.001059466132098395</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002140162672597558</v>
+        <v>0.0002099058059956951</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001881469232512527</v>
+        <v>0.001757486776130354</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003415563880839495</v>
+        <v>0.003301649855513185</v>
       </c>
       <c r="L5" t="n">
-        <v>3.219092836217395e-05</v>
+        <v>3.147707138709098e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001140959614549086</v>
+        <v>0.0001068647890104635</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003984466512089091</v>
+        <v>0.003844587028155852</v>
       </c>
       <c r="O5" t="n">
-        <v>2.930124706378508e-05</v>
+        <v>2.678385539397262e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.769799960909287e-07</v>
+        <v>4.759677398392056e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.792200788341426e-05</v>
+        <v>5.734158341098631e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.567685486867234e-07</v>
+        <v>3.913830566289079e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.569422549772487e-06</v>
+        <v>2.487561949338785e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0008049512519034685</v>
+        <v>0.0007694311655315005</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002724712709293636</v>
+        <v>0.002563492781802208</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004473757720860036</v>
+        <v>0.004459030194024529</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002752750533536022</v>
+        <v>0.0002599184462097203</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.017252949637026</v>
+        <v>2.003330158067112</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.925189980282918</v>
+        <v>8.92518998022341</v>
       </c>
     </row>
     <row r="6">
@@ -2943,73 +2943,73 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.91847591246967</v>
+        <v>10.89305201968298</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01373962941416204</v>
+        <v>0.01282232736138852</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03079085740377786</v>
+        <v>0.02857476734967646</v>
       </c>
       <c r="G6" t="n">
-        <v>3.599421573179587e-05</v>
+        <v>3.533826784116757e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009582645687425394</v>
+        <v>0.0009416546565259189</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00019129072384295</v>
+        <v>0.0001868813796941302</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001123065831364148</v>
+        <v>0.001027832706441007</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00302195521949439</v>
+        <v>0.002828996149939954</v>
       </c>
       <c r="L6" t="n">
-        <v>2.949785401874817e-05</v>
+        <v>2.881934551697532e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>6.765252205622786e-05</v>
+        <v>6.358601305521095e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003589767574783435</v>
+        <v>0.003354300193802101</v>
       </c>
       <c r="O6" t="n">
-        <v>2.371074285636719e-05</v>
+        <v>2.030728009792041e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.644170706638141e-07</v>
+        <v>4.606506127988125e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.647540433350838e-05</v>
+        <v>5.57899140535472e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>3.935332972846631e-07</v>
+        <v>2.630799976260342e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.666391801393639e-06</v>
+        <v>1.585370138917008e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005329680766877176</v>
+        <v>0.0005074101462132019</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001816761348185862</v>
+        <v>0.001716477522810486</v>
       </c>
       <c r="V6" t="n">
-        <v>0.004474124591890409</v>
+        <v>0.004450086451568004</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001969281941815567</v>
+        <v>0.000183226448066897</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.932634464651259</v>
+        <v>1.911061929788442</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.925189979790131</v>
+        <v>8.925189979607099</v>
       </c>
     </row>
     <row r="7">
@@ -3027,73 +3027,73 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.85875540380544</v>
+        <v>10.82571733311326</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0118573807538362</v>
+        <v>0.01088812799210035</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0249618465164538</v>
+        <v>0.02304894641848435</v>
       </c>
       <c r="G7" t="n">
-        <v>3.466205223224526e-05</v>
+        <v>3.385458150065116e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009177299064127787</v>
+        <v>0.000905773015519929</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001819140148745449</v>
+        <v>0.0001776478641214097</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007930724914394901</v>
+        <v>0.0006957893246142024</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002610529344917878</v>
+        <v>0.002460563826394581</v>
       </c>
       <c r="L7" t="n">
-        <v>2.834832487474959e-05</v>
+        <v>2.766097064172988e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.939832179420266e-05</v>
+        <v>4.631282320516487e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003277995852546184</v>
+        <v>0.003020780359802032</v>
       </c>
       <c r="O7" t="n">
-        <v>1.935999696519326e-05</v>
+        <v>1.54954427050206e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.605384289451959e-07</v>
+        <v>4.569446863872299e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.55610383898784e-05</v>
+        <v>5.481852080252701e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.202856507172354e-07</v>
+        <v>1.747254058409834e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.475154880498078e-06</v>
+        <v>1.409664399378769e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004611173467181575</v>
+        <v>0.0004424543270775139</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00153068411389104</v>
+        <v>0.0014560108781312</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004449761711081688</v>
+        <v>0.00442158411886585</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001710622880939379</v>
+        <v>0.0001582081497870693</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.882162744357825</v>
+        <v>1.852671284051603</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.925189979394137</v>
+        <v>8.925189979113407</v>
       </c>
     </row>
     <row r="8">
@@ -3111,73 +3111,73 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.8180080286728</v>
+        <v>10.79532945823042</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01141556514512947</v>
+        <v>0.01058181405154486</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0224828150318918</v>
+        <v>0.02091707121689519</v>
       </c>
       <c r="G8" t="n">
-        <v>3.389035324393253e-05</v>
+        <v>3.337934035364732e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008982856254188452</v>
+        <v>0.0008891996048512561</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001771217017074168</v>
+        <v>0.0001737624900552019</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0006771731769008172</v>
+        <v>0.0005963807786516016</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002448804300056377</v>
+        <v>0.002334128841608283</v>
       </c>
       <c r="L8" t="n">
-        <v>2.765541921811571e-05</v>
+        <v>2.71040534223464e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.352794636395484e-05</v>
+        <v>4.111266534990582e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00313859737679461</v>
+        <v>0.002912538779137925</v>
       </c>
       <c r="O8" t="n">
-        <v>1.660794474598603e-05</v>
+        <v>1.343481035649852e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.58608190353345e-07</v>
+        <v>4.556831621244479e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.498777083214e-05</v>
+        <v>5.439842899292991e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.667596769109674e-07</v>
+        <v>1.373230990401052e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.404529303436114e-06</v>
+        <v>1.355154411771046e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0004305359312472172</v>
+        <v>0.0004169228282149806</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001396066353467391</v>
+        <v>0.001339598441213309</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004432713402793497</v>
+        <v>0.004410358447779871</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0001574928778863483</v>
+        <v>0.0001472081074076261</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.844984079351919</v>
+        <v>1.825249118300723</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.925189979066008</v>
+        <v>8.925189978883191</v>
       </c>
     </row>
     <row r="9">
@@ -3195,73 +3195,73 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.0181735536005</v>
+        <v>10.9965874932952</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01900176836938499</v>
+        <v>0.01811068851555999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04781958141335539</v>
+        <v>0.04433260708189948</v>
       </c>
       <c r="G9" t="n">
-        <v>3.865082727739569e-05</v>
+        <v>3.806921752945501e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001108967784076361</v>
+        <v>0.001074485115876923</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002132322881441464</v>
+        <v>0.0002085693333614094</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001825800765632988</v>
+        <v>0.001697622871425569</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003550679011382641</v>
+        <v>0.00333810811535771</v>
       </c>
       <c r="L9" t="n">
-        <v>3.22195979095663e-05</v>
+        <v>3.149480810926924e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001116719534621415</v>
+        <v>0.0001036498255976518</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00397922389368878</v>
+        <v>0.003808397360833145</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95053800333665e-05</v>
+        <v>2.716550998084804e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.71722607172816e-07</v>
+        <v>4.70206826371508e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.804541033259287e-05</v>
+        <v>5.748183282585366e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>5.059932245218344e-07</v>
+        <v>4.847722732011943e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>2.319322422154328e-06</v>
+        <v>2.205621356290984e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0007681132126295463</v>
+        <v>0.0007239091855345023</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002709865058321575</v>
+        <v>0.002526413289075408</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004483748049092571</v>
+        <v>0.004470482136277214</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0002687012292583042</v>
+        <v>0.0002519523378874566</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.006980502187038</v>
+        <v>1.99059325610557</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.925189980131226</v>
+        <v>8.925189980052041</v>
       </c>
     </row>
     <row r="10">
@@ -3279,73 +3279,73 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.93939202517648</v>
+        <v>10.90827838482768</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0152022397534671</v>
+        <v>0.01410898328530927</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03771587804860253</v>
+        <v>0.03423095481113834</v>
       </c>
       <c r="G10" t="n">
-        <v>3.692877260451845e-05</v>
+        <v>3.597559159370257e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001053580870777551</v>
+        <v>0.001019814762690255</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001999136913332694</v>
+        <v>0.0001945659832336154</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001231110052292783</v>
+        <v>0.001086276849466629</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00303086397628035</v>
+        <v>0.002873608041095243</v>
       </c>
       <c r="L10" t="n">
-        <v>3.084938776627834e-05</v>
+        <v>2.992015170139257e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>7.892444792857943e-05</v>
+        <v>7.148531142234192e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003651622398944337</v>
+        <v>0.003407950193712568</v>
       </c>
       <c r="O10" t="n">
-        <v>2.565338000536192e-05</v>
+        <v>2.186257952717815e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>4.66300510404947e-07</v>
+        <v>4.633067793183591e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.708220726514603e-05</v>
+        <v>5.626430326440551e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.08919247789634e-07</v>
+        <v>2.961891139972981e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.988462934634098e-06</v>
+        <v>1.864267812418454e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0006499518852321091</v>
+        <v>0.0006057848336001974</v>
       </c>
       <c r="U10" t="n">
-        <v>0.002269036667342656</v>
+        <v>0.00208826546168496</v>
       </c>
       <c r="V10" t="n">
-        <v>0.004467505190775396</v>
+        <v>0.0044435029580982</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0002322112785824674</v>
+        <v>0.0002126036878080657</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.944265829784542</v>
+        <v>1.918597962742309</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.925189979700047</v>
+        <v>8.92518997951632</v>
       </c>
     </row>
     <row r="11">
@@ -3363,73 +3363,73 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.88714854883766</v>
+        <v>10.86199525215139</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01153065004524919</v>
+        <v>0.01268189202413571</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02248107878999553</v>
+        <v>0.02458622888367573</v>
       </c>
       <c r="G11" t="n">
-        <v>3.495559723025814e-05</v>
+        <v>3.45163181055891e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0009106286434073738</v>
+        <v>0.000902060096143756</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001839364047960227</v>
+        <v>0.0001806862074612486</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0007774857514576489</v>
+        <v>0.0007350539239766847</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002713452352711191</v>
+        <v>0.002595983512692795</v>
       </c>
       <c r="L11" t="n">
-        <v>2.856515258657355e-05</v>
+        <v>2.79745967271702e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.626331101109531e-05</v>
+        <v>4.773149134990697e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003300139308314219</v>
+        <v>0.003158234078010126</v>
       </c>
       <c r="O11" t="n">
-        <v>2.058098829970993e-05</v>
+        <v>1.740378168929434e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>4.630275099501092e-07</v>
+        <v>4.618835132529723e-07</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.575044531408423e-05</v>
+        <v>5.511580607320554e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.880657944050878e-07</v>
+        <v>2.37630699118626e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.581711234406284e-06</v>
+        <v>1.545769971481762e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0004827778440799133</v>
+        <v>0.0004706528194851993</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001563511213172279</v>
+        <v>0.001509076353165634</v>
       </c>
       <c r="V11" t="n">
-        <v>0.004456854148702482</v>
+        <v>0.004431192493218526</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0001747010238558121</v>
+        <v>0.0001663307048131952</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.913194905202194</v>
+        <v>1.88520289430888</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.925189979810746</v>
+        <v>8.925189979467607</v>
       </c>
     </row>
   </sheetData>
@@ -3598,79 +3598,79 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.901666310329683</v>
+        <v>4.878166690821577</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1520282652691768</v>
+        <v>0.142076449933259</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02279952694155886</v>
+        <v>0.02236109545418415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05578488928828166</v>
+        <v>0.05296659951498824</v>
       </c>
       <c r="H2" t="n">
-        <v>4.010483954252127e-05</v>
+        <v>3.987099995124913e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001145326241466513</v>
+        <v>0.001115047877934225</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002234417210028195</v>
+        <v>0.0002204552969457201</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002172280437535925</v>
+        <v>0.002082938453430552</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006520258697178699</v>
+        <v>0.0006361631112596295</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004087489492760882</v>
+        <v>0.003875358811066434</v>
       </c>
       <c r="N2" t="n">
-        <v>3.329041918983525e-05</v>
+        <v>3.281297100841981e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001345287036150598</v>
+        <v>0.0001275696534852123</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004181531270246569</v>
+        <v>0.004157778150090817</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.242675186689206e-05</v>
+        <v>3.146384357918766e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>4.773778149478628e-07</v>
+        <v>4.776230107809116e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>5.869530347177221e-05</v>
+        <v>5.842311683215346e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>5.318463955165452e-07</v>
+        <v>5.260035306051285e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>2.678902949203049e-06</v>
+        <v>2.602132163041634e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008761882947529459</v>
+        <v>0.0008399885645132336</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003072651191782642</v>
+        <v>0.002914470904245384</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004491492021052261</v>
+        <v>0.004490217877914886</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002992821928195261</v>
+        <v>0.0002874343647440914</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.036443937807416</v>
+        <v>2.026743697951657</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.613105248145267</v>
+        <v>2.613105248211784</v>
       </c>
     </row>
     <row r="3">
@@ -3688,79 +3688,79 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.869935921560193</v>
+        <v>4.840360513201338</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1489880991750844</v>
+        <v>0.1367993228268539</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02076609750052478</v>
+        <v>0.02005506000182299</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0526728165666643</v>
+        <v>0.04941851333391129</v>
       </c>
       <c r="H3" t="n">
-        <v>3.948394180638485e-05</v>
+        <v>3.911753746663408e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00113333566410436</v>
+        <v>0.001100074248113156</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002190167026321962</v>
+        <v>0.0002152958685212293</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002081262456268537</v>
+        <v>0.001970042623700984</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006310243618555657</v>
+        <v>0.0006130805146831815</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003869750027926281</v>
+        <v>0.00366482954191396</v>
       </c>
       <c r="N3" t="n">
-        <v>3.28577778158882e-05</v>
+        <v>3.227089836273612e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000127371563437678</v>
+        <v>0.0001197009649556254</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004126072192052787</v>
+        <v>0.004050736803665503</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.108978222078863e-05</v>
+        <v>2.95705763628912e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>4.73807930145934e-07</v>
+        <v>4.733795125129375e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>5.843554502209935e-05</v>
+        <v>5.802689914056454e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.150740251408649e-07</v>
+        <v>5.025883200395271e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>2.477733125091041e-06</v>
+        <v>2.380376850728175e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0008290980202552061</v>
+        <v>0.0007880714909629381</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002938723225670072</v>
+        <v>0.002764972894223283</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004486964668614887</v>
+        <v>0.004480739709009162</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002858948217060439</v>
+        <v>0.0002716392972616066</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.013509812112059</v>
+        <v>2.000780841864457</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.613105248839392</v>
+        <v>2.613105248961266</v>
       </c>
     </row>
     <row r="4">
@@ -3778,79 +3778,79 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.847183925656844</v>
+        <v>4.812882770376468</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1421568783114497</v>
+        <v>0.1297813404727585</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02107085790888249</v>
+        <v>0.02029872483175</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05125214951947083</v>
+        <v>0.04782931086403119</v>
       </c>
       <c r="H4" t="n">
-        <v>3.933887801134976e-05</v>
+        <v>3.876779959824269e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001120311520254866</v>
+        <v>0.0010849088577586</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002166100336657493</v>
+        <v>0.0002121268381683213</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001993025427013273</v>
+        <v>0.001860520502540842</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006316809502153868</v>
+        <v>0.0006130564338965225</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003569416533588163</v>
+        <v>0.003422024622077298</v>
       </c>
       <c r="N4" t="n">
-        <v>3.260833872528327e-05</v>
+        <v>3.187772904606673e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001214677816079299</v>
+        <v>0.0001132308690536361</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004047020145379852</v>
+        <v>0.003919628787678779</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.005916229423104e-05</v>
+        <v>2.773715584498818e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.740344445092132e-07</v>
+        <v>4.727414790302063e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.817496370844624e-05</v>
+        <v>5.761236249791588e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.737836485008045e-07</v>
+        <v>4.275304306641996e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.501976712642957e-06</v>
+        <v>2.396377718835449e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.000820155559006661</v>
+        <v>0.0007767900678165003</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002867520880812395</v>
+        <v>0.002683048207395486</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004476661901931694</v>
+        <v>0.004464258220244087</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.000281441481179075</v>
+        <v>0.0002649056565987174</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.999289847368495</v>
+        <v>1.982294353972873</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.613105249196346</v>
+        <v>2.613105249475212</v>
       </c>
     </row>
     <row r="5">
@@ -3868,79 +3868,79 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.818931402332492</v>
+        <v>4.791113459172938</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1281873922631928</v>
+        <v>0.1182890106177126</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02259225485549474</v>
+        <v>0.02201189337820754</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04960081605296998</v>
+        <v>0.04663375943952431</v>
       </c>
       <c r="H5" t="n">
-        <v>3.919861300280301e-05</v>
+        <v>3.874614160360768e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0010910869847508</v>
+        <v>0.001059466132098395</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002140162672597558</v>
+        <v>0.0002099058059956951</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001881469232512527</v>
+        <v>0.001757486776130354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006294417153693002</v>
+        <v>0.0006140965727205201</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003415563880839495</v>
+        <v>0.003301649855513185</v>
       </c>
       <c r="N5" t="n">
-        <v>3.219092836217395e-05</v>
+        <v>3.147707138709098e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001140959614549086</v>
+        <v>0.0001068647890104635</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003984466512089091</v>
+        <v>0.003844587028155852</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.930124706378508e-05</v>
+        <v>2.678385539397262e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.769799960909287e-07</v>
+        <v>4.759677398392056e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>5.792200788341426e-05</v>
+        <v>5.734158341098631e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.567685486867234e-07</v>
+        <v>3.913830566289079e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.569128164503851e-06</v>
+        <v>2.487276943047097e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0008048590265937203</v>
+        <v>0.0007693430098494871</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002724400532036946</v>
+        <v>0.002563199075923047</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004473757720860036</v>
+        <v>0.004459030194024529</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002752750533536022</v>
+        <v>0.0002599184462097203</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.985675141210097</v>
+        <v>1.971970295161116</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.613105249390596</v>
+        <v>2.613105249611211</v>
       </c>
     </row>
     <row r="6">
@@ -3958,79 +3958,79 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.617994774977132</v>
+        <v>4.589337468162601</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04136300592575508</v>
+        <v>0.03780075441389463</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01373805522991727</v>
+        <v>0.01282085827477018</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03078732961702706</v>
+        <v>0.0285714934659927</v>
       </c>
       <c r="H6" t="n">
-        <v>3.599421573179587e-05</v>
+        <v>3.533826784116757e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009582645687425394</v>
+        <v>0.0009416546565259189</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00019129072384295</v>
+        <v>0.0001868813796941302</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001123065831364148</v>
+        <v>0.001027832706441007</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004991595838911691</v>
+        <v>0.0004899292141898202</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00302195521949439</v>
+        <v>0.002828996149939954</v>
       </c>
       <c r="N6" t="n">
-        <v>2.949785401874817e-05</v>
+        <v>2.881934551697532e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>6.765252205622786e-05</v>
+        <v>6.358601305521095e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003589767574783435</v>
+        <v>0.003354300193802101</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.371074285636719e-05</v>
+        <v>2.030728009792041e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.644170706638141e-07</v>
+        <v>4.606506127988125e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>5.647540433350838e-05</v>
+        <v>5.57899140535472e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>3.935332972846631e-07</v>
+        <v>2.630799976260342e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.666200878651816e-06</v>
+        <v>1.585188499032877e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005329070131812725</v>
+        <v>0.0005073520109438052</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001816553197223083</v>
+        <v>0.001716280861621284</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004474124591890409</v>
+        <v>0.004450086451568004</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001969281941815567</v>
+        <v>0.000183226448066897</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.902381262694101</v>
+        <v>1.881146421412698</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.613105250121493</v>
+        <v>2.613105250782778</v>
       </c>
     </row>
     <row r="7">
@@ -4048,79 +4048,79 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.530217729033088</v>
+        <v>4.496633061822275</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01254387007551678</v>
+        <v>0.01154134168185622</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01185602222360194</v>
+        <v>0.01088688051161718</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02495898657428778</v>
+        <v>0.02304630564214194</v>
       </c>
       <c r="H7" t="n">
-        <v>3.466205223224526e-05</v>
+        <v>3.385458150065116e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009177299064127787</v>
+        <v>0.000905773015519929</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001819140148745449</v>
+        <v>0.0001776478641214097</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007930724914394901</v>
+        <v>0.0006957893246142024</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004707545455963314</v>
+        <v>0.0004646888140058464</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002610529344917878</v>
+        <v>0.002460563826394581</v>
       </c>
       <c r="N7" t="n">
-        <v>2.834832487474959e-05</v>
+        <v>2.766097064172988e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>4.939832179420266e-05</v>
+        <v>4.631282320516487e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003277995852546184</v>
+        <v>0.003020780359802032</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.935999696519326e-05</v>
+        <v>1.54954427050206e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>4.605384289451959e-07</v>
+        <v>4.569446863872299e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>5.55610383898784e-05</v>
+        <v>5.481852080252701e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>3.202856507172354e-07</v>
+        <v>1.747254058409834e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>1.474985868256083e-06</v>
+        <v>1.409502890547562e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000461064515332368</v>
+        <v>0.0004424036339612939</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00153050873953436</v>
+        <v>0.001455844059266967</v>
       </c>
       <c r="X7" t="n">
-        <v>0.004449761711081688</v>
+        <v>0.00442158411886585</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001710622880939379</v>
+        <v>0.0001582081497870693</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.852699619973581</v>
+        <v>1.823669815050713</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.613105251232066</v>
+        <v>2.61310525225777</v>
       </c>
     </row>
     <row r="8">
@@ -4138,79 +4138,79 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.482679926093283</v>
+        <v>4.459584068577475</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005182853889729433</v>
+        <v>0.004460776312794375</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0114142572348318</v>
+        <v>0.010580601666228</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02248023911866059</v>
+        <v>0.0209146746949102</v>
       </c>
       <c r="H8" t="n">
-        <v>3.389035324393253e-05</v>
+        <v>3.337934035364732e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008982856254188452</v>
+        <v>0.0008891996048512561</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001771217017074168</v>
+        <v>0.0001737624900552019</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0006771731769008172</v>
+        <v>0.0005963807786516016</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004589979810556905</v>
+        <v>0.0004545762296667365</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002448804300056377</v>
+        <v>0.002334128841608283</v>
       </c>
       <c r="N8" t="n">
-        <v>2.765541921811571e-05</v>
+        <v>2.71040534223464e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>4.352794636395484e-05</v>
+        <v>4.111266534990582e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00313859737679461</v>
+        <v>0.002912538779137925</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.660794474598603e-05</v>
+        <v>1.343481035649852e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>4.58608190353345e-07</v>
+        <v>4.556831621244479e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>5.498777083214e-05</v>
+        <v>5.439842899292991e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.667596769109674e-07</v>
+        <v>1.373230990401052e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>1.404368382945893e-06</v>
+        <v>1.354999148287588e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004304866036518827</v>
+        <v>0.000416875060307444</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001395906402598848</v>
+        <v>0.001339444960014497</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004432713402793497</v>
+        <v>0.004410358447779871</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001574928778863483</v>
+        <v>0.0001472081074076261</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.81610294482737</v>
+        <v>1.796676912222405</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.613105252403172</v>
+        <v>2.613105253077772</v>
       </c>
     </row>
     <row r="9">
@@ -4228,79 +4228,79 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.797903102610972</v>
+        <v>4.764945411235422</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1226329346964659</v>
+        <v>0.1110232245261395</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01899959128851271</v>
+        <v>0.01810861352797018</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04781410260243673</v>
+        <v>0.04432752778248799</v>
       </c>
       <c r="H9" t="n">
-        <v>3.865082727739569e-05</v>
+        <v>3.806921752945501e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001108967784076361</v>
+        <v>0.001074485115876923</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002132322881441464</v>
+        <v>0.0002085693333614094</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001825800765632988</v>
+        <v>0.001697622871425569</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0006064044076557117</v>
+        <v>0.0005874317082775567</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003550679011382641</v>
+        <v>0.00333810811535771</v>
       </c>
       <c r="N9" t="n">
-        <v>3.22195979095663e-05</v>
+        <v>3.149480810926924e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0001116719534621415</v>
+        <v>0.0001036498255976518</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00397922389368878</v>
+        <v>0.003808397360833145</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.95053800333665e-05</v>
+        <v>2.716550998084804e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.71722607172816e-07</v>
+        <v>4.70206826371508e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>5.804541033259287e-05</v>
+        <v>5.748183282585366e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>5.059932245218344e-07</v>
+        <v>4.847722732011943e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>2.319056691492629e-06</v>
+        <v>2.205368652649252e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0007680252079475363</v>
+        <v>0.0007238262454201688</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002709554582197972</v>
+        <v>0.002526123831492402</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004483748049092571</v>
+        <v>0.004470482136277214</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002687012292583042</v>
+        <v>0.0002519523378874566</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.975563497281408</v>
+        <v>1.95943277496286</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.613105249581534</v>
+        <v>2.61310524983796</v>
       </c>
     </row>
     <row r="10">
@@ -4318,79 +4318,79 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.65297374055048</v>
+        <v>4.614166857046909</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05555088518970927</v>
+        <v>0.04747377678283905</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01520049799424027</v>
+        <v>0.01410736678325322</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03771155684464485</v>
+        <v>0.03422703288368871</v>
       </c>
       <c r="H10" t="n">
-        <v>3.692877260451845e-05</v>
+        <v>3.597559159370257e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001053580870777551</v>
+        <v>0.001019814762690255</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001999136913332694</v>
+        <v>0.0001945659832336154</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001231110052292783</v>
+        <v>0.001086276849466629</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0005572350871556445</v>
+        <v>0.0005387477895499014</v>
       </c>
       <c r="M10" t="n">
-        <v>0.00303086397628035</v>
+        <v>0.002873608041095243</v>
       </c>
       <c r="N10" t="n">
-        <v>3.084938776627834e-05</v>
+        <v>2.992015170139257e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>7.892444792857943e-05</v>
+        <v>7.148531142234192e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003651622398944337</v>
+        <v>0.003407950193712568</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.565338000536192e-05</v>
+        <v>2.186257952717815e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.66300510404947e-07</v>
+        <v>4.633067793183591e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>5.708220726514603e-05</v>
+        <v>5.626430326440551e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>4.08919247789634e-07</v>
+        <v>2.961891139972981e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>1.988235111384381e-06</v>
+        <v>1.864054218519384e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0006498774185935457</v>
+        <v>0.0006057154272930828</v>
       </c>
       <c r="W10" t="n">
-        <v>0.00226877669804764</v>
+        <v>0.002088026203806194</v>
       </c>
       <c r="X10" t="n">
-        <v>0.004467505190775396</v>
+        <v>0.0044435029580982</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0002322112785824674</v>
+        <v>0.0002126036878080657</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.91383055199005</v>
+        <v>1.888564486312557</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.613105250218613</v>
+        <v>2.613105250900197</v>
       </c>
     </row>
     <row r="11">
@@ -4408,79 +4408,79 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.554400991006646</v>
+        <v>4.529378728762969</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0088113558685004</v>
+        <v>0.008507665310968386</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01152932894938218</v>
+        <v>0.01268043902755069</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02247850307568989</v>
+        <v>0.02458341197697613</v>
       </c>
       <c r="H11" t="n">
-        <v>3.495559723025814e-05</v>
+        <v>3.45163181055891e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0009106286434073738</v>
+        <v>0.000902060096143756</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001839364047960227</v>
+        <v>0.0001806862074612486</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0007774857514576489</v>
+        <v>0.0007350539239766847</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004788453409431045</v>
+        <v>0.000475751125884555</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002713452352711191</v>
+        <v>0.002595983512692795</v>
       </c>
       <c r="N11" t="n">
-        <v>2.856515258657355e-05</v>
+        <v>2.79745967271702e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>4.626331101109531e-05</v>
+        <v>4.773149134990697e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.003300139308314219</v>
+        <v>0.003158234078010126</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.058098829970993e-05</v>
+        <v>1.740378168929434e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>4.630275099501092e-07</v>
+        <v>4.618835132529723e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>5.575044531408423e-05</v>
+        <v>5.511580607320554e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.880657944050878e-07</v>
+        <v>2.37630699118626e-07</v>
       </c>
       <c r="U11" t="n">
-        <v>1.581530013732139e-06</v>
+        <v>1.545592868689409e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0004827225309959145</v>
+        <v>0.0004705988955958132</v>
       </c>
       <c r="W11" t="n">
-        <v>0.00156333207772114</v>
+        <v>0.001508903454452629</v>
       </c>
       <c r="X11" t="n">
-        <v>0.004456854148702482</v>
+        <v>0.004431192493218526</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0001747010238558121</v>
+        <v>0.0001663307048131952</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.883246007514016</v>
+        <v>1.855692179823078</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.613105249898393</v>
+        <v>2.61310525103112</v>
       </c>
     </row>
   </sheetData>
@@ -4494,7 +4494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -4550,20 +4550,10 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>treatment of fuel cell balance of plant, 1MWe, PEM</t>
+          <t>electricity production, wind, &gt;3MW turbine, onshore</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>treatment of fuel cell stack, 1MWe, PEM</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>electricity production, wind, &gt;3MW turbine, onshore</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>direct emissions</t>
         </is>
@@ -4575,7 +4565,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4584,39 +4574,33 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.814497822647341</v>
+        <v>2.399075197032862</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3316061237056703</v>
+        <v>0.3229212258061552</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3896056037941991</v>
+        <v>0.05132008853399483</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01620977833701715</v>
+        <v>0.01620950307353838</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1051921292319186</v>
+        <v>0.1042544840978111</v>
       </c>
       <c r="I2" t="n">
-        <v>4.975707223949856e-06</v>
+        <v>4.833115662204299e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001627403646346913</v>
+        <v>0.001560167444560521</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005707042405615806</v>
+        <v>0.005413243483327283</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007200793272003519</v>
+        <v>1.897391694870997</v>
       </c>
       <c r="M2" t="n">
-        <v>7.365330589025407e-05</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.963751056513221</v>
-      </c>
-      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4626,7 +4610,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4635,39 +4619,33 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.577894528137831</v>
+        <v>2.151921314539139</v>
       </c>
       <c r="E3" t="n">
-        <v>0.321073152438842</v>
+        <v>0.3089876738270319</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3798460614300329</v>
+        <v>0.03815515100738621</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01600793572252889</v>
+        <v>0.01598108859471932</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1045926516617706</v>
+        <v>0.1035592013147198</v>
       </c>
       <c r="I3" t="n">
-        <v>4.602060934384718e-06</v>
+        <v>4.421234556262931e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001539939701799803</v>
+        <v>0.001463738360411479</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00545828895649461</v>
+        <v>0.005135570740965104</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007160930981524359</v>
+        <v>1.678634451600719</v>
       </c>
       <c r="M3" t="n">
-        <v>7.351039303148407e-05</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.748582253197428</v>
-      </c>
-      <c r="O3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4677,7 +4655,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4686,39 +4664,33 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.337984898729337</v>
+        <v>1.940612837015408</v>
       </c>
       <c r="E4" t="n">
-        <v>0.315531445530351</v>
+        <v>0.3020604124453139</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3606817838698083</v>
+        <v>0.04608639375192548</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01611010528667946</v>
+        <v>0.0160779345664153</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1041583056940041</v>
+        <v>0.103060321274879</v>
       </c>
       <c r="I4" t="n">
-        <v>4.647090185538594e-06</v>
+        <v>4.45095404836119e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001523330265072162</v>
+        <v>0.001442784611916192</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005326040036549249</v>
+        <v>0.004983406491718102</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007087949414877527</v>
+        <v>1.466897130994517</v>
       </c>
       <c r="M4" t="n">
-        <v>7.319457898364647e-05</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.533867229218629</v>
-      </c>
-      <c r="O4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4728,7 +4700,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4737,39 +4709,33 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.22777070094808</v>
+        <v>1.897108325503867</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3161557599532963</v>
+        <v>0.3073238008523994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3218901798810227</v>
+        <v>0.06267991062657753</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01633945768732269</v>
+        <v>0.01633922733447168</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1030712096470231</v>
+        <v>0.1020909024928441</v>
       </c>
       <c r="I5" t="n">
-        <v>4.771815108560678e-06</v>
+        <v>4.619787311505666e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001494918983188619</v>
+        <v>0.001428952688614446</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005060212954792497</v>
+        <v>0.004760802612241382</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007033676546520805</v>
+        <v>1.402480107332682</v>
       </c>
       <c r="M5" t="n">
-        <v>7.29631172858842e-05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.46297783810741</v>
-      </c>
-      <c r="O5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4779,7 +4745,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4788,39 +4754,33 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.746487441609786</v>
+        <v>1.538271021178349</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2775950586237396</v>
+        <v>0.2598355802687868</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1243199140497868</v>
+        <v>0.01762308555606738</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01558487775487438</v>
+        <v>0.01551713341106996</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09821226073434985</v>
+        <v>0.09762862568343909</v>
       </c>
       <c r="I6" t="n">
-        <v>3.094747329658136e-06</v>
+        <v>2.944277570154815e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009898041569473162</v>
+        <v>0.0009423391268020161</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00337400683694085</v>
+        <v>0.003187764261500282</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0006917345102333101</v>
+        <v>1.143533535676992</v>
       </c>
       <c r="M6" t="n">
-        <v>7.263890194936925e-05</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.225644025149129</v>
-      </c>
-      <c r="O6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4830,7 +4790,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4839,39 +4799,33 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.373939156152135</v>
+        <v>1.235011769076681</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2582014555696419</v>
+        <v>0.2431522460043292</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06065012256228285</v>
+        <v>0.01591071817513</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01548406397157347</v>
+        <v>0.01541053876202197</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09666454035286512</v>
+        <v>0.09623801688947552</v>
       </c>
       <c r="I7" t="n">
-        <v>2.739590787374012e-06</v>
+        <v>2.61796483398628e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008563662376528703</v>
+        <v>0.0008217061234180729</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002842717162960237</v>
+        <v>0.00270403741382146</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0006614402326322337</v>
+        <v>0.8607718856258889</v>
       </c>
       <c r="M7" t="n">
-        <v>7.198153325312249e-05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.938503716730221</v>
-      </c>
-      <c r="O7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4881,7 +4835,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4890,39 +4844,33 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.2587070758205</v>
+        <v>1.154061313732623</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2476113112014836</v>
+        <v>0.2355715821537626</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04570984582401666</v>
+        <v>0.01840883946338094</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01545173457086182</v>
+        <v>0.01540791177997902</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09579940826704388</v>
+        <v>0.09548110359410801</v>
       </c>
       <c r="I8" t="n">
-        <v>2.608428166533415e-06</v>
+        <v>2.516731355492434e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0007995718188452967</v>
+        <v>0.0007742901808642783</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002592711159407703</v>
+        <v>0.002487841511981046</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0006294382284737161</v>
+        <v>0.7859272262012726</v>
       </c>
       <c r="M8" t="n">
-        <v>7.149862428957491e-05</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.8500389362174294</v>
-      </c>
-      <c r="O8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4932,7 +4880,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4941,39 +4889,33 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.331559636120081</v>
+        <v>1.958154102761806</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3103429465136617</v>
+        <v>0.2960962596485862</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3082212686032922</v>
+        <v>0.03361273292334656</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01590309543927488</v>
+        <v>0.01586517403584985</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1033365562115365</v>
+        <v>0.1022662252574715</v>
       </c>
       <c r="I9" t="n">
-        <v>4.307340486538316e-06</v>
+        <v>4.09618002015486e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001426505046215653</v>
+        <v>0.001344411330501191</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005032638570329566</v>
+        <v>0.004691940258858576</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0007103377946539121</v>
+        <v>1.504273246881713</v>
       </c>
       <c r="M9" t="n">
-        <v>7.330762679802308e-05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.586508637320271</v>
-      </c>
-      <c r="O9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4983,7 +4925,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4992,39 +4934,33 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.753168763145599</v>
+        <v>1.521041108487125</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2836990359725868</v>
+        <v>0.2690112247431757</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1551582724409531</v>
+        <v>0.02431599742206895</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01569118613689893</v>
+        <v>0.0156233056109026</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1009095977877071</v>
+        <v>0.09985489485305293</v>
       </c>
       <c r="I10" t="n">
-        <v>3.692883241466088e-06</v>
+        <v>3.462233689234745e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00120706118425819</v>
+        <v>0.001125036137699045</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004213952061743437</v>
+        <v>0.003878231971473939</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0006935453723401096</v>
+        <v>1.107228953433882</v>
       </c>
       <c r="M10" t="n">
-        <v>7.272157731626978e-05</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.191519682090644</v>
-      </c>
-      <c r="O10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5034,7 +4970,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5043,39 +4979,33 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.474303753888949</v>
+        <v>1.322298040883365</v>
       </c>
       <c r="E11" t="n">
-        <v>0.263036471449229</v>
+        <v>0.259685820706724</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1054363032410882</v>
+        <v>0.0261699422088576</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01567014923114065</v>
+        <v>0.01561966559088739</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09660889618577376</v>
+        <v>0.09633649346690934</v>
       </c>
       <c r="I11" t="n">
-        <v>2.937482418525668e-06</v>
+        <v>2.87073393394528e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0008965931316602087</v>
+        <v>0.0008740750855103398</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002903682163948153</v>
+        <v>0.002802588209026608</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0006685920851291757</v>
+        <v>0.9208065828980021</v>
       </c>
       <c r="M11" t="n">
-        <v>7.214487662854438e-05</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.9890079704830415</v>
-      </c>
-      <c r="O11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5090,7 +5020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5106,7 +5036,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -5146,20 +5076,10 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>treatment of fuel cell balance of plant, 1MWe, PEM</t>
+          <t>electricity production, photovoltaic, 570kWp open ground installation, multi-Si</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>treatment of fuel cell stack, 1MWe, PEM</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>electricity production, photovoltaic, 570kWp open ground installation, multi-Si</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>direct emissions</t>
         </is>
@@ -5171,7 +5091,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5180,39 +5100,33 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.59114114453739</v>
+        <v>4.063558420023185</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3316061237056703</v>
+        <v>0.3229212258061552</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3896056037941991</v>
+        <v>0.05132008853399483</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01620977833701715</v>
+        <v>0.01620950307353838</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1051921292319186</v>
+        <v>0.1042544840978111</v>
       </c>
       <c r="I2" t="n">
-        <v>4.975707223949856e-06</v>
+        <v>4.833115662204299e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001627403646346913</v>
+        <v>0.001560167444560521</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005707042405615806</v>
+        <v>0.005413243483327283</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007200793272003519</v>
+        <v>3.56187495753777</v>
       </c>
       <c r="M2" t="n">
-        <v>7.365330589025407e-05</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.740394420753286</v>
-      </c>
-      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5222,7 +5136,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5231,39 +5145,33 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.889452877438803</v>
+        <v>3.359939327028494</v>
       </c>
       <c r="E3" t="n">
-        <v>0.321073152438842</v>
+        <v>0.3089876738270319</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3798460614300329</v>
+        <v>0.03815515100738621</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01600793572252889</v>
+        <v>0.01598108859471932</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1045926516617706</v>
+        <v>0.1035592013147198</v>
       </c>
       <c r="I3" t="n">
-        <v>4.602060934384718e-06</v>
+        <v>4.421234556262931e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001539939701799803</v>
+        <v>0.001463738360411479</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00545828895649461</v>
+        <v>0.005135570740965104</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007160930981524359</v>
+        <v>2.886652452639506</v>
       </c>
       <c r="M3" t="n">
-        <v>7.351039303148407e-05</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.060140590066414</v>
-      </c>
-      <c r="O3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5273,7 +5181,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5282,39 +5190,33 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.409012861269042</v>
+        <v>2.920947784216021</v>
       </c>
       <c r="E4" t="n">
-        <v>0.315531445530351</v>
+        <v>0.3020604124453139</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3606817838698083</v>
+        <v>0.04608639375192548</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01611010528667946</v>
+        <v>0.0160779345664153</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1041583056940041</v>
+        <v>0.103060321274879</v>
       </c>
       <c r="I4" t="n">
-        <v>4.647090185538594e-06</v>
+        <v>4.45095404836119e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001523330265072162</v>
+        <v>0.001442784611916192</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005326040036549249</v>
+        <v>0.004983406491718102</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007087949414877527</v>
+        <v>2.447232078195134</v>
       </c>
       <c r="M4" t="n">
-        <v>7.319457898364647e-05</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.604895191758333</v>
-      </c>
-      <c r="O4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5324,7 +5226,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5333,39 +5235,33 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.136335139886617</v>
+        <v>2.738769801379689</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3161557599532963</v>
+        <v>0.3073238008523994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3218901798810227</v>
+        <v>0.06267991062657753</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01633945768732269</v>
+        <v>0.01633922733447168</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1030712096470231</v>
+        <v>0.1020909024928441</v>
       </c>
       <c r="I5" t="n">
-        <v>4.771815108560678e-06</v>
+        <v>4.619787311505666e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001494918983188619</v>
+        <v>0.001428952688614446</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005060212954792497</v>
+        <v>0.004760802612241382</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007033676546520805</v>
+        <v>2.244141583208501</v>
       </c>
       <c r="M5" t="n">
-        <v>7.29631172858842e-05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.371542277045949</v>
-      </c>
-      <c r="O5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5375,7 +5271,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5384,39 +5280,33 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.519660853326022</v>
+        <v>2.295094453144951</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2775950586237396</v>
+        <v>0.2598355802687868</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1243199140497868</v>
+        <v>0.01762308555606738</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01558487775487438</v>
+        <v>0.01551713341106996</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09821226073434985</v>
+        <v>0.09762862568343909</v>
       </c>
       <c r="I6" t="n">
-        <v>3.094747329658136e-06</v>
+        <v>2.944277570154815e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009898041569473162</v>
+        <v>0.0009423391268020161</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00337400683694085</v>
+        <v>0.003187764261500282</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0006917345102333101</v>
+        <v>1.900356960469816</v>
       </c>
       <c r="M6" t="n">
-        <v>7.263890194936925e-05</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.99881742953661</v>
-      </c>
-      <c r="O6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5426,7 +5316,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5435,39 +5325,33 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.968607015192468</v>
+        <v>1.835517558736002</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2582014555696419</v>
+        <v>0.2431522460043292</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06065012256228285</v>
+        <v>0.01591071817513</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01548406397157347</v>
+        <v>0.01541053876202197</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09666454035286512</v>
+        <v>0.09623801688947552</v>
       </c>
       <c r="I7" t="n">
-        <v>2.739590787374012e-06</v>
+        <v>2.61796483398628e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008563662376528703</v>
+        <v>0.0008217061234180729</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002842717162960237</v>
+        <v>0.00270403741382146</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0006614402326322337</v>
+        <v>1.461277675285213</v>
       </c>
       <c r="M7" t="n">
-        <v>7.198153325312249e-05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.533171575770538</v>
-      </c>
-      <c r="O7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5477,7 +5361,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5486,39 +5370,33 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.775069135592889</v>
+        <v>1.677517961455663</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2476113112014836</v>
+        <v>0.2355715821537626</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04570984582401666</v>
+        <v>0.01840883946338094</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01545173457086182</v>
+        <v>0.01540791177997902</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09579940826704388</v>
+        <v>0.09548110359410801</v>
       </c>
       <c r="I8" t="n">
-        <v>2.608428166533415e-06</v>
+        <v>2.516731355492434e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0007995718188452967</v>
+        <v>0.0007742901808642783</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002592711159407703</v>
+        <v>0.002487841511981046</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0006294382284737161</v>
+        <v>1.309383873924316</v>
       </c>
       <c r="M8" t="n">
-        <v>7.149862428957491e-05</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.366400995989814</v>
-      </c>
-      <c r="O8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5528,7 +5406,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5537,39 +5415,33 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.587850815181613</v>
+        <v>3.116813587193979</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3103429465136617</v>
+        <v>0.2960962596485862</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3082212686032922</v>
+        <v>0.03361273292334656</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01590309543927488</v>
+        <v>0.01586517403584985</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1033365562115365</v>
+        <v>0.1022662252574715</v>
       </c>
       <c r="I9" t="n">
-        <v>4.307340486538316e-06</v>
+        <v>4.09618002015486e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001426505046215653</v>
+        <v>0.001344411330501191</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005032638570329566</v>
+        <v>0.004691940258858576</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0007103377946539121</v>
+        <v>2.662932720331191</v>
       </c>
       <c r="M9" t="n">
-        <v>7.330762679802308e-05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.842799804473671</v>
-      </c>
-      <c r="O9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5579,7 +5451,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5588,39 +5460,33 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.681348688748633</v>
+        <v>2.379589484484473</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2836990359725868</v>
+        <v>0.2690112247431757</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1551582724409531</v>
+        <v>0.02431599742206895</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01569118613689893</v>
+        <v>0.0156233056109026</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1009095977877071</v>
+        <v>0.09985489485305293</v>
       </c>
       <c r="I10" t="n">
-        <v>3.692883241466088e-06</v>
+        <v>3.462233689234745e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00120706118425819</v>
+        <v>0.001125036137699045</v>
       </c>
       <c r="K10" t="n">
-        <v>0.004213952061743437</v>
+        <v>0.003878231971473939</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0006935453723401096</v>
+        <v>1.965777329431228</v>
       </c>
       <c r="M10" t="n">
-        <v>7.272157731626978e-05</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.119699607693676</v>
-      </c>
-      <c r="O10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5630,7 +5496,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5639,39 +5505,33 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.58843781495644</v>
+        <v>1.850332406227819</v>
       </c>
       <c r="E11" t="n">
-        <v>0.263036471449229</v>
+        <v>0.259685820706724</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1054363032410882</v>
+        <v>0.0261699422088576</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01567014923114065</v>
+        <v>0.01561966559088739</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09660889618577376</v>
+        <v>0.09633649346690934</v>
       </c>
       <c r="I11" t="n">
-        <v>2.937482418525668e-06</v>
+        <v>2.87073393394528e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0008965931316602087</v>
+        <v>0.0008740750855103398</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002903682163948153</v>
+        <v>0.002802588209026608</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0006685920851291757</v>
+        <v>1.448840948242452</v>
       </c>
       <c r="M11" t="n">
-        <v>7.214487662854438e-05</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.103142031550532</v>
-      </c>
-      <c r="O11" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results.xlsx
@@ -749,67 +749,67 @@
         <v>0.02030105077470803</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04783479141759864</v>
+        <v>0.04783479141759858</v>
       </c>
       <c r="G4" t="n">
-        <v>3.876779959824269e-05</v>
+        <v>3.876779959824276e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0010849088577586</v>
+        <v>0.001084908857758603</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002121268381683213</v>
+        <v>0.0002121268381683208</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001860520502540842</v>
+        <v>0.001860520502540841</v>
       </c>
       <c r="K4" t="n">
         <v>0.003422024622077298</v>
       </c>
       <c r="L4" t="n">
-        <v>3.187772904606673e-05</v>
+        <v>3.187772904606677e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001132308690536361</v>
+        <v>0.0001132308690536359</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003919628787678779</v>
+        <v>0.003919628787678782</v>
       </c>
       <c r="O4" t="n">
-        <v>2.773715584498818e-05</v>
+        <v>2.773715584498912e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.727414790302063e-07</v>
+        <v>4.727414790302066e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.761236249791588e-05</v>
+        <v>5.761236249791589e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.275304306641996e-07</v>
+        <v>4.275304306642038e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>2.396652309378753e-06</v>
+        <v>2.396652309378754e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007768790768258387</v>
+        <v>0.0007768790768258386</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002683355646266978</v>
+        <v>0.002683355646269267</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004464258220244087</v>
+        <v>0.004464258220244084</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002649056565987174</v>
+        <v>0.0002649056565987181</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7620424084315085</v>
+        <v>-0.7620424084315078</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.013818398393047</v>
+        <v>2.013818398393048</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.925189948607354</v>
+        <v>8.92518994860735</v>
       </c>
     </row>
     <row r="5">
@@ -830,37 +830,37 @@
         <v>10.32203259234388</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02201441562572904</v>
+        <v>0.02201441562572901</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0466391030000324</v>
+        <v>0.04663910300003229</v>
       </c>
       <c r="G5" t="n">
-        <v>3.874614160360768e-05</v>
+        <v>3.874614160360763e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001059466132098395</v>
+        <v>0.001059466132098391</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002099058059956951</v>
+        <v>0.0002099058059956948</v>
       </c>
       <c r="J5" t="n">
         <v>0.001757486776130354</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003301649855513185</v>
+        <v>0.003301649855513181</v>
       </c>
       <c r="L5" t="n">
-        <v>3.147707138709098e-05</v>
+        <v>3.147707138709096e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001068647890104635</v>
+        <v>0.0001068647890104632</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003844587028155852</v>
+        <v>0.003844587028155844</v>
       </c>
       <c r="O5" t="n">
-        <v>2.678385539397262e-05</v>
+        <v>2.678385539397046e-05</v>
       </c>
       <c r="P5" t="n">
         <v>4.759677398392056e-07</v>
@@ -869,31 +869,31 @@
         <v>5.734158341098631e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>3.913830566289079e-07</v>
+        <v>3.913830566289082e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.487561949338785e-06</v>
+        <v>2.487561949338781e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0007694311655315005</v>
+        <v>0.0007694311655323289</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002563492781802208</v>
+        <v>0.002563492781803726</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004459030194024529</v>
+        <v>0.004459030194024527</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002599184462097203</v>
+        <v>0.0002599184462097179</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6936305723171284</v>
+        <v>-0.693630572317127</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.003330158067112</v>
+        <v>2.003330158067115</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.925189951429118</v>
+        <v>8.925189951429115</v>
       </c>
     </row>
     <row r="6">
@@ -1022,7 +1022,7 @@
         <v>2.766097064172988e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.631282320516487e-05</v>
+        <v>4.631282320516488e-05</v>
       </c>
       <c r="N7" t="n">
         <v>0.003020780359802032</v>
@@ -1382,7 +1382,7 @@
         <v>0.0004706528194851993</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001509076353165634</v>
+        <v>0.001509076353165635</v>
       </c>
       <c r="V11" t="n">
         <v>0.004431192493218526</v>
@@ -1746,79 +1746,79 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.46615103166139</v>
+        <v>4.466151031661391</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1297813404727585</v>
+        <v>0.1297813404727579</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02029872483175</v>
+        <v>0.02029872483175003</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04782931086403119</v>
+        <v>0.04782931086403121</v>
       </c>
       <c r="H4" t="n">
-        <v>3.876779959824269e-05</v>
+        <v>3.876779959824276e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0010849088577586</v>
+        <v>0.001084908857758603</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002121268381683213</v>
+        <v>0.0002121268381683208</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001860520502540842</v>
+        <v>0.001860520502540841</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006130564338965225</v>
+        <v>0.0006130564338965223</v>
       </c>
       <c r="M4" t="n">
         <v>0.003422024622077298</v>
       </c>
       <c r="N4" t="n">
-        <v>3.187772904606673e-05</v>
+        <v>3.187772904606677e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001132308690536361</v>
+        <v>0.0001132308690536359</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003919628787678779</v>
+        <v>0.003919628787678782</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.773715584498818e-05</v>
+        <v>2.773715584498912e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.727414790302063e-07</v>
+        <v>4.727414790302066e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.761236249791588e-05</v>
+        <v>5.761236249791589e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.275304306641996e-07</v>
+        <v>4.275304306642038e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.396377718835449e-06</v>
+        <v>2.396377718835451e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007767900678165003</v>
+        <v>0.0007767900678165008</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002683048207395486</v>
+        <v>0.002683048207397014</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004464258220244087</v>
+        <v>0.004464258220244084</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002649056565987174</v>
+        <v>0.0002649056565987181</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.3467317410415395</v>
+        <v>-0.3467317410415393</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.982294353972873</v>
+        <v>1.982294353972874</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.613105251801673</v>
+        <v>2.613105251801671</v>
       </c>
     </row>
     <row r="5">
@@ -1836,25 +1836,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.475509325197674</v>
+        <v>4.475509325197672</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1182890106177126</v>
+        <v>0.1182890106177124</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02201189337820754</v>
+        <v>0.02201189337820753</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04663375943952431</v>
+        <v>0.04663375943952425</v>
       </c>
       <c r="H5" t="n">
-        <v>3.874614160360768e-05</v>
+        <v>3.874614160360763e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001059466132098395</v>
+        <v>0.001059466132098391</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002099058059956951</v>
+        <v>0.0002099058059956948</v>
       </c>
       <c r="K5" t="n">
         <v>0.001757486776130354</v>
@@ -1863,19 +1863,19 @@
         <v>0.0006140965727205201</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003301649855513185</v>
+        <v>0.003301649855513181</v>
       </c>
       <c r="N5" t="n">
-        <v>3.147707138709098e-05</v>
+        <v>3.147707138709096e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001068647890104635</v>
+        <v>0.0001068647890104632</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003844587028155852</v>
+        <v>0.003844587028155844</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.678385539397262e-05</v>
+        <v>2.678385539397046e-05</v>
       </c>
       <c r="R5" t="n">
         <v>4.759677398392056e-07</v>
@@ -1884,31 +1884,31 @@
         <v>5.734158341098631e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>3.913830566289079e-07</v>
+        <v>3.913830566289082e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.487276943047097e-06</v>
+        <v>2.487276943047094e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0007693430098494871</v>
+        <v>0.0007693430098491073</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002563199075923047</v>
+        <v>0.002563199075923358</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004459030194024529</v>
+        <v>0.004459030194024527</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002599184462097203</v>
+        <v>0.0002599184462097179</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.3156041360928705</v>
+        <v>-0.3156041360928701</v>
       </c>
       <c r="AA5" t="n">
         <v>1.971970295161116</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.613105251728817</v>
+        <v>2.613105251728816</v>
       </c>
     </row>
     <row r="6">
@@ -2022,7 +2022,7 @@
         <v>0.01154134168185622</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01088688051161718</v>
+        <v>0.01088688051161717</v>
       </c>
       <c r="G7" t="n">
         <v>0.02304630564214194</v>
@@ -2049,7 +2049,7 @@
         <v>2.766097064172988e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>4.631282320516487e-05</v>
+        <v>4.631282320516488e-05</v>
       </c>
       <c r="P7" t="n">
         <v>0.003020780359802032</v>
@@ -2781,64 +2781,64 @@
         <v>0.02030105077470803</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04783479141759864</v>
+        <v>0.04783479141759858</v>
       </c>
       <c r="G4" t="n">
-        <v>3.876779959824269e-05</v>
+        <v>3.876779959824276e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0010849088577586</v>
+        <v>0.001084908857758603</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002121268381683213</v>
+        <v>0.0002121268381683208</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001860520502540842</v>
+        <v>0.001860520502540841</v>
       </c>
       <c r="K4" t="n">
         <v>0.003422024622077298</v>
       </c>
       <c r="L4" t="n">
-        <v>3.187772904606673e-05</v>
+        <v>3.187772904606677e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001132308690536361</v>
+        <v>0.0001132308690536359</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003919628787678779</v>
+        <v>0.003919628787678782</v>
       </c>
       <c r="O4" t="n">
-        <v>2.773715584498818e-05</v>
+        <v>2.773715584498912e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.727414790302063e-07</v>
+        <v>4.727414790302066e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.761236249791588e-05</v>
+        <v>5.761236249791589e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.275304306641996e-07</v>
+        <v>4.275304306642038e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>2.396652309378753e-06</v>
+        <v>2.396652309378754e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007768790768258387</v>
+        <v>0.0007768790768258386</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002683355646266978</v>
+        <v>0.002683355646269267</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004464258220244087</v>
+        <v>0.004464258220244084</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002649056565987174</v>
+        <v>0.0002649056565987181</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.013818398393047</v>
+        <v>2.013818398393048</v>
       </c>
       <c r="Z4" t="n">
         <v>8.925189980241583</v>
@@ -2859,40 +2859,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.0156631934553</v>
+        <v>11.01566319345529</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02201441562572904</v>
+        <v>0.02201441562572901</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0466391030000324</v>
+        <v>0.04663910300003229</v>
       </c>
       <c r="G5" t="n">
-        <v>3.874614160360768e-05</v>
+        <v>3.874614160360763e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001059466132098395</v>
+        <v>0.001059466132098391</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002099058059956951</v>
+        <v>0.0002099058059956948</v>
       </c>
       <c r="J5" t="n">
         <v>0.001757486776130354</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003301649855513185</v>
+        <v>0.003301649855513181</v>
       </c>
       <c r="L5" t="n">
-        <v>3.147707138709098e-05</v>
+        <v>3.147707138709096e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001068647890104635</v>
+        <v>0.0001068647890104632</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003844587028155852</v>
+        <v>0.003844587028155844</v>
       </c>
       <c r="O5" t="n">
-        <v>2.678385539397262e-05</v>
+        <v>2.678385539397046e-05</v>
       </c>
       <c r="P5" t="n">
         <v>4.759677398392056e-07</v>
@@ -2901,31 +2901,31 @@
         <v>5.734158341098631e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>3.913830566289079e-07</v>
+        <v>3.913830566289082e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.487561949338785e-06</v>
+        <v>2.487561949338781e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0007694311655315005</v>
+        <v>0.0007694311655323289</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002563492781802208</v>
+        <v>0.002563492781803726</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004459030194024529</v>
+        <v>0.004459030194024527</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002599184462097203</v>
+        <v>0.0002599184462097179</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.003330158067112</v>
+        <v>2.003330158067115</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.92518998022341</v>
+        <v>8.925189980223397</v>
       </c>
     </row>
     <row r="6">
@@ -3054,7 +3054,7 @@
         <v>2.766097064172988e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.631282320516487e-05</v>
+        <v>4.631282320516488e-05</v>
       </c>
       <c r="N7" t="n">
         <v>0.003020780359802032</v>
@@ -3414,7 +3414,7 @@
         <v>0.0004706528194851993</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001509076353165634</v>
+        <v>0.001509076353165635</v>
       </c>
       <c r="V11" t="n">
         <v>0.004431192493218526</v>
@@ -3778,79 +3778,79 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.812882770376468</v>
+        <v>4.812882770376472</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1297813404727585</v>
+        <v>0.1297813404727579</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02029872483175</v>
+        <v>0.02029872483175003</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04782931086403119</v>
+        <v>0.04782931086403121</v>
       </c>
       <c r="H4" t="n">
-        <v>3.876779959824269e-05</v>
+        <v>3.876779959824276e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0010849088577586</v>
+        <v>0.001084908857758603</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002121268381683213</v>
+        <v>0.0002121268381683208</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001860520502540842</v>
+        <v>0.001860520502540841</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006130564338965225</v>
+        <v>0.0006130564338965223</v>
       </c>
       <c r="M4" t="n">
         <v>0.003422024622077298</v>
       </c>
       <c r="N4" t="n">
-        <v>3.187772904606673e-05</v>
+        <v>3.187772904606677e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001132308690536361</v>
+        <v>0.0001132308690536359</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003919628787678779</v>
+        <v>0.003919628787678782</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.773715584498818e-05</v>
+        <v>2.773715584498912e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.727414790302063e-07</v>
+        <v>4.727414790302066e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.761236249791588e-05</v>
+        <v>5.761236249791589e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.275304306641996e-07</v>
+        <v>4.275304306642038e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.396377718835449e-06</v>
+        <v>2.396377718835451e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007767900678165003</v>
+        <v>0.0007767900678165008</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002683048207395486</v>
+        <v>0.002683048207397014</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004464258220244087</v>
+        <v>0.004464258220244084</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002649056565987174</v>
+        <v>0.0002649056565987181</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.982294353972873</v>
+        <v>1.982294353972874</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.613105249475212</v>
+        <v>2.613105249475213</v>
       </c>
     </row>
     <row r="5">
@@ -3868,25 +3868,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.791113459172938</v>
+        <v>4.791113459172939</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1182890106177126</v>
+        <v>0.1182890106177124</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02201189337820754</v>
+        <v>0.02201189337820753</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04663375943952431</v>
+        <v>0.04663375943952425</v>
       </c>
       <c r="H5" t="n">
-        <v>3.874614160360768e-05</v>
+        <v>3.874614160360763e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001059466132098395</v>
+        <v>0.001059466132098391</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002099058059956951</v>
+        <v>0.0002099058059956948</v>
       </c>
       <c r="K5" t="n">
         <v>0.001757486776130354</v>
@@ -3895,19 +3895,19 @@
         <v>0.0006140965727205201</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003301649855513185</v>
+        <v>0.003301649855513181</v>
       </c>
       <c r="N5" t="n">
-        <v>3.147707138709098e-05</v>
+        <v>3.147707138709096e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001068647890104635</v>
+        <v>0.0001068647890104632</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003844587028155852</v>
+        <v>0.003844587028155844</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.678385539397262e-05</v>
+        <v>2.678385539397046e-05</v>
       </c>
       <c r="R5" t="n">
         <v>4.759677398392056e-07</v>
@@ -3916,22 +3916,22 @@
         <v>5.734158341098631e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>3.913830566289079e-07</v>
+        <v>3.913830566289082e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.487276943047097e-06</v>
+        <v>2.487276943047094e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0007693430098494871</v>
+        <v>0.0007693430098491073</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002563199075923047</v>
+        <v>0.002563199075923358</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004459030194024529</v>
+        <v>0.004459030194024527</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002599184462097203</v>
+        <v>0.0002599184462097179</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
         <v>1.971970295161116</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.613105249611211</v>
+        <v>2.613105249611212</v>
       </c>
     </row>
     <row r="6">
@@ -4054,7 +4054,7 @@
         <v>0.01154134168185622</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01088688051161718</v>
+        <v>0.01088688051161717</v>
       </c>
       <c r="G7" t="n">
         <v>0.02304630564214194</v>
@@ -4081,7 +4081,7 @@
         <v>2.766097064172988e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>4.631282320516487e-05</v>
+        <v>4.631282320516488e-05</v>
       </c>
       <c r="P7" t="n">
         <v>0.003020780359802032</v>
@@ -4664,31 +4664,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.940612837015408</v>
+        <v>1.940612837015409</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3020604124453139</v>
+        <v>0.3020604124453137</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04608639375192548</v>
+        <v>0.04608639375192557</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0160779345664153</v>
+        <v>0.01607793456641514</v>
       </c>
       <c r="H4" t="n">
-        <v>0.103060321274879</v>
+        <v>0.1030603212748783</v>
       </c>
       <c r="I4" t="n">
-        <v>4.45095404836119e-06</v>
+        <v>4.450954048361191e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001442784611916192</v>
+        <v>0.001442784611916191</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004983406491718102</v>
+        <v>0.004983406491719878</v>
       </c>
       <c r="L4" t="n">
-        <v>1.466897130994517</v>
+        <v>1.466897130994521</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -4709,31 +4709,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.897108325503867</v>
+        <v>1.897108325503863</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3073238008523994</v>
+        <v>0.3073238008523996</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06267991062657753</v>
+        <v>0.06267991062657732</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01633922733447168</v>
+        <v>0.01633922733447173</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1020909024928441</v>
+        <v>0.1020909024928442</v>
       </c>
       <c r="I5" t="n">
-        <v>4.619787311505666e-06</v>
+        <v>4.61978731150566e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001428952688614446</v>
+        <v>0.00142895268861469</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004760802612241382</v>
+        <v>0.004760802612227854</v>
       </c>
       <c r="L5" t="n">
-        <v>1.402480107332682</v>
+        <v>1.402480107332679</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -4811,7 +4811,7 @@
         <v>0.01541053876202197</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09623801688947552</v>
+        <v>0.09623801688947553</v>
       </c>
       <c r="I7" t="n">
         <v>2.61796483398628e-06</v>
@@ -5190,31 +5190,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.920947784216021</v>
+        <v>2.920947784216022</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3020604124453139</v>
+        <v>0.3020604124453137</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04608639375192548</v>
+        <v>0.04608639375192557</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0160779345664153</v>
+        <v>0.01607793456641514</v>
       </c>
       <c r="H4" t="n">
-        <v>0.103060321274879</v>
+        <v>0.1030603212748783</v>
       </c>
       <c r="I4" t="n">
-        <v>4.45095404836119e-06</v>
+        <v>4.450954048361191e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001442784611916192</v>
+        <v>0.001442784611916191</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004983406491718102</v>
+        <v>0.004983406491719878</v>
       </c>
       <c r="L4" t="n">
-        <v>2.447232078195134</v>
+        <v>2.447232078195132</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -5235,31 +5235,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.738769801379689</v>
+        <v>2.738769801379676</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3073238008523994</v>
+        <v>0.3073238008523996</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06267991062657753</v>
+        <v>0.06267991062657732</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01633922733447168</v>
+        <v>0.01633922733447173</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1020909024928441</v>
+        <v>0.1020909024928442</v>
       </c>
       <c r="I5" t="n">
-        <v>4.619787311505666e-06</v>
+        <v>4.61978731150566e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001428952688614446</v>
+        <v>0.00142895268861469</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004760802612241382</v>
+        <v>0.004760802612227854</v>
       </c>
       <c r="L5" t="n">
-        <v>2.244141583208501</v>
+        <v>2.244141583208498</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -5337,7 +5337,7 @@
         <v>0.01541053876202197</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09623801688947552</v>
+        <v>0.09623801688947553</v>
       </c>
       <c r="I7" t="n">
         <v>2.61796483398628e-06</v>

--- a/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results.xlsx
@@ -581,67 +581,67 @@
         <v>0.02236365771525902</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05297266872821096</v>
+        <v>0.05297266872821105</v>
       </c>
       <c r="G2" t="n">
-        <v>3.987099995124913e-05</v>
+        <v>3.987099995124905e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001115047877934225</v>
+        <v>0.00111504787793423</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002204552969457201</v>
+        <v>0.0002204552969457206</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002082938453430552</v>
+        <v>0.002082938453430559</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003875358811066434</v>
+        <v>0.003875358811066431</v>
       </c>
       <c r="L2" t="n">
-        <v>3.281297100841981e-05</v>
+        <v>3.281297100841984e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001275696534852123</v>
+        <v>0.0001275696534852125</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004157778150090817</v>
+        <v>0.00415777815009082</v>
       </c>
       <c r="O2" t="n">
-        <v>3.146384357918766e-05</v>
+        <v>3.146384357918802e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.776230107809116e-07</v>
+        <v>4.776230107809113e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.842311683215346e-05</v>
+        <v>5.842311683215343e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>5.260035306051285e-07</v>
+        <v>5.260035306051284e-07</v>
       </c>
       <c r="S2" t="n">
         <v>2.602430330095509e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008400848151645752</v>
+        <v>0.0008400848151645762</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002914804860842479</v>
+        <v>0.002914804860838993</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004490217877914886</v>
+        <v>0.004490217877914885</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002874343647440914</v>
+        <v>0.0002874343647440926</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.834706821546644</v>
+        <v>-0.8347068215466444</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.058974611707972</v>
+        <v>2.058974611707971</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.925189945964103</v>
+        <v>8.925189945964107</v>
       </c>
     </row>
     <row r="3">
@@ -662,70 +662,70 @@
         <v>10.24329115008202</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02005735802428355</v>
+        <v>0.02005735802428361</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0494241759873064</v>
+        <v>0.04942417598730658</v>
       </c>
       <c r="G3" t="n">
-        <v>3.911753746663408e-05</v>
+        <v>3.911753746663405e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001100074248113156</v>
+        <v>0.001100074248113151</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002152958685212293</v>
+        <v>0.0002152958685212315</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001970042623700984</v>
+        <v>0.001970042623701017</v>
       </c>
       <c r="K3" t="n">
         <v>0.00366482954191396</v>
       </c>
       <c r="L3" t="n">
-        <v>3.227089836273612e-05</v>
+        <v>3.227089836273613e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001197009649556254</v>
+        <v>0.0001197009649556328</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004050736803665503</v>
+        <v>0.004050736803665514</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95705763628912e-05</v>
+        <v>2.957057636289085e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.733795125129375e-07</v>
+        <v>4.733795125129374e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.802689914056454e-05</v>
+        <v>5.80268991405646e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.025883200395271e-07</v>
+        <v>5.025883200395064e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.380649607801304e-06</v>
+        <v>2.380649607801308e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007881617926617884</v>
+        <v>0.0007881617926623795</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002765289720491218</v>
+        <v>0.002765289720492908</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004480739709009162</v>
+        <v>0.00448073970900916</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002716392972616066</v>
+        <v>0.0002716392972616134</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8035680573876948</v>
+        <v>-0.803568057387696</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.032598873332667</v>
+        <v>2.032598873332668</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.925189947026391</v>
+        <v>8.925189947026389</v>
       </c>
     </row>
     <row r="4">
@@ -743,73 +743,73 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.26406291180962</v>
+        <v>10.26406291180963</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02030105077470803</v>
+        <v>0.02030105077470801</v>
       </c>
       <c r="F4" t="n">
         <v>0.04783479141759858</v>
       </c>
       <c r="G4" t="n">
-        <v>3.876779959824276e-05</v>
+        <v>3.876779959824283e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001084908857758603</v>
+        <v>0.001084908857758598</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002121268381683208</v>
+        <v>0.0002121268381683207</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001860520502540841</v>
+        <v>0.00186052050254085</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003422024622077298</v>
+        <v>0.003422024622077294</v>
       </c>
       <c r="L4" t="n">
-        <v>3.187772904606677e-05</v>
+        <v>3.187772904606676e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001132308690536359</v>
+        <v>0.000113230869053636</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003919628787678782</v>
+        <v>0.003919628787678777</v>
       </c>
       <c r="O4" t="n">
-        <v>2.773715584498912e-05</v>
+        <v>2.773715584498885e-05</v>
       </c>
       <c r="P4" t="n">
         <v>4.727414790302066e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.761236249791589e-05</v>
+        <v>5.76123624979159e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.275304306642038e-07</v>
+        <v>4.275304306641981e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>2.396652309378754e-06</v>
+        <v>2.396652309378753e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007768790768258386</v>
+        <v>0.0007768790768258368</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002683355646269267</v>
+        <v>0.002683355646271358</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004464258220244084</v>
+        <v>0.004464258220244089</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002649056565987181</v>
+        <v>0.0002649056565987173</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7620424084315078</v>
+        <v>-0.7620424084315075</v>
       </c>
       <c r="Y4" t="n">
         <v>2.013818398393048</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.92518994860735</v>
+        <v>8.925189948607356</v>
       </c>
     </row>
     <row r="5">
@@ -827,73 +827,73 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.32203259234388</v>
+        <v>10.32203259234389</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02201441562572901</v>
+        <v>0.02201441562572896</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04663910300003229</v>
+        <v>0.04663910300003223</v>
       </c>
       <c r="G5" t="n">
-        <v>3.874614160360763e-05</v>
+        <v>3.874614160360743e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001059466132098391</v>
+        <v>0.001059466132098388</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002099058059956948</v>
+        <v>0.0002099058059956939</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001757486776130354</v>
+        <v>0.001757486776130318</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003301649855513181</v>
+        <v>0.003301649855513173</v>
       </c>
       <c r="L5" t="n">
-        <v>3.147707138709096e-05</v>
+        <v>3.147707138709094e-05</v>
       </c>
       <c r="M5" t="n">
         <v>0.0001068647890104632</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003844587028155844</v>
+        <v>0.003844587028155843</v>
       </c>
       <c r="O5" t="n">
-        <v>2.678385539397046e-05</v>
+        <v>2.678385539397113e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.759677398392056e-07</v>
+        <v>4.759677398392054e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.734158341098631e-05</v>
+        <v>5.734158341098629e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>3.913830566289082e-07</v>
+        <v>3.91383056628908e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.487561949338781e-06</v>
+        <v>2.487561949338779e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0007694311655323289</v>
+        <v>0.0007694311655323263</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002563492781803726</v>
+        <v>0.002563492781801321</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004459030194024527</v>
+        <v>0.004459030194024531</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002599184462097179</v>
+        <v>0.0002599184462097164</v>
       </c>
       <c r="X5" t="n">
         <v>-0.693630572317127</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.003330158067115</v>
+        <v>2.003330158067122</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.925189951429115</v>
+        <v>8.925189951429118</v>
       </c>
     </row>
     <row r="6">
@@ -917,58 +917,58 @@
         <v>0.01282232736138852</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02857476734967646</v>
+        <v>0.02857476734967644</v>
       </c>
       <c r="G6" t="n">
-        <v>3.533826784116757e-05</v>
+        <v>3.53382678411675e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009416546565259189</v>
+        <v>0.0009416546565259208</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001868813796941302</v>
+        <v>0.0001868813796941294</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001027832706441007</v>
+        <v>0.001027832706440999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002828996149939954</v>
+        <v>0.002828996149939956</v>
       </c>
       <c r="L6" t="n">
-        <v>2.881934551697532e-05</v>
+        <v>2.88193455169753e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>6.358601305521095e-05</v>
+        <v>6.358601305521081e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003354300193802101</v>
+        <v>0.003354300193802096</v>
       </c>
       <c r="O6" t="n">
-        <v>2.030728009792041e-05</v>
+        <v>2.03072800979204e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.606506127988125e-07</v>
+        <v>4.606506127988123e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.57899140535472e-05</v>
+        <v>5.578991405354722e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.630799976260342e-07</v>
+        <v>2.630799976260335e-07</v>
       </c>
       <c r="S6" t="n">
         <v>1.585370138917008e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005074101462132019</v>
+        <v>0.0005074101462134038</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001716477522810486</v>
+        <v>0.001716477522806819</v>
       </c>
       <c r="V6" t="n">
-        <v>0.004450086451568004</v>
+        <v>0.004450086451568002</v>
       </c>
       <c r="W6" t="n">
-        <v>0.000183226448066897</v>
+        <v>0.0001832264480668962</v>
       </c>
       <c r="X6" t="n">
         <v>-0.2205294731201305</v>
@@ -998,70 +998,70 @@
         <v>10.75895864233425</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01088812799210035</v>
+        <v>0.01088812799210038</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02304894641848435</v>
+        <v>0.0230489464184844</v>
       </c>
       <c r="G7" t="n">
-        <v>3.385458150065116e-05</v>
+        <v>3.385458150065129e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000905773015519929</v>
+        <v>0.0009057730155199294</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001776478641214097</v>
+        <v>0.0001776478641214098</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0006957893246142024</v>
+        <v>0.0006957893246142054</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002460563826394581</v>
+        <v>0.00246056382639458</v>
       </c>
       <c r="L7" t="n">
-        <v>2.766097064172988e-05</v>
+        <v>2.766097064172991e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.631282320516488e-05</v>
+        <v>4.631282320516494e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003020780359802032</v>
+        <v>0.003020780359802037</v>
       </c>
       <c r="O7" t="n">
-        <v>1.54954427050206e-05</v>
+        <v>1.549544270502011e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.569446863872299e-07</v>
+        <v>4.569446863872306e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.481852080252701e-05</v>
+        <v>5.481852080252703e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.747254058409834e-07</v>
+        <v>1.747254058409849e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.409664399378769e-06</v>
+        <v>1.409664399378771e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004424543270775139</v>
+        <v>0.000442454327077516</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0014560108781312</v>
+        <v>0.001456010878132102</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00442158411886585</v>
+        <v>0.004421584118865849</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001582081497870693</v>
+        <v>0.0001582081497870718</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.06675868800768836</v>
+        <v>-0.06675868800768843</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.852671284051603</v>
+        <v>1.852671284051605</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.925189976342095</v>
+        <v>8.925189976342093</v>
       </c>
     </row>
     <row r="8">
@@ -1079,73 +1079,73 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.77005952698809</v>
+        <v>10.77005952698808</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01058181405154486</v>
+        <v>0.01058181405154487</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02091707121689519</v>
+        <v>0.0209170712168952</v>
       </c>
       <c r="G8" t="n">
-        <v>3.337934035364732e-05</v>
+        <v>3.337934035364725e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008891996048512561</v>
+        <v>0.0008891996048512565</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001737624900552019</v>
+        <v>0.0001737624900552022</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0005963807786516016</v>
+        <v>0.0005963807786516079</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002334128841608283</v>
+        <v>0.002334128841608282</v>
       </c>
       <c r="L8" t="n">
         <v>2.71040534223464e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.111266534990582e-05</v>
+        <v>4.111266534990594e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002912538779137925</v>
+        <v>0.002912538779137927</v>
       </c>
       <c r="O8" t="n">
-        <v>1.343481035649852e-05</v>
+        <v>1.343481035649853e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.556831621244479e-07</v>
+        <v>4.556831621244476e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.439842899292991e-05</v>
+        <v>5.439842899292986e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.373230990401052e-07</v>
+        <v>1.373230990401051e-07</v>
       </c>
       <c r="S8" t="n">
         <v>1.355154411771046e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0004169228282149806</v>
+        <v>0.0004169228282150299</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001339598441213309</v>
+        <v>0.001339598441209462</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004410358447779871</v>
+        <v>0.004410358447779869</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0001472081074076261</v>
+        <v>0.0001472081074076266</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.02526993019331653</v>
+        <v>-0.02526993019331648</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.825249118300723</v>
+        <v>1.825249118300722</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.925189977834176</v>
+        <v>8.925189977834174</v>
       </c>
     </row>
     <row r="9">
@@ -1163,73 +1163,73 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.34455406936769</v>
+        <v>10.34455406936768</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01811068851555999</v>
+        <v>0.01811068851556</v>
       </c>
       <c r="F9" t="n">
         <v>0.04433260708189948</v>
       </c>
       <c r="G9" t="n">
-        <v>3.806921752945501e-05</v>
+        <v>3.806921752945503e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001074485115876923</v>
+        <v>0.001074485115876921</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002085693333614094</v>
+        <v>0.0002085693333614085</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001697622871425569</v>
+        <v>0.001697622871425561</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00333810811535771</v>
+        <v>0.003338108115357711</v>
       </c>
       <c r="L9" t="n">
-        <v>3.149480810926924e-05</v>
+        <v>3.149480810926923e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001036498255976518</v>
+        <v>0.0001036498255976517</v>
       </c>
       <c r="N9" t="n">
         <v>0.003808397360833145</v>
       </c>
       <c r="O9" t="n">
-        <v>2.716550998084804e-05</v>
+        <v>2.716550998084769e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.70206826371508e-07</v>
+        <v>4.702068263715078e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.748183282585366e-05</v>
+        <v>5.748183282585368e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.847722732011943e-07</v>
+        <v>4.847722732011965e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>2.205621356290984e-06</v>
+        <v>2.205621356290985e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0007239091855345023</v>
+        <v>0.0007239091855345004</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002526413289075408</v>
+        <v>0.002526413289078121</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004470482136277214</v>
+        <v>0.004470482136277212</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0002519523378874566</v>
+        <v>0.0002519523378874558</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6520333968600271</v>
+        <v>-0.6520333968600263</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.99059325610557</v>
+        <v>1.990593256105569</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.925189952984555</v>
+        <v>8.925189952984546</v>
       </c>
     </row>
     <row r="10">
@@ -1247,70 +1247,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.62969562273195</v>
+        <v>10.62969562273194</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01410898328530927</v>
+        <v>0.01410898328530928</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03423095481113834</v>
+        <v>0.03423095481113831</v>
       </c>
       <c r="G10" t="n">
-        <v>3.597559159370257e-05</v>
+        <v>3.597559159370261e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001019814762690255</v>
+        <v>0.001019814762690261</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001945659832336154</v>
+        <v>0.0001945659832336182</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001086276849466629</v>
+        <v>0.001086276849466628</v>
       </c>
       <c r="K10" t="n">
-        <v>0.002873608041095243</v>
+        <v>0.002873608041095242</v>
       </c>
       <c r="L10" t="n">
-        <v>2.992015170139257e-05</v>
+        <v>2.992015170139258e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>7.148531142234192e-05</v>
+        <v>7.148531142234184e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003407950193712568</v>
+        <v>0.003407950193712574</v>
       </c>
       <c r="O10" t="n">
-        <v>2.186257952717815e-05</v>
+        <v>2.186257952717819e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>4.633067793183591e-07</v>
+        <v>4.633067793183587e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.626430326440551e-05</v>
+        <v>5.626430326440552e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>2.961891139972981e-07</v>
+        <v>2.961891139972918e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.864267812418454e-06</v>
+        <v>1.864267812418455e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0006057848336001974</v>
+        <v>0.0006057848336006019</v>
       </c>
       <c r="U10" t="n">
-        <v>0.00208826546168496</v>
+        <v>0.002088265461684969</v>
       </c>
       <c r="V10" t="n">
         <v>0.0044435029580982</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0002126036878080657</v>
+        <v>0.0002126036878080709</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2785827505310934</v>
+        <v>-0.2785827505310927</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.918597962742309</v>
+        <v>1.918597962742308</v>
       </c>
       <c r="Z10" t="n">
         <v>8.925189967951678</v>
@@ -1331,73 +1331,73 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.81399469658047</v>
+        <v>10.81399469658048</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01268189202413571</v>
+        <v>0.01268189202413572</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02458622888367573</v>
+        <v>0.02458622888367575</v>
       </c>
       <c r="G11" t="n">
-        <v>3.45163181055891e-05</v>
+        <v>3.45163181055892e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.000902060096143756</v>
+        <v>0.0009020600961437553</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001806862074612486</v>
+        <v>0.0001806862074612488</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0007350539239766847</v>
+        <v>0.0007350539239766871</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002595983512692795</v>
+        <v>0.002595983512692792</v>
       </c>
       <c r="L11" t="n">
         <v>2.79745967271702e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.773149134990697e-05</v>
+        <v>4.773149134990694e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003158234078010126</v>
+        <v>0.003158234078010134</v>
       </c>
       <c r="O11" t="n">
-        <v>1.740378168929434e-05</v>
+        <v>1.740378168929433e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>4.618835132529723e-07</v>
+        <v>4.618835132529721e-07</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.511580607320554e-05</v>
+        <v>5.511580607320561e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.37630699118626e-07</v>
+        <v>2.376306991186257e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.545769971481762e-06</v>
+        <v>1.545769971481763e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0004706528194851993</v>
+        <v>0.0004706528194848813</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001509076353165635</v>
+        <v>0.001509076353162917</v>
       </c>
       <c r="V11" t="n">
-        <v>0.004431192493218526</v>
+        <v>0.00443119249321853</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0001663307048131952</v>
+        <v>0.0001663307048131924</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.04800055357829988</v>
+        <v>-0.04800055357829974</v>
       </c>
       <c r="Y11" t="n">
         <v>1.88520289430888</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.925189977474984</v>
+        <v>8.925189977474993</v>
       </c>
     </row>
   </sheetData>
@@ -1566,79 +1566,79 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.498372411198862</v>
+        <v>4.498372411198861</v>
       </c>
       <c r="E2" t="n">
-        <v>0.142076449933259</v>
+        <v>0.1420764499332593</v>
       </c>
       <c r="F2" t="n">
         <v>0.02236109545418415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05296659951498824</v>
+        <v>0.05296659951498836</v>
       </c>
       <c r="H2" t="n">
-        <v>3.987099995124913e-05</v>
+        <v>3.987099995124905e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001115047877934225</v>
+        <v>0.00111504787793423</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002204552969457201</v>
+        <v>0.0002204552969457206</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002082938453430552</v>
+        <v>0.002082938453430559</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006361631112596295</v>
+        <v>0.0006361631112596299</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003875358811066434</v>
+        <v>0.003875358811066431</v>
       </c>
       <c r="N2" t="n">
-        <v>3.281297100841981e-05</v>
+        <v>3.281297100841984e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001275696534852123</v>
+        <v>0.0001275696534852125</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004157778150090817</v>
+        <v>0.00415777815009082</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.146384357918766e-05</v>
+        <v>3.146384357918802e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>4.776230107809116e-07</v>
+        <v>4.776230107809113e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>5.842311683215346e-05</v>
+        <v>5.842311683215343e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>5.260035306051285e-07</v>
+        <v>5.260035306051284e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>2.602132163041634e-06</v>
+        <v>2.602132163041635e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008399885645132336</v>
+        <v>0.0008399885645132345</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002914470904245384</v>
+        <v>0.002914470904246001</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004490217877914886</v>
+        <v>0.004490217877914885</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002874343647440914</v>
+        <v>0.0002874343647440926</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.3797942821710154</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.026743697951657</v>
+        <v>2.026743697951656</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.613105250760084</v>
+        <v>2.613105250760082</v>
       </c>
     </row>
     <row r="3">
@@ -1656,79 +1656,79 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.474734471092456</v>
+        <v>4.474734471092455</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1367993228268539</v>
+        <v>0.1367993228268543</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02005506000182299</v>
+        <v>0.02005506000182306</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04941851333391129</v>
+        <v>0.0494185133339114</v>
       </c>
       <c r="H3" t="n">
-        <v>3.911753746663408e-05</v>
+        <v>3.911753746663405e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001100074248113156</v>
+        <v>0.001100074248113151</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002152958685212293</v>
+        <v>0.0002152958685212315</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001970042623700984</v>
+        <v>0.001970042623701017</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006130805146831815</v>
+        <v>0.0006130805146831824</v>
       </c>
       <c r="M3" t="n">
         <v>0.00366482954191396</v>
       </c>
       <c r="N3" t="n">
-        <v>3.227089836273612e-05</v>
+        <v>3.227089836273613e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001197009649556254</v>
+        <v>0.0001197009649556328</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004050736803665503</v>
+        <v>0.004050736803665514</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.95705763628912e-05</v>
+        <v>2.957057636289085e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>4.733795125129375e-07</v>
+        <v>4.733795125129374e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>5.802689914056454e-05</v>
+        <v>5.80268991405646e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.025883200395271e-07</v>
+        <v>5.025883200395064e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>2.380376850728175e-06</v>
+        <v>2.38037685072818e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007880714909629381</v>
+        <v>0.0007880714909636279</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002764972894223283</v>
+        <v>0.002764972894225507</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004480739709009162</v>
+        <v>0.00448073970900916</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002716392972616066</v>
+        <v>0.0002716392972616134</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.3656260445621183</v>
+        <v>-0.3656260445621189</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.000780841864457</v>
+        <v>2.000780841864456</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.613105251414503</v>
+        <v>2.6131052514145</v>
       </c>
     </row>
     <row r="4">
@@ -1746,79 +1746,79 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.466151031661391</v>
+        <v>4.466151031661396</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1297813404727579</v>
+        <v>0.1297813404727581</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02029872483175003</v>
+        <v>0.02029872483175</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04782931086403121</v>
+        <v>0.04782931086403115</v>
       </c>
       <c r="H4" t="n">
-        <v>3.876779959824276e-05</v>
+        <v>3.876779959824283e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001084908857758603</v>
+        <v>0.001084908857758598</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002121268381683208</v>
+        <v>0.0002121268381683207</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001860520502540841</v>
+        <v>0.00186052050254085</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006130564338965223</v>
+        <v>0.0006130564338965215</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003422024622077298</v>
+        <v>0.003422024622077294</v>
       </c>
       <c r="N4" t="n">
-        <v>3.187772904606677e-05</v>
+        <v>3.187772904606676e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001132308690536359</v>
+        <v>0.000113230869053636</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003919628787678782</v>
+        <v>0.003919628787678777</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.773715584498912e-05</v>
+        <v>2.773715584498885e-05</v>
       </c>
       <c r="R4" t="n">
         <v>4.727414790302066e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.761236249791589e-05</v>
+        <v>5.76123624979159e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.275304306642038e-07</v>
+        <v>4.275304306641981e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.396377718835451e-06</v>
+        <v>2.396377718835448e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007767900678165008</v>
+        <v>0.0007767900678164979</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002683048207397014</v>
+        <v>0.002683048207399992</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004464258220244084</v>
+        <v>0.004464258220244089</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002649056565987181</v>
+        <v>0.0002649056565987173</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.3467317410415393</v>
+        <v>-0.3467317410415388</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.982294353972874</v>
+        <v>1.982294353972873</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.613105251801671</v>
+        <v>2.613105251801673</v>
       </c>
     </row>
     <row r="5">
@@ -1836,79 +1836,79 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.475509325197672</v>
+        <v>4.475509325197701</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1182890106177124</v>
+        <v>0.1182890106177125</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02201189337820753</v>
+        <v>0.02201189337820745</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04663375943952425</v>
+        <v>0.04663375943952414</v>
       </c>
       <c r="H5" t="n">
-        <v>3.874614160360763e-05</v>
+        <v>3.874614160360743e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001059466132098391</v>
+        <v>0.001059466132098388</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002099058059956948</v>
+        <v>0.0002099058059956939</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001757486776130354</v>
+        <v>0.001757486776130318</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006140965727205201</v>
+        <v>0.0006140965727205192</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003301649855513181</v>
+        <v>0.003301649855513173</v>
       </c>
       <c r="N5" t="n">
-        <v>3.147707138709096e-05</v>
+        <v>3.147707138709094e-05</v>
       </c>
       <c r="O5" t="n">
         <v>0.0001068647890104632</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003844587028155844</v>
+        <v>0.003844587028155843</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.678385539397046e-05</v>
+        <v>2.678385539397113e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.759677398392056e-07</v>
+        <v>4.759677398392054e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>5.734158341098631e-05</v>
+        <v>5.734158341098629e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>3.913830566289082e-07</v>
+        <v>3.91383056628908e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.487276943047094e-06</v>
+        <v>2.487276943047091e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0007693430098491073</v>
+        <v>0.0007693430098491055</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002563199075923358</v>
+        <v>0.002563199075922849</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004459030194024527</v>
+        <v>0.004459030194024531</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002599184462097179</v>
+        <v>0.0002599184462097164</v>
       </c>
       <c r="Z5" t="n">
         <v>-0.3156041360928701</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.971970295161116</v>
+        <v>1.971970295161123</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.613105251728816</v>
+        <v>2.613105251728838</v>
       </c>
     </row>
     <row r="6">
@@ -1926,70 +1926,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.488995850941786</v>
+        <v>4.488995850941781</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03780075441389463</v>
+        <v>0.03780075441389469</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01282085827477018</v>
+        <v>0.01282085827477019</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0285714934659927</v>
+        <v>0.02857149346599268</v>
       </c>
       <c r="H6" t="n">
-        <v>3.533826784116757e-05</v>
+        <v>3.53382678411675e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009416546565259189</v>
+        <v>0.0009416546565259208</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001868813796941302</v>
+        <v>0.0001868813796941294</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001027832706441007</v>
+        <v>0.001027832706440999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004899292141898202</v>
+        <v>0.0004899292141898203</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002828996149939954</v>
+        <v>0.002828996149939956</v>
       </c>
       <c r="N6" t="n">
-        <v>2.881934551697532e-05</v>
+        <v>2.88193455169753e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>6.358601305521095e-05</v>
+        <v>6.358601305521081e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003354300193802101</v>
+        <v>0.003354300193802096</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.030728009792041e-05</v>
+        <v>2.03072800979204e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.606506127988125e-07</v>
+        <v>4.606506127988123e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>5.57899140535472e-05</v>
+        <v>5.578991405354722e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.630799976260342e-07</v>
+        <v>2.630799976260335e-07</v>
       </c>
       <c r="U6" t="n">
         <v>1.585188499032877e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005073520109438052</v>
+        <v>0.0005073520109439788</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001716280861621284</v>
+        <v>0.001716280861616663</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004450086451568004</v>
+        <v>0.004450086451568002</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.000183226448066897</v>
+        <v>0.0001832264480668962</v>
       </c>
       <c r="Z6" t="n">
         <v>-0.1003416178940761</v>
@@ -1998,7 +1998,7 @@
         <v>1.881146421412698</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.61310525145604</v>
+        <v>2.613105251456039</v>
       </c>
     </row>
     <row r="7">
@@ -2016,79 +2016,79 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.466257644770501</v>
+        <v>4.466257644770502</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01154134168185622</v>
+        <v>0.01154134168185628</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01088688051161717</v>
+        <v>0.0108868805116172</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02304630564214194</v>
+        <v>0.023046305642142</v>
       </c>
       <c r="H7" t="n">
-        <v>3.385458150065116e-05</v>
+        <v>3.385458150065129e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000905773015519929</v>
+        <v>0.0009057730155199294</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001776478641214097</v>
+        <v>0.0001776478641214098</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0006957893246142024</v>
+        <v>0.0006957893246142054</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004646888140058464</v>
+        <v>0.0004646888140058468</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002460563826394581</v>
+        <v>0.00246056382639458</v>
       </c>
       <c r="N7" t="n">
-        <v>2.766097064172988e-05</v>
+        <v>2.766097064172991e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>4.631282320516488e-05</v>
+        <v>4.631282320516494e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003020780359802032</v>
+        <v>0.003020780359802037</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.54954427050206e-05</v>
+        <v>1.549544270502011e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>4.569446863872299e-07</v>
+        <v>4.569446863872306e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>5.481852080252701e-05</v>
+        <v>5.481852080252703e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.747254058409834e-07</v>
+        <v>1.747254058409849e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>1.409502890547562e-06</v>
+        <v>1.409502890547564e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0004424036339612939</v>
+        <v>0.0004424036339612934</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001455844059266967</v>
+        <v>0.001455844059265567</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00442158411886585</v>
+        <v>0.004421584118865849</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001582081497870693</v>
+        <v>0.0001582081497870718</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.03037541725558051</v>
+        <v>-0.0303754172555805</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.823669815050713</v>
+        <v>1.823669815050712</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.613105252461576</v>
+        <v>2.61310525246158</v>
       </c>
     </row>
     <row r="8">
@@ -2106,76 +2106,76 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.448086169331719</v>
+        <v>4.448086169331718</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004460776312794375</v>
+        <v>0.004460776312794462</v>
       </c>
       <c r="F8" t="n">
-        <v>0.010580601666228</v>
+        <v>0.01058060166622801</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0209146746949102</v>
+        <v>0.02091467469491021</v>
       </c>
       <c r="H8" t="n">
-        <v>3.337934035364732e-05</v>
+        <v>3.337934035364725e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008891996048512561</v>
+        <v>0.0008891996048512565</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001737624900552019</v>
+        <v>0.0001737624900552022</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0005963807786516016</v>
+        <v>0.0005963807786516079</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004545762296667365</v>
+        <v>0.0004545762296667364</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002334128841608283</v>
+        <v>0.002334128841608282</v>
       </c>
       <c r="N8" t="n">
         <v>2.71040534223464e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>4.111266534990582e-05</v>
+        <v>4.111266534990594e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002912538779137925</v>
+        <v>0.002912538779137927</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.343481035649852e-05</v>
+        <v>1.343481035649853e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>4.556831621244479e-07</v>
+        <v>4.556831621244476e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>5.439842899292991e-05</v>
+        <v>5.439842899292986e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.373230990401052e-07</v>
+        <v>1.373230990401051e-07</v>
       </c>
       <c r="U8" t="n">
         <v>1.354999148287588e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>0.000416875060307444</v>
+        <v>0.0004168750603074418</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001339444960014497</v>
+        <v>0.001339444960014767</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004410358447779871</v>
+        <v>0.004410358447779869</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001472081074076261</v>
+        <v>0.0001472081074076266</v>
       </c>
       <c r="Z8" t="n">
         <v>-0.01149789932290151</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.796676912222405</v>
+        <v>1.796676912222403</v>
       </c>
       <c r="AB8" t="n">
         <v>2.613105253154918</v>
@@ -2196,79 +2196,79 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.468268125441164</v>
+        <v>4.468268125441165</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1110232245261395</v>
+        <v>0.1110232245261394</v>
       </c>
       <c r="F9" t="n">
         <v>0.01810861352797018</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04432752778248799</v>
+        <v>0.04432752778248802</v>
       </c>
       <c r="H9" t="n">
-        <v>3.806921752945501e-05</v>
+        <v>3.806921752945503e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001074485115876923</v>
+        <v>0.001074485115876921</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002085693333614094</v>
+        <v>0.0002085693333614085</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001697622871425569</v>
+        <v>0.001697622871425561</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0005874317082775567</v>
+        <v>0.000587431708277557</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00333810811535771</v>
+        <v>0.003338108115357711</v>
       </c>
       <c r="N9" t="n">
-        <v>3.149480810926924e-05</v>
+        <v>3.149480810926923e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0001036498255976518</v>
+        <v>0.0001036498255976517</v>
       </c>
       <c r="P9" t="n">
         <v>0.003808397360833145</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.716550998084804e-05</v>
+        <v>2.716550998084769e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.70206826371508e-07</v>
+        <v>4.702068263715078e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>5.748183282585366e-05</v>
+        <v>5.748183282585368e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.847722732011943e-07</v>
+        <v>4.847722732011965e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>2.205368652649252e-06</v>
+        <v>2.205368652649251e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0007238262454201688</v>
+        <v>0.0007238262454201686</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002526123831492402</v>
+        <v>0.002526123831489725</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004470482136277214</v>
+        <v>0.004470482136277212</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002519523378874566</v>
+        <v>0.0002519523378874558</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.2966772877848641</v>
+        <v>-0.296677287784864</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95943277496286</v>
+        <v>1.959432774962861</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.613105251828566</v>
+        <v>2.613105251828569</v>
       </c>
     </row>
     <row r="10">
@@ -2289,73 +2289,73 @@
         <v>4.487410812502763</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04747377678283905</v>
+        <v>0.04747377678283894</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01410736678325322</v>
+        <v>0.01410736678325323</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03422703288368871</v>
+        <v>0.0342270328836887</v>
       </c>
       <c r="H10" t="n">
-        <v>3.597559159370257e-05</v>
+        <v>3.597559159370261e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001019814762690255</v>
+        <v>0.001019814762690261</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001945659832336154</v>
+        <v>0.0001945659832336182</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001086276849466629</v>
+        <v>0.001086276849466628</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0005387477895499014</v>
+        <v>0.0005387477895499018</v>
       </c>
       <c r="M10" t="n">
-        <v>0.002873608041095243</v>
+        <v>0.002873608041095242</v>
       </c>
       <c r="N10" t="n">
-        <v>2.992015170139257e-05</v>
+        <v>2.992015170139258e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>7.148531142234192e-05</v>
+        <v>7.148531142234184e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003407950193712568</v>
+        <v>0.003407950193712574</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.186257952717815e-05</v>
+        <v>2.186257952717819e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.633067793183591e-07</v>
+        <v>4.633067793183587e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>5.626430326440551e-05</v>
+        <v>5.626430326440552e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.961891139972981e-07</v>
+        <v>2.961891139972918e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>1.864054218519384e-06</v>
+        <v>1.864054218519383e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0006057154272930828</v>
+        <v>0.0006057154272933402</v>
       </c>
       <c r="W10" t="n">
-        <v>0.002088026203806194</v>
+        <v>0.0020880262038062</v>
       </c>
       <c r="X10" t="n">
         <v>0.0044435029580982</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0002126036878080657</v>
+        <v>0.0002126036878080709</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.1267560453946425</v>
+        <v>-0.1267560453946422</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.888564486312557</v>
+        <v>1.888564486312555</v>
       </c>
       <c r="AB10" t="n">
         <v>2.613105251750693</v>
@@ -2379,76 +2379,76 @@
         <v>4.507538323009507</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008507665310968386</v>
+        <v>0.008507665310968396</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01268043902755069</v>
+        <v>0.0126804390275507</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02458341197697613</v>
+        <v>0.02458341197697617</v>
       </c>
       <c r="H11" t="n">
-        <v>3.45163181055891e-05</v>
+        <v>3.45163181055892e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000902060096143756</v>
+        <v>0.0009020600961437553</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001806862074612486</v>
+        <v>0.0001806862074612488</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0007350539239766847</v>
+        <v>0.0007350539239766871</v>
       </c>
       <c r="L11" t="n">
-        <v>0.000475751125884555</v>
+        <v>0.0004757511258845546</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002595983512692795</v>
+        <v>0.002595983512692792</v>
       </c>
       <c r="N11" t="n">
         <v>2.79745967271702e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>4.773149134990697e-05</v>
+        <v>4.773149134990694e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.003158234078010126</v>
+        <v>0.003158234078010134</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.740378168929434e-05</v>
+        <v>1.740378168929433e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>4.618835132529723e-07</v>
+        <v>4.618835132529721e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>5.511580607320554e-05</v>
+        <v>5.511580607320561e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.37630699118626e-07</v>
+        <v>2.376306991186257e-07</v>
       </c>
       <c r="U11" t="n">
-        <v>1.545592868689409e-06</v>
+        <v>1.545592868689408e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0004705988955958132</v>
+        <v>0.0004705988955957526</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001508903454452629</v>
+        <v>0.00150890345445105</v>
       </c>
       <c r="X11" t="n">
-        <v>0.004431192493218526</v>
+        <v>0.00443119249321853</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0001663307048131952</v>
+        <v>0.0001663307048131924</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.02184040590000499</v>
+        <v>-0.02184040590000487</v>
       </c>
       <c r="AA11" t="n">
         <v>1.855692179823078</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.613105251177663</v>
+        <v>2.613105251177664</v>
       </c>
     </row>
   </sheetData>
@@ -2613,67 +2613,67 @@
         <v>0.02236365771525902</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05297266872821096</v>
+        <v>0.05297266872821105</v>
       </c>
       <c r="G2" t="n">
-        <v>3.987099995124913e-05</v>
+        <v>3.987099995124905e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001115047877934225</v>
+        <v>0.00111504787793423</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002204552969457201</v>
+        <v>0.0002204552969457206</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002082938453430552</v>
+        <v>0.002082938453430559</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003875358811066434</v>
+        <v>0.003875358811066431</v>
       </c>
       <c r="L2" t="n">
-        <v>3.281297100841981e-05</v>
+        <v>3.281297100841984e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001275696534852123</v>
+        <v>0.0001275696534852125</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004157778150090817</v>
+        <v>0.00415777815009082</v>
       </c>
       <c r="O2" t="n">
-        <v>3.146384357918766e-05</v>
+        <v>3.146384357918802e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.776230107809116e-07</v>
+        <v>4.776230107809113e-07</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.842311683215346e-05</v>
+        <v>5.842311683215343e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>5.260035306051285e-07</v>
+        <v>5.260035306051284e-07</v>
       </c>
       <c r="S2" t="n">
         <v>2.602430330095509e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008400848151645752</v>
+        <v>0.0008400848151645762</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002914804860842479</v>
+        <v>0.002914804860838993</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004490217877914886</v>
+        <v>0.004490217877914885</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002874343647440914</v>
+        <v>0.0002874343647440926</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.058974611707972</v>
+        <v>2.058974611707971</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.925189980614809</v>
+        <v>8.925189980614814</v>
       </c>
     </row>
     <row r="3">
@@ -2694,67 +2694,67 @@
         <v>11.04685924082778</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02005735802428355</v>
+        <v>0.02005735802428361</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0494241759873064</v>
+        <v>0.04942417598730658</v>
       </c>
       <c r="G3" t="n">
-        <v>3.911753746663408e-05</v>
+        <v>3.911753746663405e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001100074248113156</v>
+        <v>0.001100074248113151</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002152958685212293</v>
+        <v>0.0002152958685212315</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001970042623700984</v>
+        <v>0.001970042623701017</v>
       </c>
       <c r="K3" t="n">
         <v>0.00366482954191396</v>
       </c>
       <c r="L3" t="n">
-        <v>3.227089836273612e-05</v>
+        <v>3.227089836273613e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001197009649556254</v>
+        <v>0.0001197009649556328</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004050736803665503</v>
+        <v>0.004050736803665514</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95705763628912e-05</v>
+        <v>2.957057636289085e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>4.733795125129375e-07</v>
+        <v>4.733795125129374e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.802689914056454e-05</v>
+        <v>5.80268991405646e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.025883200395271e-07</v>
+        <v>5.025883200395064e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>2.380649607801304e-06</v>
+        <v>2.380649607801308e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007881617926617884</v>
+        <v>0.0007881617926623795</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002765289720491218</v>
+        <v>0.002765289720492908</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004480739709009162</v>
+        <v>0.00448073970900916</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002716392972616066</v>
+        <v>0.0002716392972616134</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.032598873332667</v>
+        <v>2.032598873332668</v>
       </c>
       <c r="Z3" t="n">
         <v>8.925189980384454</v>
@@ -2778,61 +2778,61 @@
         <v>11.02610535187536</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02030105077470803</v>
+        <v>0.02030105077470801</v>
       </c>
       <c r="F4" t="n">
         <v>0.04783479141759858</v>
       </c>
       <c r="G4" t="n">
-        <v>3.876779959824276e-05</v>
+        <v>3.876779959824283e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001084908857758603</v>
+        <v>0.001084908857758598</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002121268381683208</v>
+        <v>0.0002121268381683207</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001860520502540841</v>
+        <v>0.00186052050254085</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003422024622077298</v>
+        <v>0.003422024622077294</v>
       </c>
       <c r="L4" t="n">
-        <v>3.187772904606677e-05</v>
+        <v>3.187772904606676e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001132308690536359</v>
+        <v>0.000113230869053636</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003919628787678782</v>
+        <v>0.003919628787678777</v>
       </c>
       <c r="O4" t="n">
-        <v>2.773715584498912e-05</v>
+        <v>2.773715584498885e-05</v>
       </c>
       <c r="P4" t="n">
         <v>4.727414790302066e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.761236249791589e-05</v>
+        <v>5.76123624979159e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.275304306642038e-07</v>
+        <v>4.275304306641981e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>2.396652309378754e-06</v>
+        <v>2.396652309378753e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007768790768258386</v>
+        <v>0.0007768790768258368</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002683355646269267</v>
+        <v>0.002683355646271358</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004464258220244084</v>
+        <v>0.004464258220244089</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002649056565987181</v>
+        <v>0.0002649056565987173</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -2859,73 +2859,73 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.01566319345529</v>
+        <v>11.01566319345531</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02201441562572901</v>
+        <v>0.02201441562572896</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04663910300003229</v>
+        <v>0.04663910300003223</v>
       </c>
       <c r="G5" t="n">
-        <v>3.874614160360763e-05</v>
+        <v>3.874614160360743e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001059466132098391</v>
+        <v>0.001059466132098388</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002099058059956948</v>
+        <v>0.0002099058059956939</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001757486776130354</v>
+        <v>0.001757486776130318</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003301649855513181</v>
+        <v>0.003301649855513173</v>
       </c>
       <c r="L5" t="n">
-        <v>3.147707138709096e-05</v>
+        <v>3.147707138709094e-05</v>
       </c>
       <c r="M5" t="n">
         <v>0.0001068647890104632</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003844587028155844</v>
+        <v>0.003844587028155843</v>
       </c>
       <c r="O5" t="n">
-        <v>2.678385539397046e-05</v>
+        <v>2.678385539397113e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.759677398392056e-07</v>
+        <v>4.759677398392054e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.734158341098631e-05</v>
+        <v>5.734158341098629e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>3.913830566289082e-07</v>
+        <v>3.91383056628908e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.487561949338781e-06</v>
+        <v>2.487561949338779e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0007694311655323289</v>
+        <v>0.0007694311655323263</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002563492781803726</v>
+        <v>0.002563492781801321</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004459030194024527</v>
+        <v>0.004459030194024531</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002599184462097179</v>
+        <v>0.0002599184462097164</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.003330158067115</v>
+        <v>2.003330158067122</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.925189980223397</v>
+        <v>8.925189980223411</v>
       </c>
     </row>
     <row r="6">
@@ -2943,64 +2943,64 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.89305201968298</v>
+        <v>10.89305201968297</v>
       </c>
       <c r="E6" t="n">
         <v>0.01282232736138852</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02857476734967646</v>
+        <v>0.02857476734967644</v>
       </c>
       <c r="G6" t="n">
-        <v>3.533826784116757e-05</v>
+        <v>3.53382678411675e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009416546565259189</v>
+        <v>0.0009416546565259208</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001868813796941302</v>
+        <v>0.0001868813796941294</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001027832706441007</v>
+        <v>0.001027832706440999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002828996149939954</v>
+        <v>0.002828996149939956</v>
       </c>
       <c r="L6" t="n">
-        <v>2.881934551697532e-05</v>
+        <v>2.88193455169753e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>6.358601305521095e-05</v>
+        <v>6.358601305521081e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003354300193802101</v>
+        <v>0.003354300193802096</v>
       </c>
       <c r="O6" t="n">
-        <v>2.030728009792041e-05</v>
+        <v>2.03072800979204e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.606506127988125e-07</v>
+        <v>4.606506127988123e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.57899140535472e-05</v>
+        <v>5.578991405354722e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.630799976260342e-07</v>
+        <v>2.630799976260335e-07</v>
       </c>
       <c r="S6" t="n">
         <v>1.585370138917008e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005074101462132019</v>
+        <v>0.0005074101462134038</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001716477522810486</v>
+        <v>0.001716477522806819</v>
       </c>
       <c r="V6" t="n">
-        <v>0.004450086451568004</v>
+        <v>0.004450086451568002</v>
       </c>
       <c r="W6" t="n">
-        <v>0.000183226448066897</v>
+        <v>0.0001832264480668962</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
         <v>1.911061929788442</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.925189979607099</v>
+        <v>8.925189979607095</v>
       </c>
     </row>
     <row r="7">
@@ -3030,70 +3030,70 @@
         <v>10.82571733311326</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01088812799210035</v>
+        <v>0.01088812799210038</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02304894641848435</v>
+        <v>0.0230489464184844</v>
       </c>
       <c r="G7" t="n">
-        <v>3.385458150065116e-05</v>
+        <v>3.385458150065129e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000905773015519929</v>
+        <v>0.0009057730155199294</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001776478641214097</v>
+        <v>0.0001776478641214098</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0006957893246142024</v>
+        <v>0.0006957893246142054</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002460563826394581</v>
+        <v>0.00246056382639458</v>
       </c>
       <c r="L7" t="n">
-        <v>2.766097064172988e-05</v>
+        <v>2.766097064172991e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.631282320516488e-05</v>
+        <v>4.631282320516494e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003020780359802032</v>
+        <v>0.003020780359802037</v>
       </c>
       <c r="O7" t="n">
-        <v>1.54954427050206e-05</v>
+        <v>1.549544270502011e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.569446863872299e-07</v>
+        <v>4.569446863872306e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.481852080252701e-05</v>
+        <v>5.481852080252703e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.747254058409834e-07</v>
+        <v>1.747254058409849e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.409664399378769e-06</v>
+        <v>1.409664399378771e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004424543270775139</v>
+        <v>0.000442454327077516</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0014560108781312</v>
+        <v>0.001456010878132102</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00442158411886585</v>
+        <v>0.004421584118865849</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001582081497870693</v>
+        <v>0.0001582081497870718</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.852671284051603</v>
+        <v>1.852671284051605</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.925189979113407</v>
+        <v>8.925189979113409</v>
       </c>
     </row>
     <row r="8">
@@ -3114,70 +3114,70 @@
         <v>10.79532945823042</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01058181405154486</v>
+        <v>0.01058181405154487</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02091707121689519</v>
+        <v>0.0209170712168952</v>
       </c>
       <c r="G8" t="n">
-        <v>3.337934035364732e-05</v>
+        <v>3.337934035364725e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008891996048512561</v>
+        <v>0.0008891996048512565</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001737624900552019</v>
+        <v>0.0001737624900552022</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0005963807786516016</v>
+        <v>0.0005963807786516079</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002334128841608283</v>
+        <v>0.002334128841608282</v>
       </c>
       <c r="L8" t="n">
         <v>2.71040534223464e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.111266534990582e-05</v>
+        <v>4.111266534990594e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002912538779137925</v>
+        <v>0.002912538779137927</v>
       </c>
       <c r="O8" t="n">
-        <v>1.343481035649852e-05</v>
+        <v>1.343481035649853e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.556831621244479e-07</v>
+        <v>4.556831621244476e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.439842899292991e-05</v>
+        <v>5.439842899292986e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.373230990401052e-07</v>
+        <v>1.373230990401051e-07</v>
       </c>
       <c r="S8" t="n">
         <v>1.355154411771046e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0004169228282149806</v>
+        <v>0.0004169228282150299</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001339598441213309</v>
+        <v>0.001339598441209462</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004410358447779871</v>
+        <v>0.004410358447779869</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0001472081074076261</v>
+        <v>0.0001472081074076266</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.825249118300723</v>
+        <v>1.825249118300722</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.925189978883191</v>
+        <v>8.925189978883195</v>
       </c>
     </row>
     <row r="9">
@@ -3198,67 +3198,67 @@
         <v>10.9965874932952</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01811068851555999</v>
+        <v>0.01811068851556</v>
       </c>
       <c r="F9" t="n">
         <v>0.04433260708189948</v>
       </c>
       <c r="G9" t="n">
-        <v>3.806921752945501e-05</v>
+        <v>3.806921752945503e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001074485115876923</v>
+        <v>0.001074485115876921</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002085693333614094</v>
+        <v>0.0002085693333614085</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001697622871425569</v>
+        <v>0.001697622871425561</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00333810811535771</v>
+        <v>0.003338108115357711</v>
       </c>
       <c r="L9" t="n">
-        <v>3.149480810926924e-05</v>
+        <v>3.149480810926923e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001036498255976518</v>
+        <v>0.0001036498255976517</v>
       </c>
       <c r="N9" t="n">
         <v>0.003808397360833145</v>
       </c>
       <c r="O9" t="n">
-        <v>2.716550998084804e-05</v>
+        <v>2.716550998084769e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.70206826371508e-07</v>
+        <v>4.702068263715078e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.748183282585366e-05</v>
+        <v>5.748183282585368e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.847722732011943e-07</v>
+        <v>4.847722732011965e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>2.205621356290984e-06</v>
+        <v>2.205621356290985e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0007239091855345023</v>
+        <v>0.0007239091855345004</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002526413289075408</v>
+        <v>0.002526413289078121</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004470482136277214</v>
+        <v>0.004470482136277212</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0002519523378874566</v>
+        <v>0.0002519523378874558</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.99059325610557</v>
+        <v>1.990593256105569</v>
       </c>
       <c r="Z9" t="n">
         <v>8.925189980052041</v>
@@ -3282,70 +3282,70 @@
         <v>10.90827838482768</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01410898328530927</v>
+        <v>0.01410898328530928</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03423095481113834</v>
+        <v>0.03423095481113831</v>
       </c>
       <c r="G10" t="n">
-        <v>3.597559159370257e-05</v>
+        <v>3.597559159370261e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001019814762690255</v>
+        <v>0.001019814762690261</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001945659832336154</v>
+        <v>0.0001945659832336182</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001086276849466629</v>
+        <v>0.001086276849466628</v>
       </c>
       <c r="K10" t="n">
-        <v>0.002873608041095243</v>
+        <v>0.002873608041095242</v>
       </c>
       <c r="L10" t="n">
-        <v>2.992015170139257e-05</v>
+        <v>2.992015170139258e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>7.148531142234192e-05</v>
+        <v>7.148531142234184e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003407950193712568</v>
+        <v>0.003407950193712574</v>
       </c>
       <c r="O10" t="n">
-        <v>2.186257952717815e-05</v>
+        <v>2.186257952717819e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>4.633067793183591e-07</v>
+        <v>4.633067793183587e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.626430326440551e-05</v>
+        <v>5.626430326440552e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>2.961891139972981e-07</v>
+        <v>2.961891139972918e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.864267812418454e-06</v>
+        <v>1.864267812418455e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0006057848336001974</v>
+        <v>0.0006057848336006019</v>
       </c>
       <c r="U10" t="n">
-        <v>0.00208826546168496</v>
+        <v>0.002088265461684969</v>
       </c>
       <c r="V10" t="n">
         <v>0.0044435029580982</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0002126036878080657</v>
+        <v>0.0002126036878080709</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.918597962742309</v>
+        <v>1.918597962742308</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.92518997951632</v>
+        <v>8.925189979516318</v>
       </c>
     </row>
     <row r="11">
@@ -3363,64 +3363,64 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.86199525215139</v>
+        <v>10.8619952521514</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01268189202413571</v>
+        <v>0.01268189202413572</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02458622888367573</v>
+        <v>0.02458622888367575</v>
       </c>
       <c r="G11" t="n">
-        <v>3.45163181055891e-05</v>
+        <v>3.45163181055892e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.000902060096143756</v>
+        <v>0.0009020600961437553</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001806862074612486</v>
+        <v>0.0001806862074612488</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0007350539239766847</v>
+        <v>0.0007350539239766871</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002595983512692795</v>
+        <v>0.002595983512692792</v>
       </c>
       <c r="L11" t="n">
         <v>2.79745967271702e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.773149134990697e-05</v>
+        <v>4.773149134990694e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003158234078010126</v>
+        <v>0.003158234078010134</v>
       </c>
       <c r="O11" t="n">
-        <v>1.740378168929434e-05</v>
+        <v>1.740378168929433e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>4.618835132529723e-07</v>
+        <v>4.618835132529721e-07</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.511580607320554e-05</v>
+        <v>5.511580607320561e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.37630699118626e-07</v>
+        <v>2.376306991186257e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.545769971481762e-06</v>
+        <v>1.545769971481763e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0004706528194851993</v>
+        <v>0.0004706528194848813</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001509076353165635</v>
+        <v>0.001509076353162917</v>
       </c>
       <c r="V11" t="n">
-        <v>0.004431192493218526</v>
+        <v>0.00443119249321853</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0001663307048131952</v>
+        <v>0.0001663307048131924</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
         <v>1.88520289430888</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.925189979467607</v>
+        <v>8.925189979467614</v>
       </c>
     </row>
   </sheetData>
@@ -3598,79 +3598,79 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.878166690821577</v>
+        <v>4.878166690821574</v>
       </c>
       <c r="E2" t="n">
-        <v>0.142076449933259</v>
+        <v>0.1420764499332593</v>
       </c>
       <c r="F2" t="n">
         <v>0.02236109545418415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05296659951498824</v>
+        <v>0.05296659951498836</v>
       </c>
       <c r="H2" t="n">
-        <v>3.987099995124913e-05</v>
+        <v>3.987099995124905e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001115047877934225</v>
+        <v>0.00111504787793423</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002204552969457201</v>
+        <v>0.0002204552969457206</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002082938453430552</v>
+        <v>0.002082938453430559</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006361631112596295</v>
+        <v>0.0006361631112596299</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003875358811066434</v>
+        <v>0.003875358811066431</v>
       </c>
       <c r="N2" t="n">
-        <v>3.281297100841981e-05</v>
+        <v>3.281297100841984e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001275696534852123</v>
+        <v>0.0001275696534852125</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004157778150090817</v>
+        <v>0.00415777815009082</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.146384357918766e-05</v>
+        <v>3.146384357918802e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>4.776230107809116e-07</v>
+        <v>4.776230107809113e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>5.842311683215346e-05</v>
+        <v>5.842311683215343e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>5.260035306051285e-07</v>
+        <v>5.260035306051284e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>2.602132163041634e-06</v>
+        <v>2.602132163041635e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008399885645132336</v>
+        <v>0.0008399885645132345</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002914470904245384</v>
+        <v>0.002914470904246001</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004490217877914886</v>
+        <v>0.004490217877914885</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002874343647440914</v>
+        <v>0.0002874343647440926</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.026743697951657</v>
+        <v>2.026743697951656</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.613105248211784</v>
+        <v>2.61310524821178</v>
       </c>
     </row>
     <row r="3">
@@ -3691,76 +3691,76 @@
         <v>4.840360513201338</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1367993228268539</v>
+        <v>0.1367993228268543</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02005506000182299</v>
+        <v>0.02005506000182306</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04941851333391129</v>
+        <v>0.0494185133339114</v>
       </c>
       <c r="H3" t="n">
-        <v>3.911753746663408e-05</v>
+        <v>3.911753746663405e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001100074248113156</v>
+        <v>0.001100074248113151</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002152958685212293</v>
+        <v>0.0002152958685212315</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001970042623700984</v>
+        <v>0.001970042623701017</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006130805146831815</v>
+        <v>0.0006130805146831824</v>
       </c>
       <c r="M3" t="n">
         <v>0.00366482954191396</v>
       </c>
       <c r="N3" t="n">
-        <v>3.227089836273612e-05</v>
+        <v>3.227089836273613e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001197009649556254</v>
+        <v>0.0001197009649556328</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004050736803665503</v>
+        <v>0.004050736803665514</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.95705763628912e-05</v>
+        <v>2.957057636289085e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>4.733795125129375e-07</v>
+        <v>4.733795125129374e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>5.802689914056454e-05</v>
+        <v>5.80268991405646e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.025883200395271e-07</v>
+        <v>5.025883200395064e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>2.380376850728175e-06</v>
+        <v>2.38037685072818e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007880714909629381</v>
+        <v>0.0007880714909636279</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002764972894223283</v>
+        <v>0.002764972894225507</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004480739709009162</v>
+        <v>0.00448073970900916</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002716392972616066</v>
+        <v>0.0002716392972616134</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.000780841864457</v>
+        <v>2.000780841864456</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.613105248961266</v>
+        <v>2.613105248961263</v>
       </c>
     </row>
     <row r="4">
@@ -3778,79 +3778,79 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.812882770376472</v>
+        <v>4.812882770376471</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1297813404727579</v>
+        <v>0.1297813404727581</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02029872483175003</v>
+        <v>0.02029872483175</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04782931086403121</v>
+        <v>0.04782931086403115</v>
       </c>
       <c r="H4" t="n">
-        <v>3.876779959824276e-05</v>
+        <v>3.876779959824283e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001084908857758603</v>
+        <v>0.001084908857758598</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002121268381683208</v>
+        <v>0.0002121268381683207</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001860520502540841</v>
+        <v>0.00186052050254085</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006130564338965223</v>
+        <v>0.0006130564338965215</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003422024622077298</v>
+        <v>0.003422024622077294</v>
       </c>
       <c r="N4" t="n">
-        <v>3.187772904606677e-05</v>
+        <v>3.187772904606676e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001132308690536359</v>
+        <v>0.000113230869053636</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003919628787678782</v>
+        <v>0.003919628787678777</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.773715584498912e-05</v>
+        <v>2.773715584498885e-05</v>
       </c>
       <c r="R4" t="n">
         <v>4.727414790302066e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.761236249791589e-05</v>
+        <v>5.76123624979159e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.275304306642038e-07</v>
+        <v>4.275304306641981e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.396377718835451e-06</v>
+        <v>2.396377718835448e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007767900678165008</v>
+        <v>0.0007767900678164979</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002683048207397014</v>
+        <v>0.002683048207399992</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004464258220244084</v>
+        <v>0.004464258220244089</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002649056565987181</v>
+        <v>0.0002649056565987173</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.982294353972874</v>
+        <v>1.982294353972873</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.613105249475213</v>
+        <v>2.613105249475209</v>
       </c>
     </row>
     <row r="5">
@@ -3868,79 +3868,79 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.791113459172939</v>
+        <v>4.791113459172963</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1182890106177124</v>
+        <v>0.1182890106177125</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02201189337820753</v>
+        <v>0.02201189337820745</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04663375943952425</v>
+        <v>0.04663375943952414</v>
       </c>
       <c r="H5" t="n">
-        <v>3.874614160360763e-05</v>
+        <v>3.874614160360743e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001059466132098391</v>
+        <v>0.001059466132098388</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002099058059956948</v>
+        <v>0.0002099058059956939</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001757486776130354</v>
+        <v>0.001757486776130318</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006140965727205201</v>
+        <v>0.0006140965727205192</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003301649855513181</v>
+        <v>0.003301649855513173</v>
       </c>
       <c r="N5" t="n">
-        <v>3.147707138709096e-05</v>
+        <v>3.147707138709094e-05</v>
       </c>
       <c r="O5" t="n">
         <v>0.0001068647890104632</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003844587028155844</v>
+        <v>0.003844587028155843</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.678385539397046e-05</v>
+        <v>2.678385539397113e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.759677398392056e-07</v>
+        <v>4.759677398392054e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>5.734158341098631e-05</v>
+        <v>5.734158341098629e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>3.913830566289082e-07</v>
+        <v>3.91383056628908e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.487276943047094e-06</v>
+        <v>2.487276943047091e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0007693430098491073</v>
+        <v>0.0007693430098491055</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002563199075923358</v>
+        <v>0.002563199075922849</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004459030194024527</v>
+        <v>0.004459030194024531</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002599184462097179</v>
+        <v>0.0002599184462097164</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.971970295161116</v>
+        <v>1.971970295161123</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.613105249611212</v>
+        <v>2.61310524961123</v>
       </c>
     </row>
     <row r="6">
@@ -3958,70 +3958,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.589337468162601</v>
+        <v>4.589337468162595</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03780075441389463</v>
+        <v>0.03780075441389469</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01282085827477018</v>
+        <v>0.01282085827477019</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0285714934659927</v>
+        <v>0.02857149346599268</v>
       </c>
       <c r="H6" t="n">
-        <v>3.533826784116757e-05</v>
+        <v>3.53382678411675e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009416546565259189</v>
+        <v>0.0009416546565259208</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001868813796941302</v>
+        <v>0.0001868813796941294</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001027832706441007</v>
+        <v>0.001027832706440999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004899292141898202</v>
+        <v>0.0004899292141898203</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002828996149939954</v>
+        <v>0.002828996149939956</v>
       </c>
       <c r="N6" t="n">
-        <v>2.881934551697532e-05</v>
+        <v>2.88193455169753e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>6.358601305521095e-05</v>
+        <v>6.358601305521081e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003354300193802101</v>
+        <v>0.003354300193802096</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.030728009792041e-05</v>
+        <v>2.03072800979204e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.606506127988125e-07</v>
+        <v>4.606506127988123e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>5.57899140535472e-05</v>
+        <v>5.578991405354722e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.630799976260342e-07</v>
+        <v>2.630799976260335e-07</v>
       </c>
       <c r="U6" t="n">
         <v>1.585188499032877e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005073520109438052</v>
+        <v>0.0005073520109439788</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001716280861621284</v>
+        <v>0.001716280861616663</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004450086451568004</v>
+        <v>0.004450086451568002</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.000183226448066897</v>
+        <v>0.0001832264480668962</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -4030,7 +4030,7 @@
         <v>1.881146421412698</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.613105250782778</v>
+        <v>2.613105250782777</v>
       </c>
     </row>
     <row r="7">
@@ -4048,76 +4048,76 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.496633061822275</v>
+        <v>4.496633061822274</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01154134168185622</v>
+        <v>0.01154134168185628</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01088688051161717</v>
+        <v>0.0108868805116172</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02304630564214194</v>
+        <v>0.023046305642142</v>
       </c>
       <c r="H7" t="n">
-        <v>3.385458150065116e-05</v>
+        <v>3.385458150065129e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000905773015519929</v>
+        <v>0.0009057730155199294</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001776478641214097</v>
+        <v>0.0001776478641214098</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0006957893246142024</v>
+        <v>0.0006957893246142054</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004646888140058464</v>
+        <v>0.0004646888140058468</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002460563826394581</v>
+        <v>0.00246056382639458</v>
       </c>
       <c r="N7" t="n">
-        <v>2.766097064172988e-05</v>
+        <v>2.766097064172991e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>4.631282320516488e-05</v>
+        <v>4.631282320516494e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003020780359802032</v>
+        <v>0.003020780359802037</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.54954427050206e-05</v>
+        <v>1.549544270502011e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>4.569446863872299e-07</v>
+        <v>4.569446863872306e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>5.481852080252701e-05</v>
+        <v>5.481852080252703e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.747254058409834e-07</v>
+        <v>1.747254058409849e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>1.409502890547562e-06</v>
+        <v>1.409502890547564e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0004424036339612939</v>
+        <v>0.0004424036339612934</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001455844059266967</v>
+        <v>0.001455844059265567</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00442158411886585</v>
+        <v>0.004421584118865849</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001582081497870693</v>
+        <v>0.0001582081497870718</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.823669815050713</v>
+        <v>1.823669815050712</v>
       </c>
       <c r="AB7" t="n">
         <v>2.61310525225777</v>
@@ -4138,76 +4138,76 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.459584068577475</v>
+        <v>4.459584068577474</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004460776312794375</v>
+        <v>0.004460776312794462</v>
       </c>
       <c r="F8" t="n">
-        <v>0.010580601666228</v>
+        <v>0.01058060166622801</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0209146746949102</v>
+        <v>0.02091467469491021</v>
       </c>
       <c r="H8" t="n">
-        <v>3.337934035364732e-05</v>
+        <v>3.337934035364725e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008891996048512561</v>
+        <v>0.0008891996048512565</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001737624900552019</v>
+        <v>0.0001737624900552022</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0005963807786516016</v>
+        <v>0.0005963807786516079</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004545762296667365</v>
+        <v>0.0004545762296667364</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002334128841608283</v>
+        <v>0.002334128841608282</v>
       </c>
       <c r="N8" t="n">
         <v>2.71040534223464e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>4.111266534990582e-05</v>
+        <v>4.111266534990594e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002912538779137925</v>
+        <v>0.002912538779137927</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.343481035649852e-05</v>
+        <v>1.343481035649853e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>4.556831621244479e-07</v>
+        <v>4.556831621244476e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>5.439842899292991e-05</v>
+        <v>5.439842899292986e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.373230990401052e-07</v>
+        <v>1.373230990401051e-07</v>
       </c>
       <c r="U8" t="n">
         <v>1.354999148287588e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>0.000416875060307444</v>
+        <v>0.0004168750603074418</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001339444960014497</v>
+        <v>0.001339444960014767</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004410358447779871</v>
+        <v>0.004410358447779869</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001472081074076261</v>
+        <v>0.0001472081074076266</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.796676912222405</v>
+        <v>1.796676912222403</v>
       </c>
       <c r="AB8" t="n">
         <v>2.613105253077772</v>
@@ -4228,79 +4228,79 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.764945411235422</v>
+        <v>4.764945411235421</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1110232245261395</v>
+        <v>0.1110232245261394</v>
       </c>
       <c r="F9" t="n">
         <v>0.01810861352797018</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04432752778248799</v>
+        <v>0.04432752778248802</v>
       </c>
       <c r="H9" t="n">
-        <v>3.806921752945501e-05</v>
+        <v>3.806921752945503e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001074485115876923</v>
+        <v>0.001074485115876921</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002085693333614094</v>
+        <v>0.0002085693333614085</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001697622871425569</v>
+        <v>0.001697622871425561</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0005874317082775567</v>
+        <v>0.000587431708277557</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00333810811535771</v>
+        <v>0.003338108115357711</v>
       </c>
       <c r="N9" t="n">
-        <v>3.149480810926924e-05</v>
+        <v>3.149480810926923e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0001036498255976518</v>
+        <v>0.0001036498255976517</v>
       </c>
       <c r="P9" t="n">
         <v>0.003808397360833145</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.716550998084804e-05</v>
+        <v>2.716550998084769e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.70206826371508e-07</v>
+        <v>4.702068263715078e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>5.748183282585366e-05</v>
+        <v>5.748183282585368e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.847722732011943e-07</v>
+        <v>4.847722732011965e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>2.205368652649252e-06</v>
+        <v>2.205368652649251e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0007238262454201688</v>
+        <v>0.0007238262454201686</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002526123831492402</v>
+        <v>0.002526123831489725</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004470482136277214</v>
+        <v>0.004470482136277212</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002519523378874566</v>
+        <v>0.0002519523378874558</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95943277496286</v>
+        <v>1.959432774962861</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.61310524983796</v>
+        <v>2.613105249837961</v>
       </c>
     </row>
     <row r="10">
@@ -4318,76 +4318,76 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.614166857046909</v>
+        <v>4.614166857046908</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04747377678283905</v>
+        <v>0.04747377678283894</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01410736678325322</v>
+        <v>0.01410736678325323</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03422703288368871</v>
+        <v>0.0342270328836887</v>
       </c>
       <c r="H10" t="n">
-        <v>3.597559159370257e-05</v>
+        <v>3.597559159370261e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001019814762690255</v>
+        <v>0.001019814762690261</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001945659832336154</v>
+        <v>0.0001945659832336182</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001086276849466629</v>
+        <v>0.001086276849466628</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0005387477895499014</v>
+        <v>0.0005387477895499018</v>
       </c>
       <c r="M10" t="n">
-        <v>0.002873608041095243</v>
+        <v>0.002873608041095242</v>
       </c>
       <c r="N10" t="n">
-        <v>2.992015170139257e-05</v>
+        <v>2.992015170139258e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>7.148531142234192e-05</v>
+        <v>7.148531142234184e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003407950193712568</v>
+        <v>0.003407950193712574</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.186257952717815e-05</v>
+        <v>2.186257952717819e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.633067793183591e-07</v>
+        <v>4.633067793183587e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>5.626430326440551e-05</v>
+        <v>5.626430326440552e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.961891139972981e-07</v>
+        <v>2.961891139972918e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>1.864054218519384e-06</v>
+        <v>1.864054218519383e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0006057154272930828</v>
+        <v>0.0006057154272933402</v>
       </c>
       <c r="W10" t="n">
-        <v>0.002088026203806194</v>
+        <v>0.0020880262038062</v>
       </c>
       <c r="X10" t="n">
         <v>0.0044435029580982</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0002126036878080657</v>
+        <v>0.0002126036878080709</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.888564486312557</v>
+        <v>1.888564486312555</v>
       </c>
       <c r="AB10" t="n">
         <v>2.613105250900197</v>
@@ -4408,70 +4408,70 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.529378728762969</v>
+        <v>4.52937872876297</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008507665310968386</v>
+        <v>0.008507665310968396</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01268043902755069</v>
+        <v>0.0126804390275507</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02458341197697613</v>
+        <v>0.02458341197697617</v>
       </c>
       <c r="H11" t="n">
-        <v>3.45163181055891e-05</v>
+        <v>3.45163181055892e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000902060096143756</v>
+        <v>0.0009020600961437553</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001806862074612486</v>
+        <v>0.0001806862074612488</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0007350539239766847</v>
+        <v>0.0007350539239766871</v>
       </c>
       <c r="L11" t="n">
-        <v>0.000475751125884555</v>
+        <v>0.0004757511258845546</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002595983512692795</v>
+        <v>0.002595983512692792</v>
       </c>
       <c r="N11" t="n">
         <v>2.79745967271702e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>4.773149134990697e-05</v>
+        <v>4.773149134990694e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.003158234078010126</v>
+        <v>0.003158234078010134</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.740378168929434e-05</v>
+        <v>1.740378168929433e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>4.618835132529723e-07</v>
+        <v>4.618835132529721e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>5.511580607320554e-05</v>
+        <v>5.511580607320561e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.37630699118626e-07</v>
+        <v>2.376306991186257e-07</v>
       </c>
       <c r="U11" t="n">
-        <v>1.545592868689409e-06</v>
+        <v>1.545592868689408e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0004705988955958132</v>
+        <v>0.0004705988955957526</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001508903454452629</v>
+        <v>0.00150890345445105</v>
       </c>
       <c r="X11" t="n">
-        <v>0.004431192493218526</v>
+        <v>0.00443119249321853</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0001663307048131952</v>
+        <v>0.0001663307048131924</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -4480,7 +4480,7 @@
         <v>1.855692179823078</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.61310525103112</v>
+        <v>2.613105251031123</v>
       </c>
     </row>
   </sheetData>
@@ -4574,31 +4574,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.399075197032862</v>
+        <v>2.399075197032861</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3229212258061552</v>
+        <v>0.3229212258061548</v>
       </c>
       <c r="F2" t="n">
         <v>0.05132008853399483</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01620950307353838</v>
+        <v>0.0162095030735384</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1042544840978111</v>
+        <v>0.10425448409781</v>
       </c>
       <c r="I2" t="n">
         <v>4.833115662204299e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001560167444560521</v>
+        <v>0.001560167444560522</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005413243483327283</v>
+        <v>0.005413243483330634</v>
       </c>
       <c r="L2" t="n">
-        <v>1.897391694870997</v>
+        <v>1.897391694871</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -4619,31 +4619,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.151921314539139</v>
+        <v>2.151921314539146</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3089876738270319</v>
+        <v>0.3089876738270318</v>
       </c>
       <c r="F3" t="n">
         <v>0.03815515100738621</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01598108859471932</v>
+        <v>0.01598108859471926</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1035592013147198</v>
+        <v>0.1035592013147193</v>
       </c>
       <c r="I3" t="n">
-        <v>4.421234556262931e-06</v>
+        <v>4.421234556262938e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001463738360411479</v>
+        <v>0.00146373836041473</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005135570740965104</v>
+        <v>0.005135570740970298</v>
       </c>
       <c r="L3" t="n">
-        <v>1.678634451600719</v>
+        <v>1.678634451600722</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -4664,31 +4664,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.940612837015409</v>
+        <v>1.940612837015411</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3020604124453137</v>
+        <v>0.3020604124453136</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04608639375192557</v>
+        <v>0.04608639375192553</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01607793456641514</v>
+        <v>0.01607793456641526</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1030603212748783</v>
+        <v>0.1030603212748789</v>
       </c>
       <c r="I4" t="n">
-        <v>4.450954048361191e-06</v>
+        <v>4.45095404836119e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001442784611916191</v>
+        <v>0.00144278461191619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004983406491719878</v>
+        <v>0.004983406491725744</v>
       </c>
       <c r="L4" t="n">
-        <v>1.466897130994521</v>
+        <v>1.466897130994518</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -4709,31 +4709,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.897108325503863</v>
+        <v>1.897108325503856</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3073238008523996</v>
+        <v>0.3073238008523985</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06267991062657732</v>
+        <v>0.06267991062657743</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01633922733447173</v>
+        <v>0.01633922733447185</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1020909024928442</v>
+        <v>0.1020909024928436</v>
       </c>
       <c r="I5" t="n">
-        <v>4.61978731150566e-06</v>
+        <v>4.619787311505653e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00142895268861469</v>
+        <v>0.001428952688614687</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004760802612227854</v>
+        <v>0.004760802612233609</v>
       </c>
       <c r="L5" t="n">
-        <v>1.402480107332679</v>
+        <v>1.402480107332675</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -4757,28 +4757,28 @@
         <v>1.538271021178349</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2598355802687868</v>
+        <v>0.2598355802687874</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01762308555606738</v>
+        <v>0.01762308555606735</v>
       </c>
       <c r="G6" t="n">
         <v>0.01551713341106996</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09762862568343909</v>
+        <v>0.0976286256834379</v>
       </c>
       <c r="I6" t="n">
-        <v>2.944277570154815e-06</v>
+        <v>2.944277570154817e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009423391268020161</v>
+        <v>0.0009423391268020505</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003187764261500282</v>
+        <v>0.003187764261491218</v>
       </c>
       <c r="L6" t="n">
-        <v>1.143533535676992</v>
+        <v>1.143533535676993</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -4799,31 +4799,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.235011769076681</v>
+        <v>1.235011769076674</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2431522460043292</v>
+        <v>0.2431522460043293</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01591071817513</v>
+        <v>0.01591071817513002</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01541053876202197</v>
+        <v>0.01541053876202195</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09623801688947553</v>
+        <v>0.09623801688947607</v>
       </c>
       <c r="I7" t="n">
-        <v>2.61796483398628e-06</v>
+        <v>2.617964833986283e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008217061234180729</v>
+        <v>0.0008217061234180717</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00270403741382146</v>
+        <v>0.002704037413813745</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8607718856258889</v>
+        <v>0.8607718856258888</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -4844,31 +4844,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.154061313732623</v>
+        <v>1.154061313732617</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2355715821537626</v>
+        <v>0.2355715821537624</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01840883946338094</v>
+        <v>0.01840883946338097</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01540791177997902</v>
+        <v>0.01540791177997908</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09548110359410801</v>
+        <v>0.09548110359410772</v>
       </c>
       <c r="I8" t="n">
-        <v>2.516731355492434e-06</v>
+        <v>2.516731355492435e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0007742901808642783</v>
+        <v>0.0007742901808644112</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002487841511981046</v>
+        <v>0.002487841511987725</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7859272262012726</v>
+        <v>0.7859272262012731</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -4889,19 +4889,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.958154102761806</v>
+        <v>1.958154102761808</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2960962596485862</v>
+        <v>0.2960962596485859</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03361273292334656</v>
+        <v>0.03361273292334658</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01586517403584985</v>
+        <v>0.01586517403584987</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1022662252574715</v>
+        <v>0.1022662252574716</v>
       </c>
       <c r="I9" t="n">
         <v>4.09618002015486e-06</v>
@@ -4910,10 +4910,10 @@
         <v>0.001344411330501191</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004691940258858576</v>
+        <v>0.004691940258860294</v>
       </c>
       <c r="L9" t="n">
-        <v>1.504273246881713</v>
+        <v>1.504273246881715</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -4937,25 +4937,25 @@
         <v>1.521041108487125</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2690112247431757</v>
+        <v>0.2690112247431758</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02431599742206895</v>
+        <v>0.02431599742206898</v>
       </c>
       <c r="G10" t="n">
         <v>0.0156233056109026</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09985489485305293</v>
+        <v>0.09985489485305252</v>
       </c>
       <c r="I10" t="n">
-        <v>3.462233689234745e-06</v>
+        <v>3.462233689234744e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001125036137699045</v>
+        <v>0.001125036137698804</v>
       </c>
       <c r="K10" t="n">
-        <v>0.003878231971473939</v>
+        <v>0.003878231971473948</v>
       </c>
       <c r="L10" t="n">
         <v>1.107228953433882</v>
@@ -4979,31 +4979,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.322298040883365</v>
+        <v>1.322298040883372</v>
       </c>
       <c r="E11" t="n">
-        <v>0.259685820706724</v>
+        <v>0.2596858207067236</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0261699422088576</v>
+        <v>0.02616994220885761</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01561966559088739</v>
+        <v>0.01561966559088734</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09633649346690934</v>
+        <v>0.09633649346691019</v>
       </c>
       <c r="I11" t="n">
-        <v>2.87073393394528e-06</v>
+        <v>2.870733933945281e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0008740750855103398</v>
+        <v>0.0008740750855103621</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002802588209026608</v>
+        <v>0.002802588209026711</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9208065828980021</v>
+        <v>0.9208065828980035</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -5100,31 +5100,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.063558420023185</v>
+        <v>4.063558420023198</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3229212258061552</v>
+        <v>0.3229212258061548</v>
       </c>
       <c r="F2" t="n">
         <v>0.05132008853399483</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01620950307353838</v>
+        <v>0.0162095030735384</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1042544840978111</v>
+        <v>0.10425448409781</v>
       </c>
       <c r="I2" t="n">
         <v>4.833115662204299e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001560167444560521</v>
+        <v>0.001560167444560522</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005413243483327283</v>
+        <v>0.005413243483330634</v>
       </c>
       <c r="L2" t="n">
-        <v>3.56187495753777</v>
+        <v>3.561874957537773</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -5145,31 +5145,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.359939327028494</v>
+        <v>3.359939327028501</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3089876738270319</v>
+        <v>0.3089876738270318</v>
       </c>
       <c r="F3" t="n">
         <v>0.03815515100738621</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01598108859471932</v>
+        <v>0.01598108859471926</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1035592013147198</v>
+        <v>0.1035592013147193</v>
       </c>
       <c r="I3" t="n">
-        <v>4.421234556262931e-06</v>
+        <v>4.421234556262938e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001463738360411479</v>
+        <v>0.00146373836041473</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005135570740965104</v>
+        <v>0.005135570740970298</v>
       </c>
       <c r="L3" t="n">
-        <v>2.886652452639506</v>
+        <v>2.886652452639515</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -5190,31 +5190,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.920947784216022</v>
+        <v>2.920947784216024</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3020604124453137</v>
+        <v>0.3020604124453136</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04608639375192557</v>
+        <v>0.04608639375192553</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01607793456641514</v>
+        <v>0.01607793456641526</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1030603212748783</v>
+        <v>0.1030603212748789</v>
       </c>
       <c r="I4" t="n">
-        <v>4.450954048361191e-06</v>
+        <v>4.45095404836119e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001442784611916191</v>
+        <v>0.00144278461191619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004983406491719878</v>
+        <v>0.004983406491725744</v>
       </c>
       <c r="L4" t="n">
-        <v>2.447232078195132</v>
+        <v>2.44723207819513</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -5235,31 +5235,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.738769801379676</v>
+        <v>2.738769801379683</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3073238008523996</v>
+        <v>0.3073238008523985</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06267991062657732</v>
+        <v>0.06267991062657743</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01633922733447173</v>
+        <v>0.01633922733447185</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1020909024928442</v>
+        <v>0.1020909024928436</v>
       </c>
       <c r="I5" t="n">
-        <v>4.61978731150566e-06</v>
+        <v>4.619787311505653e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00142895268861469</v>
+        <v>0.001428952688614687</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004760802612227854</v>
+        <v>0.004760802612233609</v>
       </c>
       <c r="L5" t="n">
-        <v>2.244141583208498</v>
+        <v>2.244141583208499</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -5280,28 +5280,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.295094453144951</v>
+        <v>2.295094453144944</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2598355802687868</v>
+        <v>0.2598355802687874</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01762308555606738</v>
+        <v>0.01762308555606735</v>
       </c>
       <c r="G6" t="n">
         <v>0.01551713341106996</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09762862568343909</v>
+        <v>0.0976286256834379</v>
       </c>
       <c r="I6" t="n">
-        <v>2.944277570154815e-06</v>
+        <v>2.944277570154817e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009423391268020161</v>
+        <v>0.0009423391268020505</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003187764261500282</v>
+        <v>0.003187764261491218</v>
       </c>
       <c r="L6" t="n">
         <v>1.900356960469816</v>
@@ -5325,31 +5325,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.835517558736002</v>
+        <v>1.83551755873601</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2431522460043292</v>
+        <v>0.2431522460043293</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01591071817513</v>
+        <v>0.01591071817513002</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01541053876202197</v>
+        <v>0.01541053876202195</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09623801688947553</v>
+        <v>0.09623801688947607</v>
       </c>
       <c r="I7" t="n">
-        <v>2.61796483398628e-06</v>
+        <v>2.617964833986283e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008217061234180729</v>
+        <v>0.0008217061234180717</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00270403741382146</v>
+        <v>0.002704037413813745</v>
       </c>
       <c r="L7" t="n">
-        <v>1.461277675285213</v>
+        <v>1.461277675285215</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5370,31 +5370,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.677517961455663</v>
+        <v>1.67751796145567</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2355715821537626</v>
+        <v>0.2355715821537624</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01840883946338094</v>
+        <v>0.01840883946338097</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01540791177997902</v>
+        <v>0.01540791177997908</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09548110359410801</v>
+        <v>0.09548110359410772</v>
       </c>
       <c r="I8" t="n">
-        <v>2.516731355492434e-06</v>
+        <v>2.516731355492435e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0007742901808642783</v>
+        <v>0.0007742901808644112</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002487841511981046</v>
+        <v>0.002487841511987725</v>
       </c>
       <c r="L8" t="n">
-        <v>1.309383873924316</v>
+        <v>1.309383873924319</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5415,19 +5415,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.116813587193979</v>
+        <v>3.116813587193978</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2960962596485862</v>
+        <v>0.2960962596485859</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03361273292334656</v>
+        <v>0.03361273292334658</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01586517403584985</v>
+        <v>0.01586517403584987</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1022662252574715</v>
+        <v>0.1022662252574716</v>
       </c>
       <c r="I9" t="n">
         <v>4.09618002015486e-06</v>
@@ -5436,10 +5436,10 @@
         <v>0.001344411330501191</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004691940258858576</v>
+        <v>0.004691940258860294</v>
       </c>
       <c r="L9" t="n">
-        <v>2.662932720331191</v>
+        <v>2.662932720331187</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -5460,31 +5460,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.379589484484473</v>
+        <v>2.379589484484474</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2690112247431757</v>
+        <v>0.2690112247431758</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02431599742206895</v>
+        <v>0.02431599742206898</v>
       </c>
       <c r="G10" t="n">
         <v>0.0156233056109026</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09985489485305293</v>
+        <v>0.09985489485305252</v>
       </c>
       <c r="I10" t="n">
-        <v>3.462233689234745e-06</v>
+        <v>3.462233689234744e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001125036137699045</v>
+        <v>0.001125036137698804</v>
       </c>
       <c r="K10" t="n">
-        <v>0.003878231971473939</v>
+        <v>0.003878231971473948</v>
       </c>
       <c r="L10" t="n">
-        <v>1.965777329431228</v>
+        <v>1.96577732943123</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -5505,31 +5505,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.850332406227819</v>
+        <v>1.850332406227821</v>
       </c>
       <c r="E11" t="n">
-        <v>0.259685820706724</v>
+        <v>0.2596858207067236</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0261699422088576</v>
+        <v>0.02616994220885761</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01561966559088739</v>
+        <v>0.01561966559088734</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09633649346690934</v>
+        <v>0.09633649346691019</v>
       </c>
       <c r="I11" t="n">
-        <v>2.87073393394528e-06</v>
+        <v>2.870733933945281e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0008740750855103398</v>
+        <v>0.0008740750855103621</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002802588209026608</v>
+        <v>0.002802588209026711</v>
       </c>
       <c r="L11" t="n">
-        <v>1.448840948242452</v>
+        <v>1.448840948242453</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>

--- a/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Hydrogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0820F976-4D19-4CEB-9F60-4147B7C2DFA4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE57619-F541-4554-B2E2-0E09A4FCB64F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hydrogenBAU" sheetId="1" r:id="rId1"/>
@@ -514,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -1392,942 +1392,6 @@
       </c>
       <c r="Z11">
         <v>8.925189977474993</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="E14">
-        <f>E2/$D2*100</f>
-        <v>0.21828697610591524</v>
-      </c>
-      <c r="F14">
-        <f t="shared" ref="F14:K14" si="0">F2/$D2*100</f>
-        <v>0.51705511773469037</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>3.8917247457864902E-4</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>1.0883748650897362E-2</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>2.1518179516751561E-3</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>2.0331125713118722E-2</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>3.7826565178374634E-2</v>
-      </c>
-      <c r="L14">
-        <f t="shared" ref="L14:Z14" si="1">L2/$D2*100</f>
-        <v>3.2028053325068844E-4</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="1"/>
-        <v>1.2451806523208514E-3</v>
-      </c>
-      <c r="N14">
-        <f t="shared" si="1"/>
-        <v>4.0583201158695584E-2</v>
-      </c>
-      <c r="O14">
-        <f t="shared" si="1"/>
-        <v>3.0711198315668383E-4</v>
-      </c>
-      <c r="P14">
-        <f t="shared" si="1"/>
-        <v>4.6619781106214503E-6</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="1"/>
-        <v>5.7025579940225184E-4</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="1"/>
-        <v>5.1342102253016378E-6</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="1"/>
-        <v>2.540177704898699E-5</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="1"/>
-        <v>8.1998918204534022E-3</v>
-      </c>
-      <c r="U14">
-        <f t="shared" si="1"/>
-        <v>2.8450799377833239E-2</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="1"/>
-        <v>4.3828075671091427E-2</v>
-      </c>
-      <c r="W14">
-        <f t="shared" si="1"/>
-        <v>2.8055865953493901E-3</v>
-      </c>
-      <c r="X14">
-        <f t="shared" si="1"/>
-        <v>-8.1473983518391773</v>
-      </c>
-      <c r="Y14">
-        <f t="shared" si="1"/>
-        <v>20.097219676275056</v>
-      </c>
-      <c r="Z14">
-        <f t="shared" si="1"/>
-        <v>87.11690857019795</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D15">
-        <f>($D$2-D3)/$D$2*100</f>
-        <v>1.7381816828182749E-2</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ref="E15:K23" si="2">E3/$D3*100</f>
-        <v>0.1958097034479295</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="2"/>
-        <v>0.48250289153316539</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="2"/>
-        <v>3.8188446363082067E-4</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="2"/>
-        <v>1.0739460901727298E-2</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="2"/>
-        <v>2.1018231871648752E-3</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="2"/>
-        <v>1.923251613994436E-2</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="2"/>
-        <v>3.5777851944436966E-2</v>
-      </c>
-      <c r="L15">
-        <f t="shared" ref="L15:Z15" si="3">L3/$D3*100</f>
-        <v>3.150442361728411E-4</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="3"/>
-        <v>1.1685791529480671E-3</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="3"/>
-        <v>3.9545266695197645E-2</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="3"/>
-        <v>2.8868237688093121E-4</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="3"/>
-        <v>4.6213614899460018E-6</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="3"/>
-        <v>5.6648686726140716E-4</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="3"/>
-        <v>4.9065121031484306E-6</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="3"/>
-        <v>2.3241061617019894E-5</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="3"/>
-        <v>7.6944195094568665E-3</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="3"/>
-        <v>2.6996105841146239E-2</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="3"/>
-        <v>4.3743164607532234E-2</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="3"/>
-        <v>2.651875195985602E-3</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="3"/>
-        <v>-7.8448229735348445</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="3"/>
-        <v>19.843220733957097</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="3"/>
-        <v>87.132053714541954</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>($D$2-D4)/$D$2*100</f>
-        <v>-0.18536699616310948</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="2"/>
-        <v>0.1977876689682993</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="2"/>
-        <v>0.46604148696868192</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="2"/>
-        <v>3.7770422815352545E-4</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="2"/>
-        <v>1.0569974746650501E-2</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="2"/>
-        <v>2.0666946412054013E-3</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="2"/>
-        <v>1.8126550066252727E-2</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="2"/>
-        <v>3.3339864062407291E-2</v>
-      </c>
-      <c r="L16">
-        <f t="shared" ref="L16:Z16" si="4">L4/$D4*100</f>
-        <v>3.105761268219515E-4</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="4"/>
-        <v>1.1031778548761112E-3</v>
-      </c>
-      <c r="N16">
-        <f t="shared" si="4"/>
-        <v>3.8187887402452769E-2</v>
-      </c>
-      <c r="O16">
-        <f t="shared" si="4"/>
-        <v>2.7023563751811205E-4</v>
-      </c>
-      <c r="P16">
-        <f t="shared" si="4"/>
-        <v>4.6057928823320007E-6</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="4"/>
-        <v>5.6130172810640356E-4</v>
-      </c>
-      <c r="R16">
-        <f t="shared" si="4"/>
-        <v>4.1653138171268417E-6</v>
-      </c>
-      <c r="S16">
-        <f t="shared" si="4"/>
-        <v>2.3349937836226741E-5</v>
-      </c>
-      <c r="T16">
-        <f t="shared" si="4"/>
-        <v>7.5689235685799912E-3</v>
-      </c>
-      <c r="U16">
-        <f t="shared" si="4"/>
-        <v>2.6143211214965781E-2</v>
-      </c>
-      <c r="V16">
-        <f t="shared" si="4"/>
-        <v>4.3494065250784864E-2</v>
-      </c>
-      <c r="W16">
-        <f t="shared" si="4"/>
-        <v>2.5809044515298328E-3</v>
-      </c>
-      <c r="X16">
-        <f t="shared" si="4"/>
-        <v>-7.4243739051396158</v>
-      </c>
-      <c r="Y16">
-        <f t="shared" si="4"/>
-        <v>19.620090169907161</v>
-      </c>
-      <c r="Z16">
-        <f t="shared" si="4"/>
-        <v>86.9557213872706</v>
-      </c>
-    </row>
-    <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17">
-        <f>($D$2-D5)/$D$2*100</f>
-        <v>-0.75119689889031593</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="2"/>
-        <v>0.2132759747538252</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="2"/>
-        <v>0.45184029969664713</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="2"/>
-        <v>3.7537317632911193E-4</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="2"/>
-        <v>1.0264123103856701E-2</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="2"/>
-        <v>2.0335704631603887E-3</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="2"/>
-        <v>1.702655712823354E-2</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="2"/>
-        <v>3.1986431218615698E-2</v>
-      </c>
-      <c r="L17">
-        <f t="shared" ref="L17:Z17" si="5">L5/$D5*100</f>
-        <v>3.0495031967287407E-4</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="5"/>
-        <v>1.0353076107289905E-3</v>
-      </c>
-      <c r="N17">
-        <f t="shared" si="5"/>
-        <v>3.7246414344859459E-2</v>
-      </c>
-      <c r="O17">
-        <f t="shared" si="5"/>
-        <v>2.5948237572740655E-4</v>
-      </c>
-      <c r="P17">
-        <f t="shared" si="5"/>
-        <v>4.6111822994265932E-6</v>
-      </c>
-      <c r="Q17">
-        <f t="shared" si="5"/>
-        <v>5.5552608362734656E-4</v>
-      </c>
-      <c r="R17">
-        <f t="shared" si="5"/>
-        <v>3.7917246736772233E-6</v>
-      </c>
-      <c r="S17">
-        <f t="shared" si="5"/>
-        <v>2.4099535891640817E-5</v>
-      </c>
-      <c r="T17">
-        <f t="shared" si="5"/>
-        <v>7.4542601822729449E-3</v>
-      </c>
-      <c r="U17">
-        <f t="shared" si="5"/>
-        <v>2.4835154887059042E-2</v>
-      </c>
-      <c r="V17">
-        <f t="shared" si="5"/>
-        <v>4.3199148560448312E-2</v>
-      </c>
-      <c r="W17">
-        <f t="shared" si="5"/>
-        <v>2.5180936398370261E-3</v>
-      </c>
-      <c r="X17">
-        <f t="shared" si="5"/>
-        <v>-6.7199029465534741</v>
-      </c>
-      <c r="Y17">
-        <f t="shared" si="5"/>
-        <v>19.408291343248056</v>
-      </c>
-      <c r="Z17">
-        <f t="shared" si="5"/>
-        <v>86.467368433317631</v>
-      </c>
-    </row>
-    <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18">
-        <f>($D$2-D6)/$D$2*100</f>
-        <v>-4.1722557989019737</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="2"/>
-        <v>0.1201433617633051</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="2"/>
-        <v>0.2677414570877632</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="2"/>
-        <v>3.3111448317212506E-4</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="2"/>
-        <v>8.8231685922923898E-3</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="2"/>
-        <v>1.7510516285076346E-3</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="2"/>
-        <v>9.630644515749253E-3</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="2"/>
-        <v>2.6507286726489228E-2</v>
-      </c>
-      <c r="L18">
-        <f t="shared" ref="L18:Z18" si="6">L6/$D6*100</f>
-        <v>2.7003311931139955E-4</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="6"/>
-        <v>5.9579178991973317E-4</v>
-      </c>
-      <c r="N18">
-        <f t="shared" si="6"/>
-        <v>3.1429310006561045E-2</v>
-      </c>
-      <c r="O18">
-        <f t="shared" si="6"/>
-        <v>1.9027629153971424E-4</v>
-      </c>
-      <c r="P18">
-        <f t="shared" si="6"/>
-        <v>4.3162299370574423E-6</v>
-      </c>
-      <c r="Q18">
-        <f t="shared" si="6"/>
-        <v>5.2274346442463503E-4</v>
-      </c>
-      <c r="R18">
-        <f t="shared" si="6"/>
-        <v>2.4650217106959954E-6</v>
-      </c>
-      <c r="S18">
-        <f t="shared" si="6"/>
-        <v>1.4854690007541764E-5</v>
-      </c>
-      <c r="T18">
-        <f t="shared" si="6"/>
-        <v>4.7543600347048848E-3</v>
-      </c>
-      <c r="U18">
-        <f t="shared" si="6"/>
-        <v>1.6083147323328804E-2</v>
-      </c>
-      <c r="V18">
-        <f t="shared" si="6"/>
-        <v>4.169666951716483E-2</v>
-      </c>
-      <c r="W18">
-        <f t="shared" si="6"/>
-        <v>1.7168054452419417E-3</v>
-      </c>
-      <c r="X18">
-        <f t="shared" si="6"/>
-        <v>-2.0663294206890197</v>
-      </c>
-      <c r="Y18">
-        <f t="shared" si="6"/>
-        <v>17.906375208766267</v>
-      </c>
-      <c r="Z18">
-        <f t="shared" si="6"/>
-        <v>83.627745354191632</v>
-      </c>
-    </row>
-    <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19">
-        <f>($D$2-D7)/$D$2*100</f>
-        <v>-5.0159405042810317</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="2"/>
-        <v>0.10120057483312443</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="2"/>
-        <v>0.21423027250789517</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="2"/>
-        <v>3.1466411040414821E-4</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="2"/>
-        <v>8.4187796015490046E-3</v>
-      </c>
-      <c r="I19">
-        <f t="shared" si="2"/>
-        <v>1.6511622548896383E-3</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="2"/>
-        <v>6.4670694232099746E-3</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="2"/>
-        <v>2.2869906913786028E-2</v>
-      </c>
-      <c r="L19">
-        <f t="shared" ref="L19:Z19" si="7">L7/$D7*100</f>
-        <v>2.5709709983352645E-4</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="7"/>
-        <v>4.3045823248110348E-4</v>
-      </c>
-      <c r="N19">
-        <f t="shared" si="7"/>
-        <v>2.8076884206208384E-2</v>
-      </c>
-      <c r="O19">
-        <f t="shared" si="7"/>
-        <v>1.4402362923906768E-4</v>
-      </c>
-      <c r="P19">
-        <f t="shared" si="7"/>
-        <v>4.2471088659942327E-6</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" si="7"/>
-        <v>5.0951511781844412E-4</v>
-      </c>
-      <c r="R19">
-        <f t="shared" si="7"/>
-        <v>1.6239992330993541E-6</v>
-      </c>
-      <c r="S19">
-        <f t="shared" si="7"/>
-        <v>1.3102238294996661E-5</v>
-      </c>
-      <c r="T19">
-        <f t="shared" si="7"/>
-        <v>4.1124270646096814E-3</v>
-      </c>
-      <c r="U19">
-        <f t="shared" si="7"/>
-        <v>1.3533009341656953E-2</v>
-      </c>
-      <c r="V19">
-        <f t="shared" si="7"/>
-        <v>4.1096766572443551E-2</v>
-      </c>
-      <c r="W19">
-        <f t="shared" si="7"/>
-        <v>1.4704782781165815E-3</v>
-      </c>
-      <c r="X19">
-        <f t="shared" si="7"/>
-        <v>-0.62049395510274541</v>
-      </c>
-      <c r="Y19">
-        <f t="shared" si="7"/>
-        <v>17.219801150287275</v>
-      </c>
-      <c r="Z19">
-        <f t="shared" si="7"/>
-        <v>82.955890742281866</v>
-      </c>
-    </row>
-    <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20">
-        <f>($D$2-D8)/$D$2*100</f>
-        <v>-5.1242939129245446</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="2"/>
-        <v>9.8252140807843294E-2</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="2"/>
-        <v>0.19421500098936595</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="2"/>
-        <v>3.0992716679052572E-4</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="2"/>
-        <v>8.2562181074585673E-3</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="2"/>
-        <v>1.6133846764707349E-3</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="2"/>
-        <v>5.537395379822843E-3</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="2"/>
-        <v>2.1672385707426418E-2</v>
-      </c>
-      <c r="L20">
-        <f t="shared" ref="L20:Z20" si="8">L8/$D8*100</f>
-        <v>2.5166112921129073E-4</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="8"/>
-        <v>3.8173108743627692E-4</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="8"/>
-        <v>2.7042921831950527E-2</v>
-      </c>
-      <c r="O20">
-        <f t="shared" si="8"/>
-        <v>1.2474221078196459E-4</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="8"/>
-        <v>4.2310180457459598E-6</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="8"/>
-        <v>5.0508939952110697E-4</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="8"/>
-        <v>1.2750449400580838E-6</v>
-      </c>
-      <c r="S20">
-        <f t="shared" si="8"/>
-        <v>1.2582608372546517E-5</v>
-      </c>
-      <c r="T20">
-        <f t="shared" si="8"/>
-        <v>3.8711283551431325E-3</v>
-      </c>
-      <c r="U20">
-        <f t="shared" si="8"/>
-        <v>1.2438171189793691E-2</v>
-      </c>
-      <c r="V20">
-        <f t="shared" si="8"/>
-        <v>4.0950177078670762E-2</v>
-      </c>
-      <c r="W20">
-        <f t="shared" si="8"/>
-        <v>1.3668272402649788E-3</v>
-      </c>
-      <c r="X20">
-        <f t="shared" si="8"/>
-        <v>-0.2346312954909302</v>
-      </c>
-      <c r="Y20">
-        <f t="shared" si="8"/>
-        <v>16.9474376044713</v>
-      </c>
-      <c r="Z20">
-        <f t="shared" si="8"/>
-        <v>82.870386699990362</v>
-      </c>
-    </row>
-    <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21">
-        <f>($D$2-D9)/$D$2*100</f>
-        <v>-0.97102431619190166</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="2"/>
-        <v>0.17507461794983911</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="2"/>
-        <v>0.42855986623123088</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="2"/>
-        <v>3.6801216634543669E-4</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="2"/>
-        <v>1.0386964084403493E-2</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="2"/>
-        <v>2.0162235313654023E-3</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="2"/>
-        <v>1.6410788324385736E-2</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="2"/>
-        <v>3.2269231645688096E-2</v>
-      </c>
-      <c r="L21">
-        <f t="shared" ref="L21:Z21" si="9">L9/$D9*100</f>
-        <v>3.0445786157696001E-4</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="9"/>
-        <v>1.0019748062855588E-3</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="9"/>
-        <v>3.6815481221279325E-2</v>
-      </c>
-      <c r="O21">
-        <f t="shared" si="9"/>
-        <v>2.6260687313037754E-4</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="9"/>
-        <v>4.5454528365208655E-6</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="9"/>
-        <v>5.5567240927348457E-4</v>
-      </c>
-      <c r="R21">
-        <f t="shared" si="9"/>
-        <v>4.6862558787014836E-6</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="9"/>
-        <v>2.1321570185633007E-5</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="9"/>
-        <v>6.9979738196559111E-3</v>
-      </c>
-      <c r="U21">
-        <f t="shared" si="9"/>
-        <v>2.4422640861430096E-2</v>
-      </c>
-      <c r="V21">
-        <f t="shared" si="9"/>
-        <v>4.321580327483826E-2</v>
-      </c>
-      <c r="W21">
-        <f t="shared" si="9"/>
-        <v>2.4356036635115835E-3</v>
-      </c>
-      <c r="X21">
-        <f t="shared" si="9"/>
-        <v>-6.303156158184037</v>
-      </c>
-      <c r="Y21">
-        <f t="shared" si="9"/>
-        <v>19.242910257486294</v>
-      </c>
-      <c r="Z21">
-        <f t="shared" si="9"/>
-        <v>86.27911742869459</v>
-      </c>
-    </row>
-    <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22">
-        <f>($D$2-D10)/$D$2*100</f>
-        <v>-3.7542312601775847</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="2"/>
-        <v>0.13273177131372202</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="2"/>
-        <v>0.3220313734848092</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="2"/>
-        <v>3.3844423086553548E-4</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="2"/>
-        <v>9.5940166010902023E-3</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="2"/>
-        <v>1.8304003250811122E-3</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="2"/>
-        <v>1.0219265800458018E-2</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="2"/>
-        <v>2.703377540698287E-2</v>
-      </c>
-      <c r="L22">
-        <f t="shared" ref="L22:Z22" si="10">L10/$D10*100</f>
-        <v>2.8147703154742632E-4</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="10"/>
-        <v>6.725057232068644E-4</v>
-      </c>
-      <c r="N22">
-        <f t="shared" si="10"/>
-        <v>3.2060656435209348E-2</v>
-      </c>
-      <c r="O22">
-        <f t="shared" si="10"/>
-        <v>2.0567455836105383E-4</v>
-      </c>
-      <c r="P22">
-        <f t="shared" si="10"/>
-        <v>4.3586081461030972E-6</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="10"/>
-        <v>5.2931245880721671E-4</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="10"/>
-        <v>2.7864308114701047E-6</v>
-      </c>
-      <c r="S22">
-        <f t="shared" si="10"/>
-        <v>1.7538299106435929E-5</v>
-      </c>
-      <c r="T22">
-        <f t="shared" si="10"/>
-        <v>5.6989857010120958E-3</v>
-      </c>
-      <c r="U22">
-        <f t="shared" si="10"/>
-        <v>1.9645580981821786E-2</v>
-      </c>
-      <c r="V22">
-        <f t="shared" si="10"/>
-        <v>4.1802729972772013E-2</v>
-      </c>
-      <c r="W22">
-        <f t="shared" si="10"/>
-        <v>2.0000919626843427E-3</v>
-      </c>
-      <c r="X22">
-        <f t="shared" si="10"/>
-        <v>-2.6207970615389464</v>
-      </c>
-      <c r="Y22">
-        <f t="shared" si="10"/>
-        <v>18.049415814309167</v>
-      </c>
-      <c r="Z22">
-        <f t="shared" si="10"/>
-        <v>83.964680501903331</v>
-      </c>
-    </row>
-    <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23">
-        <f>($D$2-D11)/$D$2*100</f>
-        <v>-5.5531358956240853</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="2"/>
-        <v>0.11727296322926709</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="2"/>
-        <v>0.22735565878768391</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="2"/>
-        <v>3.1918194038419204E-4</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="2"/>
-        <v>8.341599209670392E-3</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="2"/>
-        <v>1.6708553363576557E-3</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="2"/>
-        <v>6.7972469434363636E-3</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="2"/>
-        <v>2.4005777564452425E-2</v>
-      </c>
-      <c r="L23">
-        <f t="shared" ref="L23:Z23" si="11">L11/$D11*100</f>
-        <v>2.5868883342448944E-4</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="11"/>
-        <v>4.4138630255663284E-4</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="11"/>
-        <v>2.9205064054717976E-2</v>
-      </c>
-      <c r="O23">
-        <f t="shared" si="11"/>
-        <v>1.6093758298954617E-4</v>
-      </c>
-      <c r="P23">
-        <f t="shared" si="11"/>
-        <v>4.2711645993226305E-6</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="11"/>
-        <v>5.0967110322916941E-4</v>
-      </c>
-      <c r="R23">
-        <f t="shared" si="11"/>
-        <v>2.1974368009794521E-6</v>
-      </c>
-      <c r="S23">
-        <f t="shared" si="11"/>
-        <v>1.4294162470511983E-5</v>
-      </c>
-      <c r="T23">
-        <f t="shared" si="11"/>
-        <v>4.3522567995498244E-3</v>
-      </c>
-      <c r="U23">
-        <f t="shared" si="11"/>
-        <v>1.3954846432836756E-2</v>
-      </c>
-      <c r="V23">
-        <f t="shared" si="11"/>
-        <v>4.0976462607474076E-2</v>
-      </c>
-      <c r="W23">
-        <f t="shared" si="11"/>
-        <v>1.5381060327853524E-3</v>
-      </c>
-      <c r="X23">
-        <f t="shared" si="11"/>
-        <v>-0.44387439540245122</v>
-      </c>
-      <c r="Y23">
-        <f t="shared" si="11"/>
-        <v>17.432992591581396</v>
-      </c>
-      <c r="Z23">
-        <f t="shared" si="11"/>
-        <v>82.533700338296356</v>
       </c>
     </row>
   </sheetData>
@@ -2337,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -3281,942 +2345,6 @@
       </c>
       <c r="AB11">
         <v>2.613105251177664</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="E14">
-        <f>E2/$D2*100</f>
-        <v>3.158396792127633</v>
-      </c>
-      <c r="F14">
-        <f t="shared" ref="F14:Z23" si="0">F2/$D2*100</f>
-        <v>0.49709302410168149</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>1.1774614165587112</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>8.8634279927532781E-4</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>2.4787807144608074E-2</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>4.900779143960806E-3</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>4.6304268811648584E-2</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="0"/>
-        <v>1.4142073023475752E-2</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="0"/>
-        <v>8.6150244062020834E-2</v>
-      </c>
-      <c r="N14">
-        <f t="shared" si="0"/>
-        <v>7.2944096239632716E-4</v>
-      </c>
-      <c r="O14">
-        <f t="shared" si="0"/>
-        <v>2.8359068975174935E-3</v>
-      </c>
-      <c r="P14">
-        <f t="shared" si="0"/>
-        <v>9.2428500133512295E-2</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="0"/>
-        <v>6.9944950535570671E-4</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="0"/>
-        <v>1.0617684956271105E-5</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="0"/>
-        <v>1.2987612294328267E-3</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="0"/>
-        <v>1.1693196616972474E-5</v>
-      </c>
-      <c r="U14">
-        <f t="shared" si="0"/>
-        <v>5.784608131962424E-5</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="0"/>
-        <v>1.8673166375066066E-2</v>
-      </c>
-      <c r="W14">
-        <f t="shared" si="0"/>
-        <v>6.4789453558587548E-2</v>
-      </c>
-      <c r="X14">
-        <f t="shared" si="0"/>
-        <v>9.9818722583668806E-2</v>
-      </c>
-      <c r="Y14">
-        <f t="shared" si="0"/>
-        <v>6.3897414102157104E-3</v>
-      </c>
-      <c r="Z14">
-        <f t="shared" si="0"/>
-        <v>-8.4429266288736731</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="D15">
-        <f>($D$2-D3)/$D$2*100</f>
-        <v>0.52547761602750676</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ref="E15:K23" si="1">E3/$D3*100</f>
-        <v>3.0571495070959225</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>0.44818435890178859</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>1.1043898504629359</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>8.7418678626273796E-4</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>2.4584123487545854E-2</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>4.8113663483739522E-3</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>4.4025911178145367E-2</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="0"/>
-        <v>1.3700936192835278E-2</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="0"/>
-        <v>8.190049187475551E-2</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="0"/>
-        <v>7.2118018557775041E-4</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="0"/>
-        <v>2.6750406248442532E-3</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="0"/>
-        <v>9.0524629558110359E-2</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="0"/>
-        <v>6.6083421382702825E-4</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="0"/>
-        <v>1.0578940841541539E-5</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="0"/>
-        <v>1.2967674286693039E-3</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="0"/>
-        <v>1.1231690355848205E-5</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="0"/>
-        <v>5.3195935224890303E-5</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="0"/>
-        <v>1.7611581112906335E-2</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="0"/>
-        <v>6.1790770202962919E-2</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="0"/>
-        <v>0.10013420322380021</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="0"/>
-        <v>6.070512094437098E-3</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="0"/>
-        <v>-8.1708992326611849</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>($D$2-D4)/$D$2*100</f>
-        <v>0.71628972864160811</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="1"/>
-        <v>2.9058878562931132</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="1"/>
-        <v>0.45450153135996674</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="1"/>
-        <v>1.070929095880548</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="1"/>
-        <v>8.6803601856297536E-4</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="1"/>
-        <v>2.4291808540899587E-2</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="1"/>
-        <v>4.7496566207571823E-3</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>4.1658253143506907E-2</v>
-      </c>
-      <c r="L16">
-        <f t="shared" si="0"/>
-        <v>1.3726728665252194E-2</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="0"/>
-        <v>7.6621336757711697E-2</v>
-      </c>
-      <c r="N16">
-        <f t="shared" si="0"/>
-        <v>7.1376289830056051E-4</v>
-      </c>
-      <c r="O16">
-        <f t="shared" si="0"/>
-        <v>2.5353121345633141E-3</v>
-      </c>
-      <c r="P16">
-        <f t="shared" si="0"/>
-        <v>8.7763014727710309E-2</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="0"/>
-        <v>6.2105279575981338E-4</v>
-      </c>
-      <c r="R16">
-        <f t="shared" si="0"/>
-        <v>1.0584986393851263E-5</v>
-      </c>
-      <c r="S16">
-        <f t="shared" si="0"/>
-        <v>1.2899779270671968E-3</v>
-      </c>
-      <c r="T16">
-        <f t="shared" si="0"/>
-        <v>9.5726818827521373E-6</v>
-      </c>
-      <c r="U16">
-        <f t="shared" si="0"/>
-        <v>5.3656441572330841E-5</v>
-      </c>
-      <c r="V16">
-        <f t="shared" si="0"/>
-        <v>1.739283025382897E-2</v>
-      </c>
-      <c r="W16">
-        <f t="shared" si="0"/>
-        <v>6.0075178568287362E-2</v>
-      </c>
-      <c r="X16">
-        <f t="shared" si="0"/>
-        <v>9.9957618732463616E-2</v>
-      </c>
-      <c r="Y16">
-        <f t="shared" si="0"/>
-        <v>5.9314083809694426E-3</v>
-      </c>
-      <c r="Z16">
-        <f t="shared" si="0"/>
-        <v>-7.7635471479466629</v>
-      </c>
-    </row>
-    <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17">
-        <f>($D$2-D5)/$D$2*100</f>
-        <v>0.50825240578662556</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="1"/>
-        <v>2.6430290280422373</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="1"/>
-        <v>0.49182990758789441</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="1"/>
-        <v>1.0419765897251065</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="1"/>
-        <v>8.6573703210630351E-4</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="1"/>
-        <v>2.3672526524153473E-2</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="1"/>
-        <v>4.6900987294093395E-3</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>3.9268978085587672E-2</v>
-      </c>
-      <c r="L17">
-        <f t="shared" si="0"/>
-        <v>1.3721266745285848E-2</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="0"/>
-        <v>7.377148868676138E-2</v>
-      </c>
-      <c r="N17">
-        <f t="shared" si="0"/>
-        <v>7.0331819464370055E-4</v>
-      </c>
-      <c r="O17">
-        <f t="shared" si="0"/>
-        <v>2.3877682124088203E-3</v>
-      </c>
-      <c r="P17">
-        <f t="shared" si="0"/>
-        <v>8.5902782204258107E-2</v>
-      </c>
-      <c r="Q17">
-        <f t="shared" si="0"/>
-        <v>5.9845379481558735E-4</v>
-      </c>
-      <c r="R17">
-        <f t="shared" si="0"/>
-        <v>1.0634940187912131E-5</v>
-      </c>
-      <c r="S17">
-        <f t="shared" si="0"/>
-        <v>1.2812303414975741E-3</v>
-      </c>
-      <c r="T17">
-        <f t="shared" si="0"/>
-        <v>8.7449947746811822E-6</v>
-      </c>
-      <c r="U17">
-        <f t="shared" si="0"/>
-        <v>5.5575282326938685E-5</v>
-      </c>
-      <c r="V17">
-        <f t="shared" si="0"/>
-        <v>1.7190066067287672E-2</v>
-      </c>
-      <c r="W17">
-        <f t="shared" si="0"/>
-        <v>5.7271673225920985E-2</v>
-      </c>
-      <c r="X17">
-        <f t="shared" si="0"/>
-        <v>9.9631793166413699E-2</v>
-      </c>
-      <c r="Y17">
-        <f t="shared" si="0"/>
-        <v>5.8075724420088154E-3</v>
-      </c>
-      <c r="Z17">
-        <f t="shared" si="0"/>
-        <v>-7.0518037872466852</v>
-      </c>
-    </row>
-    <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18">
-        <f>($D$2-D6)/$D$2*100</f>
-        <v>0.20844339685476124</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="1"/>
-        <v>0.84207594903354999</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="1"/>
-        <v>0.28560637390832971</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="1"/>
-        <v>0.6364785001972868</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="1"/>
-        <v>7.8721988200888208E-4</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="1"/>
-        <v>2.0976955376966179E-2</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="1"/>
-        <v>4.1630998534989087E-3</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
-        <v>2.2896717675187025E-2</v>
-      </c>
-      <c r="L18">
-        <f t="shared" si="0"/>
-        <v>1.0914004611678007E-2</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="0"/>
-        <v>6.3020689790712084E-2</v>
-      </c>
-      <c r="N18">
-        <f t="shared" si="0"/>
-        <v>6.4199982521545584E-4</v>
-      </c>
-      <c r="O18">
-        <f t="shared" si="0"/>
-        <v>1.4164863405224716E-3</v>
-      </c>
-      <c r="P18">
-        <f t="shared" si="0"/>
-        <v>7.4722728761230012E-2</v>
-      </c>
-      <c r="Q18">
-        <f t="shared" si="0"/>
-        <v>4.5237912380025882E-4</v>
-      </c>
-      <c r="R18">
-        <f t="shared" si="0"/>
-        <v>1.0261774082552757E-5</v>
-      </c>
-      <c r="S18">
-        <f t="shared" si="0"/>
-        <v>1.2428150059849716E-3</v>
-      </c>
-      <c r="T18">
-        <f t="shared" si="0"/>
-        <v>5.8605533701003517E-6</v>
-      </c>
-      <c r="U18">
-        <f t="shared" si="0"/>
-        <v>3.5312763737580824E-5</v>
-      </c>
-      <c r="V18">
-        <f t="shared" si="0"/>
-        <v>1.1302126974288415E-2</v>
-      </c>
-      <c r="W18">
-        <f t="shared" si="0"/>
-        <v>3.8233068566026658E-2</v>
-      </c>
-      <c r="X18">
-        <f t="shared" si="0"/>
-        <v>9.9133227103214733E-2</v>
-      </c>
-      <c r="Y18">
-        <f t="shared" si="0"/>
-        <v>4.0816800494136276E-3</v>
-      </c>
-      <c r="Z18">
-        <f t="shared" si="0"/>
-        <v>-2.2352798092478667</v>
-      </c>
-    </row>
-    <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19">
-        <f>($D$2-D7)/$D$2*100</f>
-        <v>0.71391969122896515</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="1"/>
-        <v>0.25841190992127216</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="1"/>
-        <v>0.24375845232226012</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="1"/>
-        <v>0.51600931865466149</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="1"/>
-        <v>7.5800780414652746E-4</v>
-      </c>
-      <c r="I19">
-        <f t="shared" si="1"/>
-        <v>2.0280357461699292E-2</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="1"/>
-        <v>3.9775552207431649E-3</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
-        <v>1.557879952198679E-2</v>
-      </c>
-      <c r="L19">
-        <f t="shared" si="0"/>
-        <v>1.0404433666068202E-2</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="0"/>
-        <v>5.5092294759923464E-2</v>
-      </c>
-      <c r="N19">
-        <f t="shared" si="0"/>
-        <v>6.1933217565533587E-4</v>
-      </c>
-      <c r="O19">
-        <f t="shared" si="0"/>
-        <v>1.0369492064433896E-3</v>
-      </c>
-      <c r="P19">
-        <f t="shared" si="0"/>
-        <v>6.7635604572410635E-2</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" si="0"/>
-        <v>3.4694466682108177E-4</v>
-      </c>
-      <c r="R19">
-        <f t="shared" si="0"/>
-        <v>1.0231041796754891E-5</v>
-      </c>
-      <c r="S19">
-        <f t="shared" si="0"/>
-        <v>1.2273927113612337E-3</v>
-      </c>
-      <c r="T19">
-        <f t="shared" si="0"/>
-        <v>3.9121210583444334E-6</v>
-      </c>
-      <c r="U19">
-        <f t="shared" si="0"/>
-        <v>3.1558924778957552E-5</v>
-      </c>
-      <c r="V19">
-        <f t="shared" si="0"/>
-        <v>9.9054660332750753E-3</v>
-      </c>
-      <c r="W19">
-        <f t="shared" si="0"/>
-        <v>3.2596508644551686E-2</v>
-      </c>
-      <c r="X19">
-        <f t="shared" si="0"/>
-        <v>9.8999754840454382E-2</v>
-      </c>
-      <c r="Y19">
-        <f t="shared" si="0"/>
-        <v>3.5422978782318178E-3</v>
-      </c>
-      <c r="Z19">
-        <f t="shared" si="0"/>
-        <v>-0.68010893395607808</v>
-      </c>
-    </row>
-    <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20">
-        <f>($D$2-D8)/$D$2*100</f>
-        <v>1.1178763621694283</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="1"/>
-        <v>0.10028529446102546</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="1"/>
-        <v>0.23786863076480469</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="1"/>
-        <v>0.47019490852292634</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="1"/>
-        <v>7.5042027251603742E-4</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="1"/>
-        <v>1.9990611040362333E-2</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="1"/>
-        <v>3.9064551234021692E-3</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
-        <v>1.3407581506929493E-2</v>
-      </c>
-      <c r="L20">
-        <f t="shared" si="0"/>
-        <v>1.0219591355961346E-2</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="0"/>
-        <v>5.2474901626264184E-2</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="0"/>
-        <v>6.0934191448945162E-4</v>
-      </c>
-      <c r="O20">
-        <f t="shared" si="0"/>
-        <v>9.2427762828350773E-4</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="0"/>
-        <v>6.5478470251297036E-2</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="0"/>
-        <v>3.0203574852321214E-4</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="0"/>
-        <v>1.0244476945304088E-5</v>
-      </c>
-      <c r="S20">
-        <f t="shared" si="0"/>
-        <v>1.2229625713636454E-3</v>
-      </c>
-      <c r="T20">
-        <f t="shared" si="0"/>
-        <v>3.0872400806195842E-6</v>
-      </c>
-      <c r="U20">
-        <f t="shared" si="0"/>
-        <v>3.0462520209925776E-5</v>
-      </c>
-      <c r="V20">
-        <f t="shared" si="0"/>
-        <v>9.3720095438275478E-3</v>
-      </c>
-      <c r="W20">
-        <f t="shared" si="0"/>
-        <v>3.0112837499638764E-2</v>
-      </c>
-      <c r="X20">
-        <f t="shared" si="0"/>
-        <v>9.9151821252655328E-2</v>
-      </c>
-      <c r="Y20">
-        <f t="shared" si="0"/>
-        <v>3.3094706757837641E-3</v>
-      </c>
-      <c r="Z20">
-        <f t="shared" si="0"/>
-        <v>-0.25849093037307225</v>
-      </c>
-    </row>
-    <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21">
-        <f>($D$2-D9)/$D$2*100</f>
-        <v>0.66922617795606676</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="1"/>
-        <v>2.4847037243356507</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="1"/>
-        <v>0.4052714165666203</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="1"/>
-        <v>0.99205165263244877</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="1"/>
-        <v>8.5199044597835869E-4</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="1"/>
-        <v>2.4047015212875882E-2</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="1"/>
-        <v>4.6677891188728927E-3</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="1"/>
-        <v>3.7992860405125076E-2</v>
-      </c>
-      <c r="L21">
-        <f t="shared" si="0"/>
-        <v>1.3146742580931356E-2</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="0"/>
-        <v>7.4706978669238422E-2</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="0"/>
-        <v>7.0485492869028883E-4</v>
-      </c>
-      <c r="O21">
-        <f t="shared" si="0"/>
-        <v>2.3196867933572823E-3</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="0"/>
-        <v>8.5232068754986151E-2</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="0"/>
-        <v>6.0796508217969938E-4</v>
-      </c>
-      <c r="R21">
-        <f t="shared" si="0"/>
-        <v>1.0523245543262534E-5</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="0"/>
-        <v>1.2864454686272509E-3</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="0"/>
-        <v>1.0849220762761042E-5</v>
-      </c>
-      <c r="U21">
-        <f t="shared" si="0"/>
-        <v>4.9356229096737749E-5</v>
-      </c>
-      <c r="V21">
-        <f t="shared" si="0"/>
-        <v>1.6199257186445208E-2</v>
-      </c>
-      <c r="W21">
-        <f t="shared" si="0"/>
-        <v>5.6534741438335541E-2</v>
-      </c>
-      <c r="X21">
-        <f t="shared" si="0"/>
-        <v>0.10004954964146939</v>
-      </c>
-      <c r="Y21">
-        <f t="shared" si="0"/>
-        <v>5.638702307341501E-3</v>
-      </c>
-      <c r="Z21">
-        <f t="shared" si="0"/>
-        <v>-6.6396482810791984</v>
-      </c>
-    </row>
-    <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22">
-        <f>($D$2-D10)/$D$2*100</f>
-        <v>0.24367921759453998</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="1"/>
-        <v>1.0579324863809694</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="1"/>
-        <v>0.31437653855865999</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="1"/>
-        <v>0.76273455482002683</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="1"/>
-        <v>8.0170042585510348E-4</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="1"/>
-        <v>2.2726128836897813E-2</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="1"/>
-        <v>4.335818389783282E-3</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="1"/>
-        <v>2.4207207560316479E-2</v>
-      </c>
-      <c r="L22">
-        <f t="shared" si="0"/>
-        <v>1.2005760382999702E-2</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="0"/>
-        <v>6.4037106500007393E-2</v>
-      </c>
-      <c r="N22">
-        <f t="shared" si="0"/>
-        <v>6.6675757918195177E-4</v>
-      </c>
-      <c r="O22">
-        <f t="shared" si="0"/>
-        <v>1.5930191018653883E-3</v>
-      </c>
-      <c r="P22">
-        <f t="shared" si="0"/>
-        <v>7.5944689178387439E-2</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="0"/>
-        <v>4.8719808461184264E-4</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="0"/>
-        <v>1.0324590252078093E-5</v>
-      </c>
-      <c r="S22">
-        <f t="shared" si="0"/>
-        <v>1.2538255491929262E-3</v>
-      </c>
-      <c r="T22">
-        <f t="shared" si="0"/>
-        <v>6.6004456996015097E-6</v>
-      </c>
-      <c r="U22">
-        <f t="shared" si="0"/>
-        <v>4.1539638254776684E-5</v>
-      </c>
-      <c r="V22">
-        <f t="shared" si="0"/>
-        <v>1.3498105090037758E-2</v>
-      </c>
-      <c r="W22">
-        <f t="shared" si="0"/>
-        <v>4.6530756622250175E-2</v>
-      </c>
-      <c r="X22">
-        <f t="shared" si="0"/>
-        <v>9.9021532544285279E-2</v>
-      </c>
-      <c r="Y22">
-        <f t="shared" si="0"/>
-        <v>4.7377807981323523E-3</v>
-      </c>
-      <c r="Z22">
-        <f t="shared" si="0"/>
-        <v>-2.8247033911287152</v>
-      </c>
-    </row>
-    <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23">
-        <f>($D$2-D11)/$D$2*100</f>
-        <v>-0.20376062657300439</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="1"/>
-        <v>0.18874305000446806</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>0.28131627773015727</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>0.54538442527456499</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="1"/>
-        <v>7.6574652575652435E-4</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="1"/>
-        <v>2.0012255725903288E-2</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="1"/>
-        <v>4.0085340270742649E-3</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>1.6307214077903174E-2</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="0"/>
-        <v>1.0554566412802323E-2</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="0"/>
-        <v>5.7592045295347706E-2</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="0"/>
-        <v>6.2061805629846879E-4</v>
-      </c>
-      <c r="O23">
-        <f t="shared" si="0"/>
-        <v>1.0589259132030738E-3</v>
-      </c>
-      <c r="P23">
-        <f t="shared" si="0"/>
-        <v>7.0065606805567976E-2</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="0"/>
-        <v>3.8610390954312517E-4</v>
-      </c>
-      <c r="R23">
-        <f t="shared" si="0"/>
-        <v>1.0246912619582356E-5</v>
-      </c>
-      <c r="S23">
-        <f t="shared" si="0"/>
-        <v>1.2227473650497317E-3</v>
-      </c>
-      <c r="T23">
-        <f t="shared" si="0"/>
-        <v>5.2718508882242613E-6</v>
-      </c>
-      <c r="U23">
-        <f t="shared" si="0"/>
-        <v>3.4289067733482427E-5</v>
-      </c>
-      <c r="V23">
-        <f t="shared" si="0"/>
-        <v>1.0440263884025108E-2</v>
-      </c>
-      <c r="W23">
-        <f t="shared" si="0"/>
-        <v>3.3475110943562959E-2</v>
-      </c>
-      <c r="X23">
-        <f t="shared" si="0"/>
-        <v>9.830626332334752E-2</v>
-      </c>
-      <c r="Y23">
-        <f t="shared" si="0"/>
-        <v>3.6900563654473791E-3</v>
-      </c>
-      <c r="Z23">
-        <f t="shared" si="0"/>
-        <v>-0.48453067583511705</v>
       </c>
     </row>
   </sheetData>
@@ -4226,7 +2354,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -5104,942 +3232,6 @@
       </c>
       <c r="Z11">
         <v>8.9251899794676142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="E14">
-        <f>E2/$D2*100</f>
-        <v>0.2018420958339551</v>
-      </c>
-      <c r="F14">
-        <f t="shared" ref="F14:Z23" si="0">F2/$D2*100</f>
-        <v>0.47810222344462727</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>3.5985375449851454E-4</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>1.0063809932303033E-2</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>1.9897084698653816E-3</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>1.8799458849108559E-2</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>3.4976860873725507E-2</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="0"/>
-        <v>2.9615186045166844E-4</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="0"/>
-        <v>1.1513736505946372E-3</v>
-      </c>
-      <c r="N14">
-        <f t="shared" si="0"/>
-        <v>3.7525822766208257E-2</v>
-      </c>
-      <c r="O14">
-        <f t="shared" si="0"/>
-        <v>2.8397537701007892E-4</v>
-      </c>
-      <c r="P14">
-        <f t="shared" si="0"/>
-        <v>4.3107630577248921E-6</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="0"/>
-        <v>5.2729497547746235E-4</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="0"/>
-        <v>4.7474190664686345E-6</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="0"/>
-        <v>2.3488107302318601E-5</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="0"/>
-        <v>7.5821442954478206E-3</v>
-      </c>
-      <c r="U14">
-        <f t="shared" si="0"/>
-        <v>2.6307428308443324E-2</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="0"/>
-        <v>4.0526241224441741E-2</v>
-      </c>
-      <c r="W14">
-        <f t="shared" si="0"/>
-        <v>2.5942247611428883E-3</v>
-      </c>
-      <c r="X14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <f t="shared" si="0"/>
-        <v>18.583174371001025</v>
-      </c>
-      <c r="Z14">
-        <f t="shared" si="0"/>
-        <v>80.553864414332281</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D15">
-        <f>($D$2-D3)/$D$2*100</f>
-        <v>0.29711373958273335</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ref="E15:K23" si="1">E3/$D3*100</f>
-        <v>0.18156615909573809</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>0.44740477732024619</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>3.5410551192741399E-4</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>9.9582535101689091E-3</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>1.9489328489452049E-3</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>1.7833508880243456E-2</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>3.3175307678124641E-2</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="0"/>
-        <v>2.9212736090152225E-4</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="0"/>
-        <v>1.0835746373343232E-3</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="0"/>
-        <v>3.6668674012741174E-2</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="0"/>
-        <v>2.6768310990694786E-4</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="0"/>
-        <v>4.2851954767685208E-6</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="0"/>
-        <v>5.2527961002802129E-4</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="0"/>
-        <v>4.5496037297370837E-6</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="0"/>
-        <v>2.1550465665414939E-5</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="0"/>
-        <v>7.1347138175657599E-3</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="0"/>
-        <v>2.5032361327396575E-2</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="0"/>
-        <v>4.0561209401934965E-2</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="0"/>
-        <v>2.4589731012202025E-3</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="0"/>
-        <v>18.399789741327041</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="0"/>
-        <v>80.793914232183681</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>($D$2-D4)/$D$2*100</f>
-        <v>0.48442694640235984</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="1"/>
-        <v>0.18411805553132263</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="1"/>
-        <v>0.43383216367928745</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="1"/>
-        <v>3.5160011954401529E-4</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="1"/>
-        <v>9.8394566633999443E-3</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="1"/>
-        <v>1.9238600702490239E-3</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="1"/>
-        <v>1.6873777668235373E-2</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>3.1035660488181925E-2</v>
-      </c>
-      <c r="L16">
-        <f t="shared" si="0"/>
-        <v>2.8911141358398942E-4</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="0"/>
-        <v>1.0269344019497989E-3</v>
-      </c>
-      <c r="N16">
-        <f t="shared" si="0"/>
-        <v>3.5548624492437959E-2</v>
-      </c>
-      <c r="O16">
-        <f t="shared" si="0"/>
-        <v>2.5155895903235871E-4</v>
-      </c>
-      <c r="P16">
-        <f t="shared" si="0"/>
-        <v>4.2874747151749376E-6</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="0"/>
-        <v>5.225087250605398E-4</v>
-      </c>
-      <c r="R16">
-        <f t="shared" si="0"/>
-        <v>3.8774382886835212E-6</v>
-      </c>
-      <c r="S16">
-        <f t="shared" si="0"/>
-        <v>2.1736163703270998E-5</v>
-      </c>
-      <c r="T16">
-        <f t="shared" si="0"/>
-        <v>7.04581583463378E-3</v>
-      </c>
-      <c r="U16">
-        <f t="shared" si="0"/>
-        <v>2.4336386789692369E-2</v>
-      </c>
-      <c r="V16">
-        <f t="shared" si="0"/>
-        <v>4.0488078771030347E-2</v>
-      </c>
-      <c r="W16">
-        <f t="shared" si="0"/>
-        <v>2.402531520829893E-3</v>
-      </c>
-      <c r="X16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <f t="shared" si="0"/>
-        <v>18.264095382060997</v>
-      </c>
-      <c r="Z16">
-        <f t="shared" si="0"/>
-        <v>80.945988591733837</v>
-      </c>
-    </row>
-    <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17">
-        <f>($D$2-D5)/$D$2*100</f>
-        <v>0.57867213506373627</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="1"/>
-        <v>0.19984648440239433</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="1"/>
-        <v>0.42338897060452729</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="1"/>
-        <v>3.5173680352379981E-4</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="1"/>
-        <v>9.617815228118486E-3</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="1"/>
-        <v>1.9055212773789632E-3</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="1"/>
-        <v>1.5954434565269626E-2</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>2.9972320300013969E-2</v>
-      </c>
-      <c r="L17">
-        <f t="shared" si="0"/>
-        <v>2.8574830978667066E-4</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="0"/>
-        <v>9.7011670685387625E-4</v>
-      </c>
-      <c r="N17">
-        <f t="shared" si="0"/>
-        <v>3.4901094565418553E-2</v>
-      </c>
-      <c r="O17">
-        <f t="shared" si="0"/>
-        <v>2.4314337615082593E-4</v>
-      </c>
-      <c r="P17">
-        <f t="shared" si="0"/>
-        <v>4.3208269123731938E-6</v>
-      </c>
-      <c r="Q17">
-        <f t="shared" si="0"/>
-        <v>5.2054590272017755E-4</v>
-      </c>
-      <c r="R17">
-        <f t="shared" si="0"/>
-        <v>3.5529686207312399E-6</v>
-      </c>
-      <c r="S17">
-        <f t="shared" si="0"/>
-        <v>2.2582044364035237E-5</v>
-      </c>
-      <c r="T17">
-        <f t="shared" si="0"/>
-        <v>6.9848828165830741E-3</v>
-      </c>
-      <c r="U17">
-        <f t="shared" si="0"/>
-        <v>2.3271343148221508E-2</v>
-      </c>
-      <c r="V17">
-        <f t="shared" si="0"/>
-        <v>4.0478999000929473E-2</v>
-      </c>
-      <c r="W17">
-        <f t="shared" si="0"/>
-        <v>2.3595351604807657E-3</v>
-      </c>
-      <c r="X17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <f t="shared" si="0"/>
-        <v>18.18619653565073</v>
-      </c>
-      <c r="Z17">
-        <f t="shared" si="0"/>
-        <v>81.02272031634098</v>
-      </c>
-    </row>
-    <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18">
-        <f>($D$2-D6)/$D$2*100</f>
-        <v>1.6852932702094574</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="1"/>
-        <v>0.1177110633293542</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="1"/>
-        <v>0.26232104003583079</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="1"/>
-        <v>3.2441108127743957E-4</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="1"/>
-        <v>8.6445438323843292E-3</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="1"/>
-        <v>1.7156016454933662E-3</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="1"/>
-        <v>9.4356724321501308E-3</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
-        <v>2.5970647572674407E-2</v>
-      </c>
-      <c r="L18">
-        <f t="shared" si="0"/>
-        <v>2.6456630763261566E-4</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="0"/>
-        <v>5.8373000459664931E-4</v>
-      </c>
-      <c r="N18">
-        <f t="shared" si="0"/>
-        <v>3.0793024652238089E-2</v>
-      </c>
-      <c r="O18">
-        <f t="shared" si="0"/>
-        <v>1.8642415423360311E-4</v>
-      </c>
-      <c r="P18">
-        <f t="shared" si="0"/>
-        <v>4.2288480029880456E-6</v>
-      </c>
-      <c r="Q18">
-        <f t="shared" si="0"/>
-        <v>5.1216054006479367E-4</v>
-      </c>
-      <c r="R18">
-        <f t="shared" si="0"/>
-        <v>2.415117426692415E-6</v>
-      </c>
-      <c r="S18">
-        <f t="shared" si="0"/>
-        <v>1.4553957293624934E-5</v>
-      </c>
-      <c r="T18">
-        <f t="shared" si="0"/>
-        <v>4.6581081711218287E-3</v>
-      </c>
-      <c r="U18">
-        <f t="shared" si="0"/>
-        <v>1.5757544531186173E-2</v>
-      </c>
-      <c r="V18">
-        <f t="shared" si="0"/>
-        <v>4.0852521804972682E-2</v>
-      </c>
-      <c r="W18">
-        <f t="shared" si="0"/>
-        <v>1.6820487750891029E-3</v>
-      </c>
-      <c r="X18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <f t="shared" si="0"/>
-        <v>17.543861227645742</v>
-      </c>
-      <c r="Z18">
-        <f t="shared" si="0"/>
-        <v>81.934704465561268</v>
-      </c>
-    </row>
-    <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19">
-        <f>($D$2-D7)/$D$2*100</f>
-        <v>2.2930191812655667</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="1"/>
-        <v>0.10057650368161951</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="1"/>
-        <v>0.21290918383748322</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="1"/>
-        <v>3.1272367880046418E-4</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="1"/>
-        <v>8.3668637158055854E-3</v>
-      </c>
-      <c r="I19">
-        <f t="shared" si="1"/>
-        <v>1.6409800723138021E-3</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="1"/>
-        <v>6.4271891016953993E-3</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
-        <v>2.2728875608716555E-2</v>
-      </c>
-      <c r="L19">
-        <f t="shared" si="0"/>
-        <v>2.5551166532975758E-4</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="0"/>
-        <v>4.2780373604902071E-4</v>
-      </c>
-      <c r="N19">
-        <f t="shared" si="0"/>
-        <v>2.7903743159468961E-2</v>
-      </c>
-      <c r="O19">
-        <f t="shared" si="0"/>
-        <v>1.4313548218761711E-4</v>
-      </c>
-      <c r="P19">
-        <f t="shared" si="0"/>
-        <v>4.2209183218699693E-6</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" si="0"/>
-        <v>5.0637310319243589E-4</v>
-      </c>
-      <c r="R19">
-        <f t="shared" si="0"/>
-        <v>1.6139845560768708E-6</v>
-      </c>
-      <c r="S19">
-        <f t="shared" si="0"/>
-        <v>1.3021441037139841E-5</v>
-      </c>
-      <c r="T19">
-        <f t="shared" si="0"/>
-        <v>4.0870670595116575E-3</v>
-      </c>
-      <c r="U19">
-        <f t="shared" si="0"/>
-        <v>1.3449555658344371E-2</v>
-      </c>
-      <c r="V19">
-        <f t="shared" si="0"/>
-        <v>4.0843336130172991E-2</v>
-      </c>
-      <c r="W19">
-        <f t="shared" si="0"/>
-        <v>1.4614103150758537E-3</v>
-      </c>
-      <c r="X19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <f t="shared" si="0"/>
-        <v>17.113612216575525</v>
-      </c>
-      <c r="Z19">
-        <f t="shared" si="0"/>
-        <v>82.444328671074786</v>
-      </c>
-    </row>
-    <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20">
-        <f>($D$2-D8)/$D$2*100</f>
-        <v>2.567283455580033</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="1"/>
-        <v>9.8022150157513116E-2</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="1"/>
-        <v>0.19376037848430747</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="1"/>
-        <v>3.0920168284626694E-4</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="1"/>
-        <v>8.2368917807628898E-3</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="1"/>
-        <v>1.6096080321358298E-3</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="1"/>
-        <v>5.5244333297945238E-3</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
-        <v>2.1621654537173289E-2</v>
-      </c>
-      <c r="L20">
-        <f t="shared" si="0"/>
-        <v>2.5107203561705214E-4</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="0"/>
-        <v>3.8083752338435037E-4</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="0"/>
-        <v>2.697961919927688E-2</v>
-      </c>
-      <c r="O20">
-        <f t="shared" si="0"/>
-        <v>1.244502116260635E-4</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="0"/>
-        <v>4.2211139908938326E-6</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="0"/>
-        <v>5.0390707577207096E-4</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="0"/>
-        <v>1.2720602884000842E-6</v>
-      </c>
-      <c r="S20">
-        <f t="shared" si="0"/>
-        <v>1.255315474172832E-5</v>
-      </c>
-      <c r="T20">
-        <f t="shared" si="0"/>
-        <v>3.8620667375479276E-3</v>
-      </c>
-      <c r="U20">
-        <f t="shared" si="0"/>
-        <v>1.2409055660530532E-2</v>
-      </c>
-      <c r="V20">
-        <f t="shared" si="0"/>
-        <v>4.0854320054284098E-2</v>
-      </c>
-      <c r="W20">
-        <f t="shared" si="0"/>
-        <v>1.3636277426938026E-3</v>
-      </c>
-      <c r="X20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <f t="shared" si="0"/>
-        <v>16.907766690799249</v>
-      </c>
-      <c r="Z20">
-        <f t="shared" si="0"/>
-        <v>82.67640198862648</v>
-      </c>
-    </row>
-    <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21">
-        <f>($D$2-D9)/$D$2*100</f>
-        <v>0.7508389312488557</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="1"/>
-        <v>0.16469371545129238</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="1"/>
-        <v>0.40314876873329841</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="1"/>
-        <v>3.4619119388325204E-4</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="1"/>
-        <v>9.771077768735547E-3</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="1"/>
-        <v>1.8966732496656499E-3</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="1"/>
-        <v>1.5437724407327543E-2</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="1"/>
-        <v>3.0355854644843323E-2</v>
-      </c>
-      <c r="L21">
-        <f t="shared" si="0"/>
-        <v>2.8640528826303735E-4</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="0"/>
-        <v>9.4256355129124095E-4</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="0"/>
-        <v>3.4632538168365298E-2</v>
-      </c>
-      <c r="O21">
-        <f t="shared" si="0"/>
-        <v>2.4703581904305261E-4</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="0"/>
-        <v>4.2759340264259309E-6</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="0"/>
-        <v>5.2272428024513332E-4</v>
-      </c>
-      <c r="R21">
-        <f t="shared" si="0"/>
-        <v>4.4083882704227118E-6</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="0"/>
-        <v>2.005732558064753E-5</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="0"/>
-        <v>6.5830348367243901E-3</v>
-      </c>
-      <c r="U21">
-        <f t="shared" si="0"/>
-        <v>2.2974520874030391E-2</v>
-      </c>
-      <c r="V21">
-        <f t="shared" si="0"/>
-        <v>4.0653358498742798E-2</v>
-      </c>
-      <c r="W21">
-        <f t="shared" si="0"/>
-        <v>2.291186588940208E-3</v>
-      </c>
-      <c r="X21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <f t="shared" si="0"/>
-        <v>18.101918047933204</v>
-      </c>
-      <c r="Z21">
-        <f t="shared" si="0"/>
-        <v>81.163269837064234</v>
-      </c>
-    </row>
-    <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22">
-        <f>($D$2-D10)/$D$2*100</f>
-        <v>1.5478684584066795</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="1"/>
-        <v>0.12934198035258671</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="1"/>
-        <v>0.31380712522656307</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="1"/>
-        <v>3.2980082029938879E-4</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="1"/>
-        <v>9.3489983177246459E-3</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="1"/>
-        <v>1.783654362032417E-3</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="1"/>
-        <v>9.9582794932840182E-3</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="1"/>
-        <v>2.6343369134144416E-2</v>
-      </c>
-      <c r="L22">
-        <f t="shared" si="0"/>
-        <v>2.7428848665073037E-4</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="0"/>
-        <v>6.5533083132321532E-4</v>
-      </c>
-      <c r="N22">
-        <f t="shared" si="0"/>
-        <v>3.1241870380322258E-2</v>
-      </c>
-      <c r="O22">
-        <f t="shared" si="0"/>
-        <v>2.0042190670149052E-4</v>
-      </c>
-      <c r="P22">
-        <f t="shared" si="0"/>
-        <v>4.2472951548685433E-6</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="0"/>
-        <v>5.1579453035103607E-4</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="0"/>
-        <v>2.7152691153286034E-6</v>
-      </c>
-      <c r="S22">
-        <f t="shared" si="0"/>
-        <v>1.7090394530189697E-5</v>
-      </c>
-      <c r="T22">
-        <f t="shared" si="0"/>
-        <v>5.5534412693682969E-3</v>
-      </c>
-      <c r="U22">
-        <f t="shared" si="0"/>
-        <v>1.9143859260041772E-2</v>
-      </c>
-      <c r="V22">
-        <f t="shared" si="0"/>
-        <v>4.0735144459447113E-2</v>
-      </c>
-      <c r="W22">
-        <f t="shared" si="0"/>
-        <v>1.9490123033876847E-3</v>
-      </c>
-      <c r="X22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <f t="shared" si="0"/>
-        <v>17.58845800461863</v>
-      </c>
-      <c r="Z22">
-        <f t="shared" si="0"/>
-        <v>81.820335571288325</v>
-      </c>
-    </row>
-    <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23">
-        <f>($D$2-D11)/$D$2*100</f>
-        <v>1.9655946023177087</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="1"/>
-        <v>0.11675471890510961</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>0.22635094485799959</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>3.1777143429290915E-4</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="1"/>
-        <v>8.3047366087283751E-3</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="1"/>
-        <v>1.6634716114929332E-3</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="1"/>
-        <v>6.76720903400411E-3</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>2.3899692942497042E-2</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="0"/>
-        <v>2.5754565416173756E-4</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="0"/>
-        <v>4.3943575965431326E-4</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="0"/>
-        <v>2.9076003116320574E-2</v>
-      </c>
-      <c r="O23">
-        <f t="shared" si="0"/>
-        <v>1.6022637908856771E-4</v>
-      </c>
-      <c r="P23">
-        <f t="shared" si="0"/>
-        <v>4.2522897730183442E-6</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="0"/>
-        <v>5.0741880100057125E-4</v>
-      </c>
-      <c r="R23">
-        <f t="shared" si="0"/>
-        <v>2.18772604482182E-6</v>
-      </c>
-      <c r="S23">
-        <f t="shared" si="0"/>
-        <v>1.423099472608955E-5</v>
-      </c>
-      <c r="T23">
-        <f t="shared" si="0"/>
-        <v>4.3330236163715927E-3</v>
-      </c>
-      <c r="U23">
-        <f t="shared" si="0"/>
-        <v>1.3893178169673929E-2</v>
-      </c>
-      <c r="V23">
-        <f t="shared" si="0"/>
-        <v>4.079538234322886E-2</v>
-      </c>
-      <c r="W23">
-        <f t="shared" si="0"/>
-        <v>1.5313089441854415E-3</v>
-      </c>
-      <c r="X23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <f t="shared" si="0"/>
-        <v>17.355953952709417</v>
-      </c>
-      <c r="Z23">
-        <f t="shared" si="0"/>
-        <v>82.16897330810221</v>
       </c>
     </row>
   </sheetData>
@@ -6049,7 +3241,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -6993,942 +4185,6 @@
       </c>
       <c r="AB11">
         <v>2.613105251031123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="E14">
-        <f>E2/$D2*100</f>
-        <v>2.9124968238699314</v>
-      </c>
-      <c r="F14">
-        <f t="shared" ref="F14:Z23" si="0">F2/$D2*100</f>
-        <v>0.45839137674932801</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>1.0857890447787832</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>8.1733574267291035E-4</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>2.2857928984514365E-2</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>4.5192243504207068E-3</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>4.2699206186407566E-2</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="0"/>
-        <v>1.3041028558056266E-2</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="0"/>
-        <v>7.9442935362541864E-2</v>
-      </c>
-      <c r="N14">
-        <f t="shared" si="0"/>
-        <v>6.7264964664201586E-4</v>
-      </c>
-      <c r="O14">
-        <f t="shared" si="0"/>
-        <v>2.615114684892561E-3</v>
-      </c>
-      <c r="P14">
-        <f t="shared" si="0"/>
-        <v>8.523239187200822E-2</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="0"/>
-        <v>6.4499320284376995E-4</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="0"/>
-        <v>9.7910350558453471E-6</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="0"/>
-        <v>1.1976449460425038E-3</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="0"/>
-        <v>1.0782811739394243E-5</v>
-      </c>
-      <c r="U14">
-        <f t="shared" si="0"/>
-        <v>5.3342419969732261E-5</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="0"/>
-        <v>1.7219349352979259E-2</v>
-      </c>
-      <c r="W14">
-        <f t="shared" si="0"/>
-        <v>5.9745209398638852E-2</v>
-      </c>
-      <c r="X14">
-        <f t="shared" si="0"/>
-        <v>9.2047241566455135E-2</v>
-      </c>
-      <c r="Y14">
-        <f t="shared" si="0"/>
-        <v>5.8922620517439369E-3</v>
-      </c>
-      <c r="Z14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="D15">
-        <f>($D$2-D3)/$D$2*100</f>
-        <v>0.77500790801942154</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ref="E15:K23" si="1">E3/$D3*100</f>
-        <v>2.8262217752945307</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>0.4143298819814345</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>1.0209676159271612</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>8.0815338774760663E-4</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>2.2727113922875537E-2</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>4.4479304368764509E-3</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>4.0700328381078829E-2</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="0"/>
-        <v>1.2666009339822926E-2</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="0"/>
-        <v>7.5713978988108471E-2</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="0"/>
-        <v>6.6670443812443772E-4</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="0"/>
-        <v>2.4729762303689331E-3</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="0"/>
-        <v>8.3686675664297175E-2</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="0"/>
-        <v>6.1091681667598224E-4</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="0"/>
-        <v>9.7798399772468944E-6</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="0"/>
-        <v>1.1988135797386407E-3</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="0"/>
-        <v>1.0383282787899251E-5</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="0"/>
-        <v>4.917767683287369E-5</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="0"/>
-        <v>1.62812560926874E-2</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="0"/>
-        <v>5.7123284240594673E-2</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="0"/>
-        <v>9.2570371499987078E-2</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="0"/>
-        <v>5.6119641609495624E-3</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>($D$2-D4)/$D$2*100</f>
-        <v>1.3382880205372438</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="1"/>
-        <v>2.6965406527573994</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="1"/>
-        <v>0.42175813956428865</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="1"/>
-        <v>0.99377676843539386</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="1"/>
-        <v>8.0550060011560078E-4</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="1"/>
-        <v>2.2541767782840359E-2</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="1"/>
-        <v>4.4074798470881476E-3</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>3.8657091629001328E-2</v>
-      </c>
-      <c r="L16">
-        <f t="shared" si="0"/>
-        <v>1.2737821865720768E-2</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="0"/>
-        <v>7.1101349967217634E-2</v>
-      </c>
-      <c r="N16">
-        <f t="shared" si="0"/>
-        <v>6.6234168931509707E-4</v>
-      </c>
-      <c r="O16">
-        <f t="shared" si="0"/>
-        <v>2.35266210410479E-3</v>
-      </c>
-      <c r="P16">
-        <f t="shared" si="0"/>
-        <v>8.1440354454595978E-2</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="0"/>
-        <v>5.763106472426962E-4</v>
-      </c>
-      <c r="R16">
-        <f t="shared" si="0"/>
-        <v>9.8224183215089618E-6</v>
-      </c>
-      <c r="S16">
-        <f t="shared" si="0"/>
-        <v>1.1970447909623481E-3</v>
-      </c>
-      <c r="T16">
-        <f t="shared" si="0"/>
-        <v>8.8830426806916813E-6</v>
-      </c>
-      <c r="U16">
-        <f t="shared" si="0"/>
-        <v>4.9790901486013127E-5</v>
-      </c>
-      <c r="V16">
-        <f t="shared" si="0"/>
-        <v>1.6139808611123439E-2</v>
-      </c>
-      <c r="W16">
-        <f t="shared" si="0"/>
-        <v>5.5747217113084176E-2</v>
-      </c>
-      <c r="X16">
-        <f t="shared" si="0"/>
-        <v>9.2756429633437512E-2</v>
-      </c>
-      <c r="Y16">
-        <f t="shared" si="0"/>
-        <v>5.5040953465400107E-3</v>
-      </c>
-      <c r="Z16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17">
-        <f>($D$2-D5)/$D$2*100</f>
-        <v>1.784548113380481</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="1"/>
-        <v>2.4689252639433725</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="1"/>
-        <v>0.45943168672125578</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="1"/>
-        <v>0.97333865784873341</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="1"/>
-        <v>8.0870849613099642E-4</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="1"/>
-        <v>2.21131505468725E-2</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="1"/>
-        <v>4.3811487201124979E-3</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>3.6682219928761479E-2</v>
-      </c>
-      <c r="L17">
-        <f t="shared" si="0"/>
-        <v>1.2817408269570054E-2</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="0"/>
-        <v>6.8911953007330787E-2</v>
-      </c>
-      <c r="N17">
-        <f t="shared" si="0"/>
-        <v>6.5698864481753428E-4</v>
-      </c>
-      <c r="O17">
-        <f t="shared" si="0"/>
-        <v>2.2304791969779423E-3</v>
-      </c>
-      <c r="P17">
-        <f t="shared" si="0"/>
-        <v>8.024412406254082E-2</v>
-      </c>
-      <c r="Q17">
-        <f t="shared" si="0"/>
-        <v>5.5903195827457057E-4</v>
-      </c>
-      <c r="R17">
-        <f t="shared" si="0"/>
-        <v>9.9343867327526505E-6</v>
-      </c>
-      <c r="S17">
-        <f t="shared" si="0"/>
-        <v>1.1968320913210962E-3</v>
-      </c>
-      <c r="T17">
-        <f t="shared" si="0"/>
-        <v>8.1689373454426214E-6</v>
-      </c>
-      <c r="U17">
-        <f t="shared" si="0"/>
-        <v>5.1914381995796904E-5</v>
-      </c>
-      <c r="V17">
-        <f t="shared" si="0"/>
-        <v>1.6057708013074452E-2</v>
-      </c>
-      <c r="W17">
-        <f t="shared" si="0"/>
-        <v>5.3499026849706581E-2</v>
-      </c>
-      <c r="X17">
-        <f t="shared" si="0"/>
-        <v>9.3068766415609877E-2</v>
-      </c>
-      <c r="Y17">
-        <f t="shared" si="0"/>
-        <v>5.4250112927733355E-3</v>
-      </c>
-      <c r="Z17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18">
-        <f>($D$2-D6)/$D$2*100</f>
-        <v>5.9208559478383629</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="1"/>
-        <v>0.82366473758201841</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="1"/>
-        <v>0.27936185481481268</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="1"/>
-        <v>0.62256248672494485</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="1"/>
-        <v>7.7000804770444692E-4</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="1"/>
-        <v>2.0518313657655801E-2</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="1"/>
-        <v>4.0720775273244379E-3</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
-        <v>2.2396102129584865E-2</v>
-      </c>
-      <c r="L18">
-        <f t="shared" si="0"/>
-        <v>1.0675379999587833E-2</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="0"/>
-        <v>6.1642800721573084E-2</v>
-      </c>
-      <c r="N18">
-        <f t="shared" si="0"/>
-        <v>6.2796309308048174E-4</v>
-      </c>
-      <c r="O18">
-        <f t="shared" si="0"/>
-        <v>1.3855161773637962E-3</v>
-      </c>
-      <c r="P18">
-        <f t="shared" si="0"/>
-        <v>7.3088985437914117E-2</v>
-      </c>
-      <c r="Q18">
-        <f t="shared" si="0"/>
-        <v>4.4248827284542008E-4</v>
-      </c>
-      <c r="R18">
-        <f t="shared" si="0"/>
-        <v>1.0037409887472061E-5</v>
-      </c>
-      <c r="S18">
-        <f t="shared" si="0"/>
-        <v>1.2156420058576228E-3</v>
-      </c>
-      <c r="T18">
-        <f t="shared" si="0"/>
-        <v>5.732417793441571E-6</v>
-      </c>
-      <c r="U18">
-        <f t="shared" si="0"/>
-        <v>3.45406828334097E-5</v>
-      </c>
-      <c r="V18">
-        <f t="shared" si="0"/>
-        <v>1.1055016425869944E-2</v>
-      </c>
-      <c r="W18">
-        <f t="shared" si="0"/>
-        <v>3.7397137898943826E-2</v>
-      </c>
-      <c r="X18">
-        <f t="shared" si="0"/>
-        <v>9.6965770820720568E-2</v>
-      </c>
-      <c r="Y18">
-        <f t="shared" si="0"/>
-        <v>3.9924378919176202E-3</v>
-      </c>
-      <c r="Z18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19">
-        <f>($D$2-D7)/$D$2*100</f>
-        <v>7.8212503422068052</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="1"/>
-        <v>0.25666629949963315</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="1"/>
-        <v>0.24211182815982896</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="1"/>
-        <v>0.51252359988658747</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="1"/>
-        <v>7.5288735005056486E-4</v>
-      </c>
-      <c r="I19">
-        <f t="shared" si="1"/>
-        <v>2.0143360667122398E-2</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="1"/>
-        <v>3.9506862507793219E-3</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
-        <v>1.5473562442122746E-2</v>
-      </c>
-      <c r="L19">
-        <f t="shared" si="0"/>
-        <v>1.033415018786368E-2</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="0"/>
-        <v>5.472013821375564E-2</v>
-      </c>
-      <c r="N19">
-        <f t="shared" si="0"/>
-        <v>6.1514849580633169E-4</v>
-      </c>
-      <c r="O19">
-        <f t="shared" si="0"/>
-        <v>1.0299444621882606E-3</v>
-      </c>
-      <c r="P19">
-        <f t="shared" si="0"/>
-        <v>6.7178716125390434E-2</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" si="0"/>
-        <v>3.4460100461789818E-4</v>
-      </c>
-      <c r="R19">
-        <f t="shared" si="0"/>
-        <v>1.0161929606105162E-5</v>
-      </c>
-      <c r="S19">
-        <f t="shared" si="0"/>
-        <v>1.2191014932472978E-3</v>
-      </c>
-      <c r="T19">
-        <f t="shared" si="0"/>
-        <v>3.8856941057622551E-6</v>
-      </c>
-      <c r="U19">
-        <f t="shared" si="0"/>
-        <v>3.1345739604920282E-5</v>
-      </c>
-      <c r="V19">
-        <f t="shared" si="0"/>
-        <v>9.8385531547465887E-3</v>
-      </c>
-      <c r="W19">
-        <f t="shared" si="0"/>
-        <v>3.2376314439043465E-2</v>
-      </c>
-      <c r="X19">
-        <f t="shared" si="0"/>
-        <v>9.8330996949837601E-2</v>
-      </c>
-      <c r="Y19">
-        <f t="shared" si="0"/>
-        <v>3.5183691355717937E-3</v>
-      </c>
-      <c r="Z19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20">
-        <f>($D$2-D8)/$D$2*100</f>
-        <v>8.5807363457193251</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="1"/>
-        <v>0.10002673442631992</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="1"/>
-        <v>0.2372553472145448</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="1"/>
-        <v>0.46898263096499065</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="1"/>
-        <v>7.4848550538244825E-4</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="1"/>
-        <v>1.9939070352246884E-2</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="1"/>
-        <v>3.8963833259595721E-3</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
-        <v>1.337301348019755E-2</v>
-      </c>
-      <c r="L20">
-        <f t="shared" si="0"/>
-        <v>1.0193242748123324E-2</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="0"/>
-        <v>5.233960848624223E-2</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="0"/>
-        <v>6.0777088189285105E-4</v>
-      </c>
-      <c r="O20">
-        <f t="shared" si="0"/>
-        <v>9.2189461433384587E-4</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="0"/>
-        <v>6.5309650728637883E-2</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="0"/>
-        <v>3.0125702643798329E-4</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="0"/>
-        <v>1.0218064176325803E-5</v>
-      </c>
-      <c r="S20">
-        <f t="shared" si="0"/>
-        <v>1.2198094745253221E-3</v>
-      </c>
-      <c r="T20">
-        <f t="shared" si="0"/>
-        <v>3.0792804200663646E-6</v>
-      </c>
-      <c r="U20">
-        <f t="shared" si="0"/>
-        <v>3.0383980376892146E-5</v>
-      </c>
-      <c r="V20">
-        <f t="shared" si="0"/>
-        <v>9.3478462093532708E-3</v>
-      </c>
-      <c r="W20">
-        <f t="shared" si="0"/>
-        <v>3.0035199234219743E-2</v>
-      </c>
-      <c r="X20">
-        <f t="shared" si="0"/>
-        <v>9.8896183589307088E-2</v>
-      </c>
-      <c r="Y20">
-        <f t="shared" si="0"/>
-        <v>3.3009380503635911E-3</v>
-      </c>
-      <c r="Z20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21">
-        <f>($D$2-D9)/$D$2*100</f>
-        <v>2.3209801296700872</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="1"/>
-        <v>2.329999925379084</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="1"/>
-        <v>0.38003821586856562</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="1"/>
-        <v>0.93028406323326784</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="1"/>
-        <v>7.9894341369977451E-4</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="1"/>
-        <v>2.2549788573513505E-2</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="1"/>
-        <v>4.3771610241245583E-3</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="1"/>
-        <v>3.5627330953733077E-2</v>
-      </c>
-      <c r="L21">
-        <f t="shared" si="0"/>
-        <v>1.2328193873794073E-2</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="0"/>
-        <v>7.0055537414692656E-2</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="0"/>
-        <v>6.6096891760830234E-4</v>
-      </c>
-      <c r="O21">
-        <f t="shared" si="0"/>
-        <v>2.1752573566373367E-3</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="0"/>
-        <v>7.9925309361429414E-2</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="0"/>
-        <v>5.7011167256592796E-4</v>
-      </c>
-      <c r="R21">
-        <f t="shared" si="0"/>
-        <v>9.8680422500285467E-6</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="0"/>
-        <v>1.2063481921600905E-3</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="0"/>
-        <v>1.0173721446170949E-5</v>
-      </c>
-      <c r="U21">
-        <f t="shared" si="0"/>
-        <v>4.6283188207133293E-5</v>
-      </c>
-      <c r="V21">
-        <f t="shared" si="0"/>
-        <v>1.5190651370599861E-2</v>
-      </c>
-      <c r="W21">
-        <f t="shared" si="0"/>
-        <v>5.3014748616705978E-2</v>
-      </c>
-      <c r="X21">
-        <f t="shared" si="0"/>
-        <v>9.3820217241862125E-2</v>
-      </c>
-      <c r="Y21">
-        <f t="shared" si="0"/>
-        <v>5.2876227562517119E-3</v>
-      </c>
-      <c r="Z21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22">
-        <f>($D$2-D10)/$D$2*100</f>
-        <v>5.4118657788260975</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="1"/>
-        <v>1.0288699618726491</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="1"/>
-        <v>0.30574028248909102</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="1"/>
-        <v>0.7417814297594385</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="1"/>
-        <v>7.7967686709810879E-4</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="1"/>
-        <v>2.2101818037480941E-2</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="1"/>
-        <v>4.2167088720788367E-3</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="1"/>
-        <v>2.3542209961645192E-2</v>
-      </c>
-      <c r="L22">
-        <f t="shared" si="0"/>
-        <v>1.1675949445285196E-2</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="0"/>
-        <v>6.2277939444399869E-2</v>
-      </c>
-      <c r="N22">
-        <f t="shared" si="0"/>
-        <v>6.4844104316898589E-4</v>
-      </c>
-      <c r="O22">
-        <f t="shared" si="0"/>
-        <v>1.5492571820017109E-3</v>
-      </c>
-      <c r="P22">
-        <f t="shared" si="0"/>
-        <v>7.3858408230466133E-2</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="0"/>
-        <v>4.7381423785724044E-4</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="0"/>
-        <v>1.0040962836243803E-5</v>
-      </c>
-      <c r="S22">
-        <f t="shared" si="0"/>
-        <v>1.2193816350285819E-3</v>
-      </c>
-      <c r="T22">
-        <f t="shared" si="0"/>
-        <v>6.419124474116969E-6</v>
-      </c>
-      <c r="U22">
-        <f t="shared" si="0"/>
-        <v>4.0398500450250036E-5</v>
-      </c>
-      <c r="V22">
-        <f t="shared" si="0"/>
-        <v>1.3127297864581373E-2</v>
-      </c>
-      <c r="W22">
-        <f t="shared" si="0"/>
-        <v>4.5252507516439236E-2</v>
-      </c>
-      <c r="X22">
-        <f t="shared" si="0"/>
-        <v>9.6301306297840866E-2</v>
-      </c>
-      <c r="Y22">
-        <f t="shared" si="0"/>
-        <v>4.6076289478646729E-3</v>
-      </c>
-      <c r="Z22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23">
-        <f>($D$2-D11)/$D$2*100</f>
-        <v>7.1499803956035306</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="1"/>
-        <v>0.18783294178828683</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>0.27995978669273003</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>0.54275461269917258</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="1"/>
-        <v>7.6205413970794255E-4</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="1"/>
-        <v>1.991575777082609E-2</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="1"/>
-        <v>3.9892051047494643E-3</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>1.6228581622218186E-2</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="0"/>
-        <v>1.0503672895873914E-2</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="0"/>
-        <v>5.731433973952068E-2</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="0"/>
-        <v>6.1762547144761305E-4</v>
-      </c>
-      <c r="O23">
-        <f t="shared" si="0"/>
-        <v>1.0538198328790007E-3</v>
-      </c>
-      <c r="P23">
-        <f t="shared" si="0"/>
-        <v>6.9727754447963489E-2</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="0"/>
-        <v>3.8424213852497862E-4</v>
-      </c>
-      <c r="R23">
-        <f t="shared" si="0"/>
-        <v>1.0197502591688071E-5</v>
-      </c>
-      <c r="S23">
-        <f t="shared" si="0"/>
-        <v>1.2168513470336012E-3</v>
-      </c>
-      <c r="T23">
-        <f t="shared" si="0"/>
-        <v>5.2464303240883012E-6</v>
-      </c>
-      <c r="U23">
-        <f t="shared" si="0"/>
-        <v>3.4123727805635026E-5</v>
-      </c>
-      <c r="V23">
-        <f t="shared" si="0"/>
-        <v>1.0389921527367596E-2</v>
-      </c>
-      <c r="W23">
-        <f t="shared" si="0"/>
-        <v>3.3313695868906736E-2</v>
-      </c>
-      <c r="X23">
-        <f t="shared" si="0"/>
-        <v>9.7832236131614972E-2</v>
-      </c>
-      <c r="Y23">
-        <f t="shared" si="0"/>
-        <v>3.6722631242324787E-3</v>
-      </c>
-      <c r="Z23">
-        <f t="shared" si="0"/>
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7938,7 +4194,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -8386,422 +4642,6 @@
         <v>0.92080658289800354</v>
       </c>
       <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E14">
-        <f>E2/$D2*100</f>
-        <v>13.460237770184893</v>
-      </c>
-      <c r="F14">
-        <f t="shared" ref="F14:Z23" si="0">F2/$D2*100</f>
-        <v>2.1391613150545141</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>0.6756563151328504</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>4.3456113516887811</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>2.014574477774528E-4</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>6.5032035948273434E-2</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>0.2256387582192359</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="0"/>
-        <v>79.08846280507025</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D15">
-        <f>($D$2-D3)/$D$2*100</f>
-        <v>10.302048172537111</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ref="E15:K23" si="1">E3/$D3*100</f>
-        <v>14.358688291221483</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>1.7730737062547981</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>0.74264279491751584</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>4.8124065045983082</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>2.0545521466753939E-4</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>6.8020068881013113E-2</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>0.23865048904309627</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="0"/>
-        <v>78.006311859976961</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>($D$2-D4)/$D$2*100</f>
-        <v>19.109962063067851</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="1"/>
-        <v>15.56520737592724</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="1"/>
-        <v>2.3748371067566811</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="1"/>
-        <v>0.82849779511623323</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="1"/>
-        <v>5.3107100658667061</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="1"/>
-        <v>2.293581678665276E-4</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="1"/>
-        <v>7.4346854993247294E-2</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>0.25679550277478497</v>
-      </c>
-      <c r="L16">
-        <f t="shared" si="0"/>
-        <v>75.589375841218811</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D17">
-        <f>($D$2-D5)/$D$2*100</f>
-        <v>20.923348803315118</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="1"/>
-        <v>16.199591595317884</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="1"/>
-        <v>3.3039710903134734</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="1"/>
-        <v>0.86127012963966043</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="1"/>
-        <v>5.381395522879755</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="1"/>
-        <v>2.4351731787791695E-4</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="1"/>
-        <v>7.5322672374819141E-2</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>0.25095048860581959</v>
-      </c>
-      <c r="L17">
-        <f t="shared" si="0"/>
-        <v>73.927254889896062</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D18">
-        <f>($D$2-D6)/$D$2*100</f>
-        <v>35.880666721874384</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="1"/>
-        <v>16.891404485390858</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="1"/>
-        <v>1.1456424331888981</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="1"/>
-        <v>1.0087385901077106</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="1"/>
-        <v>6.3466466142391642</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="1"/>
-        <v>1.914017445313009E-4</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="1"/>
-        <v>6.1259629403939385E-2</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
-        <v>0.20723033962177362</v>
-      </c>
-      <c r="L18">
-        <f t="shared" si="0"/>
-        <v>74.338885666650683</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D19">
-        <f>($D$2-D7)/$D$2*100</f>
-        <v>48.521339781090752</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="1"/>
-        <v>19.688253350501757</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="1"/>
-        <v>1.2883049840913885</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="1"/>
-        <v>1.247805012703908</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="1"/>
-        <v>7.7924777155302767</v>
-      </c>
-      <c r="I19">
-        <f t="shared" si="1"/>
-        <v>2.1197893813947537E-4</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="1"/>
-        <v>6.6534274732652957E-2</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
-        <v>0.21894831138616205</v>
-      </c>
-      <c r="L19">
-        <f t="shared" si="0"/>
-        <v>69.697464200638635</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D20">
-        <f>($D$2-D8)/$D$2*100</f>
-        <v>51.895575630145231</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="1"/>
-        <v>20.412397448091017</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="1"/>
-        <v>1.5951353055792743</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="1"/>
-        <v>1.3351033949959541</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="1"/>
-        <v>8.2734862054503999</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="1"/>
-        <v>2.180760524198226E-4</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="1"/>
-        <v>6.7092638116435954E-2</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
-        <v>0.215572732781521</v>
-      </c>
-      <c r="L20">
-        <f t="shared" si="0"/>
-        <v>68.10099401558864</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D21">
-        <f>($D$2-D9)/$D$2*100</f>
-        <v>18.378794246065212</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="1"/>
-        <v>15.121192925059759</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="1"/>
-        <v>1.7165519749410281</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="1"/>
-        <v>0.81021069861015571</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="1"/>
-        <v>5.2225831007495209</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="1"/>
-        <v>2.0918578442715772E-4</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="1"/>
-        <v>6.8657074977143753E-2</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="1"/>
-        <v>0.23961036836900201</v>
-      </c>
-      <c r="L21">
-        <f t="shared" si="0"/>
-        <v>76.820983841877762</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D22">
-        <f>($D$2-D10)/$D$2*100</f>
-        <v>36.598856494022151</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="1"/>
-        <v>17.685993050558825</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="1"/>
-        <v>1.5986416991881587</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="1"/>
-        <v>1.0271455205074653</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="1"/>
-        <v>6.56490441289725</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="1"/>
-        <v>2.2762262439299816E-4</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="1"/>
-        <v>7.396487388942434E-2</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="1"/>
-        <v>0.25497219962262285</v>
-      </c>
-      <c r="L22">
-        <f t="shared" si="0"/>
-        <v>72.794150483885772</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D23">
-        <f>($D$2-D11)/$D$2*100</f>
-        <v>44.883009814833244</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="1"/>
-        <v>19.638977951841959</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>1.9791258399940277</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>1.1812515112290791</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="1"/>
-        <v>7.2855355213679207</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="1"/>
-        <v>2.1710188211633924E-4</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="1"/>
-        <v>6.610272861982229E-2</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>0.21194829927709938</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="0"/>
-        <v>69.636840895782555</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8812,7 +4652,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="29.42578125" bestFit="1" customWidth="1"/>
@@ -9266,422 +5106,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E14">
-        <f>E2/$D2*100</f>
-        <v>7.9467597713117479</v>
-      </c>
-      <c r="F14">
-        <f t="shared" ref="F14:M23" si="0">F2/$D2*100</f>
-        <v>1.2629346801344092</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>0.39889922570489006</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>2.5655957986009423</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>1.1893801350041149E-4</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>3.8394118732803045E-2</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>0.13321436346668128</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="0"/>
-        <v>87.65408514829322</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D15">
-        <f>($D$2-D3)/$D$2*100</f>
-        <v>17.31534335836324</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ref="E15:K23" si="1">E3/$D3*100</f>
-        <v>9.1962277813003723</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>1.1355904763057214</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>0.47563622551639306</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>3.0821747429084114</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>1.3158673791211094E-4</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>4.3564428340711926E-2</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>0.15284712731738964</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="0"/>
-        <v>85.913826759260076</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>($D$2-D4)/$D$2*100</f>
-        <v>28.118474442915748</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="1"/>
-        <v>10.3411780956018</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="1"/>
-        <v>1.577789031387804</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="1"/>
-        <v>0.55043553511281074</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="1"/>
-        <v>3.5283178231321948</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="1"/>
-        <v>1.5238047295514445E-4</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="1"/>
-        <v>4.9394399301233322E-2</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>0.17060922891722555</v>
-      </c>
-      <c r="L16">
-        <f t="shared" si="0"/>
-        <v>83.782123440181991</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D17">
-        <f>($D$2-D5)/$D$2*100</f>
-        <v>32.601687528733791</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="1"/>
-        <v>11.221235194633044</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="1"/>
-        <v>2.2886155161708657</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="1"/>
-        <v>0.596590021046705</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="1"/>
-        <v>3.7276189638652459</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="1"/>
-        <v>1.686811103721966E-4</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="1"/>
-        <v>5.2174983377384895E-2</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>0.17382996591518229</v>
-      </c>
-      <c r="L17">
-        <f t="shared" si="0"/>
-        <v>81.939766609007819</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D18">
-        <f>($D$2-D6)/$D$2*100</f>
-        <v>43.520082255102857</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="1"/>
-        <v>11.321345834492231</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="1"/>
-        <v>0.7678588361328057</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="1"/>
-        <v>0.67609999186774183</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="1"/>
-        <v>4.2537955485735424</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="1"/>
-        <v>1.2828568193000965E-4</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="1"/>
-        <v>4.1058838581164839E-2</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
-        <v>0.13889468719350778</v>
-      </c>
-      <c r="L18">
-        <f t="shared" si="0"/>
-        <v>82.800817102136108</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D19">
-        <f>($D$2-D7)/$D$2*100</f>
-        <v>54.829797704113446</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="1"/>
-        <v>13.247067283397218</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="1"/>
-        <v>0.86682462389989867</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="1"/>
-        <v>0.83957457604677388</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="1"/>
-        <v>5.2430997694050028</v>
-      </c>
-      <c r="I19">
-        <f t="shared" si="1"/>
-        <v>1.4262815528657153E-4</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="1"/>
-        <v>4.4766998795910305E-2</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
-        <v>0.14731743648782214</v>
-      </c>
-      <c r="L19">
-        <f t="shared" si="0"/>
-        <v>79.611206568434724</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D20">
-        <f>($D$2-D8)/$D$2*100</f>
-        <v>58.718005549281784</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="1"/>
-        <v>14.042864968750893</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="1"/>
-        <v>1.0973855354375257</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="1"/>
-        <v>0.91849459344142159</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="1"/>
-        <v>5.6918081229517083</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="1"/>
-        <v>1.5002708843180052E-4</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="1"/>
-        <v>4.6156893616359204E-2</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
-        <v>0.14830491053752384</v>
-      </c>
-      <c r="L20">
-        <f t="shared" si="0"/>
-        <v>78.054834822042579</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D21">
-        <f>($D$2-D9)/$D$2*100</f>
-        <v>23.298418158925234</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="1"/>
-        <v>9.4999669170191545</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="1"/>
-        <v>1.0784325716960068</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="1"/>
-        <v>0.50901902189578996</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="1"/>
-        <v>3.2811145869503351</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="1"/>
-        <v>1.3142204066950925E-4</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="1"/>
-        <v>4.3134159066328545E-2</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="1"/>
-        <v>0.15053644138802602</v>
-      </c>
-      <c r="L21">
-        <f t="shared" si="0"/>
-        <v>85.437664006354225</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D22">
-        <f>($D$2-D10)/$D$2*100</f>
-        <v>41.440746298637201</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="1"/>
-        <v>11.304942575061668</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="1"/>
-        <v>1.0218568194478685</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="1"/>
-        <v>0.65655465838836946</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="1"/>
-        <v>4.1963076196180777</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="1"/>
-        <v>1.4549709989094271E-4</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="1"/>
-        <v>4.7278580823891032E-2</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="1"/>
-        <v>0.16297903469321084</v>
-      </c>
-      <c r="L22">
-        <f t="shared" si="0"/>
-        <v>82.609935127407311</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D23">
-        <f>($D$2-D11)/$D$2*100</f>
-        <v>54.465219520155003</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="1"/>
-        <v>14.034549675111183</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>1.4143373439699383</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>0.8441545712713513</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="1"/>
-        <v>5.2064425366308376</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="1"/>
-        <v>1.5514693058841795E-4</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="1"/>
-        <v>4.7238814094614209E-2</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>0.15146403962843658</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="0"/>
-        <v>78.301657765165103</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change breakdown results.xlsx
@@ -578,70 +578,70 @@
         <v>10.24507192971876</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02236365771525903</v>
+        <v>0.02236365771525899</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05297266872821097</v>
+        <v>0.05297266872821094</v>
       </c>
       <c r="G2" t="n">
-        <v>3.987099995124905e-05</v>
+        <v>3.987099995124904e-05</v>
       </c>
       <c r="H2" t="n">
         <v>0.001115047877934225</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002204552969457205</v>
+        <v>0.0002204552969457188</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002082938453430555</v>
+        <v>0.002082938453430552</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003875358811066433</v>
+        <v>0.003875358811066427</v>
       </c>
       <c r="L2" t="n">
-        <v>3.281297100841981e-05</v>
+        <v>3.28129710084198e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001275696534852123</v>
+        <v>0.0001275696534852122</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004157778150090823</v>
+        <v>0.004157778150090817</v>
       </c>
       <c r="O2" t="n">
-        <v>3.146384357918717e-05</v>
+        <v>3.146384357918716e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.776230107809114e-07</v>
+        <v>4.776230107809116e-07</v>
       </c>
       <c r="Q2" t="n">
         <v>5.842311683215343e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>5.260035306051294e-07</v>
+        <v>5.260035306051277e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>2.60243033009551e-06</v>
+        <v>2.602430330095508e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008400848151645775</v>
+        <v>0.0008400848151645728</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002914804860842516</v>
+        <v>0.002914804860844738</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004490217877914887</v>
+        <v>0.004490217877914886</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002874343647440931</v>
+        <v>0.0002874343647440921</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8347068215466439</v>
+        <v>-0.8347068215466442</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.058974611707973</v>
+        <v>2.058974611707972</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.925189945964103</v>
+        <v>8.925189945964096</v>
       </c>
     </row>
     <row r="3">
@@ -662,67 +662,67 @@
         <v>10.24329115008202</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02005735802428354</v>
+        <v>0.02005735802428359</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04942417598730651</v>
+        <v>0.0494241759873065</v>
       </c>
       <c r="G3" t="n">
-        <v>3.911753746663404e-05</v>
+        <v>3.91175374666341e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00110007424811315</v>
+        <v>0.001100074248113149</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00021529586852123</v>
+        <v>0.0002152958685212307</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001970042623700983</v>
+        <v>0.001970042623701009</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003664829541913957</v>
+        <v>0.00366482954191396</v>
       </c>
       <c r="L3" t="n">
         <v>3.227089836273614e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001197009649556326</v>
+        <v>0.0001197009649556325</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004050736803665508</v>
+        <v>0.004050736803665494</v>
       </c>
       <c r="O3" t="n">
-        <v>2.957057636289104e-05</v>
+        <v>2.957057636289122e-05</v>
       </c>
       <c r="P3" t="n">
         <v>4.733795125129374e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.802689914056455e-05</v>
+        <v>5.802689914056458e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.02588320039525e-07</v>
+        <v>5.025883200395254e-07</v>
       </c>
       <c r="S3" t="n">
         <v>2.380649607801306e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007881617926623802</v>
+        <v>0.0007881617926623786</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002765289720491242</v>
+        <v>0.00276528972049028</v>
       </c>
       <c r="V3" t="n">
         <v>0.00448073970900916</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00027163929726161</v>
+        <v>0.0002716392972616097</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8035680573876947</v>
+        <v>-0.8035680573876957</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.032598873332666</v>
+        <v>2.032598873332668</v>
       </c>
       <c r="Z3" t="n">
         <v>8.925189947026391</v>
@@ -746,67 +746,67 @@
         <v>10.26406291180962</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02030105077470802</v>
+        <v>0.02030105077470806</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04783479141759854</v>
+        <v>0.04783479141759856</v>
       </c>
       <c r="G4" t="n">
-        <v>3.876779959824295e-05</v>
+        <v>3.876779959824285e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001084908857758595</v>
+        <v>0.001084908857758605</v>
       </c>
       <c r="I4" t="n">
         <v>0.0002121268381683213</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00186052050254084</v>
+        <v>0.001860520502540836</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003422024622077297</v>
+        <v>0.003422024622077296</v>
       </c>
       <c r="L4" t="n">
-        <v>3.187772904606675e-05</v>
+        <v>3.187772904606676e-05</v>
       </c>
       <c r="M4" t="n">
         <v>0.0001132308690536359</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00391962878767878</v>
+        <v>0.003919628787678779</v>
       </c>
       <c r="O4" t="n">
-        <v>2.773715584498884e-05</v>
+        <v>2.773715584498891e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.727414790302068e-07</v>
+        <v>4.727414790302064e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.761236249791592e-05</v>
+        <v>5.76123624979159e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.275304306641974e-07</v>
+        <v>4.275304306641975e-07</v>
       </c>
       <c r="S4" t="n">
         <v>2.396652309378752e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.000776879076826496</v>
+        <v>0.0007768790768258387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002683355646267634</v>
+        <v>0.002683355646268093</v>
       </c>
       <c r="V4" t="n">
         <v>0.004464258220244086</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002649056565987183</v>
+        <v>0.0002649056565987174</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7620424084315076</v>
+        <v>-0.7620424084315078</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.013818398393047</v>
+        <v>2.013818398393048</v>
       </c>
       <c r="Z4" t="n">
         <v>8.925189948607352</v>
@@ -833,67 +833,67 @@
         <v>0.02201441562572901</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04663910300003231</v>
+        <v>0.0466391030000323</v>
       </c>
       <c r="G5" t="n">
-        <v>3.874614160360752e-05</v>
+        <v>3.874614160360775e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001059466132098391</v>
+        <v>0.001059466132098393</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000209905805995694</v>
+        <v>0.0002099058059956955</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001757486776130351</v>
+        <v>0.00175748677613035</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003301649855513182</v>
+        <v>0.003301649855513181</v>
       </c>
       <c r="L5" t="n">
         <v>3.147707138709097e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001068647890104635</v>
+        <v>0.0001068647890104632</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003844587028155846</v>
+        <v>0.003844587028155851</v>
       </c>
       <c r="O5" t="n">
-        <v>2.678385539397221e-05</v>
+        <v>2.678385539397214e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.759677398392054e-07</v>
+        <v>4.759677398392052e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.734158341098629e-05</v>
+        <v>5.734158341098625e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>3.913830566289083e-07</v>
+        <v>3.913830566289084e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.487561949338781e-06</v>
+        <v>2.487561949338782e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0007694311655323279</v>
+        <v>0.000769431165532088</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002563492781810747</v>
+        <v>0.002563492781801132</v>
       </c>
       <c r="V5" t="n">
         <v>0.004459030194024529</v>
       </c>
       <c r="W5" t="n">
-        <v>0.000259918446209719</v>
+        <v>0.0002599184462097193</v>
       </c>
       <c r="X5" t="n">
         <v>-0.693630572317127</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.003330158067112</v>
+        <v>2.003330158067111</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.925189951429113</v>
+        <v>8.92518995142912</v>
       </c>
     </row>
     <row r="6">
@@ -914,70 +914,70 @@
         <v>10.67252253740813</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01282232736138853</v>
+        <v>0.01282232736138852</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02857476734967648</v>
+        <v>0.02857476734967644</v>
       </c>
       <c r="G6" t="n">
-        <v>3.533826784116746e-05</v>
+        <v>3.533826784116758e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009416546565259212</v>
+        <v>0.0009416546565259211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001868813796941301</v>
+        <v>0.00018688137969413</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001027832706441012</v>
+        <v>0.001027832706441004</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002828996149939954</v>
+        <v>0.002828996149939952</v>
       </c>
       <c r="L6" t="n">
-        <v>2.881934551697529e-05</v>
+        <v>2.88193455169753e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>6.358601305521089e-05</v>
+        <v>6.358601305521087e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003354300193802097</v>
+        <v>0.003354300193802096</v>
       </c>
       <c r="O6" t="n">
-        <v>2.030728009791974e-05</v>
+        <v>2.030728009792046e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.606506127988129e-07</v>
+        <v>4.606506127988123e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.578991405354723e-05</v>
+        <v>5.57899140535472e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.630799976260321e-07</v>
+        <v>2.630799976260331e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.585370138917008e-06</v>
+        <v>1.585370138917006e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000507410146213405</v>
+        <v>0.0005074101462134057</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001716477522805638</v>
+        <v>0.001716477522806823</v>
       </c>
       <c r="V6" t="n">
-        <v>0.004450086451568002</v>
+        <v>0.004450086451568</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001832264480668985</v>
+        <v>0.0001832264480668979</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2205294731201304</v>
+        <v>-0.2205294731201305</v>
       </c>
       <c r="Y6" t="n">
         <v>1.911061929788442</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.925189970452379</v>
+        <v>8.925189970452381</v>
       </c>
     </row>
     <row r="7">
@@ -1001,67 +1001,67 @@
         <v>0.01088812799210039</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02304894641848447</v>
+        <v>0.02304894641848442</v>
       </c>
       <c r="G7" t="n">
-        <v>3.385458150065118e-05</v>
+        <v>3.385458150065119e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009057730155199298</v>
+        <v>0.0009057730155199297</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001776478641214107</v>
+        <v>0.0001776478641214098</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0006957893246142095</v>
+        <v>0.000695789324614205</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002460563826394585</v>
+        <v>0.002460563826394581</v>
       </c>
       <c r="L7" t="n">
-        <v>2.76609706417299e-05</v>
+        <v>2.766097064172989e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.631282320516497e-05</v>
+        <v>4.631282320516496e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003020780359802048</v>
+        <v>0.003020780359802037</v>
       </c>
       <c r="O7" t="n">
-        <v>1.549544270502034e-05</v>
+        <v>1.549544270502003e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.569446863872306e-07</v>
+        <v>4.569446863872303e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.481852080252705e-05</v>
+        <v>5.481852080252708e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.747254058409869e-07</v>
+        <v>1.747254058409836e-07</v>
       </c>
       <c r="S7" t="n">
         <v>1.40966439937877e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.000442454327078936</v>
+        <v>0.0004424543270775148</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001456010878133181</v>
+        <v>0.001456010878132382</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004421584118865849</v>
+        <v>0.00442158411886585</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001582081497870711</v>
+        <v>0.0001582081497870702</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.06675868800768818</v>
+        <v>-0.0667586880076883</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.852671284051605</v>
+        <v>1.852671284051604</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.925189976342095</v>
+        <v>8.925189976342097</v>
       </c>
     </row>
     <row r="8">
@@ -1082,67 +1082,67 @@
         <v>10.77005952698809</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01058181405154487</v>
+        <v>0.01058181405154486</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02091707121689521</v>
+        <v>0.02091707121689518</v>
       </c>
       <c r="G8" t="n">
-        <v>3.337934035364746e-05</v>
+        <v>3.337934035364741e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008891996048512572</v>
+        <v>0.0008891996048512556</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000173762490055203</v>
+        <v>0.0001737624900552024</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0005963807786516049</v>
+        <v>0.0005963807786516025</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002334128841608283</v>
+        <v>0.002334128841608284</v>
       </c>
       <c r="L8" t="n">
         <v>2.71040534223464e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.111266534990591e-05</v>
+        <v>4.111266534990588e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00291253877913793</v>
+        <v>0.002912538779137927</v>
       </c>
       <c r="O8" t="n">
-        <v>1.343481035649846e-05</v>
+        <v>1.343481035649854e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.55683162124448e-07</v>
+        <v>4.556831621244472e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.439842899292989e-05</v>
+        <v>5.439842899292988e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37323099040106e-07</v>
+        <v>1.373230990401045e-07</v>
       </c>
       <c r="S8" t="n">
         <v>1.355154411771047e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0004169228282149833</v>
+        <v>0.0004169228282149831</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001339598441209757</v>
+        <v>0.001339598441211655</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004410358447779868</v>
+        <v>0.004410358447779869</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0001472081074076286</v>
+        <v>0.0001472081074076278</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.02526993019331637</v>
+        <v>-0.02526993019331651</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.825249118300724</v>
+        <v>1.825249118300723</v>
       </c>
       <c r="Z8" t="n">
         <v>8.925189977834179</v>
@@ -1166,22 +1166,22 @@
         <v>10.34455406936768</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01811068851555996</v>
+        <v>0.01811068851555998</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04433260708189952</v>
+        <v>0.04433260708189954</v>
       </c>
       <c r="G9" t="n">
-        <v>3.806921752945534e-05</v>
+        <v>3.806921752945483e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001074485115876921</v>
+        <v>0.001074485115876923</v>
       </c>
       <c r="I9" t="n">
         <v>0.0002085693333614092</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001697622871425563</v>
+        <v>0.001697622871425571</v>
       </c>
       <c r="K9" t="n">
         <v>0.003338108115357711</v>
@@ -1193,43 +1193,43 @@
         <v>0.000103649825597652</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003808397360833145</v>
+        <v>0.003808397360833147</v>
       </c>
       <c r="O9" t="n">
-        <v>2.716550998084806e-05</v>
+        <v>2.716550998084797e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.702068263715077e-07</v>
+        <v>4.702068263715078e-07</v>
       </c>
       <c r="Q9" t="n">
         <v>5.748183282585372e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.847722732011976e-07</v>
+        <v>4.847722732011974e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>2.205621356290986e-06</v>
+        <v>2.205621356290984e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.000723909185534503</v>
+        <v>0.0007239091855345014</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002526413289079761</v>
+        <v>0.002526413289078392</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004470482136277213</v>
+        <v>0.004470482136277214</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0002519523378874575</v>
+        <v>0.0002519523378874577</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6520333968600273</v>
+        <v>-0.6520333968600274</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.99059325610557</v>
+        <v>1.990593256105571</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.92518995298455</v>
+        <v>8.925189952984544</v>
       </c>
     </row>
     <row r="10">
@@ -1250,70 +1250,70 @@
         <v>10.62969562273195</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01410898328530925</v>
+        <v>0.01410898328530923</v>
       </c>
       <c r="F10" t="n">
         <v>0.03423095481113823</v>
       </c>
       <c r="G10" t="n">
-        <v>3.597559159370259e-05</v>
+        <v>3.597559159370257e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001019814762690259</v>
+        <v>0.001019814762690256</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001945659832336165</v>
+        <v>0.000194565983233617</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001086276849466631</v>
+        <v>0.001086276849466623</v>
       </c>
       <c r="K10" t="n">
-        <v>0.002873608041095238</v>
+        <v>0.002873608041095242</v>
       </c>
       <c r="L10" t="n">
-        <v>2.992015170139258e-05</v>
+        <v>2.992015170139257e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>7.148531142234178e-05</v>
+        <v>7.148531142234165e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003407950193712569</v>
+        <v>0.003407950193712558</v>
       </c>
       <c r="O10" t="n">
-        <v>2.186257952717831e-05</v>
+        <v>2.186257952717799e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>4.633067793183591e-07</v>
+        <v>4.633067793183586e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.626430326440551e-05</v>
+        <v>5.626430326440547e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>2.961891139972914e-07</v>
+        <v>2.961891139972916e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.864267812418453e-06</v>
+        <v>1.864267812418452e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0006057848336005988</v>
+        <v>0.0006057848336005996</v>
       </c>
       <c r="U10" t="n">
-        <v>0.002088265461686193</v>
+        <v>0.002088265461684953</v>
       </c>
       <c r="V10" t="n">
         <v>0.0044435029580982</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0002126036878080675</v>
+        <v>0.0002126036878080639</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2785827505310929</v>
+        <v>-0.2785827505310931</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.91859796274231</v>
+        <v>1.918597962742308</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.925189967951676</v>
+        <v>8.925189967951678</v>
       </c>
     </row>
     <row r="11">
@@ -1331,73 +1331,73 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.81399469658047</v>
+        <v>10.81399469658048</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01268189202413569</v>
+        <v>0.0126818920241357</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0245862288836757</v>
+        <v>0.02458622888367568</v>
       </c>
       <c r="G11" t="n">
-        <v>3.45163181055885e-05</v>
+        <v>3.451631810558922e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0009020600961437548</v>
+        <v>0.0009020600961437607</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001806862074612487</v>
+        <v>0.0001806862074612488</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0007350539239766868</v>
+        <v>0.0007350539239766844</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00259598351269279</v>
+        <v>0.002595983512692789</v>
       </c>
       <c r="L11" t="n">
         <v>2.797459672717021e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.773149134990694e-05</v>
+        <v>4.773149134990692e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003158234078010128</v>
+        <v>0.003158234078010125</v>
       </c>
       <c r="O11" t="n">
-        <v>1.740378168929426e-05</v>
+        <v>1.740378168929425e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>4.618835132529721e-07</v>
+        <v>4.618835132529719e-07</v>
       </c>
       <c r="Q11" t="n">
         <v>5.511580607320557e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.376306991186261e-07</v>
+        <v>2.376306991186255e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.545769971481761e-06</v>
+        <v>1.545769971481763e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0004706528194848826</v>
+        <v>0.0004706528194860577</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001509076353170352</v>
+        <v>0.001509076353162545</v>
       </c>
       <c r="V11" t="n">
         <v>0.004431192493218529</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0001663307048131928</v>
+        <v>0.0001663307048131937</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.04800055357829994</v>
+        <v>-0.04800055357829981</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.88520289430888</v>
+        <v>1.885202894308881</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.925189977474981</v>
+        <v>8.925189977474989</v>
       </c>
     </row>
   </sheetData>
@@ -1566,79 +1566,79 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.498372411198862</v>
+        <v>4.498372411198856</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1420764499332589</v>
+        <v>0.1420764499332591</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02236109545418416</v>
+        <v>0.02236109545418414</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05296659951498826</v>
+        <v>0.05296659951498817</v>
       </c>
       <c r="H2" t="n">
-        <v>3.987099995124905e-05</v>
+        <v>3.987099995124904e-05</v>
       </c>
       <c r="I2" t="n">
         <v>0.001115047877934225</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002204552969457205</v>
+        <v>0.0002204552969457188</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002082938453430555</v>
+        <v>0.002082938453430552</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006361631112596297</v>
+        <v>0.0006361631112596293</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003875358811066433</v>
+        <v>0.003875358811066427</v>
       </c>
       <c r="N2" t="n">
-        <v>3.281297100841981e-05</v>
+        <v>3.28129710084198e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001275696534852123</v>
+        <v>0.0001275696534852122</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004157778150090823</v>
+        <v>0.004157778150090817</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.146384357918717e-05</v>
+        <v>3.146384357918716e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>4.776230107809114e-07</v>
+        <v>4.776230107809116e-07</v>
       </c>
       <c r="S2" t="n">
         <v>5.842311683215343e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>5.260035306051294e-07</v>
+        <v>5.260035306051277e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>2.602132163041635e-06</v>
+        <v>2.602132163041632e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008399885645132343</v>
+        <v>0.0008399885645132322</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002914470904245126</v>
+        <v>0.002914470904246598</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004490217877914887</v>
+        <v>0.004490217877914886</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002874343647440931</v>
+        <v>0.0002874343647440921</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.3797942821710153</v>
+        <v>-0.3797942821710151</v>
       </c>
       <c r="AA2" t="n">
         <v>2.026743697951657</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.613105250760084</v>
+        <v>2.613105250760076</v>
       </c>
     </row>
     <row r="3">
@@ -1662,70 +1662,70 @@
         <v>0.1367993228268541</v>
       </c>
       <c r="F3" t="n">
-        <v>0.020055060001823</v>
+        <v>0.02005506000182304</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04941851333391134</v>
+        <v>0.04941851333391135</v>
       </c>
       <c r="H3" t="n">
-        <v>3.911753746663404e-05</v>
+        <v>3.91175374666341e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00110007424811315</v>
+        <v>0.001100074248113149</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00021529586852123</v>
+        <v>0.0002152958685212307</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001970042623700983</v>
+        <v>0.001970042623701009</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006130805146831818</v>
+        <v>0.0006130805146831815</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003664829541913957</v>
+        <v>0.00366482954191396</v>
       </c>
       <c r="N3" t="n">
         <v>3.227089836273614e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001197009649556326</v>
+        <v>0.0001197009649556325</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004050736803665508</v>
+        <v>0.004050736803665494</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.957057636289104e-05</v>
+        <v>2.957057636289122e-05</v>
       </c>
       <c r="R3" t="n">
         <v>4.733795125129374e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>5.802689914056455e-05</v>
+        <v>5.802689914056458e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.02588320039525e-07</v>
+        <v>5.025883200395254e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>2.380376850728178e-06</v>
+        <v>2.380376850728177e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007880714909636281</v>
+        <v>0.0007880714909636268</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002764972894223298</v>
+        <v>0.002764972894222869</v>
       </c>
       <c r="X3" t="n">
         <v>0.00448073970900916</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00027163929726161</v>
+        <v>0.0002716392972616097</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.3656260445621181</v>
+        <v>-0.3656260445621186</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.000780841864457</v>
+        <v>2.000780841864458</v>
       </c>
       <c r="AB3" t="n">
         <v>2.613105251414501</v>
@@ -1749,76 +1749,76 @@
         <v>4.46615103166139</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1297813404727587</v>
+        <v>0.1297813404727584</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02029872483175</v>
+        <v>0.02029872483175002</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04782931086403116</v>
+        <v>0.04782931086403118</v>
       </c>
       <c r="H4" t="n">
-        <v>3.876779959824295e-05</v>
+        <v>3.876779959824285e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001084908857758595</v>
+        <v>0.001084908857758605</v>
       </c>
       <c r="J4" t="n">
         <v>0.0002121268381683213</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00186052050254084</v>
+        <v>0.001860520502540836</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006130564338965224</v>
+        <v>0.0006130564338965223</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003422024622077297</v>
+        <v>0.003422024622077296</v>
       </c>
       <c r="N4" t="n">
-        <v>3.187772904606675e-05</v>
+        <v>3.187772904606676e-05</v>
       </c>
       <c r="O4" t="n">
         <v>0.0001132308690536359</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00391962878767878</v>
+        <v>0.003919628787678779</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.773715584498884e-05</v>
+        <v>2.773715584498891e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.727414790302068e-07</v>
+        <v>4.727414790302064e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.761236249791592e-05</v>
+        <v>5.76123624979159e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.275304306641974e-07</v>
+        <v>4.275304306641975e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.396377718835448e-06</v>
+        <v>2.396377718835449e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.000776790067817694</v>
+        <v>0.0007767900678164999</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002683048207395546</v>
+        <v>0.002683048207395167</v>
       </c>
       <c r="X4" t="n">
         <v>0.004464258220244086</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002649056565987183</v>
+        <v>0.0002649056565987174</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.346731741041539</v>
+        <v>-0.3467317410415392</v>
       </c>
       <c r="AA4" t="n">
         <v>1.982294353972873</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.61310525180167</v>
+        <v>2.613105251801672</v>
       </c>
     </row>
     <row r="5">
@@ -1836,79 +1836,79 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.475509325197677</v>
+        <v>4.475509325197671</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1182890106177125</v>
+        <v>0.1182890106177126</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02201189337820752</v>
+        <v>0.02201189337820753</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04663375943952424</v>
+        <v>0.04663375943952425</v>
       </c>
       <c r="H5" t="n">
-        <v>3.874614160360752e-05</v>
+        <v>3.874614160360775e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001059466132098391</v>
+        <v>0.001059466132098393</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000209905805995694</v>
+        <v>0.0002099058059956955</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001757486776130351</v>
+        <v>0.00175748677613035</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006140965727205198</v>
+        <v>0.0006140965727205196</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003301649855513182</v>
+        <v>0.003301649855513181</v>
       </c>
       <c r="N5" t="n">
         <v>3.147707138709097e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001068647890104635</v>
+        <v>0.0001068647890104632</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003844587028155846</v>
+        <v>0.003844587028155851</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.678385539397221e-05</v>
+        <v>2.678385539397214e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.759677398392054e-07</v>
+        <v>4.759677398392052e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>5.734158341098629e-05</v>
+        <v>5.734158341098625e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>3.913830566289083e-07</v>
+        <v>3.913830566289084e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.487276943047094e-06</v>
+        <v>2.487276943047093e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0007693430098491048</v>
+        <v>0.000769343009848599</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002563199075917535</v>
+        <v>0.002563199075921302</v>
       </c>
       <c r="X5" t="n">
         <v>0.004459030194024529</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000259918446209719</v>
+        <v>0.0002599184462097193</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.31560413609287</v>
+        <v>-0.3156041360928702</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.971970295161115</v>
+        <v>1.971970295161116</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.613105251728826</v>
+        <v>2.613105251728817</v>
       </c>
     </row>
     <row r="6">
@@ -1929,73 +1929,73 @@
         <v>4.488995850941781</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03780075441389472</v>
+        <v>0.03780075441389462</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01282085827477019</v>
+        <v>0.01282085827477017</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02857149346599272</v>
+        <v>0.02857149346599271</v>
       </c>
       <c r="H6" t="n">
-        <v>3.533826784116746e-05</v>
+        <v>3.533826784116758e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009416546565259212</v>
+        <v>0.0009416546565259211</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001868813796941301</v>
+        <v>0.00018688137969413</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001027832706441012</v>
+        <v>0.001027832706441004</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004899292141898203</v>
+        <v>0.0004899292141898206</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002828996149939954</v>
+        <v>0.002828996149939952</v>
       </c>
       <c r="N6" t="n">
-        <v>2.881934551697529e-05</v>
+        <v>2.88193455169753e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>6.358601305521089e-05</v>
+        <v>6.358601305521087e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003354300193802097</v>
+        <v>0.003354300193802096</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.030728009791974e-05</v>
+        <v>2.030728009792046e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.606506127988129e-07</v>
+        <v>4.606506127988123e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>5.578991405354723e-05</v>
+        <v>5.57899140535472e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.630799976260321e-07</v>
+        <v>2.630799976260331e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.585188499032877e-06</v>
+        <v>1.585188499032875e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005073520109439801</v>
+        <v>0.0005073520109439796</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001716280861615768</v>
+        <v>0.001716280861616668</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004450086451568002</v>
+        <v>0.004450086451568</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001832264480668985</v>
+        <v>0.0001832264480668979</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.1003416178940761</v>
+        <v>-0.1003416178940762</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.881146421412698</v>
+        <v>1.881146421412697</v>
       </c>
       <c r="AB6" t="n">
         <v>2.61310525145604</v>
@@ -2016,79 +2016,79 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.466257644770509</v>
+        <v>4.466257644770503</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01154134168185626</v>
+        <v>0.01154134168185632</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01088688051161721</v>
+        <v>0.0108868805116172</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02304630564214203</v>
+        <v>0.02304630564214197</v>
       </c>
       <c r="H7" t="n">
-        <v>3.385458150065118e-05</v>
+        <v>3.385458150065119e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009057730155199298</v>
+        <v>0.0009057730155199297</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001776478641214107</v>
+        <v>0.0001776478641214098</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0006957893246142095</v>
+        <v>0.000695789324614205</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004646888140058471</v>
+        <v>0.0004646888140058466</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002460563826394585</v>
+        <v>0.002460563826394581</v>
       </c>
       <c r="N7" t="n">
-        <v>2.76609706417299e-05</v>
+        <v>2.766097064172989e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>4.631282320516497e-05</v>
+        <v>4.631282320516496e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003020780359802048</v>
+        <v>0.003020780359802037</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.549544270502034e-05</v>
+        <v>1.549544270502003e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>4.569446863872306e-07</v>
+        <v>4.569446863872303e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>5.481852080252705e-05</v>
+        <v>5.481852080252708e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.747254058409869e-07</v>
+        <v>1.747254058409836e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>1.409502890547565e-06</v>
+        <v>1.409502890547562e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0004424036339617101</v>
+        <v>0.0004424036339612946</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001455844059268914</v>
+        <v>0.00145584405926737</v>
       </c>
       <c r="X7" t="n">
-        <v>0.004421584118865849</v>
+        <v>0.00442158411886585</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001582081497870711</v>
+        <v>0.0001582081497870702</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.0303754172555804</v>
+        <v>-0.03037541725558048</v>
       </c>
       <c r="AA7" t="n">
         <v>1.823669815050713</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.613105252461581</v>
+        <v>2.613105252461578</v>
       </c>
     </row>
     <row r="8">
@@ -2109,76 +2109,76 @@
         <v>4.448086169331721</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004460776312794458</v>
+        <v>0.004460776312794461</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01058060166622802</v>
+        <v>0.01058060166622801</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02091467469491025</v>
+        <v>0.02091467469491021</v>
       </c>
       <c r="H8" t="n">
-        <v>3.337934035364746e-05</v>
+        <v>3.337934035364741e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008891996048512572</v>
+        <v>0.0008891996048512556</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000173762490055203</v>
+        <v>0.0001737624900552024</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0005963807786516049</v>
+        <v>0.0005963807786516025</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004545762296667366</v>
+        <v>0.000454576229666737</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002334128841608283</v>
+        <v>0.002334128841608284</v>
       </c>
       <c r="N8" t="n">
         <v>2.71040534223464e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>4.111266534990591e-05</v>
+        <v>4.111266534990588e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00291253877913793</v>
+        <v>0.002912538779137927</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.343481035649846e-05</v>
+        <v>1.343481035649854e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>4.55683162124448e-07</v>
+        <v>4.556831621244472e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>5.439842899292989e-05</v>
+        <v>5.439842899292988e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.37323099040106e-07</v>
+        <v>1.373230990401045e-07</v>
       </c>
       <c r="U8" t="n">
         <v>1.35499914828759e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004168750603074458</v>
+        <v>0.0004168750603074454</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001339444960013368</v>
+        <v>0.001339444960014808</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004410358447779868</v>
+        <v>0.004410358447779869</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001472081074076286</v>
+        <v>0.0001472081074076278</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.01149789932290144</v>
+        <v>-0.01149789932290148</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.796676912222407</v>
+        <v>1.796676912222406</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.613105253154919</v>
+        <v>2.613105253154918</v>
       </c>
     </row>
     <row r="9">
@@ -2196,31 +2196,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.468268125441163</v>
+        <v>4.468268125441164</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1110232245261394</v>
+        <v>0.1110232245261396</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01810861352797016</v>
+        <v>0.01810861352797017</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04432752778248803</v>
+        <v>0.04432752778248804</v>
       </c>
       <c r="H9" t="n">
-        <v>3.806921752945534e-05</v>
+        <v>3.806921752945483e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001074485115876921</v>
+        <v>0.001074485115876923</v>
       </c>
       <c r="J9" t="n">
         <v>0.0002085693333614092</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001697622871425563</v>
+        <v>0.001697622871425571</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0005874317082775565</v>
+        <v>0.0005874317082775572</v>
       </c>
       <c r="M9" t="n">
         <v>0.003338108115357711</v>
@@ -2232,43 +2232,43 @@
         <v>0.000103649825597652</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003808397360833145</v>
+        <v>0.003808397360833147</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.716550998084806e-05</v>
+        <v>2.716550998084797e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.702068263715077e-07</v>
+        <v>4.702068263715078e-07</v>
       </c>
       <c r="S9" t="n">
         <v>5.748183282585372e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.847722732011976e-07</v>
+        <v>4.847722732011974e-07</v>
       </c>
       <c r="U9" t="n">
         <v>2.205368652649252e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0007238262454201694</v>
+        <v>0.0007238262454201688</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002526123831489777</v>
+        <v>0.002526123831490013</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004470482136277213</v>
+        <v>0.004470482136277214</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002519523378874575</v>
+        <v>0.0002519523378874577</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.296677287784864</v>
+        <v>-0.2966772877848642</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.959432774962861</v>
+        <v>1.95943277496286</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.613105251828567</v>
+        <v>2.613105251828568</v>
       </c>
     </row>
     <row r="10">
@@ -2286,79 +2286,79 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.487410812502764</v>
+        <v>4.487410812502762</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04747377678283893</v>
+        <v>0.04747377678283895</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0141073667832532</v>
+        <v>0.01410736678325318</v>
       </c>
       <c r="G10" t="n">
         <v>0.03422703288368864</v>
       </c>
       <c r="H10" t="n">
-        <v>3.597559159370259e-05</v>
+        <v>3.597559159370257e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001019814762690259</v>
+        <v>0.001019814762690256</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001945659832336165</v>
+        <v>0.000194565983233617</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001086276849466631</v>
+        <v>0.001086276849466623</v>
       </c>
       <c r="L10" t="n">
         <v>0.0005387477895499012</v>
       </c>
       <c r="M10" t="n">
-        <v>0.002873608041095238</v>
+        <v>0.002873608041095242</v>
       </c>
       <c r="N10" t="n">
-        <v>2.992015170139258e-05</v>
+        <v>2.992015170139257e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>7.148531142234178e-05</v>
+        <v>7.148531142234165e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003407950193712569</v>
+        <v>0.003407950193712558</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.186257952717831e-05</v>
+        <v>2.186257952717799e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.633067793183591e-07</v>
+        <v>4.633067793183586e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>5.626430326440551e-05</v>
+        <v>5.626430326440547e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.961891139972914e-07</v>
+        <v>2.961891139972916e-07</v>
       </c>
       <c r="U10" t="n">
         <v>1.864054218519383e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0006057154272933403</v>
+        <v>0.0006057154272933388</v>
       </c>
       <c r="W10" t="n">
-        <v>0.002088026203804737</v>
+        <v>0.002088026203806185</v>
       </c>
       <c r="X10" t="n">
         <v>0.0044435029580982</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0002126036878080675</v>
+        <v>0.0002126036878080639</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.1267560453946422</v>
+        <v>-0.1267560453946423</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.888564486312556</v>
+        <v>1.888564486312555</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.613105251750696</v>
+        <v>2.613105251750693</v>
       </c>
     </row>
     <row r="11">
@@ -2376,79 +2376,79 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.507538323009506</v>
+        <v>4.507538323009513</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008507665310968394</v>
+        <v>0.008507665310968377</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01268043902755068</v>
+        <v>0.01268043902755069</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02458341197697613</v>
+        <v>0.02458341197697611</v>
       </c>
       <c r="H11" t="n">
-        <v>3.45163181055885e-05</v>
+        <v>3.451631810558922e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0009020600961437548</v>
+        <v>0.0009020600961437607</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001806862074612487</v>
+        <v>0.0001806862074612488</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0007350539239766868</v>
+        <v>0.0007350539239766844</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004757511258845543</v>
+        <v>0.0004757511258845547</v>
       </c>
       <c r="M11" t="n">
-        <v>0.00259598351269279</v>
+        <v>0.002595983512692789</v>
       </c>
       <c r="N11" t="n">
         <v>2.797459672717021e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>4.773149134990694e-05</v>
+        <v>4.773149134990692e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.003158234078010128</v>
+        <v>0.003158234078010125</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.740378168929426e-05</v>
+        <v>1.740378168929425e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>4.618835132529721e-07</v>
+        <v>4.618835132529719e-07</v>
       </c>
       <c r="S11" t="n">
         <v>5.511580607320557e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.376306991186261e-07</v>
+        <v>2.376306991186255e-07</v>
       </c>
       <c r="U11" t="n">
         <v>1.545592868689409e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0004705988955957545</v>
+        <v>0.0004705988955976574</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001508903454453128</v>
+        <v>0.001508903454453346</v>
       </c>
       <c r="X11" t="n">
         <v>0.004431192493218529</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0001663307048131928</v>
+        <v>0.0001663307048131937</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.02184040590000499</v>
+        <v>-0.02184040590000493</v>
       </c>
       <c r="AA11" t="n">
         <v>1.855692179823079</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.61310525117766</v>
+        <v>2.613105251177666</v>
       </c>
     </row>
   </sheetData>
@@ -2610,70 +2610,70 @@
         <v>11.07977878591611</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02236365771525903</v>
+        <v>0.02236365771525899</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05297266872821097</v>
+        <v>0.05297266872821094</v>
       </c>
       <c r="G2" t="n">
-        <v>3.987099995124905e-05</v>
+        <v>3.987099995124904e-05</v>
       </c>
       <c r="H2" t="n">
         <v>0.001115047877934225</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002204552969457205</v>
+        <v>0.0002204552969457188</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002082938453430555</v>
+        <v>0.002082938453430552</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003875358811066433</v>
+        <v>0.003875358811066427</v>
       </c>
       <c r="L2" t="n">
-        <v>3.281297100841981e-05</v>
+        <v>3.28129710084198e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001275696534852123</v>
+        <v>0.0001275696534852122</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004157778150090823</v>
+        <v>0.004157778150090817</v>
       </c>
       <c r="O2" t="n">
-        <v>3.146384357918717e-05</v>
+        <v>3.146384357918716e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>4.776230107809114e-07</v>
+        <v>4.776230107809116e-07</v>
       </c>
       <c r="Q2" t="n">
         <v>5.842311683215343e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>5.260035306051294e-07</v>
+        <v>5.260035306051277e-07</v>
       </c>
       <c r="S2" t="n">
-        <v>2.60243033009551e-06</v>
+        <v>2.602430330095508e-06</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008400848151645775</v>
+        <v>0.0008400848151645728</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002914804860842516</v>
+        <v>0.002914804860844738</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004490217877914887</v>
+        <v>0.004490217877914886</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0002874343647440931</v>
+        <v>0.0002874343647440921</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.058974611707973</v>
+        <v>2.058974611707972</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.92518998061481</v>
+        <v>8.925189980614803</v>
       </c>
     </row>
     <row r="3">
@@ -2694,70 +2694,70 @@
         <v>11.04685924082778</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02005735802428354</v>
+        <v>0.02005735802428359</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04942417598730651</v>
+        <v>0.0494241759873065</v>
       </c>
       <c r="G3" t="n">
-        <v>3.911753746663404e-05</v>
+        <v>3.91175374666341e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00110007424811315</v>
+        <v>0.001100074248113149</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00021529586852123</v>
+        <v>0.0002152958685212307</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001970042623700983</v>
+        <v>0.001970042623701009</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003664829541913957</v>
+        <v>0.00366482954191396</v>
       </c>
       <c r="L3" t="n">
         <v>3.227089836273614e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001197009649556326</v>
+        <v>0.0001197009649556325</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004050736803665508</v>
+        <v>0.004050736803665494</v>
       </c>
       <c r="O3" t="n">
-        <v>2.957057636289104e-05</v>
+        <v>2.957057636289122e-05</v>
       </c>
       <c r="P3" t="n">
         <v>4.733795125129374e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.802689914056455e-05</v>
+        <v>5.802689914056458e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.02588320039525e-07</v>
+        <v>5.025883200395254e-07</v>
       </c>
       <c r="S3" t="n">
         <v>2.380649607801306e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007881617926623802</v>
+        <v>0.0007881617926623786</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002765289720491242</v>
+        <v>0.00276528972049028</v>
       </c>
       <c r="V3" t="n">
         <v>0.00448073970900916</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00027163929726161</v>
+        <v>0.0002716392972616097</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.032598873332666</v>
+        <v>2.032598873332668</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.925189980384454</v>
+        <v>8.925189980384456</v>
       </c>
     </row>
     <row r="4">
@@ -2778,67 +2778,67 @@
         <v>11.02610535187536</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02030105077470802</v>
+        <v>0.02030105077470806</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04783479141759854</v>
+        <v>0.04783479141759856</v>
       </c>
       <c r="G4" t="n">
-        <v>3.876779959824295e-05</v>
+        <v>3.876779959824285e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001084908857758595</v>
+        <v>0.001084908857758605</v>
       </c>
       <c r="I4" t="n">
         <v>0.0002121268381683213</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00186052050254084</v>
+        <v>0.001860520502540836</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003422024622077297</v>
+        <v>0.003422024622077296</v>
       </c>
       <c r="L4" t="n">
-        <v>3.187772904606675e-05</v>
+        <v>3.187772904606676e-05</v>
       </c>
       <c r="M4" t="n">
         <v>0.0001132308690536359</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00391962878767878</v>
+        <v>0.003919628787678779</v>
       </c>
       <c r="O4" t="n">
-        <v>2.773715584498884e-05</v>
+        <v>2.773715584498891e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>4.727414790302068e-07</v>
+        <v>4.727414790302064e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.761236249791592e-05</v>
+        <v>5.76123624979159e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.275304306641974e-07</v>
+        <v>4.275304306641975e-07</v>
       </c>
       <c r="S4" t="n">
         <v>2.396652309378752e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>0.000776879076826496</v>
+        <v>0.0007768790768258387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002683355646267634</v>
+        <v>0.002683355646268093</v>
       </c>
       <c r="V4" t="n">
         <v>0.004464258220244086</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0002649056565987183</v>
+        <v>0.0002649056565987174</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.013818398393047</v>
+        <v>2.013818398393048</v>
       </c>
       <c r="Z4" t="n">
         <v>8.925189980241583</v>
@@ -2865,67 +2865,67 @@
         <v>0.02201441562572901</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04663910300003231</v>
+        <v>0.0466391030000323</v>
       </c>
       <c r="G5" t="n">
-        <v>3.874614160360752e-05</v>
+        <v>3.874614160360775e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001059466132098391</v>
+        <v>0.001059466132098393</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000209905805995694</v>
+        <v>0.0002099058059956955</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001757486776130351</v>
+        <v>0.00175748677613035</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003301649855513182</v>
+        <v>0.003301649855513181</v>
       </c>
       <c r="L5" t="n">
         <v>3.147707138709097e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001068647890104635</v>
+        <v>0.0001068647890104632</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003844587028155846</v>
+        <v>0.003844587028155851</v>
       </c>
       <c r="O5" t="n">
-        <v>2.678385539397221e-05</v>
+        <v>2.678385539397214e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.759677398392054e-07</v>
+        <v>4.759677398392052e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.734158341098629e-05</v>
+        <v>5.734158341098625e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>3.913830566289083e-07</v>
+        <v>3.913830566289084e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.487561949338781e-06</v>
+        <v>2.487561949338782e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0007694311655323279</v>
+        <v>0.000769431165532088</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002563492781810747</v>
+        <v>0.002563492781801132</v>
       </c>
       <c r="V5" t="n">
         <v>0.004459030194024529</v>
       </c>
       <c r="W5" t="n">
-        <v>0.000259918446209719</v>
+        <v>0.0002599184462097193</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.003330158067112</v>
+        <v>2.003330158067111</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.925189980223399</v>
+        <v>8.925189980223408</v>
       </c>
     </row>
     <row r="6">
@@ -2943,64 +2943,64 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.89305201968298</v>
+        <v>10.89305201968297</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01282232736138853</v>
+        <v>0.01282232736138852</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02857476734967648</v>
+        <v>0.02857476734967644</v>
       </c>
       <c r="G6" t="n">
-        <v>3.533826784116746e-05</v>
+        <v>3.533826784116758e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009416546565259212</v>
+        <v>0.0009416546565259211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001868813796941301</v>
+        <v>0.00018688137969413</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001027832706441012</v>
+        <v>0.001027832706441004</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002828996149939954</v>
+        <v>0.002828996149939952</v>
       </c>
       <c r="L6" t="n">
-        <v>2.881934551697529e-05</v>
+        <v>2.88193455169753e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>6.358601305521089e-05</v>
+        <v>6.358601305521087e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003354300193802097</v>
+        <v>0.003354300193802096</v>
       </c>
       <c r="O6" t="n">
-        <v>2.030728009791974e-05</v>
+        <v>2.030728009792046e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.606506127988129e-07</v>
+        <v>4.606506127988123e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.578991405354723e-05</v>
+        <v>5.57899140535472e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.630799976260321e-07</v>
+        <v>2.630799976260331e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.585370138917008e-06</v>
+        <v>1.585370138917006e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000507410146213405</v>
+        <v>0.0005074101462134057</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001716477522805638</v>
+        <v>0.001716477522806823</v>
       </c>
       <c r="V6" t="n">
-        <v>0.004450086451568002</v>
+        <v>0.004450086451568</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001832264480668985</v>
+        <v>0.0001832264480668979</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
         <v>1.911061929788442</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.925189979607097</v>
+        <v>8.925189979607095</v>
       </c>
     </row>
     <row r="7">
@@ -3033,64 +3033,64 @@
         <v>0.01088812799210039</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02304894641848447</v>
+        <v>0.02304894641848442</v>
       </c>
       <c r="G7" t="n">
-        <v>3.385458150065118e-05</v>
+        <v>3.385458150065119e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009057730155199298</v>
+        <v>0.0009057730155199297</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001776478641214107</v>
+        <v>0.0001776478641214098</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0006957893246142095</v>
+        <v>0.000695789324614205</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002460563826394585</v>
+        <v>0.002460563826394581</v>
       </c>
       <c r="L7" t="n">
-        <v>2.76609706417299e-05</v>
+        <v>2.766097064172989e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>4.631282320516497e-05</v>
+        <v>4.631282320516496e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003020780359802048</v>
+        <v>0.003020780359802037</v>
       </c>
       <c r="O7" t="n">
-        <v>1.549544270502034e-05</v>
+        <v>1.549544270502003e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>4.569446863872306e-07</v>
+        <v>4.569446863872303e-07</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.481852080252705e-05</v>
+        <v>5.481852080252708e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.747254058409869e-07</v>
+        <v>1.747254058409836e-07</v>
       </c>
       <c r="S7" t="n">
         <v>1.40966439937877e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.000442454327078936</v>
+        <v>0.0004424543270775148</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001456010878133181</v>
+        <v>0.001456010878132382</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004421584118865849</v>
+        <v>0.00442158411886585</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001582081497870711</v>
+        <v>0.0001582081497870702</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.852671284051605</v>
+        <v>1.852671284051604</v>
       </c>
       <c r="Z7" t="n">
         <v>8.92518997911341</v>
@@ -3114,70 +3114,70 @@
         <v>10.79532945823042</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01058181405154487</v>
+        <v>0.01058181405154486</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02091707121689521</v>
+        <v>0.02091707121689518</v>
       </c>
       <c r="G8" t="n">
-        <v>3.337934035364746e-05</v>
+        <v>3.337934035364741e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008891996048512572</v>
+        <v>0.0008891996048512556</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000173762490055203</v>
+        <v>0.0001737624900552024</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0005963807786516049</v>
+        <v>0.0005963807786516025</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002334128841608283</v>
+        <v>0.002334128841608284</v>
       </c>
       <c r="L8" t="n">
         <v>2.71040534223464e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.111266534990591e-05</v>
+        <v>4.111266534990588e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00291253877913793</v>
+        <v>0.002912538779137927</v>
       </c>
       <c r="O8" t="n">
-        <v>1.343481035649846e-05</v>
+        <v>1.343481035649854e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.55683162124448e-07</v>
+        <v>4.556831621244472e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.439842899292989e-05</v>
+        <v>5.439842899292988e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37323099040106e-07</v>
+        <v>1.373230990401045e-07</v>
       </c>
       <c r="S8" t="n">
         <v>1.355154411771047e-06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0004169228282149833</v>
+        <v>0.0004169228282149831</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001339598441209757</v>
+        <v>0.001339598441211655</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004410358447779868</v>
+        <v>0.004410358447779869</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0001472081074076286</v>
+        <v>0.0001472081074076278</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.825249118300724</v>
+        <v>1.825249118300723</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.925189978883196</v>
+        <v>8.925189978883195</v>
       </c>
     </row>
     <row r="9">
@@ -3195,25 +3195,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.9965874932952</v>
+        <v>10.99658749329519</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01811068851555996</v>
+        <v>0.01811068851555998</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04433260708189952</v>
+        <v>0.04433260708189954</v>
       </c>
       <c r="G9" t="n">
-        <v>3.806921752945534e-05</v>
+        <v>3.806921752945483e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001074485115876921</v>
+        <v>0.001074485115876923</v>
       </c>
       <c r="I9" t="n">
         <v>0.0002085693333614092</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001697622871425563</v>
+        <v>0.001697622871425571</v>
       </c>
       <c r="K9" t="n">
         <v>0.003338108115357711</v>
@@ -3225,43 +3225,43 @@
         <v>0.000103649825597652</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003808397360833145</v>
+        <v>0.003808397360833147</v>
       </c>
       <c r="O9" t="n">
-        <v>2.716550998084806e-05</v>
+        <v>2.716550998084797e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>4.702068263715077e-07</v>
+        <v>4.702068263715078e-07</v>
       </c>
       <c r="Q9" t="n">
         <v>5.748183282585372e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.847722732011976e-07</v>
+        <v>4.847722732011974e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>2.205621356290986e-06</v>
+        <v>2.205621356290984e-06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.000723909185534503</v>
+        <v>0.0007239091855345014</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002526413289079761</v>
+        <v>0.002526413289078392</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004470482136277213</v>
+        <v>0.004470482136277214</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0002519523378874575</v>
+        <v>0.0002519523378874577</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.99059325610557</v>
+        <v>1.990593256105571</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.925189980052043</v>
+        <v>8.925189980052034</v>
       </c>
     </row>
     <row r="10">
@@ -3282,70 +3282,70 @@
         <v>10.90827838482768</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01410898328530925</v>
+        <v>0.01410898328530923</v>
       </c>
       <c r="F10" t="n">
         <v>0.03423095481113823</v>
       </c>
       <c r="G10" t="n">
-        <v>3.597559159370259e-05</v>
+        <v>3.597559159370257e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001019814762690259</v>
+        <v>0.001019814762690256</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001945659832336165</v>
+        <v>0.000194565983233617</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001086276849466631</v>
+        <v>0.001086276849466623</v>
       </c>
       <c r="K10" t="n">
-        <v>0.002873608041095238</v>
+        <v>0.002873608041095242</v>
       </c>
       <c r="L10" t="n">
-        <v>2.992015170139258e-05</v>
+        <v>2.992015170139257e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>7.148531142234178e-05</v>
+        <v>7.148531142234165e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.003407950193712569</v>
+        <v>0.003407950193712558</v>
       </c>
       <c r="O10" t="n">
-        <v>2.186257952717831e-05</v>
+        <v>2.186257952717799e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>4.633067793183591e-07</v>
+        <v>4.633067793183586e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.626430326440551e-05</v>
+        <v>5.626430326440547e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>2.961891139972914e-07</v>
+        <v>2.961891139972916e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.864267812418453e-06</v>
+        <v>1.864267812418452e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0006057848336005988</v>
+        <v>0.0006057848336005996</v>
       </c>
       <c r="U10" t="n">
-        <v>0.002088265461686193</v>
+        <v>0.002088265461684953</v>
       </c>
       <c r="V10" t="n">
         <v>0.0044435029580982</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0002126036878080675</v>
+        <v>0.0002126036878080639</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.91859796274231</v>
+        <v>1.918597962742308</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.925189979516317</v>
+        <v>8.92518997951632</v>
       </c>
     </row>
     <row r="11">
@@ -3366,70 +3366,70 @@
         <v>10.8619952521514</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01268189202413569</v>
+        <v>0.0126818920241357</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0245862288836757</v>
+        <v>0.02458622888367568</v>
       </c>
       <c r="G11" t="n">
-        <v>3.45163181055885e-05</v>
+        <v>3.451631810558922e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0009020600961437548</v>
+        <v>0.0009020600961437607</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001806862074612487</v>
+        <v>0.0001806862074612488</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0007350539239766868</v>
+        <v>0.0007350539239766844</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00259598351269279</v>
+        <v>0.002595983512692789</v>
       </c>
       <c r="L11" t="n">
         <v>2.797459672717021e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>4.773149134990694e-05</v>
+        <v>4.773149134990692e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003158234078010128</v>
+        <v>0.003158234078010125</v>
       </c>
       <c r="O11" t="n">
-        <v>1.740378168929426e-05</v>
+        <v>1.740378168929425e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>4.618835132529721e-07</v>
+        <v>4.618835132529719e-07</v>
       </c>
       <c r="Q11" t="n">
         <v>5.511580607320557e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.376306991186261e-07</v>
+        <v>2.376306991186255e-07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.545769971481761e-06</v>
+        <v>1.545769971481763e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0004706528194848826</v>
+        <v>0.0004706528194860577</v>
       </c>
       <c r="U11" t="n">
-        <v>0.001509076353170352</v>
+        <v>0.001509076353162545</v>
       </c>
       <c r="V11" t="n">
         <v>0.004431192493218529</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0001663307048131928</v>
+        <v>0.0001663307048131937</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.88520289430888</v>
+        <v>1.885202894308881</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.925189979467604</v>
+        <v>8.925189979467611</v>
       </c>
     </row>
   </sheetData>
@@ -3598,70 +3598,70 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.878166690821575</v>
+        <v>4.878166690821574</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1420764499332589</v>
+        <v>0.1420764499332591</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02236109545418416</v>
+        <v>0.02236109545418414</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05296659951498826</v>
+        <v>0.05296659951498817</v>
       </c>
       <c r="H2" t="n">
-        <v>3.987099995124905e-05</v>
+        <v>3.987099995124904e-05</v>
       </c>
       <c r="I2" t="n">
         <v>0.001115047877934225</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002204552969457205</v>
+        <v>0.0002204552969457188</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002082938453430555</v>
+        <v>0.002082938453430552</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006361631112596297</v>
+        <v>0.0006361631112596293</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003875358811066433</v>
+        <v>0.003875358811066427</v>
       </c>
       <c r="N2" t="n">
-        <v>3.281297100841981e-05</v>
+        <v>3.28129710084198e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0001275696534852123</v>
+        <v>0.0001275696534852122</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004157778150090823</v>
+        <v>0.004157778150090817</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.146384357918717e-05</v>
+        <v>3.146384357918716e-05</v>
       </c>
       <c r="R2" t="n">
-        <v>4.776230107809114e-07</v>
+        <v>4.776230107809116e-07</v>
       </c>
       <c r="S2" t="n">
         <v>5.842311683215343e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>5.260035306051294e-07</v>
+        <v>5.260035306051277e-07</v>
       </c>
       <c r="U2" t="n">
-        <v>2.602132163041635e-06</v>
+        <v>2.602132163041632e-06</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008399885645132343</v>
+        <v>0.0008399885645132322</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002914470904245126</v>
+        <v>0.002914470904246598</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004490217877914887</v>
+        <v>0.004490217877914886</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002874343647440931</v>
+        <v>0.0002874343647440921</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -3670,7 +3670,7 @@
         <v>2.026743697951657</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.613105248211781</v>
+        <v>2.613105248211779</v>
       </c>
     </row>
     <row r="3">
@@ -3694,70 +3694,70 @@
         <v>0.1367993228268541</v>
       </c>
       <c r="F3" t="n">
-        <v>0.020055060001823</v>
+        <v>0.02005506000182304</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04941851333391134</v>
+        <v>0.04941851333391135</v>
       </c>
       <c r="H3" t="n">
-        <v>3.911753746663404e-05</v>
+        <v>3.91175374666341e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00110007424811315</v>
+        <v>0.001100074248113149</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00021529586852123</v>
+        <v>0.0002152958685212307</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001970042623700983</v>
+        <v>0.001970042623701009</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006130805146831818</v>
+        <v>0.0006130805146831815</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003664829541913957</v>
+        <v>0.00366482954191396</v>
       </c>
       <c r="N3" t="n">
         <v>3.227089836273614e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001197009649556326</v>
+        <v>0.0001197009649556325</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004050736803665508</v>
+        <v>0.004050736803665494</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.957057636289104e-05</v>
+        <v>2.957057636289122e-05</v>
       </c>
       <c r="R3" t="n">
         <v>4.733795125129374e-07</v>
       </c>
       <c r="S3" t="n">
-        <v>5.802689914056455e-05</v>
+        <v>5.802689914056458e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>5.02588320039525e-07</v>
+        <v>5.025883200395254e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>2.380376850728178e-06</v>
+        <v>2.380376850728177e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0007880714909636281</v>
+        <v>0.0007880714909636268</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002764972894223298</v>
+        <v>0.002764972894222869</v>
       </c>
       <c r="X3" t="n">
         <v>0.00448073970900916</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00027163929726161</v>
+        <v>0.0002716392972616097</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.000780841864457</v>
+        <v>2.000780841864458</v>
       </c>
       <c r="AB3" t="n">
         <v>2.613105248961264</v>
@@ -3778,70 +3778,70 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.812882770376467</v>
+        <v>4.812882770376468</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1297813404727587</v>
+        <v>0.1297813404727584</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02029872483175</v>
+        <v>0.02029872483175002</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04782931086403116</v>
+        <v>0.04782931086403118</v>
       </c>
       <c r="H4" t="n">
-        <v>3.876779959824295e-05</v>
+        <v>3.876779959824285e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001084908857758595</v>
+        <v>0.001084908857758605</v>
       </c>
       <c r="J4" t="n">
         <v>0.0002121268381683213</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00186052050254084</v>
+        <v>0.001860520502540836</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006130564338965224</v>
+        <v>0.0006130564338965223</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003422024622077297</v>
+        <v>0.003422024622077296</v>
       </c>
       <c r="N4" t="n">
-        <v>3.187772904606675e-05</v>
+        <v>3.187772904606676e-05</v>
       </c>
       <c r="O4" t="n">
         <v>0.0001132308690536359</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00391962878767878</v>
+        <v>0.003919628787678779</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.773715584498884e-05</v>
+        <v>2.773715584498891e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>4.727414790302068e-07</v>
+        <v>4.727414790302064e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>5.761236249791592e-05</v>
+        <v>5.76123624979159e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.275304306641974e-07</v>
+        <v>4.275304306641975e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.396377718835448e-06</v>
+        <v>2.396377718835449e-06</v>
       </c>
       <c r="V4" t="n">
-        <v>0.000776790067817694</v>
+        <v>0.0007767900678164999</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002683048207395546</v>
+        <v>0.002683048207395167</v>
       </c>
       <c r="X4" t="n">
         <v>0.004464258220244086</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002649056565987183</v>
+        <v>0.0002649056565987174</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -3850,7 +3850,7 @@
         <v>1.982294353972873</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.613105249475208</v>
+        <v>2.613105249475212</v>
       </c>
     </row>
     <row r="5">
@@ -3868,79 +3868,79 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.791113459172941</v>
+        <v>4.791113459172938</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1182890106177125</v>
+        <v>0.1182890106177126</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02201189337820752</v>
+        <v>0.02201189337820753</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04663375943952424</v>
+        <v>0.04663375943952425</v>
       </c>
       <c r="H5" t="n">
-        <v>3.874614160360752e-05</v>
+        <v>3.874614160360775e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001059466132098391</v>
+        <v>0.001059466132098393</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000209905805995694</v>
+        <v>0.0002099058059956955</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001757486776130351</v>
+        <v>0.00175748677613035</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006140965727205198</v>
+        <v>0.0006140965727205196</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003301649855513182</v>
+        <v>0.003301649855513181</v>
       </c>
       <c r="N5" t="n">
         <v>3.147707138709097e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0001068647890104635</v>
+        <v>0.0001068647890104632</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003844587028155846</v>
+        <v>0.003844587028155851</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.678385539397221e-05</v>
+        <v>2.678385539397214e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.759677398392054e-07</v>
+        <v>4.759677398392052e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>5.734158341098629e-05</v>
+        <v>5.734158341098625e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>3.913830566289083e-07</v>
+        <v>3.913830566289084e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.487276943047094e-06</v>
+        <v>2.487276943047093e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0007693430098491048</v>
+        <v>0.000769343009848599</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002563199075917535</v>
+        <v>0.002563199075921302</v>
       </c>
       <c r="X5" t="n">
         <v>0.004459030194024529</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000259918446209719</v>
+        <v>0.0002599184462097193</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.971970295161115</v>
+        <v>1.971970295161116</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.613105249611221</v>
+        <v>2.613105249611214</v>
       </c>
     </row>
     <row r="6">
@@ -3958,79 +3958,79 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.589337468162595</v>
+        <v>4.589337468162596</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03780075441389472</v>
+        <v>0.03780075441389462</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01282085827477019</v>
+        <v>0.01282085827477017</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02857149346599272</v>
+        <v>0.02857149346599271</v>
       </c>
       <c r="H6" t="n">
-        <v>3.533826784116746e-05</v>
+        <v>3.533826784116758e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009416546565259212</v>
+        <v>0.0009416546565259211</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001868813796941301</v>
+        <v>0.00018688137969413</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001027832706441012</v>
+        <v>0.001027832706441004</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004899292141898203</v>
+        <v>0.0004899292141898206</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002828996149939954</v>
+        <v>0.002828996149939952</v>
       </c>
       <c r="N6" t="n">
-        <v>2.881934551697529e-05</v>
+        <v>2.88193455169753e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>6.358601305521089e-05</v>
+        <v>6.358601305521087e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003354300193802097</v>
+        <v>0.003354300193802096</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.030728009791974e-05</v>
+        <v>2.030728009792046e-05</v>
       </c>
       <c r="R6" t="n">
-        <v>4.606506127988129e-07</v>
+        <v>4.606506127988123e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>5.578991405354723e-05</v>
+        <v>5.57899140535472e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>2.630799976260321e-07</v>
+        <v>2.630799976260331e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.585188499032877e-06</v>
+        <v>1.585188499032875e-06</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005073520109439801</v>
+        <v>0.0005073520109439796</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001716280861615768</v>
+        <v>0.001716280861616668</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004450086451568002</v>
+        <v>0.004450086451568</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001832264480668985</v>
+        <v>0.0001832264480668979</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.881146421412698</v>
+        <v>1.881146421412697</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.613105250782778</v>
+        <v>2.613105250782779</v>
       </c>
     </row>
     <row r="7">
@@ -4048,70 +4048,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.496633061822279</v>
+        <v>4.496633061822275</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01154134168185626</v>
+        <v>0.01154134168185632</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01088688051161721</v>
+        <v>0.0108868805116172</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02304630564214203</v>
+        <v>0.02304630564214197</v>
       </c>
       <c r="H7" t="n">
-        <v>3.385458150065118e-05</v>
+        <v>3.385458150065119e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009057730155199298</v>
+        <v>0.0009057730155199297</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001776478641214107</v>
+        <v>0.0001776478641214098</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0006957893246142095</v>
+        <v>0.000695789324614205</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004646888140058471</v>
+        <v>0.0004646888140058466</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002460563826394585</v>
+        <v>0.002460563826394581</v>
       </c>
       <c r="N7" t="n">
-        <v>2.76609706417299e-05</v>
+        <v>2.766097064172989e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>4.631282320516497e-05</v>
+        <v>4.631282320516496e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003020780359802048</v>
+        <v>0.003020780359802037</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.549544270502034e-05</v>
+        <v>1.549544270502003e-05</v>
       </c>
       <c r="R7" t="n">
-        <v>4.569446863872306e-07</v>
+        <v>4.569446863872303e-07</v>
       </c>
       <c r="S7" t="n">
-        <v>5.481852080252705e-05</v>
+        <v>5.481852080252708e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.747254058409869e-07</v>
+        <v>1.747254058409836e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>1.409502890547565e-06</v>
+        <v>1.409502890547562e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0004424036339617101</v>
+        <v>0.0004424036339612946</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001455844059268914</v>
+        <v>0.00145584405926737</v>
       </c>
       <c r="X7" t="n">
-        <v>0.004421584118865849</v>
+        <v>0.00442158411886585</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001582081497870711</v>
+        <v>0.0001582081497870702</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v>1.823669815050713</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.613105252257771</v>
+        <v>2.613105252257769</v>
       </c>
     </row>
     <row r="8">
@@ -4138,79 +4138,79 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.459584068577476</v>
+        <v>4.459584068577477</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004460776312794458</v>
+        <v>0.004460776312794461</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01058060166622802</v>
+        <v>0.01058060166622801</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02091467469491025</v>
+        <v>0.02091467469491021</v>
       </c>
       <c r="H8" t="n">
-        <v>3.337934035364746e-05</v>
+        <v>3.337934035364741e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008891996048512572</v>
+        <v>0.0008891996048512556</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000173762490055203</v>
+        <v>0.0001737624900552024</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0005963807786516049</v>
+        <v>0.0005963807786516025</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004545762296667366</v>
+        <v>0.000454576229666737</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002334128841608283</v>
+        <v>0.002334128841608284</v>
       </c>
       <c r="N8" t="n">
         <v>2.71040534223464e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>4.111266534990591e-05</v>
+        <v>4.111266534990588e-05</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00291253877913793</v>
+        <v>0.002912538779137927</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.343481035649846e-05</v>
+        <v>1.343481035649854e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>4.55683162124448e-07</v>
+        <v>4.556831621244472e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>5.439842899292989e-05</v>
+        <v>5.439842899292988e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.37323099040106e-07</v>
+        <v>1.373230990401045e-07</v>
       </c>
       <c r="U8" t="n">
         <v>1.35499914828759e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004168750603074458</v>
+        <v>0.0004168750603074454</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001339444960013368</v>
+        <v>0.001339444960014808</v>
       </c>
       <c r="X8" t="n">
-        <v>0.004410358447779868</v>
+        <v>0.004410358447779869</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0001472081074076286</v>
+        <v>0.0001472081074076278</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.796676912222407</v>
+        <v>1.796676912222406</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.613105253077772</v>
+        <v>2.613105253077773</v>
       </c>
     </row>
     <row r="9">
@@ -4228,31 +4228,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.764945411235419</v>
+        <v>4.764945411235418</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1110232245261394</v>
+        <v>0.1110232245261396</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01810861352797016</v>
+        <v>0.01810861352797017</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04432752778248803</v>
+        <v>0.04432752778248804</v>
       </c>
       <c r="H9" t="n">
-        <v>3.806921752945534e-05</v>
+        <v>3.806921752945483e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001074485115876921</v>
+        <v>0.001074485115876923</v>
       </c>
       <c r="J9" t="n">
         <v>0.0002085693333614092</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001697622871425563</v>
+        <v>0.001697622871425571</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0005874317082775565</v>
+        <v>0.0005874317082775572</v>
       </c>
       <c r="M9" t="n">
         <v>0.003338108115357711</v>
@@ -4264,43 +4264,43 @@
         <v>0.000103649825597652</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003808397360833145</v>
+        <v>0.003808397360833147</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.716550998084806e-05</v>
+        <v>2.716550998084797e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>4.702068263715077e-07</v>
+        <v>4.702068263715078e-07</v>
       </c>
       <c r="S9" t="n">
         <v>5.748183282585372e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>4.847722732011976e-07</v>
+        <v>4.847722732011974e-07</v>
       </c>
       <c r="U9" t="n">
         <v>2.205368652649252e-06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0007238262454201694</v>
+        <v>0.0007238262454201688</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002526123831489777</v>
+        <v>0.002526123831490013</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004470482136277213</v>
+        <v>0.004470482136277214</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0002519523378874575</v>
+        <v>0.0002519523378874577</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.959432774962861</v>
+        <v>1.95943277496286</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.613105249837959</v>
+        <v>2.613105249837958</v>
       </c>
     </row>
     <row r="10">
@@ -4318,76 +4318,76 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.614166857046908</v>
+        <v>4.614166857046909</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04747377678283893</v>
+        <v>0.04747377678283895</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0141073667832532</v>
+        <v>0.01410736678325318</v>
       </c>
       <c r="G10" t="n">
         <v>0.03422703288368864</v>
       </c>
       <c r="H10" t="n">
-        <v>3.597559159370259e-05</v>
+        <v>3.597559159370257e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001019814762690259</v>
+        <v>0.001019814762690256</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001945659832336165</v>
+        <v>0.000194565983233617</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001086276849466631</v>
+        <v>0.001086276849466623</v>
       </c>
       <c r="L10" t="n">
         <v>0.0005387477895499012</v>
       </c>
       <c r="M10" t="n">
-        <v>0.002873608041095238</v>
+        <v>0.002873608041095242</v>
       </c>
       <c r="N10" t="n">
-        <v>2.992015170139258e-05</v>
+        <v>2.992015170139257e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>7.148531142234178e-05</v>
+        <v>7.148531142234165e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003407950193712569</v>
+        <v>0.003407950193712558</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.186257952717831e-05</v>
+        <v>2.186257952717799e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>4.633067793183591e-07</v>
+        <v>4.633067793183586e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>5.626430326440551e-05</v>
+        <v>5.626430326440547e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.961891139972914e-07</v>
+        <v>2.961891139972916e-07</v>
       </c>
       <c r="U10" t="n">
         <v>1.864054218519383e-06</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0006057154272933403</v>
+        <v>0.0006057154272933388</v>
       </c>
       <c r="W10" t="n">
-        <v>0.002088026203804737</v>
+        <v>0.002088026203806185</v>
       </c>
       <c r="X10" t="n">
         <v>0.0044435029580982</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0002126036878080675</v>
+        <v>0.0002126036878080639</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.888564486312556</v>
+        <v>1.888564486312555</v>
       </c>
       <c r="AB10" t="n">
         <v>2.613105250900198</v>
@@ -4408,70 +4408,70 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.529378728762964</v>
+        <v>4.529378728762972</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008507665310968394</v>
+        <v>0.008507665310968377</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01268043902755068</v>
+        <v>0.01268043902755069</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02458341197697613</v>
+        <v>0.02458341197697611</v>
       </c>
       <c r="H11" t="n">
-        <v>3.45163181055885e-05</v>
+        <v>3.451631810558922e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0009020600961437548</v>
+        <v>0.0009020600961437607</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001806862074612487</v>
+        <v>0.0001806862074612488</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0007350539239766868</v>
+        <v>0.0007350539239766844</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004757511258845543</v>
+        <v>0.0004757511258845547</v>
       </c>
       <c r="M11" t="n">
-        <v>0.00259598351269279</v>
+        <v>0.002595983512692789</v>
       </c>
       <c r="N11" t="n">
         <v>2.797459672717021e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>4.773149134990694e-05</v>
+        <v>4.773149134990692e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.003158234078010128</v>
+        <v>0.003158234078010125</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.740378168929426e-05</v>
+        <v>1.740378168929425e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>4.618835132529721e-07</v>
+        <v>4.618835132529719e-07</v>
       </c>
       <c r="S11" t="n">
         <v>5.511580607320557e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.376306991186261e-07</v>
+        <v>2.376306991186255e-07</v>
       </c>
       <c r="U11" t="n">
         <v>1.545592868689409e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0004705988955957545</v>
+        <v>0.0004705988955976574</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001508903454453128</v>
+        <v>0.001508903454453346</v>
       </c>
       <c r="X11" t="n">
         <v>0.004431192493218529</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0001663307048131928</v>
+        <v>0.0001663307048131937</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -4480,7 +4480,7 @@
         <v>1.855692179823079</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.613105251031114</v>
+        <v>2.61310525103112</v>
       </c>
     </row>
   </sheetData>
@@ -4574,31 +4574,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.399075197032862</v>
+        <v>2.399075197032854</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3229212258061554</v>
+        <v>0.322921225806155</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05132008853399484</v>
+        <v>0.05132008853399474</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01620950307353841</v>
+        <v>0.0162095030735384</v>
       </c>
       <c r="H2" t="n">
-        <v>0.10425448409781</v>
+        <v>0.1042544840978092</v>
       </c>
       <c r="I2" t="n">
-        <v>4.833115662204297e-06</v>
+        <v>4.833115662204296e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001560167444560522</v>
+        <v>0.001560167444560518</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005413243483328968</v>
+        <v>0.005413243483322671</v>
       </c>
       <c r="L2" t="n">
-        <v>1.897391694870995</v>
+        <v>1.897391694870993</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -4619,31 +4619,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.151921314539145</v>
+        <v>2.151921314539141</v>
       </c>
       <c r="E3" t="n">
-        <v>0.308987673827032</v>
+        <v>0.3089876738270315</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03815515100738626</v>
+        <v>0.03815515100738619</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01598108859471935</v>
+        <v>0.01598108859471932</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1035592013147193</v>
+        <v>0.1035592013147192</v>
       </c>
       <c r="I3" t="n">
         <v>4.421234556262935e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001463738360414731</v>
+        <v>0.00146373836041473</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00513557074096514</v>
+        <v>0.005135570740963085</v>
       </c>
       <c r="L3" t="n">
-        <v>1.678634451600722</v>
+        <v>1.678634451600724</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -4664,31 +4664,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.940612837015407</v>
+        <v>1.940612837015408</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3020604124453138</v>
+        <v>0.3020604124453136</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04608639375192532</v>
+        <v>0.04608639375192548</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01607793456641522</v>
+        <v>0.01607793456641525</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1030603212748789</v>
+        <v>0.103060321274879</v>
       </c>
       <c r="I4" t="n">
-        <v>4.450954048361186e-06</v>
+        <v>4.450954048361187e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001442784611917505</v>
+        <v>0.001442784611916191</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004983406491719901</v>
+        <v>0.004983406491718334</v>
       </c>
       <c r="L4" t="n">
-        <v>1.466897130994516</v>
+        <v>1.46689713099452</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -4709,16 +4709,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.897108325503849</v>
+        <v>1.897108325503864</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3073238008523991</v>
+        <v>0.3073238008523994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06267991062657738</v>
+        <v>0.06267991062657755</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01633922733447172</v>
+        <v>0.01633922733447179</v>
       </c>
       <c r="H5" t="n">
         <v>0.1020909024928441</v>
@@ -4727,10 +4727,10 @@
         <v>4.619787311505655e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001428952688614692</v>
+        <v>0.001428952688615918</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004760802612223015</v>
+        <v>0.004760802612231642</v>
       </c>
       <c r="L5" t="n">
         <v>1.402480107332681</v>
@@ -4754,31 +4754,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.538271021178348</v>
+        <v>1.538271021178349</v>
       </c>
       <c r="E6" t="n">
         <v>0.2598355802687869</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01762308555606739</v>
+        <v>0.01762308555606729</v>
       </c>
       <c r="G6" t="n">
         <v>0.01551713341106995</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09762862568343858</v>
+        <v>0.09762862568343868</v>
       </c>
       <c r="I6" t="n">
-        <v>2.944277570154816e-06</v>
+        <v>2.944277570154814e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009423391268020504</v>
+        <v>0.0009423391268020523</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003187764261495563</v>
+        <v>0.003187764261491228</v>
       </c>
       <c r="L6" t="n">
-        <v>1.143533535676994</v>
+        <v>1.143533535676992</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -4799,31 +4799,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.23501176907669</v>
+        <v>1.235011769076686</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2431522460043292</v>
+        <v>0.2431522460043287</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01591071817513006</v>
+        <v>0.01591071817513003</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01541053876202196</v>
+        <v>0.01541053876202199</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09623801688947572</v>
+        <v>0.0962380168894757</v>
       </c>
       <c r="I7" t="n">
-        <v>2.617964833986284e-06</v>
+        <v>2.617964833986279e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008217061234213301</v>
+        <v>0.0008217061234180734</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002704037413820807</v>
+        <v>0.002704037413821256</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8607718856258926</v>
+        <v>0.8607718856258886</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -4844,31 +4844,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.15406131373262</v>
+        <v>1.154061313732617</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2355715821537628</v>
+        <v>0.2355715821537625</v>
       </c>
       <c r="F8" t="n">
         <v>0.01840883946338096</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01540791177997902</v>
+        <v>0.01540791177997903</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09548110359410812</v>
+        <v>0.09548110359410804</v>
       </c>
       <c r="I8" t="n">
         <v>2.516731355492436e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0007742901808642834</v>
+        <v>0.0007742901808642826</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00248784151199073</v>
+        <v>0.002487841511991098</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7859272262012733</v>
+        <v>0.7859272262012732</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -4889,31 +4889,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.958154102761805</v>
+        <v>1.95815410276181</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2960962596485859</v>
+        <v>0.2960962596485861</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03361273292334658</v>
+        <v>0.03361273292334663</v>
       </c>
       <c r="G9" t="n">
         <v>0.01586517403584983</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1022662252574711</v>
+        <v>0.1022662252574716</v>
       </c>
       <c r="I9" t="n">
-        <v>4.096180020154864e-06</v>
+        <v>4.09618002015486e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001344411330501191</v>
+        <v>0.001344411330501195</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004691940258858216</v>
+        <v>0.00469194025885708</v>
       </c>
       <c r="L9" t="n">
-        <v>1.504273246881714</v>
+        <v>1.504273246881715</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -4937,28 +4937,28 @@
         <v>1.521041108487123</v>
       </c>
       <c r="E10" t="n">
-        <v>0.269011224743176</v>
+        <v>0.2690112247431757</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02431599742206897</v>
+        <v>0.02431599742206899</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01562330561090261</v>
+        <v>0.01562330561090268</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09985489485305188</v>
+        <v>0.09985489485305185</v>
       </c>
       <c r="I10" t="n">
-        <v>3.462233689234743e-06</v>
+        <v>3.462233689234744e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001125036137698809</v>
+        <v>0.001125036137698806</v>
       </c>
       <c r="K10" t="n">
-        <v>0.003878231971476178</v>
+        <v>0.003878231971473931</v>
       </c>
       <c r="L10" t="n">
-        <v>1.10722895343388</v>
+        <v>1.107228953433881</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -4979,31 +4979,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.322298040883371</v>
+        <v>1.322298040883373</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2596858207067237</v>
+        <v>0.2596858207067239</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02616994220885759</v>
+        <v>0.02616994220885763</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01561966559088741</v>
+        <v>0.0156196655908874</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09633649346690966</v>
+        <v>0.09633649346690976</v>
       </c>
       <c r="I11" t="n">
-        <v>2.870733933945281e-06</v>
+        <v>2.870733933945282e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0008740750855103635</v>
+        <v>0.0008740750855162587</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002802588209024384</v>
+        <v>0.00280258820902306</v>
       </c>
       <c r="L11" t="n">
-        <v>0.920806582898002</v>
+        <v>0.9208065828980001</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -5100,31 +5100,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.063558420023194</v>
+        <v>4.063558420023184</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3229212258061554</v>
+        <v>0.322921225806155</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05132008853399484</v>
+        <v>0.05132008853399474</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01620950307353841</v>
+        <v>0.0162095030735384</v>
       </c>
       <c r="H2" t="n">
-        <v>0.10425448409781</v>
+        <v>0.1042544840978092</v>
       </c>
       <c r="I2" t="n">
-        <v>4.833115662204297e-06</v>
+        <v>4.833115662204296e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001560167444560522</v>
+        <v>0.001560167444560518</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005413243483328968</v>
+        <v>0.005413243483322671</v>
       </c>
       <c r="L2" t="n">
-        <v>3.561874957537775</v>
+        <v>3.561874957537773</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -5145,31 +5145,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.359939327028498</v>
+        <v>3.359939327028495</v>
       </c>
       <c r="E3" t="n">
-        <v>0.308987673827032</v>
+        <v>0.3089876738270315</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03815515100738626</v>
+        <v>0.03815515100738619</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01598108859471935</v>
+        <v>0.01598108859471932</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1035592013147193</v>
+        <v>0.1035592013147192</v>
       </c>
       <c r="I3" t="n">
         <v>4.421234556262935e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001463738360414731</v>
+        <v>0.00146373836041473</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00513557074096514</v>
+        <v>0.005135570740963085</v>
       </c>
       <c r="L3" t="n">
-        <v>2.886652452639511</v>
+        <v>2.886652452639512</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -5190,28 +5190,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.920947784216022</v>
+        <v>2.920947784216021</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3020604124453138</v>
+        <v>0.3020604124453136</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04608639375192532</v>
+        <v>0.04608639375192548</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01607793456641522</v>
+        <v>0.01607793456641525</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1030603212748789</v>
+        <v>0.103060321274879</v>
       </c>
       <c r="I4" t="n">
-        <v>4.450954048361186e-06</v>
+        <v>4.450954048361187e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001442784611917505</v>
+        <v>0.001442784611916191</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004983406491719901</v>
+        <v>0.004983406491718334</v>
       </c>
       <c r="L4" t="n">
         <v>2.447232078195134</v>
@@ -5235,16 +5235,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.738769801379684</v>
+        <v>2.738769801379692</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3073238008523991</v>
+        <v>0.3073238008523994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06267991062657738</v>
+        <v>0.06267991062657755</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01633922733447172</v>
+        <v>0.01633922733447179</v>
       </c>
       <c r="H5" t="n">
         <v>0.1020909024928441</v>
@@ -5253,13 +5253,13 @@
         <v>4.619787311505655e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001428952688614692</v>
+        <v>0.001428952688615918</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004760802612223015</v>
+        <v>0.004760802612231642</v>
       </c>
       <c r="L5" t="n">
-        <v>2.244141583208501</v>
+        <v>2.244141583208502</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -5280,31 +5280,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.295094453144944</v>
+        <v>2.295094453144946</v>
       </c>
       <c r="E6" t="n">
         <v>0.2598355802687869</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01762308555606739</v>
+        <v>0.01762308555606729</v>
       </c>
       <c r="G6" t="n">
         <v>0.01551713341106995</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09762862568343858</v>
+        <v>0.09762862568343868</v>
       </c>
       <c r="I6" t="n">
-        <v>2.944277570154816e-06</v>
+        <v>2.944277570154814e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009423391268020504</v>
+        <v>0.0009423391268020523</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003187764261495563</v>
+        <v>0.003187764261491228</v>
       </c>
       <c r="L6" t="n">
-        <v>1.900356960469817</v>
+        <v>1.900356960469815</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -5325,31 +5325,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.835517558736011</v>
+        <v>1.835517558736007</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2431522460043292</v>
+        <v>0.2431522460043287</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01591071817513006</v>
+        <v>0.01591071817513003</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01541053876202196</v>
+        <v>0.01541053876202199</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09623801688947572</v>
+        <v>0.0962380168894757</v>
       </c>
       <c r="I7" t="n">
-        <v>2.617964833986284e-06</v>
+        <v>2.617964833986279e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008217061234213301</v>
+        <v>0.0008217061234180734</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002704037413820807</v>
+        <v>0.002704037413821256</v>
       </c>
       <c r="L7" t="n">
-        <v>1.461277675285214</v>
+        <v>1.461277675285213</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5370,31 +5370,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.677517961455669</v>
+        <v>1.67751796145567</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2355715821537628</v>
+        <v>0.2355715821537625</v>
       </c>
       <c r="F8" t="n">
         <v>0.01840883946338096</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01540791177997902</v>
+        <v>0.01540791177997903</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09548110359410812</v>
+        <v>0.09548110359410804</v>
       </c>
       <c r="I8" t="n">
         <v>2.516731355492436e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0007742901808642834</v>
+        <v>0.0007742901808642826</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00248784151199073</v>
+        <v>0.002487841511991098</v>
       </c>
       <c r="L8" t="n">
-        <v>1.309383873924318</v>
+        <v>1.309383873924317</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5415,31 +5415,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.116813587193979</v>
+        <v>3.116813587193978</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2960962596485859</v>
+        <v>0.2960962596485861</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03361273292334658</v>
+        <v>0.03361273292334663</v>
       </c>
       <c r="G9" t="n">
         <v>0.01586517403584983</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1022662252574711</v>
+        <v>0.1022662252574716</v>
       </c>
       <c r="I9" t="n">
-        <v>4.096180020154864e-06</v>
+        <v>4.09618002015486e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001344411330501191</v>
+        <v>0.001344411330501195</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004691940258858216</v>
+        <v>0.00469194025885708</v>
       </c>
       <c r="L9" t="n">
-        <v>2.662932720331192</v>
+        <v>2.662932720331193</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -5460,31 +5460,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.37958948448447</v>
+        <v>2.379589484484471</v>
       </c>
       <c r="E10" t="n">
-        <v>0.269011224743176</v>
+        <v>0.2690112247431757</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02431599742206897</v>
+        <v>0.02431599742206899</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01562330561090261</v>
+        <v>0.01562330561090268</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09985489485305188</v>
+        <v>0.09985489485305185</v>
       </c>
       <c r="I10" t="n">
-        <v>3.462233689234743e-06</v>
+        <v>3.462233689234744e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001125036137698809</v>
+        <v>0.001125036137698806</v>
       </c>
       <c r="K10" t="n">
-        <v>0.003878231971476178</v>
+        <v>0.003878231971473931</v>
       </c>
       <c r="L10" t="n">
-        <v>1.965777329431226</v>
+        <v>1.965777329431225</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -5505,28 +5505,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.850332406227825</v>
+        <v>1.850332406227822</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2596858207067237</v>
+        <v>0.2596858207067239</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02616994220885759</v>
+        <v>0.02616994220885763</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01561966559088741</v>
+        <v>0.0156196655908874</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09633649346690966</v>
+        <v>0.09633649346690976</v>
       </c>
       <c r="I11" t="n">
-        <v>2.870733933945281e-06</v>
+        <v>2.870733933945282e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0008740750855103635</v>
+        <v>0.0008740750855162587</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002802588209024384</v>
+        <v>0.00280258820902306</v>
       </c>
       <c r="L11" t="n">
         <v>1.448840948242454</v>
